--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W75"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,21 +508,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-11 · prices = 2026-09-11 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-14 · prices = 2026-09-11 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>49 investable · NEW 9 · ACTIVE+ 40 · ACTIVE 0   ·   R2 44 · MOMENTUM 0 · R1 5 (advisory)   ·   9 row(s) read 0.00%: admitted at the 2026-09-11 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>50 investable · NEW 1 · ACTIVE+ 49 · ACTIVE 0   ·   R2 45 · MOMENTUM 0 · R1 5 (advisory)   ·   9 row(s) read 0.00%: admitted at the 2026-09-11 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 49 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.77% from entry, worst single -13.05%</t>
+          <t>🛡 DOWNSIDE · 50 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.74% from entry, worst single -13.05%</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=9 · 228 scored · 48 already in CURRENT · biggest blocker: model disagreement (162) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=1 · 228 scored · 49 already in CURRENT · biggest blocker: model disagreement (170) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 52 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 45 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -697,14 +697,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1232</v>
+        <v>406.6</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1232</v>
+        <v>406.6</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -715,11 +715,11 @@
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>28.3</v>
+        <v>37</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1199.9714</v>
+        <v>391.6786</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,17 +746,17 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>2.6</v>
+        <v>3.67</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-2.6</v>
+        <v>-3.67</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1280.04</v>
+        <v>428.98</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ACC-20260911-3a092f</t>
+          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -793,30 +793,30 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>4056.8</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>4056.8</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
+      <c r="K9" s="5" t="n">
+        <v>1.73</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>35</v>
+        <v>33.3</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>3872.6145</v>
+        <v>18.43</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>4.54</v>
+        <v>5.2</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-4.54</v>
+        <v>-3.56</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>4333.08</v>
+        <v>20.21</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AIAENG-20260911-5d7269</t>
+          <t>IND-R2-IRB-20260909-153c95</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -894,34 +894,34 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>11644</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>11770</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>388.4</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>388.4</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
+      <c r="K10" s="5" t="n">
+        <v>1.08</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>31.2</v>
+        <v>43.6</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>376.1785</v>
+        <v>11221</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>3.15</v>
+        <v>4.66</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.15</v>
+        <v>-3.63</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>406.73</v>
+        <v>12467.93</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
+          <t>IND-R2-OFSS-20260909-1e09a0</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -995,34 +995,34 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>2197.4</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>2215</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>1350.1</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>1350.1</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
+      <c r="K11" s="5" t="n">
+        <v>0.8</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>33.3</v>
+        <v>37.1</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1315.6</v>
+        <v>2112.7571</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1049,22 +1049,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2.56</v>
+        <v>4.62</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.56</v>
+        <v>-3.85</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1401.85</v>
+        <v>2341.29</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CIPLA-20260911-5f4a49</t>
+          <t>IND-R2-TCS-20260909-fb0a7f</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1096,34 +1096,34 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1949</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>1964.4</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>373.25</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>373.25</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
+      <c r="K12" s="5" t="n">
+        <v>0.79</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>28.4</v>
+        <v>40.6</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>362.4286</v>
+        <v>1891.4857</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>2.9</v>
+        <v>3.71</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.9</v>
+        <v>-2.95</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>389.48</v>
+        <v>2054.6</v>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DABUR-20260911-8f250f</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1197,34 +1197,34 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>503.95</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>1276.6</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>1276.6</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
+      <c r="K13" s="5" t="n">
+        <v>0.79</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1232.8857</v>
+        <v>482.9429</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1251,22 +1251,22 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.42</v>
+        <v>4.17</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.42</v>
+        <v>-3.41</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1342.17</v>
+        <v>530.45</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWSTEEL-20260911-176cf3</t>
+          <t>IND-R2-OIL-20260909-82436d</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1298,34 +1298,34 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1038.3</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>1042.1</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>400.4</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>400.4</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
+      <c r="K14" s="5" t="n">
+        <v>0.37</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>32.3</v>
+        <v>38.3</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>386.3857</v>
+        <v>984.8428</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.5</v>
+        <v>5.49</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.5</v>
+        <v>-5.15</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>421.42</v>
+        <v>1120.78</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260911-098cc1</t>
+          <t>IND-R2-INFY-20260909-f2b7ad</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1399,34 +1399,34 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>172.76</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>1725</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>1725</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
+      <c r="K15" s="5" t="n">
+        <v>0.31</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>31.3</v>
+        <v>30.1</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1649.0429</v>
+        <v>165.6072</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-4.4</v>
+        <v>-4.14</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1838.94</v>
+        <v>184.71</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
+          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>8128.5</v>
+        <v>1232</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8128.5</v>
+        <v>1232</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1523,11 +1523,11 @@
         <v>0</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>38.7</v>
+        <v>28.3</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7774</v>
+        <v>1199.9714</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.36</v>
+        <v>2.6</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-4.36</v>
+        <v>-2.6</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>8660.25</v>
+        <v>1280.04</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-ACC-20260911-3a092f</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1601,30 +1601,30 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>19.11</v>
+        <v>4056.8</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>19.44</v>
+        <v>4056.8</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K17" s="5" t="n">
-        <v>1.73</v>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>18.43</v>
+        <v>3872.6145</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.2</v>
+        <v>4.54</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-3.56</v>
+        <v>-4.54</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>20.21</v>
+        <v>4333.08</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260909-153c95</t>
+          <t>IND-R2-AIAENG-20260911-5d7269</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1702,34 +1702,34 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>11644</v>
+        <v>388.4</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>11770</v>
+        <v>388.4</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K18" s="5" t="n">
-        <v>1.08</v>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>43.6</v>
+        <v>31.2</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>11221</v>
+        <v>376.1785</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>4.66</v>
+        <v>3.15</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-3.63</v>
+        <v>-3.15</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>12467.93</v>
+        <v>406.73</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260909-1e09a0</t>
+          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1803,34 +1803,34 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2197.4</v>
+        <v>1350.1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2215</v>
+        <v>1350.1</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K19" s="5" t="n">
-        <v>0.8</v>
+      <c r="K19" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>37.1</v>
+        <v>33.3</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2112.7571</v>
+        <v>1315.6</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1857,22 +1857,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>4.62</v>
+        <v>2.56</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.85</v>
+        <v>-2.56</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2341.29</v>
+        <v>1401.85</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260909-fb0a7f</t>
+          <t>IND-R2-CIPLA-20260911-5f4a49</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1904,34 +1904,34 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1949</v>
+        <v>373.25</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1964.4</v>
+        <v>373.25</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K20" s="5" t="n">
-        <v>0.79</v>
+      <c r="K20" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>40.6</v>
+        <v>28.4</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1891.4857</v>
+        <v>362.4286</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>3.71</v>
+        <v>2.9</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.95</v>
+        <v>-2.9</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>2054.6</v>
+        <v>389.48</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IPCALAB-20260909-af9aea</t>
+          <t>IND-R2-DABUR-20260911-8f250f</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2005,34 +2005,34 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>500</v>
+        <v>1276.6</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>503.95</v>
+        <v>1276.6</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K21" s="5" t="n">
-        <v>0.79</v>
+      <c r="K21" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>35.4</v>
+        <v>40.6</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>482.9429</v>
+        <v>1232.8857</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.17</v>
+        <v>3.42</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.41</v>
+        <v>-3.42</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>530.45</v>
+        <v>1342.17</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260909-82436d</t>
+          <t>IND-R2-JSWSTEEL-20260911-176cf3</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2106,34 +2106,34 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1038.3</v>
+        <v>400.4</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1042.1</v>
+        <v>400.4</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K22" s="5" t="n">
-        <v>0.37</v>
+      <c r="K22" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>38.3</v>
+        <v>32.3</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>984.8428</v>
+        <v>386.3857</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2160,22 +2160,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>5.49</v>
+        <v>3.5</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-5.15</v>
+        <v>-3.5</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1120.78</v>
+        <v>421.42</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260909-f2b7ad</t>
+          <t>IND-R2-LICI-20260911-098cc1</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2207,34 +2207,34 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>172.76</v>
+        <v>1725</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>173.3</v>
+        <v>1725</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K23" s="5" t="n">
-        <v>0.31</v>
+      <c r="K23" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>30.1</v>
+        <v>31.3</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>165.6072</v>
+        <v>1649.0429</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2261,22 +2261,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-4.14</v>
+        <v>-4.4</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>184.71</v>
+        <v>1838.94</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
+          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2308,34 +2308,34 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>434.2</v>
+        <v>8128.5</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>432.9</v>
+        <v>8128.5</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K24" s="6" t="n">
-        <v>-0.3</v>
+      <c r="K24" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>33.3</v>
+        <v>38.7</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>417.55</v>
+        <v>7774</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2362,22 +2362,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.55</v>
+        <v>4.36</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-3.83</v>
+        <v>-4.36</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>456.13</v>
+        <v>8660.25</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260909-3c298a</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1244.4</v>
+        <v>434.2</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1237.2</v>
+        <v>432.9</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
         </is>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.58</v>
+        <v>-0.3</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>1204.5857</v>
+        <v>417.55</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2463,22 +2463,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.64</v>
+        <v>3.55</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-3.2</v>
+        <v>-3.83</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1294.16</v>
+        <v>456.13</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AXISBANK-20260909-3abb74</t>
+          <t>IND-R2-COALINDIA-20260909-3c298a</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>292.9</v>
+        <v>1244.4</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>290.9</v>
+        <v>1237.2</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.68</v>
+        <v>-0.58</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>34.3</v>
+        <v>32.9</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>274.9429</v>
+        <v>1204.5857</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2564,22 +2564,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>5.49</v>
+        <v>2.64</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-6.13</v>
+        <v>-3.2</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>315.92</v>
+        <v>1294.16</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
+          <t>IND-R2-AXISBANK-20260909-3abb74</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>370</v>
+        <v>292.9</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>367.45</v>
+        <v>290.9</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2631,14 +2631,14 @@
         </is>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>31.2</v>
+        <v>34.3</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>348.7929</v>
+        <v>274.9429</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>5.08</v>
+        <v>5.49</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-5.73</v>
+        <v>-6.13</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>397.71</v>
+        <v>315.92</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
+          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2410.1</v>
+        <v>370</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2391.9</v>
+        <v>367.45</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -2732,14 +2732,14 @@
         </is>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.76</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>40.6</v>
+        <v>31.2</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>2288.3428</v>
+        <v>348.7929</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.33</v>
+        <v>5.08</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-5.05</v>
+        <v>-5.73</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2579.94</v>
+        <v>397.71</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GLENMARK-20260909-ef0373</t>
+          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>339.55</v>
+        <v>2410.1</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>336.75</v>
+        <v>2391.9</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2833,14 +2833,14 @@
         </is>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.82</v>
+        <v>-0.76</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>32.3</v>
+        <v>40.6</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>327.9071</v>
+        <v>2288.3428</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2867,22 +2867,22 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-3.43</v>
+        <v>-5.05</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>353.62</v>
+        <v>2579.94</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PATANJALI-20260909-508e75</t>
+          <t>IND-R2-GLENMARK-20260909-ef0373</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1007.2</v>
+        <v>339.55</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>998</v>
+        <v>336.75</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -2934,14 +2934,14 @@
         </is>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.91</v>
+        <v>-0.82</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>35</v>
+        <v>32.3</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>967.7286</v>
+        <v>327.9071</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.03</v>
+        <v>2.63</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.92</v>
+        <v>-3.43</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1050.01</v>
+        <v>353.62</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20260909-a73231</t>
+          <t>IND-R2-PATANJALI-20260909-508e75</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1260</v>
+        <v>1007.2</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1248.2</v>
+        <v>998</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -3035,14 +3035,14 @@
         </is>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.91</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1190.3857</v>
+        <v>967.7286</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3069,22 +3069,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>4.63</v>
+        <v>3.03</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-5.52</v>
+        <v>-3.92</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1348.37</v>
+        <v>1050.01</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NAUKRI-20260909-930931</t>
+          <t>IND-R2-SBIN-20260909-a73231</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12603</v>
+        <v>1260</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>12483</v>
+        <v>1248.2</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -3136,14 +3136,14 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.95</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>31.3</v>
+        <v>33.3</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>12048.8571</v>
+        <v>1190.3857</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3170,22 +3170,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.48</v>
+        <v>4.63</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-4.4</v>
+        <v>-5.52</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>13267.29</v>
+        <v>1348.37</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARUTI-20260909-c59a94</t>
+          <t>IND-R2-NAUKRI-20260909-930931</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>25455</v>
+        <v>12603</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>25195</v>
+        <v>12483</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -3237,14 +3237,14 @@
         </is>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-1.02</v>
+        <v>-0.95</v>
       </c>
       <c r="L33" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>24409.2857</v>
+        <v>12048.8571</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3271,22 +3271,22 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.12</v>
+        <v>3.48</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-4.11</v>
+        <v>-4.4</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>26635.71</v>
+        <v>13267.29</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
+          <t>IND-R2-MARUTI-20260909-c59a94</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1952</v>
+        <v>25455</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1931.8</v>
+        <v>25195</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -3338,14 +3338,14 @@
         </is>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-1.03</v>
+        <v>-1.02</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1889.9429</v>
+        <v>24409.2857</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3372,22 +3372,22 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>2.17</v>
+        <v>3.12</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-3.18</v>
+        <v>-4.11</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2020.51</v>
+        <v>26635.71</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
+          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>818.3</v>
+        <v>1952</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>808.5</v>
+        <v>1931.8</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -3439,14 +3439,14 @@
         </is>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-1.2</v>
+        <v>-1.03</v>
       </c>
       <c r="L35" s="4" t="n">
         <v>31.2</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>778.3714</v>
+        <v>1889.9429</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>3.73</v>
+        <v>2.17</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-4.88</v>
+        <v>-3.18</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>866.9299999999999</v>
+        <v>2020.51</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
+          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>315.55</v>
+        <v>818.3</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>311.75</v>
+        <v>808.5</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>302.3786</v>
+        <v>778.3714</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3574,22 +3574,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>3.01</v>
+        <v>3.73</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-4.17</v>
+        <v>-4.88</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>329.25</v>
+        <v>866.9299999999999</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RECLTD-20260909-84e6d1</t>
+          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>694.35</v>
+        <v>315.55</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>684.85</v>
+        <v>311.75</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-1.37</v>
+        <v>-1.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>34.8</v>
+        <v>31.2</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>660.7643</v>
+        <v>302.3786</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3675,22 +3675,22 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>3.52</v>
+        <v>3.01</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-4.84</v>
+        <v>-4.17</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>729</v>
+        <v>329.25</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
+          <t>IND-R2-RECLTD-20260909-84e6d1</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>470.4</v>
+        <v>694.35</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>463.75</v>
+        <v>684.85</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -3742,14 +3742,14 @@
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-1.41</v>
+        <v>-1.37</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>28.4</v>
+        <v>34.8</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>453.4071</v>
+        <v>660.7643</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3776,22 +3776,22 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>2.23</v>
+        <v>3.52</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-3.61</v>
+        <v>-4.84</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>486.55</v>
+        <v>729</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRCTC-20260909-add681</t>
+          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>6291</v>
+        <v>470.4</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>6189.5</v>
+        <v>463.75</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -3843,14 +3843,14 @@
         </is>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-1.61</v>
+        <v>-1.41</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>33.3</v>
+        <v>28.4</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>5959.1429</v>
+        <v>453.4071</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3877,22 +3877,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>3.72</v>
+        <v>2.23</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-5.28</v>
+        <v>-3.61</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>6638.36</v>
+        <v>486.55</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260909-2f64b0</t>
+          <t>IND-R2-IRCTC-20260909-add681</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>154.28</v>
+        <v>6291</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>151.76</v>
+        <v>6189.5</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -3944,14 +3944,14 @@
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-1.63</v>
+        <v>-1.61</v>
       </c>
       <c r="L40" s="4" t="n">
         <v>33.3</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>145.5286</v>
+        <v>5959.1429</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3978,22 +3978,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>4.11</v>
+        <v>3.72</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-5.67</v>
+        <v>-5.28</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>163.68</v>
+        <v>6638.36</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20260909-938c43</t>
+          <t>IND-R2-ATUL-20260909-2f64b0</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>5163.5</v>
+        <v>154.28</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>5070</v>
+        <v>151.76</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -4045,14 +4045,14 @@
         </is>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-1.81</v>
+        <v>-1.63</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>31.3</v>
+        <v>33.3</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>4920.3571</v>
+        <v>145.5286</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4079,22 +4079,22 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>2.95</v>
+        <v>4.11</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-4.71</v>
+        <v>-5.67</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>5385.18</v>
+        <v>163.68</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ALKEM-20260909-517913</t>
+          <t>IND-R2-IGL-20260909-938c43</t>
         </is>
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>3134.7</v>
+        <v>5163.5</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>3077.1</v>
+        <v>5070</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -4146,14 +4146,14 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-1.84</v>
+        <v>-1.81</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>11.2</v>
+        <v>31.3</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>2959.643</v>
+        <v>4920.3571</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4180,22 +4180,22 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>3.82</v>
+        <v>2.95</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-5.58</v>
+        <v>-4.71</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>3307.14</v>
+        <v>5385.18</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MM-20260909-3a8a06</t>
+          <t>IND-R2-ALKEM-20260909-517913</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>860.45</v>
+        <v>3134.7</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>841.6</v>
+        <v>3077.1</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -4247,14 +4247,14 @@
         </is>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-2.19</v>
+        <v>-1.84</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>35</v>
+        <v>11.2</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>811.05</v>
+        <v>2959.643</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="S43" s="4" t="n">
-        <v>3.63</v>
+        <v>3.82</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-5.74</v>
+        <v>-5.58</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>903.71</v>
+        <v>3307.14</v>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260909-3ab469</t>
+          <t>IND-R2-MM-20260909-3a8a06</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>273.3</v>
+        <v>860.45</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>266.5</v>
+        <v>841.6</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -4348,14 +4348,14 @@
         </is>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-2.49</v>
+        <v>-2.19</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>28.4</v>
+        <v>35</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>255.3143</v>
+        <v>811.05</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
@@ -4382,22 +4382,22 @@
         </is>
       </c>
       <c r="S44" s="4" t="n">
-        <v>4.2</v>
+        <v>3.63</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>-6.58</v>
+        <v>-5.74</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>289.39</v>
+        <v>903.71</v>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
+          <t>IND-R2-INDIANB-20260909-3ab469</t>
         </is>
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4429,19 +4429,19 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>233.86</v>
+        <v>273.3</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>227.29</v>
+        <v>266.5</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -4449,16 +4449,14 @@
         </is>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-2.81</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-2.49</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>28.4</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -4477,7 +4475,7 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>220.1271</v>
+        <v>255.3143</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4485,22 +4483,22 @@
         </is>
       </c>
       <c r="S45" s="4" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>-5.87</v>
+        <v>-6.58</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>244.86</v>
+        <v>289.39</v>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
+          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4510,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4532,19 +4530,19 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>2825</v>
+        <v>233.86</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>2743.9</v>
+        <v>227.29</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -4552,10 +4550,12 @@
         </is>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-2.87</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>36.1</v>
+        <v>-2.81</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>2620.0107</v>
+        <v>220.1271</v>
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
@@ -4586,22 +4586,22 @@
         </is>
       </c>
       <c r="S46" s="4" t="n">
-        <v>4.52</v>
+        <v>3.15</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>-7.26</v>
+        <v>-5.87</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>3067.12</v>
+        <v>244.86</v>
       </c>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
+          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>3365.2</v>
+        <v>2825</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>3263.8</v>
+        <v>2743.9</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-3.01</v>
+        <v>-2.87</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>40.4</v>
+        <v>36.1</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>3085.7715</v>
+        <v>2620.0107</v>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
@@ -4687,22 +4687,22 @@
         </is>
       </c>
       <c r="S47" s="4" t="n">
-        <v>5.45</v>
+        <v>4.52</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7.26</v>
       </c>
       <c r="U47" s="4" t="n">
-        <v>3608.33</v>
+        <v>3067.12</v>
       </c>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MCX-20260909-1bc45f</t>
+          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4734,19 +4734,19 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>117.05</v>
+        <v>3365.2</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>113.04</v>
+        <v>3263.8</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -4754,12 +4754,10 @@
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-3.43</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-3.01</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>40.4</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
@@ -4782,7 +4780,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>109.1857</v>
+        <v>3085.7715</v>
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -4790,22 +4788,22 @@
         </is>
       </c>
       <c r="S48" s="4" t="n">
-        <v>3.41</v>
+        <v>5.45</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>-6.72</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>121.93</v>
+        <v>3608.33</v>
       </c>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260908-d0ae28</t>
+          <t>IND-R2-MCX-20260909-1bc45f</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4815,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4837,19 +4835,19 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>187.94</v>
+        <v>117.05</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>179.03</v>
+        <v>113.04</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -4857,14 +4855,16 @@
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-4.74</v>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v>40.6</v>
+        <v>-3.43</v>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>169.1236</v>
+        <v>109.1857</v>
       </c>
       <c r="R49" s="4" t="inlineStr">
         <is>
@@ -4891,22 +4891,22 @@
         </is>
       </c>
       <c r="S49" s="4" t="n">
-        <v>5.53</v>
+        <v>3.41</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>-10.01</v>
+        <v>-6.72</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>206.77</v>
+        <v>121.93</v>
       </c>
       <c r="V49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260909-29ffd5</t>
+          <t>IND-R2-IEX-20260908-d0ae28</t>
         </is>
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>275</v>
+        <v>187.94</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>260.95</v>
+        <v>179.03</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-5.11</v>
+        <v>-4.74</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>35.4</v>
+        <v>40.6</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>245.8929</v>
+        <v>169.1236</v>
       </c>
       <c r="R50" s="4" t="inlineStr">
         <is>
@@ -4992,22 +4992,22 @@
         </is>
       </c>
       <c r="S50" s="4" t="n">
-        <v>5.77</v>
+        <v>5.53</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>-10.58</v>
+        <v>-10.01</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>296.13</v>
+        <v>206.77</v>
       </c>
       <c r="V50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260909-bbba1f</t>
+          <t>IND-R2-SAIL-20260909-29ffd5</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -5048,10 +5048,10 @@
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>385.3</v>
+        <v>275</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>356</v>
+        <v>260.95</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-7.6</v>
+        <v>-5.11</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>335.0214</v>
+        <v>245.8929</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -5093,22 +5093,22 @@
         </is>
       </c>
       <c r="S51" s="4" t="n">
-        <v>5.89</v>
+        <v>5.77</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>-13.05</v>
+        <v>-10.58</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>412.84</v>
+        <v>296.13</v>
       </c>
       <c r="V51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
+          <t>IND-R2-VEDL-20260909-bbba1f</t>
         </is>
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5120,12 +5120,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -5135,41 +5135,39 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-05</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>417.6</v>
+        <v>385.3</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>432.9</v>
+        <v>356</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K52" s="5" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+      <c r="K52" s="6" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5188,7 +5186,7 @@
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>407.3714</v>
+        <v>335.0214</v>
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
@@ -5196,22 +5194,22 @@
         </is>
       </c>
       <c r="S52" s="4" t="n">
-        <v>5.9</v>
+        <v>5.89</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>-2.45</v>
+        <v>-13.05</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>432.94</v>
+        <v>412.84</v>
       </c>
       <c r="V52" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
         </is>
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5221,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -5243,19 +5241,19 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-08-05</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>397</v>
+        <v>417.6</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>411</v>
+        <v>432.9</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -5263,7 +5261,7 @@
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>3.53</v>
+        <v>3.66</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -5272,7 +5270,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5291,7 +5289,7 @@
         </is>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>386.4571</v>
+        <v>407.3714</v>
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
@@ -5299,17 +5297,17 @@
         </is>
       </c>
       <c r="S53" s="4" t="n">
-        <v>5.97</v>
+        <v>5.9</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>-2.66</v>
+        <v>-2.45</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>412.81</v>
+        <v>432.94</v>
       </c>
       <c r="V53" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
         </is>
       </c>
       <c r="W53" s="4" t="inlineStr">
@@ -5326,7 +5324,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -5355,10 +5353,10 @@
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>389.85</v>
+        <v>397</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>401.25</v>
+        <v>411</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -5366,7 +5364,7 @@
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>2.92</v>
+        <v>3.53</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -5375,7 +5373,7 @@
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5394,7 +5392,7 @@
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>378.3286</v>
+        <v>386.4571</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
@@ -5402,17 +5400,17 @@
         </is>
       </c>
       <c r="S54" s="4" t="n">
-        <v>5.71</v>
+        <v>5.97</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>-2.96</v>
+        <v>-2.66</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>407.13</v>
+        <v>412.81</v>
       </c>
       <c r="V54" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
       <c r="W54" s="4" t="inlineStr">
@@ -5429,7 +5427,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -5449,19 +5447,19 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-11</t>
+          <t>Admitted 2026-08-04</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>239.45</v>
+        <v>389.85</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>239.6</v>
+        <v>401.25</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -5469,7 +5467,7 @@
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>0.06</v>
+        <v>2.92</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -5478,7 +5476,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5497,7 +5495,7 @@
         </is>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>232.2186</v>
+        <v>378.3286</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5505,17 +5503,17 @@
         </is>
       </c>
       <c r="S55" s="4" t="n">
-        <v>3.08</v>
+        <v>5.71</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>-3.02</v>
+        <v>-2.96</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>250.3</v>
+        <v>407.13</v>
       </c>
       <c r="V55" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
         </is>
       </c>
       <c r="W55" s="4" t="inlineStr">
@@ -5532,215 +5530,318 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-11</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>239.45</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>239.6</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>232.2186</v>
+      </c>
+      <c r="R56" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S56" s="4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T56" s="4" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="U56" s="4" t="n">
+        <v>250.3</v>
+      </c>
+      <c r="V56" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
+        </is>
+      </c>
+      <c r="W56" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
           <t>TATASTEEL</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-28</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>187.46</v>
       </c>
-      <c r="I56" s="4" t="n">
+      <c r="I57" s="4" t="n">
         <v>182.09</v>
       </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="J57" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K56" s="6" t="n">
+      <c r="K57" s="6" t="n">
         <v>-2.86</v>
       </c>
-      <c r="L56" s="4" t="inlineStr">
+      <c r="L57" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="N57" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O56" s="4" t="inlineStr">
+      <c r="O57" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P56" s="4" t="inlineStr">
+      <c r="P57" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q56" s="4" t="n">
+      <c r="Q57" s="4" t="n">
         <v>181.8114</v>
       </c>
-      <c r="R56" s="4" t="inlineStr">
+      <c r="R57" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S56" s="4" t="n">
+      <c r="S57" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="T56" s="4" t="n">
+      <c r="T57" s="4" t="n">
         <v>-3.01</v>
       </c>
-      <c r="U56" s="4" t="n">
+      <c r="U57" s="4" t="n">
         <v>195.93</v>
       </c>
-      <c r="V56" s="4" t="inlineStr">
+      <c r="V57" s="4" t="inlineStr">
         <is>
           <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
-      <c r="W56" s="4" t="inlineStr">
+      <c r="W57" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -5751,7 +5852,6 @@
     <mergeCell ref="A68:W68"/>
     <mergeCell ref="A67:W67"/>
     <mergeCell ref="A64:W64"/>
-    <mergeCell ref="A59:W59"/>
     <mergeCell ref="A73:W73"/>
     <mergeCell ref="A60:W60"/>
     <mergeCell ref="A1:W1"/>
@@ -5766,6 +5866,7 @@
     <mergeCell ref="A3:W3"/>
     <mergeCell ref="A71:W71"/>
     <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A76:W76"/>
     <mergeCell ref="A5:W5"/>
     <mergeCell ref="A4:W4"/>
     <mergeCell ref="A62:W62"/>
@@ -5806,7 +5907,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · 2026-09-11</t>
+          <t>AEGIS INDIA · EXIT HISTORY · 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -5909,7 +6010,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -5952,7 +6053,7 @@
         <v>-7.06</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -5983,17 +6084,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -6003,34 +6104,34 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2744.3</v>
+        <v>1449.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2588.5</v>
+        <v>1371.8</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-5.68</v>
+        <v>-5.36</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Holding horizon reached</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -6040,34 +6141,34 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>EXIT_HORIZON · trigger crossed 2026-09-11 · stop_source=dyna</t>
+          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -6077,34 +6178,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>113.36</v>
+        <v>1413.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>115.63</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>2</v>
+        <v>1350.1</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-4.49</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Holding horizon reached</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -6114,17 +6215,17 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>EXIT_HORIZON · trigger crossed 2026-09-11 · stop_source=dyna</t>
+          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
@@ -6136,12 +6237,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -6165,13 +6266,13 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5499</v>
+        <v>2744.3</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5510</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>0.2</v>
+        <v>2588.5</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-5.68</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>37</v>
@@ -6193,7 +6294,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
@@ -6210,12 +6311,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -6239,13 +6340,13 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>284.85</v>
+        <v>113.36</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>260.1</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>-8.69</v>
+        <v>115.63</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>38</v>
@@ -6267,7 +6368,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ITC-20260804-e0ebbb</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -6284,12 +6385,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -6299,34 +6400,34 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1449.5</v>
+        <v>5499</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1371.8</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>-5.36</v>
+        <v>5510</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0.2</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
+          <t>Holding horizon reached</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -6336,17 +6437,17 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_HORIZON · trigger crossed 2026-09-11 · stop_source=dyna</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -6358,12 +6459,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -6383,20 +6484,20 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>553.3</v>
+        <v>284.85</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>560.25</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>1.26</v>
+        <v>260.1</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-8.69</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -6415,7 +6516,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20260806-03d0a7</t>
+          <t>IND-R2-ITC-20260804-e0ebbb</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -6432,12 +6533,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -6447,34 +6548,34 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1413.5</v>
+        <v>553.3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1350.1</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>-4.49</v>
+        <v>560.25</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>1.26</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
+          <t>Holding horizon reached</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -6484,17 +6585,17 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_HORIZON · trigger crossed 2026-09-11 · stop_source=dyna</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R2-GNFC-20260806-03d0a7</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W76"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,21 +508,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-14 · prices = 2026-09-11 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-15 · prices = 2026-09-11 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>50 investable · NEW 1 · ACTIVE+ 49 · ACTIVE 0   ·   R2 45 · MOMENTUM 0 · R1 5 (advisory)   ·   9 row(s) read 0.00%: admitted at the 2026-09-11 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>54 investable · NEW 4 · ACTIVE+ 50 · ACTIVE 0   ·   R2 49 · MOMENTUM 0 · R1 5 (advisory)   ·   9 row(s) read 0.00%: admitted at the 2026-09-11 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 50 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.74% from entry, worst single -13.05%</t>
+          <t>🛡 DOWNSIDE · 54 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.66% from entry, worst single -13.05%</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=1 · 228 scored · 49 already in CURRENT · biggest blocker: model disagreement (170) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=4 · 228 scored · 52 already in CURRENT · biggest blocker: model disagreement (167) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 45 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 49 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -697,14 +697,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>406.6</v>
+        <v>123.15</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>406.6</v>
+        <v>123.15</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>37</v>
+        <v>30.2</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>391.6786</v>
+        <v>118.53</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,17 +746,17 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.67</v>
+        <v>-3.75</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>428.98</v>
+        <v>130.08</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
+          <t>IND-R2-CANBK-20260915-4a780b</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -793,34 +793,34 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>19.11</v>
+        <v>411</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>19.44</v>
+        <v>411</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K9" s="5" t="n">
-        <v>1.73</v>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>33.3</v>
+        <v>34.1</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>18.43</v>
+        <v>397.4143</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>5.2</v>
+        <v>3.31</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.56</v>
+        <v>-3.31</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>20.21</v>
+        <v>431.38</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260909-153c95</t>
+          <t>IND-R2-KOTAKBANK-20260915-bbcfac</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -894,34 +894,34 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11644</v>
+        <v>285</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11770</v>
+        <v>285</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K10" s="5" t="n">
-        <v>1.08</v>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>43.6</v>
+        <v>35.4</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>11221</v>
+        <v>277.2643</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>4.66</v>
+        <v>2.71</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.63</v>
+        <v>-2.71</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>12467.93</v>
+        <v>296.6</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260909-1e09a0</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -995,34 +995,34 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2197.4</v>
+        <v>461.75</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2215</v>
+        <v>461.75</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K11" s="5" t="n">
-        <v>0.8</v>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>37.1</v>
+        <v>31.2</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2112.7571</v>
+        <v>439.8286</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1049,22 +1049,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.62</v>
+        <v>4.75</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.85</v>
+        <v>-4.75</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2341.29</v>
+        <v>494.63</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260909-fb0a7f</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1949</v>
+        <v>19.11</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1964.4</v>
+        <v>19.44</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1116,14 +1116,14 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.79</v>
+        <v>1.73</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>40.6</v>
+        <v>33.3</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1891.4857</v>
+        <v>18.43</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>3.71</v>
+        <v>5.2</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.95</v>
+        <v>-3.56</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2054.6</v>
+        <v>20.21</v>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IPCALAB-20260909-af9aea</t>
+          <t>IND-R2-IRB-20260909-153c95</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>500</v>
+        <v>11644</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>503.95</v>
+        <v>11770</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1217,14 +1217,14 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>35.4</v>
+        <v>43.6</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>482.9429</v>
+        <v>11221</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1251,22 +1251,22 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>4.17</v>
+        <v>4.66</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.41</v>
+        <v>-3.63</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>530.45</v>
+        <v>12467.93</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260909-82436d</t>
+          <t>IND-R2-OFSS-20260909-1e09a0</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1038.3</v>
+        <v>2197.4</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1042.1</v>
+        <v>2215</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.37</v>
+        <v>0.8</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>38.3</v>
+        <v>37.1</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>984.8428</v>
+        <v>2112.7571</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>5.49</v>
+        <v>4.62</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-5.15</v>
+        <v>-3.85</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1120.78</v>
+        <v>2341.29</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260909-f2b7ad</t>
+          <t>IND-R2-TCS-20260909-fb0a7f</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>172.76</v>
+        <v>1949</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>173.3</v>
+        <v>1964.4</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1419,14 +1419,14 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.31</v>
+        <v>0.79</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>30.1</v>
+        <v>40.6</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>165.6072</v>
+        <v>1891.4857</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.44</v>
+        <v>3.71</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-4.14</v>
+        <v>-2.95</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>184.71</v>
+        <v>2054.6</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1500,34 +1500,34 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>503.95</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
-        <v>1232</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>1232</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0</v>
+      <c r="K16" s="5" t="n">
+        <v>0.79</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>28.3</v>
+        <v>35.4</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1199.9714</v>
+        <v>482.9429</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>2.6</v>
+        <v>4.17</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.6</v>
+        <v>-3.41</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1280.04</v>
+        <v>530.45</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ACC-20260911-3a092f</t>
+          <t>IND-R2-OIL-20260909-82436d</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1601,34 +1601,34 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1038.3</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>1042.1</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
-        <v>4056.8</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>4056.8</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0</v>
+      <c r="K17" s="5" t="n">
+        <v>0.37</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>35</v>
+        <v>38.3</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3872.6145</v>
+        <v>984.8428</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>4.54</v>
+        <v>5.49</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-4.54</v>
+        <v>-5.15</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4333.08</v>
+        <v>1120.78</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AIAENG-20260911-5d7269</t>
+          <t>IND-R2-INFY-20260909-f2b7ad</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1702,34 +1702,34 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>172.76</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
-        <v>388.4</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>388.4</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
+      <c r="K18" s="5" t="n">
+        <v>0.31</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>31.2</v>
+        <v>30.1</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>376.1785</v>
+        <v>165.6072</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.15</v>
+        <v>4.44</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-3.15</v>
+        <v>-4.14</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>406.73</v>
+        <v>184.71</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
+          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1350.1</v>
+        <v>1232</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1350.1</v>
+        <v>1232</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1826,11 +1826,11 @@
         <v>0</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>33.3</v>
+        <v>28.3</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1315.6</v>
+        <v>1199.9714</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1857,22 +1857,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.56</v>
+        <v>-2.6</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1401.85</v>
+        <v>1280.04</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CIPLA-20260911-5f4a49</t>
+          <t>IND-R2-ACC-20260911-3a092f</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>373.25</v>
+        <v>4056.8</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>373.25</v>
+        <v>4056.8</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1927,11 +1927,11 @@
         <v>0</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>28.4</v>
+        <v>35</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>362.4286</v>
+        <v>3872.6145</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>2.9</v>
+        <v>4.54</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.9</v>
+        <v>-4.54</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>389.48</v>
+        <v>4333.08</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DABUR-20260911-8f250f</t>
+          <t>IND-R2-AIAENG-20260911-5d7269</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1276.6</v>
+        <v>388.4</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1276.6</v>
+        <v>388.4</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>40.6</v>
+        <v>31.2</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1232.8857</v>
+        <v>376.1785</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.42</v>
+        <v>-3.15</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1342.17</v>
+        <v>406.73</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWSTEEL-20260911-176cf3</t>
+          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>400.4</v>
+        <v>1350.1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>400.4</v>
+        <v>1350.1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -2129,11 +2129,11 @@
         <v>0</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>32.3</v>
+        <v>33.3</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>386.3857</v>
+        <v>1315.6</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2160,22 +2160,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.5</v>
+        <v>-2.56</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>421.42</v>
+        <v>1401.85</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260911-098cc1</t>
+          <t>IND-R2-CIPLA-20260911-5f4a49</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1725</v>
+        <v>373.25</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1725</v>
+        <v>373.25</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -2230,11 +2230,11 @@
         <v>0</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>31.3</v>
+        <v>28.4</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1649.0429</v>
+        <v>362.4286</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2261,22 +2261,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-4.4</v>
+        <v>-2.9</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1838.94</v>
+        <v>389.48</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
+          <t>IND-R2-DABUR-20260911-8f250f</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>8128.5</v>
+        <v>1276.6</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8128.5</v>
+        <v>1276.6</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -2331,11 +2331,11 @@
         <v>0</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>38.7</v>
+        <v>40.6</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>7774</v>
+        <v>1232.8857</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2362,22 +2362,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.36</v>
+        <v>3.42</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-4.36</v>
+        <v>-3.42</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>8660.25</v>
+        <v>1342.17</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-JSWSTEEL-20260911-176cf3</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2409,34 +2409,34 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>434.2</v>
+        <v>400.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>432.9</v>
+        <v>400.4</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K25" s="6" t="n">
-        <v>-0.3</v>
+      <c r="K25" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>417.55</v>
+        <v>386.3857</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2463,22 +2463,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-3.83</v>
+        <v>-3.5</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>456.13</v>
+        <v>421.42</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260909-3c298a</t>
+          <t>IND-R2-LICI-20260911-098cc1</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2510,34 +2510,34 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1244.4</v>
+        <v>1725</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1237.2</v>
+        <v>1725</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K26" s="6" t="n">
-        <v>-0.58</v>
+      <c r="K26" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>32.9</v>
+        <v>31.3</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1204.5857</v>
+        <v>1649.0429</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2564,22 +2564,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.64</v>
+        <v>4.4</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-3.2</v>
+        <v>-4.4</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1294.16</v>
+        <v>1838.94</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AXISBANK-20260909-3abb74</t>
+          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2611,34 +2611,34 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>292.9</v>
+        <v>8128.5</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>290.9</v>
+        <v>8128.5</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K27" s="6" t="n">
-        <v>-0.68</v>
+      <c r="K27" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>34.3</v>
+        <v>38.7</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>274.9429</v>
+        <v>7774</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>5.49</v>
+        <v>4.36</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-6.13</v>
+        <v>-4.36</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>315.92</v>
+        <v>8660.25</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2712,34 +2712,34 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-14</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>370</v>
+        <v>406.6</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>367.45</v>
+        <v>406.6</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K28" s="6" t="n">
-        <v>-0.6899999999999999</v>
+      <c r="K28" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>31.2</v>
+        <v>37</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>348.7929</v>
+        <v>391.6786</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>5.08</v>
+        <v>3.67</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-5.73</v>
+        <v>-3.67</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>397.71</v>
+        <v>428.98</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
+          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2410.1</v>
+        <v>434.2</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2391.9</v>
+        <v>432.9</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2833,14 +2833,14 @@
         </is>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.76</v>
+        <v>-0.3</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>40.6</v>
+        <v>33.3</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2288.3428</v>
+        <v>417.55</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2867,22 +2867,22 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-5.05</v>
+        <v>-3.83</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2579.94</v>
+        <v>456.13</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GLENMARK-20260909-ef0373</t>
+          <t>IND-R2-COALINDIA-20260909-3c298a</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>339.55</v>
+        <v>1244.4</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>336.75</v>
+        <v>1237.2</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -2934,14 +2934,14 @@
         </is>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.82</v>
+        <v>-0.58</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>32.3</v>
+        <v>32.9</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>327.9071</v>
+        <v>1204.5857</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.43</v>
+        <v>-3.2</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>353.62</v>
+        <v>1294.16</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PATANJALI-20260909-508e75</t>
+          <t>IND-R2-AXISBANK-20260909-3abb74</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1007.2</v>
+        <v>292.9</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>998</v>
+        <v>290.9</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.91</v>
+        <v>-0.68</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>35</v>
+        <v>34.3</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>967.7286</v>
+        <v>274.9429</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3069,22 +3069,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>3.03</v>
+        <v>5.49</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-3.92</v>
+        <v>-6.13</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1050.01</v>
+        <v>315.92</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20260909-a73231</t>
+          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1260</v>
+        <v>370</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1248.2</v>
+        <v>367.45</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -3136,14 +3136,14 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1190.3857</v>
+        <v>348.7929</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3170,22 +3170,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.63</v>
+        <v>5.08</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-5.52</v>
+        <v>-5.73</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1348.37</v>
+        <v>397.71</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NAUKRI-20260909-930931</t>
+          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12603</v>
+        <v>2410.1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>12483</v>
+        <v>2391.9</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -3237,14 +3237,14 @@
         </is>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.95</v>
+        <v>-0.76</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>31.3</v>
+        <v>40.6</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>12048.8571</v>
+        <v>2288.3428</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3271,22 +3271,22 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.48</v>
+        <v>4.33</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-4.4</v>
+        <v>-5.05</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>13267.29</v>
+        <v>2579.94</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARUTI-20260909-c59a94</t>
+          <t>IND-R2-GLENMARK-20260909-ef0373</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>25455</v>
+        <v>339.55</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>25195</v>
+        <v>336.75</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -3338,14 +3338,14 @@
         </is>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-1.02</v>
+        <v>-0.82</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>31.3</v>
+        <v>32.3</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>24409.2857</v>
+        <v>327.9071</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3372,22 +3372,22 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-4.11</v>
+        <v>-3.43</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>26635.71</v>
+        <v>353.62</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
+          <t>IND-R2-PATANJALI-20260909-508e75</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1952</v>
+        <v>1007.2</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1931.8</v>
+        <v>998</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -3439,14 +3439,14 @@
         </is>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-1.03</v>
+        <v>-0.91</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>31.2</v>
+        <v>35</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>1889.9429</v>
+        <v>967.7286</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.17</v>
+        <v>3.03</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-3.18</v>
+        <v>-3.92</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>2020.51</v>
+        <v>1050.01</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
+          <t>IND-R2-SBIN-20260909-a73231</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>818.3</v>
+        <v>1260</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>808.5</v>
+        <v>1248.2</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -3540,14 +3540,14 @@
         </is>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-1.2</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>31.2</v>
+        <v>33.3</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>778.3714</v>
+        <v>1190.3857</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3574,22 +3574,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>3.73</v>
+        <v>4.63</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-4.88</v>
+        <v>-5.52</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>866.9299999999999</v>
+        <v>1348.37</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
+          <t>IND-R2-NAUKRI-20260909-930931</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>315.55</v>
+        <v>12603</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>311.75</v>
+        <v>12483</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -3641,14 +3641,14 @@
         </is>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-1.2</v>
+        <v>-0.95</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>302.3786</v>
+        <v>12048.8571</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3675,22 +3675,22 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>3.01</v>
+        <v>3.48</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-4.17</v>
+        <v>-4.4</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>329.25</v>
+        <v>13267.29</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RECLTD-20260909-84e6d1</t>
+          <t>IND-R2-MARUTI-20260909-c59a94</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>694.35</v>
+        <v>25455</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>684.85</v>
+        <v>25195</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -3742,14 +3742,14 @@
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-1.37</v>
+        <v>-1.02</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>34.8</v>
+        <v>31.3</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>660.7643</v>
+        <v>24409.2857</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3776,22 +3776,22 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>3.52</v>
+        <v>3.12</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-4.84</v>
+        <v>-4.11</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>729</v>
+        <v>26635.71</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
+          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>470.4</v>
+        <v>1952</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>463.75</v>
+        <v>1931.8</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -3843,14 +3843,14 @@
         </is>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-1.41</v>
+        <v>-1.03</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>28.4</v>
+        <v>31.2</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>453.4071</v>
+        <v>1889.9429</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3877,22 +3877,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-3.61</v>
+        <v>-3.18</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>486.55</v>
+        <v>2020.51</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRCTC-20260909-add681</t>
+          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>6291</v>
+        <v>818.3</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>6189.5</v>
+        <v>808.5</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -3944,14 +3944,14 @@
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-1.61</v>
+        <v>-1.2</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>5959.1429</v>
+        <v>778.3714</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3978,22 +3978,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-5.28</v>
+        <v>-4.88</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>6638.36</v>
+        <v>866.9299999999999</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260909-2f64b0</t>
+          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>154.28</v>
+        <v>315.55</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>151.76</v>
+        <v>311.75</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -4045,14 +4045,14 @@
         </is>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-1.63</v>
+        <v>-1.2</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>145.5286</v>
+        <v>302.3786</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4079,22 +4079,22 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>4.11</v>
+        <v>3.01</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-5.67</v>
+        <v>-4.17</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>163.68</v>
+        <v>329.25</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20260909-938c43</t>
+          <t>IND-R2-RECLTD-20260909-84e6d1</t>
         </is>
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>5163.5</v>
+        <v>694.35</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>5070</v>
+        <v>684.85</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -4146,14 +4146,14 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-1.81</v>
+        <v>-1.37</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>31.3</v>
+        <v>34.8</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>4920.3571</v>
+        <v>660.7643</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4180,22 +4180,22 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>2.95</v>
+        <v>3.52</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-4.71</v>
+        <v>-4.84</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>5385.18</v>
+        <v>729</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ALKEM-20260909-517913</t>
+          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>3134.7</v>
+        <v>470.4</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>3077.1</v>
+        <v>463.75</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-1.84</v>
+        <v>-1.41</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>11.2</v>
+        <v>28.4</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>2959.643</v>
+        <v>453.4071</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="S43" s="4" t="n">
-        <v>3.82</v>
+        <v>2.23</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-5.58</v>
+        <v>-3.61</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>3307.14</v>
+        <v>486.55</v>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MM-20260909-3a8a06</t>
+          <t>IND-R2-IRCTC-20260909-add681</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>860.45</v>
+        <v>6291</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>841.6</v>
+        <v>6189.5</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -4348,14 +4348,14 @@
         </is>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-2.19</v>
+        <v>-1.61</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>35</v>
+        <v>33.3</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>811.05</v>
+        <v>5959.1429</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
@@ -4382,22 +4382,22 @@
         </is>
       </c>
       <c r="S44" s="4" t="n">
-        <v>3.63</v>
+        <v>3.72</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>-5.74</v>
+        <v>-5.28</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>903.71</v>
+        <v>6638.36</v>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260909-3ab469</t>
+          <t>IND-R2-ATUL-20260909-2f64b0</t>
         </is>
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>273.3</v>
+        <v>154.28</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>266.5</v>
+        <v>151.76</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-2.49</v>
+        <v>-1.63</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>28.4</v>
+        <v>33.3</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>255.3143</v>
+        <v>145.5286</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4483,22 +4483,22 @@
         </is>
       </c>
       <c r="S45" s="4" t="n">
-        <v>4.2</v>
+        <v>4.11</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>-6.58</v>
+        <v>-5.67</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>289.39</v>
+        <v>163.68</v>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
+          <t>IND-R2-IGL-20260909-938c43</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4530,19 +4530,19 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>233.86</v>
+        <v>5163.5</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>227.29</v>
+        <v>5070</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -4550,16 +4550,14 @@
         </is>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-2.81</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-1.81</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>31.3</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -4578,7 +4576,7 @@
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>220.1271</v>
+        <v>4920.3571</v>
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
@@ -4586,17 +4584,17 @@
         </is>
       </c>
       <c r="S46" s="4" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>-5.87</v>
+        <v>-4.71</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>244.86</v>
+        <v>5385.18</v>
       </c>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
+          <t>IND-R2-ALKEM-20260909-517913</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
@@ -4613,7 +4611,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4642,10 +4640,10 @@
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>2825</v>
+        <v>3134.7</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>2743.9</v>
+        <v>3077.1</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -4653,14 +4651,14 @@
         </is>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-2.87</v>
+        <v>-1.84</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>36.1</v>
+        <v>11.2</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4679,7 +4677,7 @@
         </is>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>2620.0107</v>
+        <v>2959.643</v>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
@@ -4687,22 +4685,22 @@
         </is>
       </c>
       <c r="S47" s="4" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>-7.26</v>
+        <v>-5.58</v>
       </c>
       <c r="U47" s="4" t="n">
-        <v>3067.12</v>
+        <v>3307.14</v>
       </c>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
+          <t>IND-R2-MM-20260909-3a8a06</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4712,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4743,10 +4741,10 @@
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>3365.2</v>
+        <v>860.45</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>3263.8</v>
+        <v>841.6</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -4754,10 +4752,10 @@
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-3.01</v>
+        <v>-2.19</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>40.4</v>
+        <v>35</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
@@ -4780,7 +4778,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>3085.7715</v>
+        <v>811.05</v>
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -4788,22 +4786,22 @@
         </is>
       </c>
       <c r="S48" s="4" t="n">
-        <v>5.45</v>
+        <v>3.63</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5.74</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>3608.33</v>
+        <v>903.71</v>
       </c>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MCX-20260909-1bc45f</t>
+          <t>IND-R2-INDIANB-20260909-3ab469</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4813,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4835,19 +4833,19 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>117.05</v>
+        <v>273.3</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>113.04</v>
+        <v>266.5</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -4855,16 +4853,14 @@
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-3.43</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-2.49</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>28.4</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4883,7 +4879,7 @@
         </is>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>109.1857</v>
+        <v>255.3143</v>
       </c>
       <c r="R49" s="4" t="inlineStr">
         <is>
@@ -4891,22 +4887,22 @@
         </is>
       </c>
       <c r="S49" s="4" t="n">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>-6.72</v>
+        <v>-6.58</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>121.93</v>
+        <v>289.39</v>
       </c>
       <c r="V49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260908-d0ae28</t>
+          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
         </is>
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4914,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4938,19 +4934,19 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>187.94</v>
+        <v>233.86</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>179.03</v>
+        <v>227.29</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -4958,14 +4954,16 @@
         </is>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-4.74</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>40.6</v>
+        <v>-2.81</v>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -4984,7 +4982,7 @@
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>169.1236</v>
+        <v>220.1271</v>
       </c>
       <c r="R50" s="4" t="inlineStr">
         <is>
@@ -4992,22 +4990,22 @@
         </is>
       </c>
       <c r="S50" s="4" t="n">
-        <v>5.53</v>
+        <v>3.15</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>-10.01</v>
+        <v>-5.87</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>206.77</v>
+        <v>244.86</v>
       </c>
       <c r="V50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260909-29ffd5</t>
+          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5017,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -5048,10 +5046,10 @@
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>275</v>
+        <v>2825</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>260.95</v>
+        <v>2743.9</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -5059,14 +5057,14 @@
         </is>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-5.11</v>
+        <v>-2.87</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>35.4</v>
+        <v>36.1</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5085,7 +5083,7 @@
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>245.8929</v>
+        <v>2620.0107</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -5093,22 +5091,22 @@
         </is>
       </c>
       <c r="S51" s="4" t="n">
-        <v>5.77</v>
+        <v>4.52</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>-10.58</v>
+        <v>-7.26</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>296.13</v>
+        <v>3067.12</v>
       </c>
       <c r="V51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260909-bbba1f</t>
+          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
         </is>
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5118,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -5149,10 +5147,10 @@
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>385.3</v>
+        <v>3365.2</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>356</v>
+        <v>3263.8</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -5160,14 +5158,14 @@
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-7.6</v>
+        <v>-3.01</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5186,7 +5184,7 @@
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>335.0214</v>
+        <v>3085.7715</v>
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
@@ -5194,22 +5192,22 @@
         </is>
       </c>
       <c r="S52" s="4" t="n">
-        <v>5.89</v>
+        <v>5.45</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>-13.05</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>412.84</v>
+        <v>3608.33</v>
       </c>
       <c r="V52" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
+          <t>IND-R2-MCX-20260909-1bc45f</t>
         </is>
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5221,12 +5219,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5236,32 +5234,32 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-05</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>417.6</v>
+        <v>117.05</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>432.9</v>
+        <v>113.04</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K53" s="5" t="n">
-        <v>3.66</v>
+      <c r="K53" s="6" t="n">
+        <v>-3.43</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -5270,7 +5268,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5289,7 +5287,7 @@
         </is>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>407.3714</v>
+        <v>109.1857</v>
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
@@ -5297,22 +5295,22 @@
         </is>
       </c>
       <c r="S53" s="4" t="n">
-        <v>5.9</v>
+        <v>3.41</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>-2.45</v>
+        <v>-6.72</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>432.94</v>
+        <v>121.93</v>
       </c>
       <c r="V53" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R2-IEX-20260908-d0ae28</t>
         </is>
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5322,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -5339,41 +5337,39 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>397</v>
+        <v>187.94</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>411</v>
+        <v>179.03</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K54" s="5" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+      <c r="K54" s="6" t="n">
+        <v>-4.74</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5392,7 +5388,7 @@
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>386.4571</v>
+        <v>169.1236</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
@@ -5400,22 +5396,22 @@
         </is>
       </c>
       <c r="S54" s="4" t="n">
-        <v>5.97</v>
+        <v>5.53</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>-2.66</v>
+        <v>-10.01</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>412.81</v>
+        <v>206.77</v>
       </c>
       <c r="V54" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-SAIL-20260909-29ffd5</t>
         </is>
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5423,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5442,41 +5438,39 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>389.85</v>
+        <v>275</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>401.25</v>
+        <v>260.95</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K55" s="5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+      <c r="K55" s="6" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>35.4</v>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5495,7 +5489,7 @@
         </is>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>378.3286</v>
+        <v>245.8929</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5503,22 +5497,22 @@
         </is>
       </c>
       <c r="S55" s="4" t="n">
-        <v>5.71</v>
+        <v>5.77</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>-2.96</v>
+        <v>-10.58</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>407.13</v>
+        <v>296.13</v>
       </c>
       <c r="V55" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R2-VEDL-20260909-bbba1f</t>
         </is>
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5524,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -5545,41 +5539,39 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>239.45</v>
+        <v>385.3</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>239.6</v>
+        <v>356</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K56" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+      <c r="K56" s="6" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -5598,7 +5590,7 @@
         </is>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>232.2186</v>
+        <v>335.0214</v>
       </c>
       <c r="R56" s="4" t="inlineStr">
         <is>
@@ -5606,22 +5598,22 @@
         </is>
       </c>
       <c r="S56" s="4" t="n">
-        <v>3.08</v>
+        <v>5.89</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>-3.02</v>
+        <v>-13.05</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>250.3</v>
+        <v>412.84</v>
       </c>
       <c r="V56" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
         </is>
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5633,215 +5625,627 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-05</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>432.9</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>407.3714</v>
+      </c>
+      <c r="R57" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S57" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T57" s="4" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>432.94</v>
+      </c>
+      <c r="V57" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+        </is>
+      </c>
+      <c r="W57" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>397</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>411</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>386.4571</v>
+      </c>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S58" s="4" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>412.81</v>
+      </c>
+      <c r="V58" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+        </is>
+      </c>
+      <c r="W58" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>401.25</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P59" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="n">
+        <v>378.3286</v>
+      </c>
+      <c r="R59" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S59" s="4" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="T59" s="4" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>407.13</v>
+      </c>
+      <c r="V59" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
+        </is>
+      </c>
+      <c r="W59" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-11</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>239.45</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>239.6</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="n">
+        <v>232.2186</v>
+      </c>
+      <c r="R60" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S60" s="4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T60" s="4" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="U60" s="4" t="n">
+        <v>250.3</v>
+      </c>
+      <c r="V60" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
+        </is>
+      </c>
+      <c r="W60" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
           <t>TATASTEEL</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-28</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H61" s="4" t="n">
         <v>187.46</v>
       </c>
-      <c r="I57" s="4" t="n">
+      <c r="I61" s="4" t="n">
         <v>182.09</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K57" s="6" t="n">
+      <c r="K61" s="6" t="n">
         <v>-2.86</v>
       </c>
-      <c r="L57" s="4" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N57" s="4" t="inlineStr">
+      <c r="N61" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O57" s="4" t="inlineStr">
+      <c r="O61" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P57" s="4" t="inlineStr">
+      <c r="P61" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q57" s="4" t="n">
+      <c r="Q61" s="4" t="n">
         <v>181.8114</v>
       </c>
-      <c r="R57" s="4" t="inlineStr">
+      <c r="R61" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S57" s="4" t="n">
+      <c r="S61" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="T57" s="4" t="n">
+      <c r="T61" s="4" t="n">
         <v>-3.01</v>
       </c>
-      <c r="U57" s="4" t="n">
+      <c r="U61" s="4" t="n">
         <v>195.93</v>
       </c>
-      <c r="V57" s="4" t="inlineStr">
+      <c r="V61" s="4" t="inlineStr">
         <is>
           <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
-      <c r="W57" s="4" t="inlineStr">
+      <c r="W61" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -5851,16 +6255,18 @@
   <mergeCells count="23">
     <mergeCell ref="A68:W68"/>
     <mergeCell ref="A67:W67"/>
+    <mergeCell ref="A77:W77"/>
     <mergeCell ref="A64:W64"/>
     <mergeCell ref="A73:W73"/>
-    <mergeCell ref="A60:W60"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A70:W70"/>
-    <mergeCell ref="A61:W61"/>
+    <mergeCell ref="A79:W79"/>
     <mergeCell ref="A6:W6"/>
     <mergeCell ref="A69:W69"/>
+    <mergeCell ref="A78:W78"/>
     <mergeCell ref="A65:W65"/>
     <mergeCell ref="A66:W66"/>
+    <mergeCell ref="A80:W80"/>
     <mergeCell ref="A75:W75"/>
     <mergeCell ref="A74:W74"/>
     <mergeCell ref="A3:W3"/>
@@ -5869,9 +6275,7 @@
     <mergeCell ref="A76:W76"/>
     <mergeCell ref="A5:W5"/>
     <mergeCell ref="A4:W4"/>
-    <mergeCell ref="A62:W62"/>
     <mergeCell ref="A72:W72"/>
-    <mergeCell ref="A63:W63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5907,7 +6311,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · 2026-09-14</t>
+          <t>AEGIS INDIA · EXIT HISTORY · 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6414,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -6053,7 +6457,7 @@
         <v>-7.06</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -6084,7 +6488,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -6127,7 +6531,7 @@
         <v>-5.36</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -6158,7 +6562,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -6201,7 +6605,7 @@
         <v>-4.49</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -529,14 +529,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 11 position(s) left CURRENT on a STOP BREACH (R1 11 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>🔴 11 position(s) left CURRENT on a STOP BREACH (R1 11 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 3 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=4 · 228 scored · 52 already in CURRENT · biggest blocker: model disagreement (167) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=4 · 228 scored · 52 already in CURRENT · biggest blocker: model disagreement (165) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=4 · 228 scored · 52 already in CURRENT · biggest blocker: model disagreement (165) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 49 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (7 day(s) old) · ensemble STALE (7 day(s) old) · feature_store STALE (56 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 49 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -508,14 +508,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-15 · prices = 2026-09-11 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-16 · prices = 2026-09-11 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>54 investable · NEW 4 · ACTIVE+ 50 · ACTIVE 0   ·   R2 49 · MOMENTUM 0 · R1 5 (advisory)   ·   9 row(s) read 0.00%: admitted at the 2026-09-11 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>54 investable · NEW 0 · ACTIVE+ 54 · ACTIVE 0   ·   R2 49 · MOMENTUM 0 · R1 5 (advisory)   ·   9 row(s) read 0.00%: admitted at the 2026-09-11 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=4 · 228 scored · 52 already in CURRENT · biggest blocker: model disagreement (167) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (7 day(s) old) · ensemble STALE (7 day(s) old) · feature_store STALE (56 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 49 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -682,44 +682,44 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>123.15</v>
+        <v>19.11</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>123.15</v>
+        <v>19.44</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K8" s="4" t="n">
-        <v>0</v>
+      <c r="K8" s="5" t="n">
+        <v>1.73</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>30.2</v>
+        <v>33.3</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>118.53</v>
+        <v>18.43</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,22 +746,22 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.75</v>
+        <v>-3.56</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>130.08</v>
+        <v>20.21</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260915-4a780b</t>
+          <t>IND-R2-IRB-20260909-153c95</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -783,44 +783,44 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>411</v>
+        <v>11644</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>411</v>
+        <v>11770</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
+      <c r="K9" s="5" t="n">
+        <v>1.08</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>34.1</v>
+        <v>43.6</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>397.4143</v>
+        <v>11221</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>3.31</v>
+        <v>4.66</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.31</v>
+        <v>-3.63</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>431.38</v>
+        <v>12467.93</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260915-bbcfac</t>
+          <t>IND-R2-OFSS-20260909-1e09a0</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -884,44 +884,44 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>285</v>
+        <v>2197.4</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>285</v>
+        <v>2215</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
+      <c r="K10" s="5" t="n">
+        <v>0.8</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>35.4</v>
+        <v>37.1</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>277.2643</v>
+        <v>2112.7571</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>2.71</v>
+        <v>4.62</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.71</v>
+        <v>-3.85</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>296.6</v>
+        <v>2341.29</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-TCS-20260909-fb0a7f</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -985,44 +985,44 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>461.75</v>
+        <v>1949</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>461.75</v>
+        <v>1964.4</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
+      <c r="K11" s="5" t="n">
+        <v>0.79</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>31.2</v>
+        <v>40.6</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>439.8286</v>
+        <v>1891.4857</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1049,22 +1049,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.75</v>
+        <v>3.71</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-4.75</v>
+        <v>-2.95</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>494.63</v>
+        <v>2054.6</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>19.11</v>
+        <v>500</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>19.44</v>
+        <v>503.95</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1116,14 +1116,14 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1.73</v>
+        <v>0.79</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>33.3</v>
+        <v>35.4</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>18.43</v>
+        <v>482.9429</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>5.2</v>
+        <v>4.17</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.56</v>
+        <v>-3.41</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>20.21</v>
+        <v>530.45</v>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260909-153c95</t>
+          <t>IND-R2-OIL-20260909-82436d</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>11644</v>
+        <v>1038.3</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11770</v>
+        <v>1042.1</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1.08</v>
+        <v>0.37</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>43.6</v>
+        <v>38.3</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>11221</v>
+        <v>984.8428</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1251,22 +1251,22 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>4.66</v>
+        <v>5.49</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.63</v>
+        <v>-5.15</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>12467.93</v>
+        <v>1120.78</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260909-1e09a0</t>
+          <t>IND-R2-INFY-20260909-f2b7ad</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2197.4</v>
+        <v>172.76</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2215</v>
+        <v>173.3</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1318,14 +1318,14 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.8</v>
+        <v>0.31</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>37.1</v>
+        <v>30.1</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2112.7571</v>
+        <v>165.6072</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.85</v>
+        <v>-4.14</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2341.29</v>
+        <v>184.71</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260909-fb0a7f</t>
+          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1394,39 +1394,39 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1949</v>
+        <v>1232</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1964.4</v>
+        <v>1232</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K15" s="5" t="n">
-        <v>0.79</v>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>40.6</v>
+        <v>28.3</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1891.4857</v>
+        <v>1199.9714</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>3.71</v>
+        <v>2.6</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.95</v>
+        <v>-2.6</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2054.6</v>
+        <v>1280.04</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IPCALAB-20260909-af9aea</t>
+          <t>IND-R2-ACC-20260911-3a092f</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1495,39 +1495,39 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>500</v>
+        <v>4056.8</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>503.95</v>
+        <v>4056.8</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K16" s="5" t="n">
-        <v>0.79</v>
+      <c r="K16" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>35.4</v>
+        <v>35</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>482.9429</v>
+        <v>3872.6145</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.17</v>
+        <v>4.54</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-3.41</v>
+        <v>-4.54</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>530.45</v>
+        <v>4333.08</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260909-82436d</t>
+          <t>IND-R2-AIAENG-20260911-5d7269</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1596,39 +1596,39 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1038.3</v>
+        <v>388.4</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1042.1</v>
+        <v>388.4</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K17" s="5" t="n">
-        <v>0.37</v>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>38.3</v>
+        <v>31.2</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>984.8428</v>
+        <v>376.1785</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.49</v>
+        <v>3.15</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-5.15</v>
+        <v>-3.15</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1120.78</v>
+        <v>406.73</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260909-f2b7ad</t>
+          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1697,35 +1697,35 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>172.76</v>
+        <v>123.15</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>173.3</v>
+        <v>123.15</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K18" s="5" t="n">
-        <v>0.31</v>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>165.6072</v>
+        <v>118.53</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>4.44</v>
+        <v>3.75</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.14</v>
+        <v>-3.75</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>184.71</v>
+        <v>130.08</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
+          <t>IND-R2-CANBK-20260915-4a780b</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1232</v>
+        <v>1350.1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1232</v>
+        <v>1350.1</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1826,11 +1826,11 @@
         <v>0</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>28.3</v>
+        <v>33.3</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1199.9714</v>
+        <v>1315.6</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1857,22 +1857,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.6</v>
+        <v>-2.56</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1280.04</v>
+        <v>1401.85</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ACC-20260911-3a092f</t>
+          <t>IND-R2-CIPLA-20260911-5f4a49</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4056.8</v>
+        <v>373.25</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4056.8</v>
+        <v>373.25</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1927,11 +1927,11 @@
         <v>0</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>35</v>
+        <v>28.4</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>3872.6145</v>
+        <v>362.4286</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>4.54</v>
+        <v>2.9</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-4.54</v>
+        <v>-2.9</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>4333.08</v>
+        <v>389.48</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AIAENG-20260911-5d7269</t>
+          <t>IND-R2-DABUR-20260911-8f250f</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>388.4</v>
+        <v>1276.6</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>388.4</v>
+        <v>1276.6</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>31.2</v>
+        <v>40.6</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>376.1785</v>
+        <v>1232.8857</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.15</v>
+        <v>-3.42</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>406.73</v>
+        <v>1342.17</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
+          <t>IND-R2-JSWSTEEL-20260911-176cf3</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2101,24 +2101,24 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1350.1</v>
+        <v>411</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1350.1</v>
+        <v>411</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -2129,11 +2129,11 @@
         <v>0</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>33.3</v>
+        <v>34.1</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1315.6</v>
+        <v>397.4143</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2160,22 +2160,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.56</v>
+        <v>3.31</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.56</v>
+        <v>-3.31</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1401.85</v>
+        <v>431.38</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CIPLA-20260911-5f4a49</t>
+          <t>IND-R2-KOTAKBANK-20260915-bbcfac</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>373.25</v>
+        <v>400.4</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>373.25</v>
+        <v>400.4</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -2230,11 +2230,11 @@
         <v>0</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>28.4</v>
+        <v>32.3</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>362.4286</v>
+        <v>386.3857</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2261,22 +2261,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.9</v>
+        <v>-3.5</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>389.48</v>
+        <v>421.42</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DABUR-20260911-8f250f</t>
+          <t>IND-R2-LICI-20260911-098cc1</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1276.6</v>
+        <v>1725</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1276.6</v>
+        <v>1725</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -2331,11 +2331,11 @@
         <v>0</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>40.6</v>
+        <v>31.3</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1232.8857</v>
+        <v>1649.0429</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2362,22 +2362,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.42</v>
+        <v>4.4</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-3.42</v>
+        <v>-4.4</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1342.17</v>
+        <v>1838.94</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWSTEEL-20260911-176cf3</t>
+          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>400.4</v>
+        <v>285</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>400.4</v>
+        <v>285</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -2432,11 +2432,11 @@
         <v>0</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>32.3</v>
+        <v>35.4</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>386.3857</v>
+        <v>277.2643</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2463,22 +2463,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.5</v>
+        <v>2.71</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-3.5</v>
+        <v>-2.71</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>421.42</v>
+        <v>296.6</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260911-098cc1</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1725</v>
+        <v>8128.5</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1725</v>
+        <v>8128.5</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -2533,11 +2533,11 @@
         <v>0</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>31.3</v>
+        <v>38.7</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1649.0429</v>
+        <v>7774</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2564,22 +2564,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-4.4</v>
+        <v>-4.36</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1838.94</v>
+        <v>8660.25</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2606,24 +2606,24 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-14</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>8128.5</v>
+        <v>406.6</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8128.5</v>
+        <v>406.6</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2634,11 +2634,11 @@
         <v>0</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>38.7</v>
+        <v>37</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>7774</v>
+        <v>391.6786</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.36</v>
+        <v>3.67</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-4.36</v>
+        <v>-3.67</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>8660.25</v>
+        <v>428.98</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2707,24 +2707,24 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-14</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>406.6</v>
+        <v>461.75</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>406.6</v>
+        <v>461.75</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -2735,11 +2735,11 @@
         <v>0</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>37</v>
+        <v>31.2</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>391.6786</v>
+        <v>439.8286</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2766,17 +2766,17 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.67</v>
+        <v>4.75</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-3.67</v>
+        <v>-4.75</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>428.98</v>
+        <v>494.63</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · 2026-09-15</t>
+          <t>AEGIS INDIA · EXIT HISTORY · 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -6457,7 +6457,7 @@
         <v>-7.06</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -6531,7 +6531,7 @@
         <v>-5.36</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -6605,7 +6605,7 @@
         <v>-4.49</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W80"/>
+  <dimension ref="A1:W82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,21 +508,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-16 · prices = 2026-09-11 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-16 · prices = 2026-09-15 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>54 investable · NEW 0 · ACTIVE+ 54 · ACTIVE 0   ·   R2 49 · MOMENTUM 0 · R1 5 (advisory)   ·   9 row(s) read 0.00%: admitted at the 2026-09-11 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>56 investable · NEW 3 · ACTIVE+ 53 · ACTIVE 0   ·   R2 51 · MOMENTUM 0 · R1 5 (advisory)   ·   4 row(s) read 0.00%: admitted at the 2026-09-15 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 54 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.66% from entry, worst single -13.05%</t>
+          <t>🛡 DOWNSIDE · 56 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.36% from entry, worst single -13.05%</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=4 · 228 scored · 52 already in CURRENT · biggest blocker: model disagreement (167) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 228 scored · 52 already in CURRENT · biggest blocker: model disagreement (166) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 49 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -692,34 +692,34 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>19.11</v>
+        <v>406.2</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>19.44</v>
+        <v>406.2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>1.73</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>33.3</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>18.43</v>
+        <v>390.4</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,22 +746,22 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>5.2</v>
+        <v>3.89</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.56</v>
+        <v>-3.89</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>20.21</v>
+        <v>429.9</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260909-153c95</t>
+          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -793,34 +793,34 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>11644</v>
+        <v>132.03</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>11770</v>
+        <v>132.03</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>1.08</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>43.6</v>
+        <v>28.7</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>11221</v>
+        <v>127.9057</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>4.66</v>
+        <v>3.12</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.63</v>
+        <v>-3.12</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>12467.93</v>
+        <v>138.22</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260909-1e09a0</t>
+          <t>IND-R2-IOC-20260916-b0f93c</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -894,34 +894,34 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2197.4</v>
+        <v>80.5</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2215</v>
+        <v>80.5</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0.8</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>37.1</v>
+        <v>31.2</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2112.7571</v>
+        <v>76.8771</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.85</v>
+        <v>-4.5</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2341.29</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260909-fb0a7f</t>
+          <t>IND-R2-NMDC-20260916-75297f</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1004,25 +1004,25 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1949</v>
+        <v>1038.3</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1964.4</v>
+        <v>1077</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.79</v>
+        <v>3.73</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>40.6</v>
+        <v>38.3</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1891.4857</v>
+        <v>1014.9714</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1049,22 +1049,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>3.71</v>
+        <v>5.76</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.95</v>
+        <v>-2.25</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2054.6</v>
+        <v>1120.78</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IPCALAB-20260909-af9aea</t>
+          <t>IND-R2-INFY-20260909-f2b7ad</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>500</v>
+        <v>694.35</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>503.95</v>
+        <v>716.55</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.79</v>
+        <v>3.2</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>35.4</v>
+        <v>34.8</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>482.9429</v>
+        <v>687.25</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.17</v>
+        <v>4.09</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.41</v>
+        <v>-1.02</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>530.45</v>
+        <v>729</v>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260909-82436d</t>
+          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1192,39 +1192,39 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1038.3</v>
+        <v>373.25</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1042.1</v>
+        <v>384.9</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.37</v>
+        <v>3.12</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>38.3</v>
+        <v>28.4</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>984.8428</v>
+        <v>372.3857</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1251,22 +1251,22 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>5.49</v>
+        <v>3.25</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-5.15</v>
+        <v>-0.23</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1120.78</v>
+        <v>389.48</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260909-f2b7ad</t>
+          <t>IND-R2-DABUR-20260911-8f250f</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1307,25 +1307,25 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>172.76</v>
+        <v>2197.4</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>173.3</v>
+        <v>2251</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.31</v>
+        <v>2.44</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>30.1</v>
+        <v>37.1</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>165.6072</v>
+        <v>2142.5</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.44</v>
+        <v>4.82</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-4.14</v>
+        <v>-2.5</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>184.71</v>
+        <v>2341.29</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
+          <t>IND-R2-TCS-20260909-fb0a7f</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1394,39 +1394,39 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1232</v>
+        <v>292.9</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1232</v>
+        <v>297.5</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1.57</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>28.3</v>
+        <v>34.3</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1199.9714</v>
+        <v>283.3839</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.6</v>
+        <v>4.74</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.6</v>
+        <v>-3.25</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1280.04</v>
+        <v>315.92</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ACC-20260911-3a092f</t>
+          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1495,39 +1495,39 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4056.8</v>
+        <v>11644</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4056.8</v>
+        <v>11770</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1.08</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>35</v>
+        <v>43.6</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>3872.6145</v>
+        <v>11221</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.54</v>
+        <v>4.66</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-4.54</v>
+        <v>-3.63</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4333.08</v>
+        <v>12467.93</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AIAENG-20260911-5d7269</t>
+          <t>IND-R2-OFSS-20260909-1e09a0</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1596,39 +1596,39 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>388.4</v>
+        <v>370</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>388.4</v>
+        <v>373.7</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>31.2</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>376.1785</v>
+        <v>352.9</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>3.15</v>
+        <v>5.57</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-3.15</v>
+        <v>-4.62</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>406.73</v>
+        <v>397.71</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
+          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1697,39 +1697,39 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
-        <v>123.15</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>123.15</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
+      <c r="K18" s="5" t="n">
+        <v>0.37</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>30.2</v>
+        <v>33.3</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>118.53</v>
+        <v>18.43</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.75</v>
+        <v>3.91</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-3.75</v>
+        <v>-3.56</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>130.08</v>
+        <v>20.21</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260915-4a780b</t>
+          <t>IND-R2-IRB-20260909-153c95</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1798,35 +1798,35 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1350.1</v>
+        <v>818.3</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1350.1</v>
+        <v>819.15</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.1</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1315.6</v>
+        <v>788.0929</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1857,22 +1857,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.56</v>
+        <v>3.79</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.56</v>
+        <v>-3.69</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1401.85</v>
+        <v>866.9299999999999</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CIPLA-20260911-5f4a49</t>
+          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1913,25 +1913,25 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>373.25</v>
+        <v>1350.1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>373.25</v>
+        <v>1351</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>28.4</v>
+        <v>33.3</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>362.4286</v>
+        <v>1315.6</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.9</v>
+        <v>-2.56</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>389.48</v>
+        <v>1401.85</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DABUR-20260911-8f250f</t>
+          <t>IND-R2-CIPLA-20260911-5f4a49</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1276.6</v>
+        <v>4056.8</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1276.6</v>
+        <v>4056.8</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>40.6</v>
+        <v>35</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1232.8857</v>
+        <v>3872.6145</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2059,17 +2059,17 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.42</v>
+        <v>4.54</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.42</v>
+        <v>-4.54</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1342.17</v>
+        <v>4333.08</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWSTEEL-20260911-176cf3</t>
+          <t>IND-R2-AIAENG-20260911-5d7269</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2115,21 +2115,21 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>411</v>
+        <v>122.37</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>411</v>
+        <v>122.37</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>34.1</v>
+        <v>30.2</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>397.4143</v>
+        <v>118.53</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2160,22 +2160,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.31</v>
+        <v>-3.14</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>431.38</v>
+        <v>128.89</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260915-bbcfac</t>
+          <t>IND-R2-CANBK-20260915-4a780b</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2202,35 +2202,35 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>400.4</v>
+        <v>409.8</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>400.4</v>
+        <v>409.8</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>32.3</v>
+        <v>34.1</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>386.3857</v>
+        <v>397.4143</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2261,22 +2261,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-3.5</v>
+        <v>-3.02</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>421.42</v>
+        <v>432.43</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260911-098cc1</t>
+          <t>IND-R2-KOTAKBANK-20260915-bbcfac</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2303,39 +2303,39 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1725</v>
+        <v>285</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1725</v>
+        <v>285</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>31.3</v>
+        <v>35.4</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1649.0429</v>
+        <v>277.2643</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2362,22 +2362,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.4</v>
+        <v>2.71</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-4.4</v>
+        <v>-2.71</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1838.94</v>
+        <v>296.6</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2404,39 +2404,39 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>8128.5</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>8128.5</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>285</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>285</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>35.4</v>
+        <v>38.7</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>277.2643</v>
+        <v>7774</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2463,22 +2463,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.71</v>
+        <v>4.36</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-2.71</v>
+        <v>-4.36</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>296.6</v>
+        <v>8660.25</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2505,39 +2505,39 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>8128.5</v>
+        <v>464.25</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8128.5</v>
+        <v>464.25</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>38.7</v>
+        <v>31.2</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>7774</v>
+        <v>440.6143</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2564,22 +2564,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.36</v>
+        <v>5.09</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-4.36</v>
+        <v>-5.09</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>8660.25</v>
+        <v>499.7</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2606,35 +2606,35 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-14</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>406.6</v>
+        <v>172.76</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>406.6</v>
+        <v>172.45</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>-0.18</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>37</v>
+        <v>30.1</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>391.6786</v>
+        <v>165.6072</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>3.67</v>
+        <v>3.97</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-3.67</v>
+        <v>-4.14</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>428.98</v>
+        <v>184.71</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
+          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2707,39 +2707,39 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>339.55</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>338.55</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
-        <v>461.75</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>461.75</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>0</v>
+      <c r="K28" s="6" t="n">
+        <v>-0.29</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>31.2</v>
+        <v>32.3</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>439.8286</v>
+        <v>329.05</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.75</v>
+        <v>2.81</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-4.75</v>
+        <v>-3.09</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>494.63</v>
+        <v>353.62</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-PATANJALI-20260909-508e75</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2808,39 +2808,39 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>434.2</v>
+        <v>1232</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>432.9</v>
+        <v>1225.2</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.3</v>
+        <v>-0.55</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>33.3</v>
+        <v>28.3</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>417.55</v>
+        <v>1199.9714</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2867,22 +2867,22 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.55</v>
+        <v>2.06</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-3.83</v>
+        <v>-2.6</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>456.13</v>
+        <v>1280.04</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260909-3c298a</t>
+          <t>IND-R2-ACC-20260911-3a092f</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2923,25 +2923,25 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1244.4</v>
+        <v>1952</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1237.2</v>
+        <v>1938.1</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.58</v>
+        <v>-0.71</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>32.9</v>
+        <v>31.2</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1204.5857</v>
+        <v>1893.4428</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2968,17 +2968,17 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.2</v>
+        <v>-3</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1294.16</v>
+        <v>2020.51</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AXISBANK-20260909-3abb74</t>
+          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3024,25 +3024,25 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>292.9</v>
+        <v>1949</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>290.9</v>
+        <v>1932.4</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.68</v>
+        <v>-0.85</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>34.3</v>
+        <v>40.6</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>274.9429</v>
+        <v>1891.4857</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3069,22 +3069,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.49</v>
+        <v>2.12</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-6.13</v>
+        <v>-2.95</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>315.92</v>
+        <v>2054.6</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -3125,25 +3125,25 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>370</v>
+        <v>1260</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>367.45</v>
+        <v>1248.2</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>31.2</v>
+        <v>33.3</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>348.7929</v>
+        <v>1190.3857</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3170,22 +3170,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>5.08</v>
+        <v>4.63</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-5.73</v>
+        <v>-5.52</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>397.71</v>
+        <v>1348.37</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
+          <t>IND-R2-NAUKRI-20260909-930931</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -3226,21 +3226,21 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2410.1</v>
+        <v>25455</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2391.9</v>
+        <v>25195</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.76</v>
+        <v>-1.02</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>40.6</v>
+        <v>31.3</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>2288.3428</v>
+        <v>24409.2857</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3271,17 +3271,17 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.33</v>
+        <v>3.12</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-5.05</v>
+        <v>-4.11</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2579.94</v>
+        <v>26635.71</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GLENMARK-20260909-ef0373</t>
+          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -3327,25 +3327,25 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>339.55</v>
+        <v>2410.1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>336.75</v>
+        <v>2371.7</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.82</v>
+        <v>-1.59</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>32.3</v>
+        <v>40.6</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>327.9071</v>
+        <v>2288.3428</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3372,17 +3372,17 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>2.63</v>
+        <v>3.51</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-3.43</v>
+        <v>-5.05</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>353.62</v>
+        <v>2579.94</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PATANJALI-20260909-508e75</t>
+          <t>IND-R2-GLENMARK-20260909-ef0373</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1007.2</v>
+        <v>6291</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>998</v>
+        <v>6189.5</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.91</v>
+        <v>-1.61</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>35</v>
+        <v>33.3</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>967.7286</v>
+        <v>5959.1429</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>3.03</v>
+        <v>3.72</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-3.92</v>
+        <v>-5.28</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1050.01</v>
+        <v>6638.36</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20260909-a73231</t>
+          <t>IND-R2-ATUL-20260909-2f64b0</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3515,39 +3515,39 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1260</v>
+        <v>388.4</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1248.2</v>
+        <v>381.75</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.71</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>1190.3857</v>
+        <v>376.1785</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3574,22 +3574,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>4.63</v>
+        <v>1.46</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-5.52</v>
+        <v>-3.15</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>1348.37</v>
+        <v>406.73</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NAUKRI-20260909-930931</t>
+          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3630,25 +3630,25 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>12603</v>
+        <v>1244.4</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>12483</v>
+        <v>1222.9</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.95</v>
+        <v>-1.73</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>31.3</v>
+        <v>32.9</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>12048.8571</v>
+        <v>1204.5857</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3675,17 +3675,17 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>3.48</v>
+        <v>1.5</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-4.4</v>
+        <v>-3.2</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>13267.29</v>
+        <v>1294.16</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARUTI-20260909-c59a94</t>
+          <t>IND-R2-AXISBANK-20260909-3abb74</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -3731,18 +3731,18 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>25455</v>
+        <v>5163.5</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>25195</v>
+        <v>5070</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-1.02</v>
+        <v>-1.81</v>
       </c>
       <c r="L38" s="4" t="n">
         <v>31.3</v>
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>24409.2857</v>
+        <v>4920.3571</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3776,17 +3776,17 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-4.11</v>
+        <v>-4.71</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>26635.71</v>
+        <v>5385.18</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
+          <t>IND-R2-ALKEM-20260909-517913</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3818,39 +3818,39 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-14</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1952</v>
+        <v>412.55</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>1931.8</v>
+        <v>403.6</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-1.03</v>
+        <v>-2.17</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>31.2</v>
+        <v>37</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>1889.9429</v>
+        <v>391.6786</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3877,22 +3877,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>2.17</v>
+        <v>2.95</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-3.18</v>
+        <v>-5.06</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>2020.51</v>
+        <v>435.12</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
+          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3919,39 +3919,39 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>818.3</v>
+        <v>400.4</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>808.5</v>
+        <v>391.5</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-1.2</v>
+        <v>-2.22</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>31.2</v>
+        <v>32.3</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>778.3714</v>
+        <v>386.3857</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3978,22 +3978,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>3.73</v>
+        <v>1.31</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-4.88</v>
+        <v>-3.5</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>866.9299999999999</v>
+        <v>421.42</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
+          <t>IND-R2-LICI-20260911-098cc1</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -4037,15 +4037,15 @@
         <v>315.55</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>311.75</v>
+        <v>308.5</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-1.2</v>
+        <v>-2.23</v>
       </c>
       <c r="L41" s="4" t="n">
         <v>31.2</v>
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>3.01</v>
+        <v>1.98</v>
       </c>
       <c r="T41" s="4" t="n">
         <v>-4.17</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -4135,25 +4135,25 @@
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>694.35</v>
+        <v>470.4</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>684.85</v>
+        <v>458.55</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-1.37</v>
+        <v>-2.52</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>34.8</v>
+        <v>28.4</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>660.7643</v>
+        <v>453.4071</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4180,17 +4180,17 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>3.52</v>
+        <v>1.12</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-4.84</v>
+        <v>-3.61</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>729</v>
+        <v>486.55</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
+          <t>IND-R2-IRCTC-20260909-add681</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -4236,25 +4236,25 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>470.4</v>
+        <v>154.28</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>463.75</v>
+        <v>150.03</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-1.41</v>
+        <v>-2.75</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>28.4</v>
+        <v>33.3</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>453.4071</v>
+        <v>145.5286</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="S43" s="4" t="n">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-3.61</v>
+        <v>-5.67</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>486.55</v>
+        <v>163.68</v>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRCTC-20260909-add681</t>
+          <t>IND-R2-IGL-20260909-938c43</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -4337,25 +4337,25 @@
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>6291</v>
+        <v>860.45</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>6189.5</v>
+        <v>836.75</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-1.61</v>
+        <v>-2.75</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>5959.1429</v>
+        <v>811.05</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
@@ -4382,17 +4382,17 @@
         </is>
       </c>
       <c r="S44" s="4" t="n">
-        <v>3.72</v>
+        <v>3.07</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>-5.28</v>
+        <v>-5.74</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>6638.36</v>
+        <v>903.71</v>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260909-2f64b0</t>
+          <t>IND-R2-INDIANB-20260909-3ab469</t>
         </is>
       </c>
       <c r="W44" s="4" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -4438,25 +4438,25 @@
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>154.28</v>
+        <v>2825</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>151.76</v>
+        <v>2743.9</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-1.63</v>
+        <v>-2.87</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>33.3</v>
+        <v>36.1</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>145.5286</v>
+        <v>2620.0107</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4483,22 +4483,22 @@
         </is>
       </c>
       <c r="S45" s="4" t="n">
-        <v>4.11</v>
+        <v>4.52</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>-5.67</v>
+        <v>-7.26</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>163.68</v>
+        <v>3067.12</v>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20260909-938c43</t>
+          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -4539,25 +4539,25 @@
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>5163.5</v>
+        <v>500</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>5070</v>
+        <v>485.6</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-1.81</v>
+        <v>-2.88</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>31.3</v>
+        <v>35.4</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>4920.3571</v>
+        <v>482.9429</v>
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
@@ -4584,22 +4584,22 @@
         </is>
       </c>
       <c r="S46" s="4" t="n">
-        <v>2.95</v>
+        <v>0.55</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>-4.71</v>
+        <v>-3.41</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>5385.18</v>
+        <v>530.45</v>
       </c>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ALKEM-20260909-517913</t>
+          <t>IND-R2-OIL-20260909-82436d</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -4640,21 +4640,21 @@
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>3134.7</v>
+        <v>12603</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>3077.1</v>
+        <v>12231</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-1.84</v>
+        <v>-2.95</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>11.2</v>
+        <v>31.3</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>2959.643</v>
+        <v>12048.8571</v>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
@@ -4685,17 +4685,17 @@
         </is>
       </c>
       <c r="S47" s="4" t="n">
-        <v>3.82</v>
+        <v>1.49</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>-5.58</v>
+        <v>-4.4</v>
       </c>
       <c r="U47" s="4" t="n">
-        <v>3307.14</v>
+        <v>13267.29</v>
       </c>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MM-20260909-3a8a06</t>
+          <t>IND-R2-MARUTI-20260909-c59a94</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4727,39 +4727,39 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>860.45</v>
+        <v>1725</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>841.6</v>
+        <v>1668.5</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-2.19</v>
+        <v>-3.28</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>35</v>
+        <v>31.3</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>811.05</v>
+        <v>1649.0429</v>
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -4786,22 +4786,22 @@
         </is>
       </c>
       <c r="S48" s="4" t="n">
-        <v>3.63</v>
+        <v>1.17</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>-5.74</v>
+        <v>-4.4</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>903.71</v>
+        <v>1838.94</v>
       </c>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260909-3ab469</t>
+          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -4842,25 +4842,25 @@
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>273.3</v>
+        <v>3134.7</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>266.5</v>
+        <v>3029.5</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-2.49</v>
+        <v>-3.36</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>28.4</v>
+        <v>11.2</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>255.3143</v>
+        <v>2959.643</v>
       </c>
       <c r="R49" s="4" t="inlineStr">
         <is>
@@ -4887,17 +4887,17 @@
         </is>
       </c>
       <c r="S49" s="4" t="n">
-        <v>4.2</v>
+        <v>2.31</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>-6.58</v>
+        <v>-5.58</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>289.39</v>
+        <v>3307.14</v>
       </c>
       <c r="V49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
+          <t>IND-R2-MM-20260909-3a8a06</t>
         </is>
       </c>
       <c r="W49" s="4" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4929,41 +4929,39 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>233.86</v>
+        <v>434.2</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>227.29</v>
+        <v>419.25</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-2.81</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-3.44</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -4982,7 +4980,7 @@
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>220.1271</v>
+        <v>417.55</v>
       </c>
       <c r="R50" s="4" t="inlineStr">
         <is>
@@ -4990,22 +4988,22 @@
         </is>
       </c>
       <c r="S50" s="4" t="n">
-        <v>3.15</v>
+        <v>0.41</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>-5.87</v>
+        <v>-3.83</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>244.86</v>
+        <v>456.13</v>
       </c>
       <c r="V50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
+          <t>IND-R2-COALINDIA-20260909-3c298a</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5015,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -5032,35 +5030,37 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>2825</v>
+        <v>233.86</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>2743.9</v>
+        <v>225.6</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-2.87</v>
-      </c>
-      <c r="L51" s="4" t="n">
-        <v>36.1</v>
+        <v>-3.53</v>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>2620.0107</v>
+        <v>220.1271</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -5091,22 +5091,22 @@
         </is>
       </c>
       <c r="S51" s="4" t="n">
-        <v>4.52</v>
+        <v>2.43</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>-7.26</v>
+        <v>-5.87</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>3067.12</v>
+        <v>244.86</v>
       </c>
       <c r="V51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
+          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
         </is>
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -5147,21 +5147,21 @@
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>3365.2</v>
+        <v>1007.2</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>3263.8</v>
+        <v>968</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-3.01</v>
+        <v>-3.89</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>40.4</v>
+        <v>35</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>3085.7715</v>
+        <v>967.7286</v>
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
@@ -5192,17 +5192,17 @@
         </is>
       </c>
       <c r="S52" s="4" t="n">
-        <v>5.45</v>
+        <v>0.03</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>-8.300000000000001</v>
+        <v>-3.92</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>3608.33</v>
+        <v>1050.01</v>
       </c>
       <c r="V52" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MCX-20260909-1bc45f</t>
+          <t>IND-R2-SBIN-20260909-a73231</t>
         </is>
       </c>
       <c r="W52" s="4" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -5251,15 +5251,15 @@
         <v>117.05</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>113.04</v>
+        <v>112</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-3.43</v>
+        <v>-4.31</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="S53" s="4" t="n">
-        <v>3.41</v>
+        <v>2.51</v>
       </c>
       <c r="T53" s="4" t="n">
         <v>-6.72</v>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -5351,25 +5351,25 @@
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>187.94</v>
+        <v>273.3</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>179.03</v>
+        <v>261.05</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-4.74</v>
+        <v>-4.48</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>40.6</v>
+        <v>28.4</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>169.1236</v>
+        <v>255.3143</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
@@ -5396,22 +5396,22 @@
         </is>
       </c>
       <c r="S54" s="4" t="n">
-        <v>5.53</v>
+        <v>2.2</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>-10.01</v>
+        <v>-6.58</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>206.77</v>
+        <v>289.39</v>
       </c>
       <c r="V54" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260909-29ffd5</t>
+          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
         </is>
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5452,25 +5452,25 @@
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>275</v>
+        <v>3365.2</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>260.95</v>
+        <v>3173.5</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-5.11</v>
+        <v>-5.7</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>35.4</v>
+        <v>40.4</v>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>245.8929</v>
+        <v>3085.7715</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5497,22 +5497,22 @@
         </is>
       </c>
       <c r="S55" s="4" t="n">
-        <v>5.77</v>
+        <v>2.76</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>-10.58</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>296.13</v>
+        <v>3608.33</v>
       </c>
       <c r="V55" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260909-bbba1f</t>
+          <t>IND-R2-MCX-20260909-1bc45f</t>
         </is>
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -5553,21 +5553,21 @@
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>385.3</v>
+        <v>275</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>356</v>
+        <v>257</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-7.6</v>
+        <v>-6.55</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>335.0214</v>
+        <v>245.8929</v>
       </c>
       <c r="R56" s="4" t="inlineStr">
         <is>
@@ -5598,17 +5598,17 @@
         </is>
       </c>
       <c r="S56" s="4" t="n">
-        <v>5.89</v>
+        <v>4.32</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>-13.05</v>
+        <v>-10.58</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>412.84</v>
+        <v>296.13</v>
       </c>
       <c r="V56" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
+          <t>IND-R2-VEDL-20260909-bbba1f</t>
         </is>
       </c>
       <c r="W56" s="4" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5640,41 +5640,39 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-05</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>417.6</v>
+        <v>187.94</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>432.9</v>
+        <v>173</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>-7.95</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -5693,7 +5691,7 @@
         </is>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>407.3714</v>
+        <v>169.1236</v>
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
@@ -5701,22 +5699,22 @@
         </is>
       </c>
       <c r="S57" s="4" t="n">
-        <v>5.9</v>
+        <v>2.24</v>
       </c>
       <c r="T57" s="4" t="n">
-        <v>-2.45</v>
+        <v>-10.01</v>
       </c>
       <c r="U57" s="4" t="n">
-        <v>432.94</v>
+        <v>206.77</v>
       </c>
       <c r="V57" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R2-SAIL-20260909-29ffd5</t>
         </is>
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5728,12 +5726,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -5743,41 +5741,39 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>397</v>
+        <v>385.3</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>411</v>
+        <v>350.55</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>-9.02</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -5796,7 +5792,7 @@
         </is>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>386.4571</v>
+        <v>335.0214</v>
       </c>
       <c r="R58" s="4" t="inlineStr">
         <is>
@@ -5804,22 +5800,22 @@
         </is>
       </c>
       <c r="S58" s="4" t="n">
-        <v>5.97</v>
+        <v>4.43</v>
       </c>
       <c r="T58" s="4" t="n">
-        <v>-2.66</v>
+        <v>-13.05</v>
       </c>
       <c r="U58" s="4" t="n">
-        <v>412.81</v>
+        <v>412.84</v>
       </c>
       <c r="V58" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
         </is>
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5827,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -5860,18 +5856,18 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>389.85</v>
+        <v>397</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>401.25</v>
+        <v>409.8</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -5880,7 +5876,7 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -5899,7 +5895,7 @@
         </is>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>378.3286</v>
+        <v>386.4571</v>
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
@@ -5907,17 +5903,17 @@
         </is>
       </c>
       <c r="S59" s="4" t="n">
-        <v>5.71</v>
+        <v>5.7</v>
       </c>
       <c r="T59" s="4" t="n">
-        <v>-2.96</v>
+        <v>-2.66</v>
       </c>
       <c r="U59" s="4" t="n">
-        <v>407.13</v>
+        <v>412.81</v>
       </c>
       <c r="V59" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
       <c r="W59" s="4" t="inlineStr">
@@ -5934,7 +5930,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -5954,27 +5950,27 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-11</t>
+          <t>Admitted 2026-08-05</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>239.45</v>
+        <v>417.6</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>239.6</v>
+        <v>419.25</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6002,7 +5998,7 @@
         </is>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>232.2186</v>
+        <v>407.3714</v>
       </c>
       <c r="R60" s="4" t="inlineStr">
         <is>
@@ -6010,17 +6006,17 @@
         </is>
       </c>
       <c r="S60" s="4" t="n">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="T60" s="4" t="n">
-        <v>-3.02</v>
+        <v>-2.45</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>250.3</v>
+        <v>432.94</v>
       </c>
       <c r="V60" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
         </is>
       </c>
       <c r="W60" s="4" t="inlineStr">
@@ -6037,215 +6033,421 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-11</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>239.45</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>235.95</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="n">
+        <v>232.2186</v>
+      </c>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T61" s="4" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="U61" s="4" t="n">
+        <v>250.3</v>
+      </c>
+      <c r="V61" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
+        </is>
+      </c>
+      <c r="W61" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="n">
+        <v>378.3286</v>
+      </c>
+      <c r="R62" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S62" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T62" s="4" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="U62" s="4" t="n">
+        <v>407.13</v>
+      </c>
+      <c r="V62" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
+        </is>
+      </c>
+      <c r="W62" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
           <t>TATASTEEL</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-28</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="H61" s="4" t="n">
+      <c r="H63" s="4" t="n">
         <v>187.46</v>
       </c>
-      <c r="I61" s="4" t="n">
-        <v>182.09</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K61" s="6" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
+      <c r="I63" s="4" t="n">
+        <v>183.65</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M61" s="4" t="inlineStr">
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N61" s="4" t="inlineStr">
+      <c r="N63" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O61" s="4" t="inlineStr">
+      <c r="O63" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P61" s="4" t="inlineStr">
+      <c r="P63" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q61" s="4" t="n">
+      <c r="Q63" s="4" t="n">
         <v>181.8114</v>
       </c>
-      <c r="R61" s="4" t="inlineStr">
+      <c r="R63" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S61" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="T61" s="4" t="n">
+      <c r="S63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" s="4" t="n">
         <v>-3.01</v>
       </c>
-      <c r="U61" s="4" t="n">
+      <c r="U63" s="4" t="n">
         <v>195.93</v>
       </c>
-      <c r="V61" s="4" t="inlineStr">
+      <c r="V63" s="4" t="inlineStr">
         <is>
           <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
-      <c r="W61" s="4" t="inlineStr">
+      <c r="W63" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -6256,7 +6458,7 @@
     <mergeCell ref="A68:W68"/>
     <mergeCell ref="A67:W67"/>
     <mergeCell ref="A77:W77"/>
-    <mergeCell ref="A64:W64"/>
+    <mergeCell ref="A82:W82"/>
     <mergeCell ref="A73:W73"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A70:W70"/>
@@ -6264,7 +6466,6 @@
     <mergeCell ref="A6:W6"/>
     <mergeCell ref="A69:W69"/>
     <mergeCell ref="A78:W78"/>
-    <mergeCell ref="A65:W65"/>
     <mergeCell ref="A66:W66"/>
     <mergeCell ref="A80:W80"/>
     <mergeCell ref="A75:W75"/>
@@ -6276,6 +6477,7 @@
     <mergeCell ref="A5:W5"/>
     <mergeCell ref="A4:W4"/>
     <mergeCell ref="A72:W72"/>
+    <mergeCell ref="A81:W81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6287,7 +6489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6318,14 +6520,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>66 records · ADMINISTRATIVE 21 · ADVISORY/HISTORICAL 5 · REALIZED EXIT 29 · STOP-BREACH MARK 11   ·   Canonical lifecycle historical coverage begins 2026-08-04 · earlier closures are not held in any provable AEGIS source</t>
+          <t>67 records · ADMINISTRATIVE 21 · ADVISORY/HISTORICAL 5 · REALIZED EXIT 30 · STOP-BREACH MARK 11   ·   Canonical lifecycle historical coverage begins 2026-08-04 · earlier closures are not held in any provable AEGIS source</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>📊 REALIZED PRODUCTION PERFORMANCE · 29 closed trade(s) · win 12/29 · avg -1.45%   ·   EXCLUDED from this line: orphan auto-closes, administrative records, advisory rows, and 11 STOP-BREACH MARK(s) whose stop was passed but which are NOT sold - their price and P&amp;L are today's mark, not a realized result</t>
+          <t>📊 REALIZED PRODUCTION PERFORMANCE · 30 closed trade(s) · win 12/30 · avg -1.53%   ·   EXCLUDED from this line: orphan auto-closes, administrative records, advisory rows, and 11 STOP-BREACH MARK(s) whose stop was passed but which are NOT sold - their price and P&amp;L are today's mark, not a realized result</t>
         </is>
       </c>
     </row>
@@ -6451,10 +6653,10 @@
         <v>1191</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1106.9</v>
+        <v>1099</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-7.06</v>
+        <v>-7.72</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>36</v>
@@ -6493,12 +6695,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -6508,54 +6710,52 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1449.5</v>
+        <v>1276.6</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1371.8</v>
+        <v>1229.2</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-5.36</v>
+        <v>-3.71</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>EXIT_STOP · trigger crossed 2026-09-15 ·</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-09-15 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R2-JSWSTEEL-20260911-176cf3</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -6567,12 +6767,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -6592,20 +6792,20 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1413.5</v>
+        <v>1449.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1350.1</v>
+        <v>1350.4</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-4.49</v>
+        <v>-6.84</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -6619,12 +6819,12 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
@@ -6636,17 +6836,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -6656,34 +6856,34 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2744.3</v>
+        <v>1413.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2588.5</v>
+        <v>1351</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-5.68</v>
+        <v>-4.42</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Holding horizon reached</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -6693,17 +6893,17 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>EXIT_HORIZON · trigger crossed 2026-09-11 · stop_source=dyna</t>
+          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
@@ -6715,12 +6915,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -6740,20 +6940,20 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>115.63</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>2</v>
+        <v>2588.5</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>-5.68</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -6772,7 +6972,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -6789,12 +6989,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -6814,20 +7014,20 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5510</v>
+        <v>115.63</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -6846,7 +7046,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -6863,12 +7063,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -6888,20 +7088,20 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>284.85</v>
+        <v>5499</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>260.1</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>-8.69</v>
+        <v>5510</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.2</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -6920,7 +7120,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ITC-20260804-e0ebbb</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -6937,12 +7137,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -6962,20 +7162,20 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>553.3</v>
+        <v>284.85</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>560.25</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>1.26</v>
+        <v>260.1</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>-8.69</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -6994,7 +7194,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20260806-03d0a7</t>
+          <t>IND-R2-ITC-20260804-e0ebbb</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -7011,7 +7211,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -7036,20 +7236,20 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>452.35</v>
+        <v>553.3</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>414.95</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>-8.27</v>
+        <v>560.25</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>1.26</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -7068,7 +7268,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
+          <t>IND-R2-GNFC-20260806-03d0a7</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -7085,12 +7285,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -7114,13 +7314,13 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>709</v>
+        <v>452.35</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>644.1</v>
+        <v>414.95</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-9.15</v>
+        <v>-8.27</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>38</v>
@@ -7142,7 +7342,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -7159,12 +7359,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -7184,20 +7384,20 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>11475</v>
+        <v>709</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>11020</v>
+        <v>644.1</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-3.97</v>
+        <v>-9.15</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -7216,7 +7416,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -7228,17 +7428,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -7248,34 +7448,34 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>381.6</v>
+        <v>11475</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>363.5</v>
+        <v>11020</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-4.74</v>
+        <v>-3.97</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
+          <t>Holding horizon reached</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -7285,17 +7485,17 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 369.75 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_HORIZON · trigger crossed 2026-09-11 · stop_source=dyna</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATAPOWER-20260804-29907f</t>
+          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -7307,12 +7507,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -7322,34 +7522,34 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>454.85</v>
+        <v>381.6</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>454.85</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>0</v>
+        <v>363</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-4.87</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -7359,17 +7559,17 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+15.5pp)</t>
+          <t>STOP BREACHED - stop 369.75 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260908-c6e7dc</t>
+          <t>IND-R1-TATAPOWER-20260804-29907f</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7581,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -7396,34 +7596,34 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1048.7</v>
+        <v>454.85</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>998</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>-4.83</v>
+        <v>454.85</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -7433,17 +7633,17 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1011.5999 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>Rotation → GNFC.NS (+15.5pp)</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-SBIN-20260821-b637f4</t>
+          <t>IND-R2-SUNTV-20260908-c6e7dc</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7655,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -7480,20 +7680,20 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1642.5</v>
+        <v>1048.7</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1546.5</v>
+        <v>968</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-5.84</v>
+        <v>-7.7</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -7507,12 +7707,12 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1594.6857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1011.5999 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
+          <t>IND-R1-SBIN-20260821-b637f4</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
@@ -7529,12 +7729,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -7544,34 +7744,34 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>289</v>
+        <v>1642.5</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>289</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>0</v>
+        <v>1521.1</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-7.39</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -7581,17 +7781,17 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+19.4pp)</t>
+          <t>STOP BREACHED - stop 1594.6857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260908-f20701</t>
+          <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7803,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -7618,34 +7818,34 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2410</v>
+        <v>289</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2065.6</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>-14.29</v>
+        <v>289</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -7655,17 +7855,17 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 2314.8285 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>Rotation → GNFC.NS (+19.4pp)</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-LUPIN-20260805-71abab</t>
+          <t>IND-R2-PETRONET-20260908-f20701</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
@@ -7677,12 +7877,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -7702,20 +7902,20 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>507.9</v>
+        <v>2410</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>463.75</v>
+        <v>2063.2</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-8.69</v>
+        <v>-14.39</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -7729,12 +7929,12 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 493.3286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 2314.8285 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-IRCTC-20260804-afbb8f</t>
+          <t>IND-R1-LUPIN-20260805-71abab</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
@@ -7751,12 +7951,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -7776,20 +7976,20 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2064.9</v>
+        <v>507.9</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1931.8</v>
+        <v>458.55</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-6.45</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -7803,12 +8003,12 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1990.457 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 493.3286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-HINDUNILVR-20260812-08d1f5</t>
+          <t>IND-R1-IRCTC-20260804-afbb8f</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -7825,7 +8025,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -7850,20 +8050,20 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>385.15</v>
+        <v>2064.9</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>373.25</v>
+        <v>1938.1</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-3.09</v>
+        <v>-6.14</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -7877,12 +8077,12 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 377.5071 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1990.457 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-DABUR-20260828-be7819</t>
+          <t>IND-R1-HINDUNILVR-20260812-08d1f5</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
@@ -7899,7 +8099,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -7924,20 +8124,20 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5454.5</v>
+        <v>385.15</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4954</v>
+        <v>384.9</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-9.18</v>
+        <v>-0.06</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -7951,12 +8151,12 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 5283.7143 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 377.5071 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BRITANNIA-20260804-3de31c</t>
+          <t>IND-R1-DABUR-20260828-be7819</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -7968,17 +8168,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -7988,34 +8188,34 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>414.35</v>
+        <v>5454.5</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>414.35</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>0</v>
+        <v>4954</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>-9.18</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -8025,29 +8225,29 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+18.2pp)</t>
+          <t>STOP BREACHED - stop 5283.7143 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RBLBANK-20260907-a63a75</t>
+          <t>IND-R1-BRITANNIA-20260804-3de31c</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -8067,25 +8267,25 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>391.3</v>
+        <v>414.35</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>415.35</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>6.15</v>
+        <v>414.35</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -8099,34 +8299,34 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+17.1pp)</t>
+          <t>Rotation → GNFC.NS (+18.2pp)</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-RBLBANK-20260907-a63a75</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -8136,34 +8336,34 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>ADVISORY/HISTORICAL</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>177.09</v>
+        <v>391.3</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>177.09</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>0</v>
+        <v>415.35</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>6.15</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -8173,17 +8373,17 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Retired-runner cleanup · producer guard added 2026-09-02 · t</t>
+          <t>Rotation → GNFC.NS (+17.1pp)</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-WIPRO-20260902-25d63c</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>registry:advisory</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -8195,12 +8395,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -8210,12 +8410,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>ADVISORY/HISTORICAL</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -8224,10 +8424,10 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2891.8</v>
+        <v>177.09</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2891.8</v>
+        <v>177.09</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>0</v>
@@ -8237,7 +8437,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -8247,34 +8447,34 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+57.0pp)</t>
+          <t>Retired-runner cleanup · producer guard added 2026-09-02 · t</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIENT-20260902-51452a</t>
+          <t>IND-R1-WIPRO-20260902-25d63c</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:advisory</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -8284,34 +8484,34 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>ADVISORY/HISTORICAL</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>347.25</v>
+        <v>2891.8</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>326.5</v>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>-5.98</v>
+        <v>2891.8</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -8321,17 +8521,17 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
+          <t>Rotation → GNFC.NS (+57.0pp)</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-NTPC-20260804-b96a36</t>
+          <t>IND-R2-ADANIENT-20260902-51452a</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>registry:advisory</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
@@ -8343,12 +8543,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -8358,12 +8558,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADVISORY/HISTORICAL</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -8372,20 +8572,20 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2383.9</v>
+        <v>347.25</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2160.2</v>
+        <v>326.5</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-9.380000000000001</v>
+        <v>-5.98</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>27</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -8395,17 +8595,17 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+13.0pp)</t>
+          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LUPIN-20260804-def33a</t>
+          <t>IND-R1-NTPC-20260804-b96a36</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:advisory</t>
         </is>
       </c>
     </row>
@@ -8417,12 +8617,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -8437,25 +8637,25 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>398.8</v>
+        <v>2383.9</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>398.8</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>0</v>
+        <v>2160.2</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>-9.380000000000001</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -8469,34 +8669,34 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+52.9pp)</t>
+          <t>Rotation → GNFC.NS (+13.0pp)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
+          <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -8506,34 +8706,34 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>ADVISORY/HISTORICAL</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1955.3</v>
+        <v>398.8</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1912</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>-2.21</v>
+        <v>398.8</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -8543,17 +8743,17 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
+          <t>Rotation → GNFC.NS (+52.9pp)</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
+          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>registry:advisory</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
@@ -8565,12 +8765,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -8590,20 +8790,20 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>289</v>
+        <v>1955.3</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>268.15</v>
+        <v>1912</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-7.21</v>
+        <v>-2.21</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -8622,7 +8822,7 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ITC-20260805-3cdd2a</t>
+          <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
@@ -8639,12 +8839,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -8654,34 +8854,34 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADVISORY/HISTORICAL</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>415.15</v>
+        <v>289</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>402.55</v>
+        <v>268.15</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-3.04</v>
+        <v>-7.21</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -8691,34 +8891,34 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+14.3pp)</t>
+          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R1-ITC-20260805-3cdd2a</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:advisory</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -8728,34 +8928,34 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>ADVISORY/HISTORICAL</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>283.4</v>
+        <v>415.15</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>264.9</v>
+        <v>402.55</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-6.53</v>
+        <v>-3.04</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -8765,34 +8965,34 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
+          <t>Rotation → GNFC.NS (+14.3pp)</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-POWERGRID-20260805-b39825</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>registry:advisory</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -8802,34 +9002,34 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>ADVISORY/HISTORICAL</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>847.5</v>
+        <v>283.4</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>847.5</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>0</v>
+        <v>264.9</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>-6.53</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -8839,34 +9039,34 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+56.7pp)</t>
+          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARICO-20260826-1c5a1c</t>
+          <t>IND-R1-POWERGRID-20260805-b39825</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:advisory</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -8886,14 +9086,14 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1702.7</v>
+        <v>847.5</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>1702.7</v>
+        <v>847.5</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>0</v>
@@ -8913,12 +9113,12 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+57.6pp)</t>
+          <t>Rotation → GNFC.NS (+56.7pp)</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
+          <t>IND-R2-MARICO-20260826-1c5a1c</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
@@ -8930,17 +9130,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -8960,14 +9160,14 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>244.55</v>
+        <v>1702.7</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>244.55</v>
+        <v>1702.7</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>0</v>
@@ -8987,12 +9187,12 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+10.1pp)</t>
+          <t>Rotation → GNFC.NS (+57.6pp)</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260824-89850d</t>
+          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -9004,17 +9204,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -9034,14 +9234,14 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1114.2</v>
+        <v>244.55</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1114.2</v>
+        <v>244.55</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>0</v>
@@ -9061,12 +9261,12 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+14.5pp)</t>
+          <t>Rotation → GNFC.NS (+10.1pp)</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MGL-20260821-142d93</t>
+          <t>IND-R2-JIOFIN-20260824-89850d</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -9083,12 +9283,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -9112,10 +9312,10 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>402.8</v>
+        <v>1114.2</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>402.8</v>
+        <v>1114.2</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>0</v>
@@ -9135,12 +9335,12 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+13.3pp)</t>
+          <t>Rotation → GNFC.NS (+14.5pp)</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
+          <t>IND-R2-MGL-20260821-142d93</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -9157,12 +9357,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -9186,10 +9386,10 @@
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>8693</v>
+        <v>402.8</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>8693</v>
+        <v>402.8</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>0</v>
@@ -9209,12 +9409,12 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+61.4pp)</t>
+          <t>Rotation → GNFC.NS (+13.3pp)</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
+          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -9226,17 +9426,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -9256,14 +9456,14 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>174.9</v>
+        <v>8693</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>174.9</v>
+        <v>8693</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>0</v>
@@ -9273,7 +9473,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
@@ -9283,12 +9483,12 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.8pp alpha</t>
+          <t>Rotation → GNFC.NS (+61.4pp)</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260820-80f37d</t>
+          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -9300,17 +9500,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -9330,14 +9530,14 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>5220</v>
+        <v>174.9</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>5220</v>
+        <v>174.9</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
@@ -9357,12 +9557,12 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +60.0pp alpha</t>
+          <t>→ GNFC.NS · +11.8pp alpha</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
+          <t>IND-R2-SAIL-20260820-80f37d</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
@@ -9379,12 +9579,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -9399,25 +9599,25 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>129.2</v>
+        <v>5220</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>124.4</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>-3.72</v>
+        <v>5220</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -9431,17 +9631,17 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +12.2pp alpha</t>
+          <t>→ GNFC.NS · +60.0pp alpha</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
@@ -9453,12 +9653,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -9478,20 +9678,20 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>552.4</v>
+        <v>129.2</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>558</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>1.01</v>
+        <v>124.4</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>-3.72</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -9505,12 +9705,12 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +14.7pp alpha</t>
+          <t>→ GNFC.NS · +12.2pp alpha</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
@@ -9522,12 +9722,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -9552,20 +9752,20 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>377</v>
+        <v>552.4</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>387.55</v>
+        <v>558</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -9579,12 +9779,12 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +9.8pp alpha</t>
+          <t>→ GNFC.NS · +14.7pp alpha</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -9601,12 +9801,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -9630,13 +9830,13 @@
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1384</v>
+        <v>377</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1327.6</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>-4.08</v>
+        <v>387.55</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>2.8</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>12</v>
@@ -9653,12 +9853,12 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +56.7pp alpha</t>
+          <t>→ GNFC.NS · +9.8pp alpha</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
@@ -9670,17 +9870,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -9700,20 +9900,20 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>2439.4</v>
+        <v>1384</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>2361</v>
+        <v>1327.6</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-3.21</v>
+        <v>-4.08</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -9727,12 +9927,12 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +6.7pp alpha</t>
+          <t>→ GNFC.NS · +56.7pp alpha</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260804-a45359</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -9749,12 +9949,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -9769,25 +9969,25 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>3940</v>
+        <v>2439.4</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3940</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>0</v>
+        <v>2361</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>-3.21</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -9801,17 +10001,17 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.5pp alpha</t>
+          <t>→ GNFC.NS · +6.7pp alpha</t>
         </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
+          <t>IND-R2-TCS-20260804-a45359</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -9823,12 +10023,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -9843,25 +10043,25 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>11600</v>
+        <v>3940</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>11828</v>
-      </c>
-      <c r="J51" s="5" t="n">
-        <v>1.97</v>
+        <v>3940</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -9875,34 +10075,34 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +6.6pp alpha</t>
+          <t>→ GNFC.NS · +7.5pp alpha</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260805-f0f538</t>
+          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -9917,25 +10117,25 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1779.2</v>
+        <v>11600</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>1779.2</v>
-      </c>
-      <c r="J52" s="4" t="n">
-        <v>0</v>
+        <v>11828</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>1.97</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -9949,34 +10149,34 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +8.1pp alpha</t>
+          <t>→ GNFC.NS · +6.6pp alpha</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
+          <t>IND-R2-OFSS-20260805-f0f538</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -9996,14 +10196,14 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>181.14</v>
+        <v>1779.2</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>181.14</v>
+        <v>1779.2</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>0</v>
@@ -10023,12 +10223,12 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +9.4pp alpha</t>
+          <t>→ GNFC.NS · +8.1pp alpha</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
+          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -10045,12 +10245,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -10074,10 +10274,10 @@
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>4924</v>
+        <v>181.14</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>4924</v>
+        <v>181.14</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>0</v>
@@ -10097,12 +10297,12 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +60.1pp alpha</t>
+          <t>→ TCS.NS · +9.4pp alpha</t>
         </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
+          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
@@ -10119,12 +10319,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -10148,10 +10348,10 @@
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>129</v>
+        <v>4924</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>129</v>
+        <v>4924</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>0</v>
@@ -10171,12 +10371,12 @@
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +6.5pp alpha</t>
+          <t>→ TCS.NS · +60.1pp alpha</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260810-788da8</t>
+          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -10193,12 +10393,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -10213,25 +10413,25 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>7454.5</v>
+        <v>129</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>7095</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>-4.82</v>
+        <v>129</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -10245,29 +10445,29 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +62.1pp alpha</t>
+          <t>→ TCS.NS · +6.5pp alpha</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
+          <t>IND-R2-CANBK-20260810-788da8</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -10292,20 +10492,20 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1327.7</v>
+        <v>7454.5</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>1285</v>
+        <v>7095</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-3.22</v>
+        <v>-4.82</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -10319,12 +10519,12 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +64.8pp alpha</t>
+          <t>→ TCS.NS · +62.1pp alpha</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
@@ -10341,12 +10541,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -10370,13 +10570,13 @@
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1595</v>
+        <v>1327.7</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>1584.8</v>
+        <v>1285</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.64</v>
+        <v>-3.22</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>2</v>
@@ -10393,12 +10593,12 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +62.5pp alpha</t>
+          <t>→ GNFC.NS · +64.8pp alpha</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PRESTIGE-20260805-488bde</t>
+          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
@@ -10415,12 +10615,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -10444,13 +10644,13 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>450</v>
+        <v>1595</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>442.8</v>
+        <v>1584.8</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-1.6</v>
+        <v>-0.64</v>
       </c>
       <c r="K59" s="4" t="n">
         <v>2</v>
@@ -10467,12 +10667,12 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +10.3pp alpha</t>
+          <t>→ GNFC.NS · +62.5pp alpha</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260805-6635e1</t>
+          <t>IND-R2-PRESTIGE-20260805-488bde</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
@@ -10489,12 +10689,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -10518,13 +10718,13 @@
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>845</v>
+        <v>450</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>889.5</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>5.27</v>
+        <v>442.8</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>-1.6</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>2</v>
@@ -10541,12 +10741,12 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.4pp alpha</t>
+          <t>→ GNFC.NS · +10.3pp alpha</t>
         </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
+          <t>IND-R2-OIL-20260805-6635e1</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
@@ -10563,12 +10763,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -10588,20 +10788,20 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>471.2</v>
+        <v>845</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>473.3</v>
+        <v>889.5</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>0.45</v>
+        <v>5.27</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -10615,12 +10815,12 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +60.7pp alpha</t>
+          <t>→ GNFC.NS · +7.4pp alpha</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -10637,12 +10837,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -10662,20 +10862,20 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>6793.5</v>
+        <v>471.2</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>6774</v>
-      </c>
-      <c r="J62" s="6" t="n">
-        <v>-0.29</v>
+        <v>473.3</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>0.45</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -10689,12 +10889,12 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +8.0pp alpha</t>
+          <t>→ GNFC.NS · +60.7pp alpha</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
+          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
@@ -10706,12 +10906,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -10736,17 +10936,17 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>268.5</v>
+        <v>6793.5</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>278.8</v>
-      </c>
-      <c r="J63" s="5" t="n">
-        <v>3.84</v>
+        <v>6774</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>-0.29</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>2</v>
@@ -10763,12 +10963,12 @@
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.6pp alpha</t>
+          <t>→ GNFC.NS · +8.0pp alpha</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260804-563905</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -10785,12 +10985,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -10810,20 +11010,20 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1167.5</v>
+        <v>268.5</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>1177</v>
+        <v>278.8</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.84</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -10837,12 +11037,12 @@
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.7pp alpha</t>
+          <t>→ GNFC.NS · +11.6pp alpha</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260805-ea04e5</t>
+          <t>IND-R2-VEDL-20260804-563905</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
@@ -10859,12 +11059,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -10884,20 +11084,20 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>5470.5</v>
+        <v>1167.5</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>5651.5</v>
+        <v>1177</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>3.31</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -10911,12 +11111,12 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +10.6pp alpha</t>
+          <t>→ GNFC.NS · +11.7pp alpha</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
+          <t>IND-R2-INFY-20260805-ea04e5</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
@@ -10933,12 +11133,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -10962,13 +11162,13 @@
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>1363.6</v>
+        <v>5470.5</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>1351.3</v>
-      </c>
-      <c r="J66" s="6" t="n">
-        <v>-0.9</v>
+        <v>5651.5</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>3.31</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>2</v>
@@ -10985,12 +11185,12 @@
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.8pp alpha</t>
+          <t>→ GNFC.NS · +10.6pp alpha</t>
         </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
+          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
@@ -11007,12 +11207,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -11032,20 +11232,20 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>2195</v>
+        <v>1363.6</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>2182</v>
+        <v>1351.3</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>-0.59</v>
+        <v>-0.9</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -11059,12 +11259,12 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +59.7pp alpha</t>
+          <t>→ GNFC.NS · +7.8pp alpha</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
+          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -11076,17 +11276,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -11101,29 +11301,29 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>567.3</v>
+        <v>2195</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>567.3</v>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>0</v>
+        <v>2182</v>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>-0.59</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Outperformance exit</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr">
@@ -11133,17 +11333,17 @@
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+52.0pp)</t>
+          <t>→ GNFC.NS · +59.7pp alpha</t>
         </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWENERGY-20260804-1210a0</t>
+          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11355,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -11184,10 +11384,10 @@
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>939.95</v>
+        <v>567.3</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>939.95</v>
+        <v>567.3</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>0</v>
@@ -11207,12 +11407,12 @@
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+          <t>Rotation → LUPIN.NS (+52.0pp)</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+          <t>IND-R2-JSWENERGY-20260804-1210a0</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
@@ -11229,7 +11429,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -11258,10 +11458,10 @@
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>425.05</v>
+        <v>939.95</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>425.05</v>
+        <v>939.95</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>0</v>
@@ -11286,66 +11486,140 @@
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
+          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+        </is>
+      </c>
+      <c r="P70" s="4" t="inlineStr">
+        <is>
+          <t>registry:administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>425.05</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>425.05</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>Rotation swap</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
           <t>IND-R2-BIOCON-20260804-954a24</t>
         </is>
       </c>
-      <c r="P70" s="4" t="inlineStr">
+      <c r="P71" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>Closed positions held by the canonical lifecycle dataset. Coverage begins on the date named in the banner · AEGIS had no position registry before then, only a recommendation list with expiry semantics, so earlier closures cannot be proven and are not invented.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>P&amp;L % · (Exit − Entry) / Entry. It is a REALIZED result only on a REALIZED EXIT row · on every other Record Type it is a mark.</t>
+          <t>Closed positions held by the canonical lifecycle dataset. Coverage begins on the date named in the banner · AEGIS had no position registry before then, only a recommendation list with expiry semantics, so earlier closures cannot be proven and are not invented.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Record Type is the population; Source is the provenance. They are different questions and they disagree: 463 USA rows arrived from registry:production yet are ORPHAN AUTO-CLOSE. Build performance statistics on Record Type, never on Source.</t>
+          <t>P&amp;L % · (Exit − Entry) / Entry. It is a REALIZED result only on a REALIZED EXIT row · on every other Record Type it is a mark.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>REALIZED EXIT · a trade that actually closed · the only population in the realized performance line. ORPHAN AUTO-CLOSE · a reconstructed record for a position that was never properly tracked · not a trade. ADMINISTRATIVE · same-day or zero-delta bookkeeping · not a trade. ADVISORY/HISTORICAL · retired R1 · never counted in production P&amp;L. STOP-BREACH MARK · the price passed the stop and the row left CURRENT.</t>
+          <t>Record Type is the population; Source is the provenance. They are different questions and they disagree: 463 USA rows arrived from registry:production yet are ORPHAN AUTO-CLOSE. Build performance statistics on Record Type, never on Source.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK rows are MARKS, not fills. The position is still open in its engine, Exit Price is the latest close, and P&amp;L % is the live unrealized figure. They carry their own Record Type precisely so they are never counted in the realized win-rate or average return alongside trades that actually closed.</t>
+          <t>REALIZED EXIT · a trade that actually closed · the only population in the realized performance line. ORPHAN AUTO-CLOSE · a reconstructed record for a position that was never properly tracked · not a trade. ADMINISTRATIVE · same-day or zero-delta bookkeeping · not a trade. ADVISORY/HISTORICAL · retired R1 · never counted in production P&amp;L. STOP-BREACH MARK · the price passed the stop and the row left CURRENT.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Exit Date on a breach row is the day the breach was FIRST observed, not today, and it never moves. A position that later recovers above its stop stays here · recovering does not undo having passed the stop.</t>
+          <t>STOP-BREACH MARK rows are MARKS, not fills. The position is still open in its engine, Exit Price is the latest close, and P&amp;L % is the live unrealized figure. They carry their own Record Type precisely so they are never counted in the realized win-rate or average return alongside trades that actually closed.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE means the canonical price source had no value · never fabricated and never backfilled from today's state.</t>
+          <t>Exit Date on a breach row is the day the breach was FIRST observed, not today, and it never moves. A position that later recovers above its stop stays here · recovering does not undo having passed the stop.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE means the canonical price source had no value · never fabricated and never backfilled from today's state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>Sector · the company's CURRENT classification from the canonical sector cache, not its sector as of the exit date. No point-in-time sector history exists, so this column describes the company today and must not be read as evidence about what the sector was when the trade was live. NOT_AVAILABLE means the canonical source has no entry · it is never guessed.</t>
         </is>
@@ -11362,7 +11636,7 @@
     <mergeCell ref="A77:P77"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A78:P78"/>
-    <mergeCell ref="A73:P73"/>
+    <mergeCell ref="A81:P81"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 228 scored · 52 already in CURRENT · biggest blocker: model disagreement (166) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=3 · 228 scored · 54 already in CURRENT · biggest blocker: model disagreement (163) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 49 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 52 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W82"/>
+  <dimension ref="A1:W84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,42 +508,42 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-16 · prices = 2026-09-15 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-16 · prices = 2026-09-16 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>56 investable · NEW 3 · ACTIVE+ 53 · ACTIVE 0   ·   R2 51 · MOMENTUM 0 · R1 5 (advisory)   ·   4 row(s) read 0.00%: admitted at the 2026-09-15 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>58 investable · NEW 7 · ACTIVE+ 51 · ACTIVE 0   ·   R2 53 · MOMENTUM 0 · R1 5 (advisory)   ·   7 row(s) read 0.00%: admitted at the 2026-09-16 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 56 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.36% from entry, worst single -13.05%</t>
+          <t>🛡 DOWNSIDE · 58 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.14% from entry, worst single -13.05%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 11 position(s) left CURRENT on a STOP BREACH (R1 11 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 3 newly breached today</t>
+          <t>🔴 11 position(s) left CURRENT on a STOP BREACH (R1 11 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=3 · 228 scored · 54 already in CURRENT · biggest blocker: model disagreement (163) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=7 · 228 scored · 56 already in CURRENT · biggest blocker: model disagreement (162) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 52 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 56 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>AARTIIND</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>406.2</v>
+        <v>468.8</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>406.2</v>
+        <v>468.8</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>33.3</v>
+        <v>31.1</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>390.4</v>
+        <v>443.3714</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,22 +746,22 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.89</v>
+        <v>5.42</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.89</v>
+        <v>-5.42</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>429.9</v>
+        <v>506.94</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
+          <t>IND-R2-AARTIIND-20260916-4cc858</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -802,25 +802,25 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>132.03</v>
+        <v>407.75</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>132.03</v>
+        <v>407.75</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>28.7</v>
+        <v>33.3</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>127.9057</v>
+        <v>390.4</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,17 +847,17 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>3.12</v>
+        <v>4.26</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.12</v>
+        <v>-4.26</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>138.22</v>
+        <v>436.95</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IOC-20260916-b0f93c</t>
+          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -903,25 +903,25 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>80.5</v>
+        <v>133.9</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>80.5</v>
+        <v>133.9</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>31.2</v>
+        <v>28.7</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>76.8771</v>
+        <v>129.8171</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-4.5</v>
+        <v>-3.05</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>85.93000000000001</v>
+        <v>140.02</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NMDC-20260916-75297f</t>
+          <t>IND-R2-IOC-20260916-b0f93c</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -995,34 +995,34 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1038.3</v>
+        <v>321.75</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1077</v>
+        <v>321.75</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>3.73</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>38.3</v>
+        <v>33.2</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1014.9714</v>
+        <v>306.2946</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1049,22 +1049,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>5.76</v>
+        <v>4.8</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.25</v>
+        <v>-4.8</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1120.78</v>
+        <v>352.66</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260909-f2b7ad</t>
+          <t>IND-R2-MANAPPURAM-20260916-6576e5</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1096,34 +1096,34 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>694.35</v>
+        <v>1065.9</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>716.55</v>
+        <v>1065.9</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>3.2</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>34.8</v>
+        <v>29.1</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>687.25</v>
+        <v>1023.6857</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.09</v>
+        <v>3.96</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.02</v>
+        <v>-3.96</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>729</v>
+        <v>1129.22</v>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
+          <t>IND-R2-MGL-20260916-149e8e</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1197,34 +1197,34 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>373.25</v>
+        <v>80.52</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>384.9</v>
+        <v>80.52</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>3.12</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>28.4</v>
+        <v>31.2</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>372.3857</v>
+        <v>77.14570000000001</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1251,22 +1251,22 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.25</v>
+        <v>4.19</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.23</v>
+        <v>-4.19</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>389.48</v>
+        <v>85.58</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DABUR-20260911-8f250f</t>
+          <t>IND-R2-NMDC-20260916-75297f</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1298,30 +1298,30 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2197.4</v>
+        <v>3389.4</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2251</v>
+        <v>3389.4</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>2.44</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>37.1</v>
+        <v>31.1</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2142.5</v>
+        <v>3235.2428</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.82</v>
+        <v>4.55</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-2.5</v>
+        <v>-4.55</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2341.29</v>
+        <v>3620.64</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260909-fb0a7f</t>
+          <t>IND-R2-TATAELXSI-20260916-69ea7c</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1408,25 +1408,25 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>292.9</v>
+        <v>339.55</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>297.5</v>
+        <v>352.55</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>1.57</v>
+        <v>3.83</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>34.3</v>
+        <v>32.3</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>283.3839</v>
+        <v>339.7714</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1453,17 +1453,17 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.74</v>
+        <v>3.62</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-3.25</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>315.92</v>
+        <v>353.62</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
+          <t>IND-R2-PATANJALI-20260909-508e75</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1500,34 +1500,34 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>11644</v>
+        <v>373.25</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>11770</v>
+        <v>386.1</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1.08</v>
+        <v>3.44</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>43.6</v>
+        <v>28.4</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>11221</v>
+        <v>374.1643</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.66</v>
+        <v>3.09</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-3.63</v>
+        <v>0.24</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>12467.93</v>
+        <v>389.48</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260909-1e09a0</t>
+          <t>IND-R2-DABUR-20260911-8f250f</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1610,25 +1610,25 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>370</v>
+        <v>694.35</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>373.7</v>
+        <v>716.25</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>1</v>
+        <v>3.15</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>31.2</v>
+        <v>34.8</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>352.9</v>
+        <v>688.1929</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1655,17 +1655,17 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.57</v>
+        <v>3.92</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-4.62</v>
+        <v>-0.89</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>397.71</v>
+        <v>729</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
+          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1711,25 +1711,25 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>19.11</v>
+        <v>25455</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>19.18</v>
+        <v>26140</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.37</v>
+        <v>2.69</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>33.3</v>
+        <v>31.3</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>18.43</v>
+        <v>25235</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1756,17 +1756,17 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.91</v>
+        <v>3.46</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-3.56</v>
+        <v>-0.86</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>20.21</v>
+        <v>26635.71</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260909-153c95</t>
+          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1812,25 +1812,25 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>818.3</v>
+        <v>1038.3</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>819.15</v>
+        <v>1065.3</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>31.2</v>
+        <v>38.3</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>788.0929</v>
+        <v>1014.9714</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1857,17 +1857,17 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>3.79</v>
+        <v>4.72</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.69</v>
+        <v>-2.25</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>866.9299999999999</v>
+        <v>1120.78</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
+          <t>IND-R2-INFY-20260909-f2b7ad</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1904,34 +1904,34 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1350.1</v>
+        <v>292.9</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1351</v>
+        <v>296.35</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>33.3</v>
+        <v>34.3</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1315.6</v>
+        <v>283.3839</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>2.62</v>
+        <v>4.38</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.56</v>
+        <v>-3.25</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1401.85</v>
+        <v>315.92</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CIPLA-20260911-5f4a49</t>
+          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2005,34 +2005,34 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>4056.8</v>
+        <v>1952</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4056.8</v>
+        <v>1974</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>1.13</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>35</v>
+        <v>31.2</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3872.6145</v>
+        <v>1926.3857</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.54</v>
+        <v>2.41</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-4.54</v>
+        <v>-1.31</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>4333.08</v>
+        <v>2020.51</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AIAENG-20260911-5d7269</t>
+          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2106,34 +2106,34 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>122.37</v>
+        <v>8128.5</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>122.37</v>
+        <v>8217</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1.09</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>30.2</v>
+        <v>38.7</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>118.53</v>
+        <v>7841.2143</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2160,22 +2160,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>3.14</v>
+        <v>4.57</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.14</v>
+        <v>-3.53</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>128.89</v>
+        <v>8660.25</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260915-4a780b</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2207,34 +2207,34 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>409.8</v>
+        <v>5163.5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>409.8</v>
+        <v>5209.5</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.89</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>34.1</v>
+        <v>31.3</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>397.4143</v>
+        <v>5048.2143</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2261,22 +2261,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-3.02</v>
+        <v>-2.23</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>432.43</v>
+        <v>5385.18</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260915-bbcfac</t>
+          <t>IND-R2-ALKEM-20260909-517913</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2317,25 +2317,25 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>285</v>
+        <v>409.8</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>285</v>
+        <v>413.1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>35.4</v>
+        <v>34.1</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>277.2643</v>
+        <v>401.05</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2362,22 +2362,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-2.71</v>
+        <v>-2.14</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>296.6</v>
+        <v>432.43</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-KOTAKBANK-20260915-bbcfac</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2418,25 +2418,25 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>8128.5</v>
+        <v>1350.1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8128.5</v>
+        <v>1358.9</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.65</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>38.7</v>
+        <v>33.3</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>7774</v>
+        <v>1321.3286</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2463,17 +2463,17 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>4.36</v>
+        <v>2.76</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-4.36</v>
+        <v>-2.13</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>8660.25</v>
+        <v>1401.85</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-CIPLA-20260911-5f4a49</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2510,34 +2510,34 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>464.25</v>
+        <v>2197.4</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>464.25</v>
+        <v>2211.4</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0.64</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>31.2</v>
+        <v>37.1</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>440.6143</v>
+        <v>2142.5</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2564,22 +2564,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>5.09</v>
+        <v>3.12</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-5.09</v>
+        <v>-2.5</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>499.7</v>
+        <v>2341.29</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-TCS-20260909-fb0a7f</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2611,30 +2611,30 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>172.76</v>
+        <v>122.37</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>172.45</v>
+        <v>122.94</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>-0.18</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0.47</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>165.6072</v>
+        <v>118.8757</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>3.97</v>
+        <v>3.31</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-4.14</v>
+        <v>-2.86</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>184.71</v>
+        <v>128.89</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
+          <t>IND-R2-CANBK-20260915-4a780b</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2721,25 +2721,25 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>339.55</v>
+        <v>1244.4</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>338.55</v>
+        <v>1246.4</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>-0.29</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.16</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>32.3</v>
+        <v>32.9</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>329.05</v>
+        <v>1205.9572</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2766,17 +2766,17 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>2.81</v>
+        <v>3.24</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>-3.09</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>353.62</v>
+        <v>1294.16</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PATANJALI-20260909-508e75</t>
+          <t>IND-R2-AXISBANK-20260909-3abb74</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2813,34 +2813,34 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1232</v>
+        <v>818.3</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1225.2</v>
+        <v>818.1</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.55</v>
+        <v>-0.02</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>28.3</v>
+        <v>31.2</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1199.9714</v>
+        <v>788.0929</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2867,22 +2867,22 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2.06</v>
+        <v>3.67</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-2.6</v>
+        <v>-3.69</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1280.04</v>
+        <v>866.9299999999999</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ACC-20260911-3a092f</t>
+          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2923,18 +2923,18 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1952</v>
+        <v>370</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1938.1</v>
+        <v>369.8</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.71</v>
+        <v>-0.05</v>
       </c>
       <c r="L30" s="4" t="n">
         <v>31.2</v>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1893.4428</v>
+        <v>352.9</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2968,17 +2968,17 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>2.3</v>
+        <v>4.57</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3</v>
+        <v>-4.62</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2020.51</v>
+        <v>397.71</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
+          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3015,34 +3015,34 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1949</v>
+        <v>464.25</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1932.4</v>
+        <v>464</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.85</v>
+        <v>-0.05</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>40.6</v>
+        <v>31.2</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1891.4857</v>
+        <v>440.6143</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3069,22 +3069,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>2.12</v>
+        <v>5.04</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-2.95</v>
+        <v>-5.09</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2054.6</v>
+        <v>499.7</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IPCALAB-20260909-af9aea</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3116,34 +3116,34 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1260</v>
+        <v>1232</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1248.2</v>
+        <v>1229.4</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.21</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>33.3</v>
+        <v>28.3</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1190.3857</v>
+        <v>1199.9714</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3170,22 +3170,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.63</v>
+        <v>2.39</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-5.52</v>
+        <v>-2.6</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1348.37</v>
+        <v>1280.04</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NAUKRI-20260909-930931</t>
+          <t>IND-R2-ACC-20260911-3a092f</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3226,25 +3226,25 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>25455</v>
+        <v>11644</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>25195</v>
+        <v>11620</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-1.02</v>
+        <v>-0.21</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>31.3</v>
+        <v>43.6</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>24409.2857</v>
+        <v>11221</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3271,22 +3271,22 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.12</v>
+        <v>3.43</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-4.11</v>
+        <v>-3.63</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>26635.71</v>
+        <v>12467.93</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
+          <t>IND-R2-OFSS-20260909-1e09a0</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3327,25 +3327,25 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2410.1</v>
+        <v>1260</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2371.7</v>
+        <v>1257.1</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-1.59</v>
+        <v>-0.23</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>40.6</v>
+        <v>33.3</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>2288.3428</v>
+        <v>1195.8571</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3372,22 +3372,22 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>3.51</v>
+        <v>4.87</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-5.05</v>
+        <v>-5.09</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2579.94</v>
+        <v>1348.37</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GLENMARK-20260909-ef0373</t>
+          <t>IND-R2-NAUKRI-20260909-930931</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>6291</v>
+        <v>19.11</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>6189.5</v>
+        <v>19.02</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-1.61</v>
+        <v>-0.47</v>
       </c>
       <c r="L35" s="4" t="n">
         <v>33.3</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>5959.1429</v>
+        <v>18.43</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-5.28</v>
+        <v>-3.56</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>6638.36</v>
+        <v>20.21</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260909-2f64b0</t>
+          <t>IND-R2-IRB-20260909-153c95</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3520,34 +3520,34 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>388.4</v>
+        <v>1949</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>381.75</v>
+        <v>1933</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-1.71</v>
+        <v>-0.82</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>31.2</v>
+        <v>40.6</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>376.1785</v>
+        <v>1891.4857</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3574,22 +3574,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-3.15</v>
+        <v>-2.95</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>406.73</v>
+        <v>2054.6</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3630,21 +3630,21 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1244.4</v>
+        <v>315.55</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>1222.9</v>
+        <v>312.75</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-1.73</v>
+        <v>-0.89</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>32.9</v>
+        <v>31.2</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>1204.5857</v>
+        <v>303.0643</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3675,17 +3675,17 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-3.2</v>
+        <v>-3.96</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>1294.16</v>
+        <v>329.25</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AXISBANK-20260909-3abb74</t>
+          <t>IND-R2-RECLTD-20260909-84e6d1</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3731,25 +3731,25 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>5163.5</v>
+        <v>172.76</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>5070</v>
+        <v>171.2</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-1.81</v>
+        <v>-0.9</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>31.3</v>
+        <v>30.1</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>4920.3571</v>
+        <v>165.6072</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3776,22 +3776,22 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-4.71</v>
+        <v>-4.14</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>5385.18</v>
+        <v>184.71</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ALKEM-20260909-517913</t>
+          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3823,34 +3823,34 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-14</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>412.55</v>
+        <v>285</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>403.6</v>
+        <v>282.4</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-2.17</v>
+        <v>-0.91</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>37</v>
+        <v>35.4</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>391.6786</v>
+        <v>277.2643</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3877,22 +3877,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>2.95</v>
+        <v>1.82</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-5.06</v>
+        <v>-2.71</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>435.12</v>
+        <v>296.6</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3924,34 +3924,34 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>400.4</v>
+        <v>2410.1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>391.5</v>
+        <v>2385.1</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-2.22</v>
+        <v>-1.04</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>32.3</v>
+        <v>40.6</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>386.3857</v>
+        <v>2288.3428</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3978,22 +3978,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>1.31</v>
+        <v>4.06</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-3.5</v>
+        <v>-5.05</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>421.42</v>
+        <v>2579.94</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260911-098cc1</t>
+          <t>IND-R2-GLENMARK-20260909-ef0373</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4025,34 +4025,34 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>315.55</v>
+        <v>388.4</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>308.5</v>
+        <v>382.9</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-2.23</v>
+        <v>-1.42</v>
       </c>
       <c r="L41" s="4" t="n">
         <v>31.2</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>302.3786</v>
+        <v>376.1785</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4079,22 +4079,22 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-4.17</v>
+        <v>-3.15</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>329.25</v>
+        <v>406.73</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RECLTD-20260909-84e6d1</t>
+          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
         </is>
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>470.4</v>
+        <v>1725</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>458.55</v>
+        <v>1700</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-2.52</v>
+        <v>-1.45</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>28.4</v>
+        <v>31.3</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>453.4071</v>
+        <v>1649.0429</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4180,22 +4180,22 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-3.61</v>
+        <v>-4.4</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>486.55</v>
+        <v>1838.94</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRCTC-20260909-add681</t>
+          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4236,25 +4236,25 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>154.28</v>
+        <v>3134.7</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>150.03</v>
+        <v>3087.5</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-2.75</v>
+        <v>-1.51</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>33.3</v>
+        <v>11.2</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>145.5286</v>
+        <v>2965.8715</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="S43" s="4" t="n">
-        <v>3</v>
+        <v>3.94</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-5.67</v>
+        <v>-5.39</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>163.68</v>
+        <v>3307.14</v>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20260909-938c43</t>
+          <t>IND-R2-MM-20260909-3a8a06</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4337,21 +4337,21 @@
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>860.45</v>
+        <v>2825</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>836.75</v>
+        <v>2778.3</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-2.75</v>
+        <v>-1.65</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>811.05</v>
+        <v>2625.3002</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
@@ -4382,22 +4382,22 @@
         </is>
       </c>
       <c r="S44" s="4" t="n">
-        <v>3.07</v>
+        <v>5.51</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>-5.74</v>
+        <v>-7.07</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>903.71</v>
+        <v>3067.12</v>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260909-3ab469</t>
+          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
         </is>
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4438,21 +4438,21 @@
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>2825</v>
+        <v>860.45</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>2743.9</v>
+        <v>844.6</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-2.87</v>
+        <v>-1.84</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>36.1</v>
+        <v>35</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>2620.0107</v>
+        <v>811.05</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4483,22 +4483,22 @@
         </is>
       </c>
       <c r="S45" s="4" t="n">
-        <v>4.52</v>
+        <v>3.97</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>-7.26</v>
+        <v>-5.74</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>3067.12</v>
+        <v>903.71</v>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
+          <t>IND-R2-INDIANB-20260909-3ab469</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4530,34 +4530,34 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>500</v>
+        <v>400.4</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>485.6</v>
+        <v>392.3</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-2.88</v>
+        <v>-2.02</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>482.9429</v>
+        <v>386.3857</v>
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
@@ -4584,22 +4584,22 @@
         </is>
       </c>
       <c r="S46" s="4" t="n">
-        <v>0.55</v>
+        <v>1.51</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>-3.41</v>
+        <v>-3.5</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>530.45</v>
+        <v>421.42</v>
       </c>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260909-82436d</t>
+          <t>IND-R2-LICI-20260911-098cc1</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4643,15 +4643,15 @@
         <v>12603</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>12231</v>
+        <v>12296</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-2.95</v>
+        <v>-2.44</v>
       </c>
       <c r="L47" s="4" t="n">
         <v>31.3</v>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="S47" s="4" t="n">
-        <v>1.49</v>
+        <v>2.01</v>
       </c>
       <c r="T47" s="4" t="n">
         <v>-4.4</v>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4732,34 +4732,34 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1725</v>
+        <v>1007.2</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1668.5</v>
+        <v>981.8</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-3.28</v>
+        <v>-2.52</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>31.3</v>
+        <v>35</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>1649.0429</v>
+        <v>967.7286</v>
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -4786,22 +4786,22 @@
         </is>
       </c>
       <c r="S48" s="4" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>-4.4</v>
+        <v>-3.92</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>1838.94</v>
+        <v>1050.01</v>
       </c>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
+          <t>IND-R2-SBIN-20260909-a73231</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4842,25 +4842,25 @@
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>3134.7</v>
+        <v>6291</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>3029.5</v>
+        <v>6129.5</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-3.36</v>
+        <v>-2.57</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>11.2</v>
+        <v>33.3</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>2959.643</v>
+        <v>5959.1429</v>
       </c>
       <c r="R49" s="4" t="inlineStr">
         <is>
@@ -4887,22 +4887,22 @@
         </is>
       </c>
       <c r="S49" s="4" t="n">
-        <v>2.31</v>
+        <v>2.78</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>-5.58</v>
+        <v>-5.28</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>3307.14</v>
+        <v>6638.36</v>
       </c>
       <c r="V49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MM-20260909-3a8a06</t>
+          <t>IND-R2-ATUL-20260909-2f64b0</t>
         </is>
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4943,21 +4943,21 @@
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>434.2</v>
+        <v>500</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>419.25</v>
+        <v>484.7</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-3.44</v>
+        <v>-3.06</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>33.3</v>
+        <v>35.4</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>417.55</v>
+        <v>482.9429</v>
       </c>
       <c r="R50" s="4" t="inlineStr">
         <is>
@@ -4988,17 +4988,17 @@
         </is>
       </c>
       <c r="S50" s="4" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>-3.83</v>
+        <v>-3.41</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>456.13</v>
+        <v>530.45</v>
       </c>
       <c r="V50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260909-3c298a</t>
+          <t>IND-R2-OIL-20260909-82436d</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -5035,32 +5035,30 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-09-14</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>233.86</v>
+        <v>412.55</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>225.6</v>
+        <v>399.8</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-3.09</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>37</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
@@ -5083,7 +5081,7 @@
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>220.1271</v>
+        <v>391.6786</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -5091,22 +5089,22 @@
         </is>
       </c>
       <c r="S51" s="4" t="n">
-        <v>2.43</v>
+        <v>2.03</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>-5.87</v>
+        <v>-5.06</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>244.86</v>
+        <v>435.12</v>
       </c>
       <c r="V51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
+          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
         </is>
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5116,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -5147,25 +5145,25 @@
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1007.2</v>
+        <v>434.2</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>968</v>
+        <v>420.75</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-3.89</v>
+        <v>-3.1</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>35</v>
+        <v>33.3</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5184,7 +5182,7 @@
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>967.7286</v>
+        <v>417.55</v>
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
@@ -5192,22 +5190,22 @@
         </is>
       </c>
       <c r="S52" s="4" t="n">
-        <v>0.03</v>
+        <v>0.76</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>-3.92</v>
+        <v>-3.83</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>1050.01</v>
+        <v>456.13</v>
       </c>
       <c r="V52" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20260909-a73231</t>
+          <t>IND-R2-COALINDIA-20260909-3c298a</t>
         </is>
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5217,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -5248,18 +5246,18 @@
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>117.05</v>
+        <v>233.86</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>112</v>
+        <v>226.4</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-4.31</v>
+        <v>-3.19</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -5287,7 +5285,7 @@
         </is>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>109.1857</v>
+        <v>220.1271</v>
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
@@ -5295,22 +5293,22 @@
         </is>
       </c>
       <c r="S53" s="4" t="n">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>-6.72</v>
+        <v>-5.87</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>121.93</v>
+        <v>244.86</v>
       </c>
       <c r="V53" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260908-d0ae28</t>
+          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
         </is>
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5320,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -5351,21 +5349,21 @@
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>273.3</v>
+        <v>154.28</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>261.05</v>
+        <v>148.23</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-4.48</v>
+        <v>-3.92</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>28.4</v>
+        <v>33.3</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
@@ -5388,7 +5386,7 @@
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>255.3143</v>
+        <v>145.5286</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
@@ -5396,22 +5394,22 @@
         </is>
       </c>
       <c r="S54" s="4" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>-6.58</v>
+        <v>-5.67</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>289.39</v>
+        <v>163.68</v>
       </c>
       <c r="V54" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
+          <t>IND-R2-IGL-20260909-938c43</t>
         </is>
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5421,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -5443,30 +5441,32 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>3365.2</v>
+        <v>117.05</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>3173.5</v>
+        <v>111.85</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v>40.4</v>
+        <v>-4.44</v>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>3085.7715</v>
+        <v>109.1857</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5497,22 +5497,22 @@
         </is>
       </c>
       <c r="S55" s="4" t="n">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>-8.300000000000001</v>
+        <v>-6.72</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>3608.33</v>
+        <v>121.93</v>
       </c>
       <c r="V55" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MCX-20260909-1bc45f</t>
+          <t>IND-R2-IEX-20260908-d0ae28</t>
         </is>
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -5553,25 +5553,25 @@
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>275</v>
+        <v>273.3</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>257</v>
+        <v>258.6</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-6.55</v>
+        <v>-5.38</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>35.4</v>
+        <v>28.4</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>245.8929</v>
+        <v>255.3143</v>
       </c>
       <c r="R56" s="4" t="inlineStr">
         <is>
@@ -5598,22 +5598,22 @@
         </is>
       </c>
       <c r="S56" s="4" t="n">
-        <v>4.32</v>
+        <v>1.27</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>-10.58</v>
+        <v>-6.58</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>296.13</v>
+        <v>289.39</v>
       </c>
       <c r="V56" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260909-bbba1f</t>
+          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
         </is>
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>187.94</v>
+        <v>275</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>173</v>
+        <v>255.2</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-7.95</v>
+        <v>-7.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>169.1236</v>
+        <v>245.8929</v>
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
@@ -5699,17 +5699,17 @@
         </is>
       </c>
       <c r="S57" s="4" t="n">
-        <v>2.24</v>
+        <v>3.65</v>
       </c>
       <c r="T57" s="4" t="n">
-        <v>-10.01</v>
+        <v>-10.58</v>
       </c>
       <c r="U57" s="4" t="n">
-        <v>206.77</v>
+        <v>296.13</v>
       </c>
       <c r="V57" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260909-29ffd5</t>
+          <t>IND-R2-VEDL-20260909-bbba1f</t>
         </is>
       </c>
       <c r="W57" s="4" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -5755,18 +5755,18 @@
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>385.3</v>
+        <v>187.94</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>350.55</v>
+        <v>174.2</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-9.02</v>
+        <v>-7.31</v>
       </c>
       <c r="L58" s="4" t="n">
         <v>40.6</v>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>335.0214</v>
+        <v>169.1236</v>
       </c>
       <c r="R58" s="4" t="inlineStr">
         <is>
@@ -5800,17 +5800,17 @@
         </is>
       </c>
       <c r="S58" s="4" t="n">
-        <v>4.43</v>
+        <v>2.91</v>
       </c>
       <c r="T58" s="4" t="n">
-        <v>-13.05</v>
+        <v>-10.01</v>
       </c>
       <c r="U58" s="4" t="n">
-        <v>412.84</v>
+        <v>206.77</v>
       </c>
       <c r="V58" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
+          <t>IND-R2-SAIL-20260909-29ffd5</t>
         </is>
       </c>
       <c r="W58" s="4" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -5842,37 +5842,35 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>397</v>
+        <v>3365.2</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>409.8</v>
+        <v>3115</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>40.4</v>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
@@ -5895,7 +5893,7 @@
         </is>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>386.4571</v>
+        <v>3085.7715</v>
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
@@ -5903,22 +5901,22 @@
         </is>
       </c>
       <c r="S59" s="4" t="n">
-        <v>5.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="T59" s="4" t="n">
-        <v>-2.66</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="U59" s="4" t="n">
-        <v>412.81</v>
+        <v>3608.33</v>
       </c>
       <c r="V59" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-MCX-20260909-1bc45f</t>
         </is>
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5930,12 +5928,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -5945,41 +5943,39 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-05</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>417.6</v>
+        <v>385.3</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>419.25</v>
+        <v>356.15</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>-7.57</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -5998,7 +5994,7 @@
         </is>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>407.3714</v>
+        <v>335.0214</v>
       </c>
       <c r="R60" s="4" t="inlineStr">
         <is>
@@ -6006,22 +6002,22 @@
         </is>
       </c>
       <c r="S60" s="4" t="n">
-        <v>2.83</v>
+        <v>5.93</v>
       </c>
       <c r="T60" s="4" t="n">
-        <v>-2.45</v>
+        <v>-13.05</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>432.94</v>
+        <v>412.84</v>
       </c>
       <c r="V60" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
         </is>
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6029,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -6053,27 +6049,27 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-11</t>
+          <t>Admitted 2026-08-04</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>239.45</v>
+        <v>397</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>235.95</v>
+        <v>413.1</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K61" s="6" t="n">
-        <v>-1.46</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>4.06</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6082,7 +6078,7 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6101,7 +6097,7 @@
         </is>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>232.2186</v>
+        <v>386.4571</v>
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
@@ -6109,17 +6105,19 @@
         </is>
       </c>
       <c r="S61" s="4" t="n">
-        <v>1.58</v>
+        <v>6.45</v>
       </c>
       <c r="T61" s="4" t="n">
-        <v>-3.02</v>
-      </c>
-      <c r="U61" s="4" t="n">
-        <v>250.3</v>
+        <v>-2.66</v>
+      </c>
+      <c r="U61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V61" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
       <c r="W61" s="4" t="inlineStr">
@@ -6136,7 +6134,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -6156,27 +6154,27 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-08-05</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>389.85</v>
+        <v>417.6</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>382.9</v>
+        <v>420.75</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K62" s="6" t="n">
-        <v>-1.78</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>0.75</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -6185,7 +6183,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -6204,7 +6202,7 @@
         </is>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>378.3286</v>
+        <v>407.3714</v>
       </c>
       <c r="R62" s="4" t="inlineStr">
         <is>
@@ -6212,17 +6210,17 @@
         </is>
       </c>
       <c r="S62" s="4" t="n">
-        <v>1.19</v>
+        <v>3.18</v>
       </c>
       <c r="T62" s="4" t="n">
-        <v>-2.96</v>
+        <v>-2.45</v>
       </c>
       <c r="U62" s="4" t="n">
-        <v>407.13</v>
+        <v>432.94</v>
       </c>
       <c r="V62" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
         </is>
       </c>
       <c r="W62" s="4" t="inlineStr">
@@ -6239,215 +6237,421 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="n">
+        <v>378.3286</v>
+      </c>
+      <c r="R63" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S63" s="4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T63" s="4" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="U63" s="4" t="n">
+        <v>407.13</v>
+      </c>
+      <c r="V63" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
+        </is>
+      </c>
+      <c r="W63" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
           <t>TATASTEEL</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-28</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="H64" s="4" t="n">
         <v>187.46</v>
       </c>
-      <c r="I63" s="4" t="n">
-        <v>183.65</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K63" s="6" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
+      <c r="I64" s="4" t="n">
+        <v>184.35</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M63" s="4" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N63" s="4" t="inlineStr">
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O63" s="4" t="inlineStr">
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P63" s="4" t="inlineStr">
+      <c r="P64" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q63" s="4" t="n">
+      <c r="Q64" s="4" t="n">
         <v>181.8114</v>
       </c>
-      <c r="R63" s="4" t="inlineStr">
+      <c r="R64" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T63" s="4" t="n">
+      <c r="S64" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T64" s="4" t="n">
         <v>-3.01</v>
       </c>
-      <c r="U63" s="4" t="n">
+      <c r="U64" s="4" t="n">
         <v>195.93</v>
       </c>
-      <c r="V63" s="4" t="inlineStr">
+      <c r="V64" s="4" t="inlineStr">
         <is>
           <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
-      <c r="W63" s="4" t="inlineStr">
+      <c r="W64" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-11</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>239.45</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>235.03</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="n">
+        <v>232.2186</v>
+      </c>
+      <c r="R65" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S65" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T65" s="4" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="U65" s="4" t="n">
+        <v>250.3</v>
+      </c>
+      <c r="V65" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
+        </is>
+      </c>
+      <c r="W65" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -6456,8 +6660,8 @@
   </sheetData>
   <mergeCells count="23">
     <mergeCell ref="A68:W68"/>
-    <mergeCell ref="A67:W67"/>
     <mergeCell ref="A77:W77"/>
+    <mergeCell ref="A83:W83"/>
     <mergeCell ref="A82:W82"/>
     <mergeCell ref="A73:W73"/>
     <mergeCell ref="A1:W1"/>
@@ -6466,7 +6670,7 @@
     <mergeCell ref="A6:W6"/>
     <mergeCell ref="A69:W69"/>
     <mergeCell ref="A78:W78"/>
-    <mergeCell ref="A66:W66"/>
+    <mergeCell ref="A84:W84"/>
     <mergeCell ref="A80:W80"/>
     <mergeCell ref="A75:W75"/>
     <mergeCell ref="A74:W74"/>
@@ -6489,7 +6693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6520,14 +6724,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>67 records · ADMINISTRATIVE 21 · ADVISORY/HISTORICAL 5 · REALIZED EXIT 30 · STOP-BREACH MARK 11   ·   Canonical lifecycle historical coverage begins 2026-08-04 · earlier closures are not held in any provable AEGIS source</t>
+          <t>69 records · ADMINISTRATIVE 21 · ADVISORY/HISTORICAL 5 · REALIZED EXIT 32 · STOP-BREACH MARK 11   ·   Canonical lifecycle historical coverage begins 2026-08-04 · earlier closures are not held in any provable AEGIS source</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>📊 REALIZED PRODUCTION PERFORMANCE · 30 closed trade(s) · win 12/30 · avg -1.53%   ·   EXCLUDED from this line: orphan auto-closes, administrative records, advisory rows, and 11 STOP-BREACH MARK(s) whose stop was passed but which are NOT sold - their price and P&amp;L are today's mark, not a realized result</t>
+          <t>📊 REALIZED PRODUCTION PERFORMANCE · 32 closed trade(s) · win 12/32 · avg -1.72%   ·   EXCLUDED from this line: orphan auto-closes, administrative records, advisory rows, and 11 STOP-BREACH MARK(s) whose stop was passed but which are NOT sold - their price and P&amp;L are today's mark, not a realized result</t>
         </is>
       </c>
     </row>
@@ -6653,10 +6857,10 @@
         <v>1191</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1099</v>
+        <v>1098.4</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-7.72</v>
+        <v>-7.77</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>36</v>
@@ -6727,10 +6931,10 @@
         <v>1276.6</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1229.2</v>
+        <v>1242.7</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-3.71</v>
+        <v>-2.66</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>5</v>
@@ -6767,12 +6971,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -6782,54 +6986,52 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1449.5</v>
+        <v>470.4</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1350.4</v>
+        <v>450.7</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-6.84</v>
+        <v>-4.19</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>EXIT_STOP · trigger crossed 2026-09-16 ·</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>28.4</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-09-16 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R2-IRCTC-20260909-add681</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -6841,12 +7043,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -6866,20 +7068,20 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1413.5</v>
+        <v>1449.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-4.42</v>
+        <v>-6.86</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -6893,12 +7095,12 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
@@ -6910,17 +7112,17 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -6930,34 +7132,34 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2744.3</v>
+        <v>1413.5</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2588.5</v>
+        <v>1358.9</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-5.68</v>
+        <v>-3.86</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Holding horizon reached</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -6967,86 +7169,84 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>EXIT_HORIZON · trigger crossed 2026-09-11 · stop_source=dyna</t>
+          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>AIAENG</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>REALIZED EXIT</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>REALIZED EXIT</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="H10" s="4" t="n">
-        <v>113.36</v>
+        <v>4056.8</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>115.63</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>2</v>
+        <v>3819</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-5.86</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Holding horizon reached</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>EXIT_STOP · trigger crossed 2026-09-16 ·</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>35</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>EXIT_HORIZON · trigger crossed 2026-09-11 · stop_source=dyna</t>
+          <t>EXIT_STOP · trigger crossed 2026-09-16 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-AIAENG-20260911-5d7269</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -7063,12 +7263,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -7092,13 +7292,13 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5499</v>
+        <v>2744.3</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5510</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>0.2</v>
+        <v>2588.5</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-5.68</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>37</v>
@@ -7120,7 +7320,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -7137,12 +7337,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -7166,13 +7366,13 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>284.85</v>
+        <v>113.36</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>260.1</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>-8.69</v>
+        <v>115.63</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>38</v>
@@ -7194,7 +7394,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ITC-20260804-e0ebbb</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -7211,12 +7411,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -7236,20 +7436,20 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>553.3</v>
+        <v>5499</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>560.25</v>
+        <v>5510</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1.26</v>
+        <v>0.2</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -7268,7 +7468,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20260806-03d0a7</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -7285,12 +7485,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -7314,13 +7514,13 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>452.35</v>
+        <v>284.85</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>414.95</v>
+        <v>260.1</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-8.27</v>
+        <v>-8.69</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>38</v>
@@ -7342,7 +7542,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
+          <t>IND-R2-ITC-20260804-e0ebbb</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -7359,12 +7559,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -7384,20 +7584,20 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>709</v>
+        <v>553.3</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>644.1</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>-9.15</v>
+        <v>560.25</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>1.26</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -7416,7 +7616,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+          <t>IND-R2-GNFC-20260806-03d0a7</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -7433,12 +7633,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -7458,20 +7658,20 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>11475</v>
+        <v>452.35</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>11020</v>
+        <v>414.95</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-3.97</v>
+        <v>-8.27</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -7490,7 +7690,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -7502,17 +7702,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -7522,12 +7722,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -7536,20 +7736,20 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>381.6</v>
+        <v>709</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>363</v>
+        <v>644.1</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-4.87</v>
+        <v>-9.15</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
+          <t>Holding horizon reached</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -7559,34 +7759,34 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 369.75 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_HORIZON · trigger crossed 2026-09-11 · stop_source=dyna</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATAPOWER-20260804-29907f</t>
+          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -7601,29 +7801,29 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>454.85</v>
+        <v>11475</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>454.85</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>0</v>
+        <v>11020</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-3.97</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Holding horizon reached</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -7633,17 +7833,17 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+15.5pp)</t>
+          <t>EXIT_HORIZON · trigger crossed 2026-09-11 · stop_source=dyna</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260908-c6e7dc</t>
+          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7855,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -7680,20 +7880,20 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1048.7</v>
+        <v>381.6</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>968</v>
+        <v>363.6</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-7.7</v>
+        <v>-4.72</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -7707,12 +7907,12 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1011.5999 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 369.75 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-SBIN-20260821-b637f4</t>
+          <t>IND-R1-TATAPOWER-20260804-29907f</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
@@ -7729,12 +7929,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -7744,34 +7944,34 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1642.5</v>
+        <v>454.85</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1521.1</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>-7.39</v>
+        <v>454.85</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -7781,17 +7981,17 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1594.6857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>Rotation → GNFC.NS (+15.5pp)</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
+          <t>IND-R2-SUNTV-20260908-c6e7dc</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
@@ -7803,12 +8003,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -7818,34 +8018,34 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>289</v>
+        <v>1048.7</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>289</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>0</v>
+        <v>981.8</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>-6.38</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -7855,17 +8055,17 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+19.4pp)</t>
+          <t>STOP BREACHED - stop 1011.5999 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260908-f20701</t>
+          <t>IND-R1-SBIN-20260821-b637f4</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
@@ -7877,12 +8077,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -7902,20 +8102,20 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2410</v>
+        <v>1642.5</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2063.2</v>
+        <v>1541.2</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-14.39</v>
+        <v>-6.17</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -7929,12 +8129,12 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 2314.8285 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1594.6857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-LUPIN-20260805-71abab</t>
+          <t>IND-R1-PIDILITIND-20260804-cf5c6a</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
@@ -7951,12 +8151,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -7966,34 +8166,34 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>507.9</v>
+        <v>289</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>458.55</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>-9.720000000000001</v>
+        <v>289</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -8003,17 +8203,17 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 493.3286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>Rotation → GNFC.NS (+19.4pp)</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-IRCTC-20260804-afbb8f</t>
+          <t>IND-R2-PETRONET-20260908-f20701</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8225,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -8050,20 +8250,20 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2064.9</v>
+        <v>2410</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1938.1</v>
+        <v>2040.6</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-6.14</v>
+        <v>-15.33</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -8077,12 +8277,12 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1990.457 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 2314.8285 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-HINDUNILVR-20260812-08d1f5</t>
+          <t>IND-R1-LUPIN-20260805-71abab</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
@@ -8099,12 +8299,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -8124,20 +8324,20 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>385.15</v>
+        <v>507.9</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>384.9</v>
+        <v>450.7</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.06</v>
+        <v>-11.26</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -8151,12 +8351,12 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 377.5071 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 493.3286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-DABUR-20260828-be7819</t>
+          <t>IND-R1-IRCTC-20260804-afbb8f</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -8173,7 +8373,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -8198,20 +8398,20 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5454.5</v>
+        <v>2064.9</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4954</v>
+        <v>1974</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-9.18</v>
+        <v>-4.4</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -8225,12 +8425,12 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 5283.7143 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1990.457 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BRITANNIA-20260804-3de31c</t>
+          <t>IND-R1-HINDUNILVR-20260812-08d1f5</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
@@ -8242,17 +8442,17 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -8262,34 +8462,34 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>414.35</v>
+        <v>385.15</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>414.35</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>0</v>
+        <v>386.1</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>0.25</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -8299,34 +8499,34 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+18.2pp)</t>
+          <t>STOP BREACHED - stop 377.5071 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RBLBANK-20260907-a63a75</t>
+          <t>IND-R1-DABUR-20260828-be7819</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -8336,34 +8536,34 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>391.3</v>
+        <v>5454.5</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>415.35</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>6.15</v>
+        <v>5006.5</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>-8.210000000000001</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Stop breached</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -8373,34 +8573,34 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+17.1pp)</t>
+          <t>STOP BREACHED - stop 5283.7143 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R1-BRITANNIA-20260804-3de31c</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -8410,24 +8610,24 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>ADVISORY/HISTORICAL</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>177.09</v>
+        <v>414.35</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>177.09</v>
+        <v>414.35</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>0</v>
@@ -8437,7 +8637,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -8447,34 +8647,34 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>Retired-runner cleanup · producer guard added 2026-09-02 · t</t>
+          <t>Rotation → GNFC.NS (+18.2pp)</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-WIPRO-20260902-25d63c</t>
+          <t>IND-R2-RBLBANK-20260907-a63a75</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>registry:advisory</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -8489,25 +8689,25 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2891.8</v>
+        <v>391.3</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2891.8</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>0</v>
+        <v>415.35</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>6.15</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -8521,34 +8721,34 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+57.0pp)</t>
+          <t>Rotation → GNFC.NS (+17.1pp)</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIENT-20260902-51452a</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -8568,24 +8768,24 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>347.25</v>
+        <v>177.09</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>326.5</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>-5.98</v>
+        <v>177.09</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t xml:space="preserve">Retired-runner cleanup · producer guard </t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -8595,12 +8795,12 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
+          <t>Retired-runner cleanup · producer guard added 2026-09-02 · t</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-NTPC-20260804-b96a36</t>
+          <t>IND-R1-WIPRO-20260902-25d63c</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
@@ -8612,17 +8812,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -8637,25 +8837,25 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2383.9</v>
+        <v>2891.8</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2160.2</v>
-      </c>
-      <c r="J32" s="6" t="n">
-        <v>-9.380000000000001</v>
+        <v>2891.8</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -8669,17 +8869,17 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+13.0pp)</t>
+          <t>Rotation → GNFC.NS (+57.0pp)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LUPIN-20260804-def33a</t>
+          <t>IND-R2-ADANIENT-20260902-51452a</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
@@ -8691,12 +8891,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -8706,34 +8906,34 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>ADVISORY/HISTORICAL</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>398.8</v>
+        <v>347.25</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>398.8</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>0</v>
+        <v>326.5</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>-5.98</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -8743,29 +8943,29 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+52.9pp)</t>
+          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
+          <t>IND-R1-NTPC-20260804-b96a36</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:advisory</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -8780,12 +8980,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>ADVISORY/HISTORICAL</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -8794,20 +8994,20 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1955.3</v>
+        <v>2383.9</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1912</v>
+        <v>2160.2</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-2.21</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -8817,34 +9017,34 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
+          <t>Rotation → GNFC.NS (+13.0pp)</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
+          <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>registry:advisory</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -8854,34 +9054,34 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>ADVISORY/HISTORICAL</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>289</v>
+        <v>398.8</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>268.15</v>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>-7.21</v>
+        <v>398.8</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>Historical reconciliation</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -8891,17 +9091,17 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
+          <t>Rotation → GNFC.NS (+52.9pp)</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ITC-20260805-3cdd2a</t>
+          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>registry:advisory</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
@@ -8913,12 +9113,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -8928,12 +9128,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADVISORY/HISTORICAL</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -8942,20 +9142,20 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>415.15</v>
+        <v>1955.3</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>402.55</v>
+        <v>1912</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-3.04</v>
+        <v>-2.21</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>24</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -8965,34 +9165,34 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+14.3pp)</t>
+          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R1-SUNPHARMA-20260804-48ab60</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:advisory</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -9016,16 +9216,16 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>283.4</v>
+        <v>289</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>264.9</v>
+        <v>268.15</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-6.53</v>
+        <v>-7.21</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -9044,7 +9244,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-POWERGRID-20260805-b39825</t>
+          <t>IND-R1-ITC-20260805-3cdd2a</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -9056,17 +9256,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -9081,25 +9281,25 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>847.5</v>
+        <v>415.15</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>847.5</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>0</v>
+        <v>402.55</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>-3.04</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -9113,34 +9313,34 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+56.7pp)</t>
+          <t>Rotation → GNFC.NS (+14.3pp)</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARICO-20260826-1c5a1c</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -9150,34 +9350,34 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>ADVISORY/HISTORICAL</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1702.7</v>
+        <v>283.4</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>1702.7</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>0</v>
+        <v>264.9</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>-6.53</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Historical reconciliation</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -9187,34 +9387,34 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+57.6pp)</t>
+          <t>Registry-sync · aegis_history had EXIT status without oreg.c</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
+          <t>IND-R1-POWERGRID-20260805-b39825</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:advisory</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -9234,14 +9434,14 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>244.55</v>
+        <v>847.5</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>244.55</v>
+        <v>847.5</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>0</v>
@@ -9261,12 +9461,12 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+10.1pp)</t>
+          <t>Rotation → GNFC.NS (+56.7pp)</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260824-89850d</t>
+          <t>IND-R2-MARICO-20260826-1c5a1c</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -9278,17 +9478,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -9308,14 +9508,14 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1114.2</v>
+        <v>1702.7</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>1114.2</v>
+        <v>1702.7</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>0</v>
@@ -9335,12 +9535,12 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+14.5pp)</t>
+          <t>Rotation → GNFC.NS (+57.6pp)</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MGL-20260821-142d93</t>
+          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -9352,12 +9552,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -9382,14 +9582,14 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>402.8</v>
+        <v>244.55</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>402.8</v>
+        <v>244.55</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>0</v>
@@ -9409,12 +9609,12 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+13.3pp)</t>
+          <t>Rotation → GNFC.NS (+10.1pp)</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
+          <t>IND-R2-JIOFIN-20260824-89850d</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -9431,12 +9631,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -9460,10 +9660,10 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>8693</v>
+        <v>1114.2</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>8693</v>
+        <v>1114.2</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>0</v>
@@ -9483,12 +9683,12 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+61.4pp)</t>
+          <t>Rotation → GNFC.NS (+14.5pp)</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
+          <t>IND-R2-MGL-20260821-142d93</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -9500,17 +9700,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -9530,14 +9730,14 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>174.9</v>
+        <v>402.8</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>174.9</v>
+        <v>402.8</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
@@ -9547,7 +9747,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
@@ -9557,12 +9757,12 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.8pp alpha</t>
+          <t>Rotation → GNFC.NS (+13.3pp)</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260820-80f37d</t>
+          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
@@ -9574,17 +9774,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -9604,14 +9804,14 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>5220</v>
+        <v>8693</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>5220</v>
+        <v>8693</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>0</v>
@@ -9621,7 +9821,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -9631,12 +9831,12 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +60.0pp alpha</t>
+          <t>Rotation → GNFC.NS (+61.4pp)</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
+          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -9648,17 +9848,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -9673,25 +9873,25 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>129.2</v>
+        <v>174.9</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>124.4</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>-3.72</v>
+        <v>174.9</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -9705,17 +9905,17 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +12.2pp alpha</t>
+          <t>→ GNFC.NS · +11.8pp alpha</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-SAIL-20260820-80f37d</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
@@ -9727,12 +9927,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -9747,25 +9947,25 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>552.4</v>
+        <v>5220</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>558</v>
-      </c>
-      <c r="J47" s="5" t="n">
-        <v>1.01</v>
+        <v>5220</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -9779,34 +9979,34 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +14.7pp alpha</t>
+          <t>→ GNFC.NS · +60.0pp alpha</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -9830,16 +10030,16 @@
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>377</v>
+        <v>129.2</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>387.55</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>2.8</v>
+        <v>124.4</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>-3.72</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -9853,12 +10053,12 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +9.8pp alpha</t>
+          <t>→ GNFC.NS · +12.2pp alpha</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
@@ -9870,17 +10070,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -9900,20 +10100,20 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>1384</v>
+        <v>552.4</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>1327.6</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>-4.08</v>
+        <v>558</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>1.01</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -9927,12 +10127,12 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +56.7pp alpha</t>
+          <t>→ GNFC.NS · +14.7pp alpha</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -9944,17 +10144,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -9974,20 +10174,20 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>2439.4</v>
+        <v>377</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>2361</v>
-      </c>
-      <c r="J50" s="6" t="n">
-        <v>-3.21</v>
+        <v>387.55</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>2.8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -10001,12 +10201,12 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +6.7pp alpha</t>
+          <t>→ GNFC.NS · +9.8pp alpha</t>
         </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260804-a45359</t>
+          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
@@ -10018,17 +10218,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -10043,25 +10243,25 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>3940</v>
+        <v>1384</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>3940</v>
-      </c>
-      <c r="J51" s="4" t="n">
-        <v>0</v>
+        <v>1327.6</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>-4.08</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -10075,17 +10275,17 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.5pp alpha</t>
+          <t>→ GNFC.NS · +56.7pp alpha</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10297,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -10122,20 +10322,20 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>11600</v>
+        <v>2439.4</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>11828</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>1.97</v>
+        <v>2361</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>-3.21</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -10149,12 +10349,12 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +6.6pp alpha</t>
+          <t>→ GNFC.NS · +6.7pp alpha</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260805-f0f538</t>
+          <t>IND-R2-TCS-20260804-a45359</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
@@ -10166,17 +10366,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -10196,14 +10396,14 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1779.2</v>
+        <v>3940</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>1779.2</v>
+        <v>3940</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>0</v>
@@ -10223,12 +10423,12 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +8.1pp alpha</t>
+          <t>→ GNFC.NS · +7.5pp alpha</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
+          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -10240,17 +10440,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -10265,25 +10465,25 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>181.14</v>
+        <v>11600</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>181.14</v>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>0</v>
+        <v>11828</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>1.97</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -10297,34 +10497,34 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +9.4pp alpha</t>
+          <t>→ GNFC.NS · +6.6pp alpha</t>
         </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
+          <t>IND-R2-OFSS-20260805-f0f538</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -10344,14 +10544,14 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>4924</v>
+        <v>1779.2</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>4924</v>
+        <v>1779.2</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>0</v>
@@ -10371,12 +10571,12 @@
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +60.1pp alpha</t>
+          <t>→ GNFC.NS · +8.1pp alpha</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
+          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -10393,7 +10593,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -10422,10 +10622,10 @@
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>129</v>
+        <v>181.14</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>129</v>
+        <v>181.14</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>0</v>
@@ -10445,12 +10645,12 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +6.5pp alpha</t>
+          <t>→ TCS.NS · +9.4pp alpha</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260810-788da8</t>
+          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
@@ -10467,12 +10667,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -10487,25 +10687,25 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>7454.5</v>
+        <v>4924</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>7095</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>-4.82</v>
+        <v>4924</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -10519,34 +10719,34 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +62.1pp alpha</t>
+          <t>→ TCS.NS · +60.1pp alpha</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
+          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -10561,25 +10761,25 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>ADMINISTRATIVE</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1327.7</v>
+        <v>129</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>1285</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>-3.22</v>
+        <v>129</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -10593,34 +10793,34 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +64.8pp alpha</t>
+          <t>→ TCS.NS · +6.5pp alpha</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
+          <t>IND-R2-CANBK-20260810-788da8</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>registry:administrative</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -10640,20 +10840,20 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1595</v>
+        <v>7454.5</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1584.8</v>
+        <v>7095</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.64</v>
+        <v>-4.82</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -10667,12 +10867,12 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +62.5pp alpha</t>
+          <t>→ TCS.NS · +62.1pp alpha</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PRESTIGE-20260805-488bde</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
@@ -10689,12 +10889,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -10718,13 +10918,13 @@
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>450</v>
+        <v>1327.7</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>442.8</v>
+        <v>1285</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-1.6</v>
+        <v>-3.22</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>2</v>
@@ -10741,12 +10941,12 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +10.3pp alpha</t>
+          <t>→ GNFC.NS · +64.8pp alpha</t>
         </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260805-6635e1</t>
+          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
@@ -10763,12 +10963,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -10792,13 +10992,13 @@
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>845</v>
+        <v>1595</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>889.5</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>5.27</v>
+        <v>1584.8</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>-0.64</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>2</v>
@@ -10815,12 +11015,12 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.4pp alpha</t>
+          <t>→ GNFC.NS · +62.5pp alpha</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
+          <t>IND-R2-PRESTIGE-20260805-488bde</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -10837,12 +11037,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -10862,20 +11062,20 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>471.2</v>
+        <v>450</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v>0.45</v>
+        <v>442.8</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>-1.6</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -10889,12 +11089,12 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +60.7pp alpha</t>
+          <t>→ GNFC.NS · +10.3pp alpha</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
+          <t>IND-R2-OIL-20260805-6635e1</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
@@ -10911,12 +11111,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -10940,13 +11140,13 @@
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>6793.5</v>
+        <v>845</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>6774</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>-0.29</v>
+        <v>889.5</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>5.27</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>2</v>
@@ -10963,12 +11163,12 @@
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +8.0pp alpha</t>
+          <t>→ GNFC.NS · +7.4pp alpha</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -10980,50 +11180,50 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>REALIZED EXIT</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>VEDL</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>REALIZED EXIT</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="H64" s="4" t="n">
-        <v>268.5</v>
+        <v>471.2</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>278.8</v>
+        <v>473.3</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>3.84</v>
+        <v>0.45</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -11037,12 +11237,12 @@
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.6pp alpha</t>
+          <t>→ GNFC.NS · +60.7pp alpha</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260804-563905</t>
+          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
@@ -11054,17 +11254,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -11088,16 +11288,16 @@
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>1167.5</v>
+        <v>6793.5</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>1177</v>
-      </c>
-      <c r="J65" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>6774</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>-0.29</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -11111,12 +11311,12 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.7pp alpha</t>
+          <t>→ GNFC.NS · +8.0pp alpha</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260805-ea04e5</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
@@ -11133,12 +11333,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -11162,13 +11362,13 @@
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>5470.5</v>
+        <v>268.5</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>5651.5</v>
+        <v>278.8</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>3.31</v>
+        <v>3.84</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>2</v>
@@ -11185,12 +11385,12 @@
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +10.6pp alpha</t>
+          <t>→ GNFC.NS · +11.6pp alpha</t>
         </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
+          <t>IND-R2-VEDL-20260804-563905</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
@@ -11207,7 +11407,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -11232,20 +11432,20 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>1363.6</v>
+        <v>1167.5</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>1351.3</v>
-      </c>
-      <c r="J67" s="6" t="n">
-        <v>-0.9</v>
+        <v>1177</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -11259,12 +11459,12 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.8pp alpha</t>
+          <t>→ GNFC.NS · +11.7pp alpha</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
+          <t>IND-R2-INFY-20260805-ea04e5</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -11281,7 +11481,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -11306,20 +11506,20 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>2195</v>
+        <v>5470.5</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>2182</v>
-      </c>
-      <c r="J68" s="6" t="n">
-        <v>-0.59</v>
+        <v>5651.5</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>3.31</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -11333,12 +11533,12 @@
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +59.7pp alpha</t>
+          <t>→ GNFC.NS · +10.6pp alpha</t>
         </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
+          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
@@ -11350,54 +11550,54 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>REALIZED EXIT</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVE</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="H69" s="4" t="n">
-        <v>567.3</v>
+        <v>1363.6</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>567.3</v>
-      </c>
-      <c r="J69" s="4" t="n">
-        <v>0</v>
+        <v>1351.3</v>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>-0.9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Outperformance exit</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
@@ -11407,34 +11607,34 @@
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+52.0pp)</t>
+          <t>→ GNFC.NS · +7.8pp alpha</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWENERGY-20260804-1210a0</t>
+          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -11449,29 +11649,29 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVE</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>939.95</v>
+        <v>2195</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>939.95</v>
-      </c>
-      <c r="J70" s="4" t="n">
-        <v>0</v>
+        <v>2182</v>
+      </c>
+      <c r="J70" s="6" t="n">
+        <v>-0.59</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap</t>
+          <t>Outperformance exit</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
@@ -11481,17 +11681,17 @@
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+          <t>→ GNFC.NS · +59.7pp alpha</t>
         </is>
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>registry:administrative</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -11503,12 +11703,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -11532,10 +11732,10 @@
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>425.05</v>
+        <v>567.3</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>425.05</v>
+        <v>567.3</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>0</v>
@@ -11555,87 +11755,235 @@
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
+          <t>Rotation → LUPIN.NS (+52.0pp)</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-JSWENERGY-20260804-1210a0</t>
+        </is>
+      </c>
+      <c r="P71" s="4" t="inlineStr">
+        <is>
+          <t>registry:administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>939.95</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>939.95</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>Rotation swap</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
           <t>Rotation → LUPIN.NS (+51.8pp)</t>
         </is>
       </c>
-      <c r="O71" s="4" t="inlineStr">
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+        </is>
+      </c>
+      <c r="P72" s="4" t="inlineStr">
+        <is>
+          <t>registry:administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>425.05</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>425.05</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>Rotation swap</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+        </is>
+      </c>
+      <c r="O73" s="4" t="inlineStr">
         <is>
           <t>IND-R2-BIOCON-20260804-954a24</t>
         </is>
       </c>
-      <c r="P71" s="4" t="inlineStr">
+      <c r="P73" s="4" t="inlineStr">
         <is>
           <t>registry:administrative</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>Closed positions held by the canonical lifecycle dataset. Coverage begins on the date named in the banner · AEGIS had no position registry before then, only a recommendation list with expiry semantics, so earlier closures cannot be proven and are not invented.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>P&amp;L % · (Exit − Entry) / Entry. It is a REALIZED result only on a REALIZED EXIT row · on every other Record Type it is a mark.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Record Type is the population; Source is the provenance. They are different questions and they disagree: 463 USA rows arrived from registry:production yet are ORPHAN AUTO-CLOSE. Build performance statistics on Record Type, never on Source.</t>
+          <t>Closed positions held by the canonical lifecycle dataset. Coverage begins on the date named in the banner · AEGIS had no position registry before then, only a recommendation list with expiry semantics, so earlier closures cannot be proven and are not invented.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>REALIZED EXIT · a trade that actually closed · the only population in the realized performance line. ORPHAN AUTO-CLOSE · a reconstructed record for a position that was never properly tracked · not a trade. ADMINISTRATIVE · same-day or zero-delta bookkeeping · not a trade. ADVISORY/HISTORICAL · retired R1 · never counted in production P&amp;L. STOP-BREACH MARK · the price passed the stop and the row left CURRENT.</t>
+          <t>P&amp;L % · (Exit − Entry) / Entry. It is a REALIZED result only on a REALIZED EXIT row · on every other Record Type it is a mark.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK rows are MARKS, not fills. The position is still open in its engine, Exit Price is the latest close, and P&amp;L % is the live unrealized figure. They carry their own Record Type precisely so they are never counted in the realized win-rate or average return alongside trades that actually closed.</t>
+          <t>Record Type is the population; Source is the provenance. They are different questions and they disagree: 463 USA rows arrived from registry:production yet are ORPHAN AUTO-CLOSE. Build performance statistics on Record Type, never on Source.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Exit Date on a breach row is the day the breach was FIRST observed, not today, and it never moves. A position that later recovers above its stop stays here · recovering does not undo having passed the stop.</t>
+          <t>REALIZED EXIT · a trade that actually closed · the only population in the realized performance line. ORPHAN AUTO-CLOSE · a reconstructed record for a position that was never properly tracked · not a trade. ADMINISTRATIVE · same-day or zero-delta bookkeeping · not a trade. ADVISORY/HISTORICAL · retired R1 · never counted in production P&amp;L. STOP-BREACH MARK · the price passed the stop and the row left CURRENT.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE means the canonical price source had no value · never fabricated and never backfilled from today's state.</t>
+          <t>STOP-BREACH MARK rows are MARKS, not fills. The position is still open in its engine, Exit Price is the latest close, and P&amp;L % is the live unrealized figure. They carry their own Record Type precisely so they are never counted in the realized win-rate or average return alongside trades that actually closed.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
+          <t>Exit Date on a breach row is the day the breach was FIRST observed, not today, and it never moves. A position that later recovers above its stop stays here · recovering does not undo having passed the stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE means the canonical price source had no value · never fabricated and never backfilled from today's state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
           <t>Sector · the company's CURRENT classification from the canonical sector cache, not its sector as of the exit date. No point-in-time sector history exists, so this column describes the company today and must not be read as evidence about what the sector was when the trade was live. NOT_AVAILABLE means the canonical source has no entry · it is never guessed.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A75:P75"/>
     <mergeCell ref="A76:P76"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A80:P80"/>
     <mergeCell ref="A79:P79"/>
-    <mergeCell ref="A74:P74"/>
     <mergeCell ref="A77:P77"/>
+    <mergeCell ref="A83:P83"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A78:P78"/>
+    <mergeCell ref="A82:P82"/>
     <mergeCell ref="A81:P81"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W84"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -515,14 +515,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>58 investable · NEW 7 · ACTIVE+ 51 · ACTIVE 0   ·   R2 53 · MOMENTUM 0 · R1 5 (advisory)   ·   7 row(s) read 0.00%: admitted at the 2026-09-16 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>59 investable · NEW 8 · ACTIVE+ 51 · ACTIVE 0   ·   R2 54 · MOMENTUM 0 · R1 5 (advisory)   ·   8 row(s) read 0.00%: admitted at the 2026-09-16 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 58 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.14% from entry, worst single -13.05%</t>
+          <t>🛡 DOWNSIDE · 59 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.14% from entry, worst single -13.05%</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=7 · 228 scored · 56 already in CURRENT · biggest blocker: model disagreement (162) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=8 · 228 scored · 57 already in CURRENT · biggest blocker: model disagreement (161) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 56 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 57 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1399,34 +1399,34 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>339.55</v>
+        <v>177.94</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>352.55</v>
+        <v>177.94</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K15" s="5" t="n">
-        <v>3.83</v>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>32.3</v>
+        <v>30.1</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>339.7714</v>
+        <v>170.5643</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>3.62</v>
+        <v>4.15</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-4.15</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>353.62</v>
+        <v>189</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PATANJALI-20260909-508e75</t>
+          <t>IND-R2-UNIONBANK-20260916-d5e59d</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1500,19 +1500,19 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>373.25</v>
+        <v>339.55</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>386.1</v>
+        <v>352.55</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>3.44</v>
+        <v>3.83</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>28.4</v>
+        <v>32.3</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>374.1643</v>
+        <v>339.7714</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.09</v>
+        <v>3.62</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>389.48</v>
+        <v>353.62</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DABUR-20260911-8f250f</t>
+          <t>IND-R2-PATANJALI-20260909-508e75</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1601,19 +1601,19 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>694.35</v>
+        <v>373.25</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>716.25</v>
+        <v>386.1</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1621,14 +1621,14 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>34.8</v>
+        <v>28.4</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>688.1929</v>
+        <v>374.1643</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>3.92</v>
+        <v>3.09</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.89</v>
+        <v>0.24</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>729</v>
+        <v>389.48</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
+          <t>IND-R2-DABUR-20260911-8f250f</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>25455</v>
+        <v>694.35</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>26140</v>
+        <v>716.25</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1722,14 +1722,14 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>2.69</v>
+        <v>3.15</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>31.3</v>
+        <v>34.8</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>25235</v>
+        <v>688.1929</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1756,17 +1756,17 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.46</v>
+        <v>3.92</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.86</v>
+        <v>-0.89</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>26635.71</v>
+        <v>729</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
+          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1038.3</v>
+        <v>25455</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1065.3</v>
+        <v>26140</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1823,14 +1823,14 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>38.3</v>
+        <v>31.3</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1014.9714</v>
+        <v>25235</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1857,17 +1857,17 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>4.72</v>
+        <v>3.46</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.25</v>
+        <v>-0.86</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1120.78</v>
+        <v>26635.71</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260909-f2b7ad</t>
+          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>292.9</v>
+        <v>1038.3</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>296.35</v>
+        <v>1065.3</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1924,14 +1924,14 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1.18</v>
+        <v>2.6</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>34.3</v>
+        <v>38.3</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>283.3839</v>
+        <v>1014.9714</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1958,17 +1958,17 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>4.38</v>
+        <v>4.72</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-3.25</v>
+        <v>-2.25</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>315.92</v>
+        <v>1120.78</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
+          <t>IND-R2-INFY-20260909-f2b7ad</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1952</v>
+        <v>292.9</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1974</v>
+        <v>296.35</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -2025,14 +2025,14 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>31.2</v>
+        <v>34.3</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1926.3857</v>
+        <v>283.3839</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2059,17 +2059,17 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.41</v>
+        <v>4.38</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.31</v>
+        <v>-3.25</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2020.51</v>
+        <v>315.92</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
+          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>8128.5</v>
+        <v>1952</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>8217</v>
+        <v>1974</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -2126,14 +2126,14 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>38.7</v>
+        <v>31.2</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>7841.2143</v>
+        <v>1926.3857</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2160,22 +2160,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>4.57</v>
+        <v>2.41</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.53</v>
+        <v>-1.31</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>8660.25</v>
+        <v>2020.51</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2207,19 +2207,19 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>5163.5</v>
+        <v>8128.5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5209.5</v>
+        <v>8217</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -2227,14 +2227,14 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.89</v>
+        <v>1.09</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>31.3</v>
+        <v>38.7</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>5048.2143</v>
+        <v>7841.2143</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2261,22 +2261,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.1</v>
+        <v>4.57</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.23</v>
+        <v>-3.53</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>5385.18</v>
+        <v>8660.25</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ALKEM-20260909-517913</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2308,19 +2308,19 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>409.8</v>
+        <v>5163.5</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>413.1</v>
+        <v>5209.5</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -2328,14 +2328,14 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>34.1</v>
+        <v>31.3</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>401.05</v>
+        <v>5048.2143</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2362,22 +2362,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-2.14</v>
+        <v>-2.23</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>432.43</v>
+        <v>5385.18</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260915-bbcfac</t>
+          <t>IND-R2-ALKEM-20260909-517913</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2409,19 +2409,19 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1350.1</v>
+        <v>409.8</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1358.9</v>
+        <v>413.1</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>33.3</v>
+        <v>34.1</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>1321.3286</v>
+        <v>401.05</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2463,22 +2463,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-2.13</v>
+        <v>-2.14</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1401.85</v>
+        <v>432.43</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CIPLA-20260911-5f4a49</t>
+          <t>IND-R2-KOTAKBANK-20260915-bbcfac</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2510,19 +2510,19 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2197.4</v>
+        <v>1350.1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2211.4</v>
+        <v>1358.9</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -2530,14 +2530,14 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>37.1</v>
+        <v>33.3</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2142.5</v>
+        <v>1321.3286</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2564,22 +2564,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.12</v>
+        <v>2.76</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-2.5</v>
+        <v>-2.13</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2341.29</v>
+        <v>1401.85</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260909-fb0a7f</t>
+          <t>IND-R2-CIPLA-20260911-5f4a49</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2611,19 +2611,19 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>122.37</v>
+        <v>2197.4</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>122.94</v>
+        <v>2211.4</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2631,14 +2631,14 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>30.2</v>
+        <v>37.1</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>118.8757</v>
+        <v>2142.5</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>3.31</v>
+        <v>3.12</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.86</v>
+        <v>-2.5</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>128.89</v>
+        <v>2341.29</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260915-4a780b</t>
+          <t>IND-R2-TCS-20260909-fb0a7f</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2712,19 +2712,19 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1244.4</v>
+        <v>122.37</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1246.4</v>
+        <v>122.94</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>32.9</v>
+        <v>30.2</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1205.9572</v>
+        <v>118.8757</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-3.09</v>
+        <v>-2.86</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1294.16</v>
+        <v>128.89</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AXISBANK-20260909-3abb74</t>
+          <t>IND-R2-CANBK-20260915-4a780b</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2822,25 +2822,25 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>818.3</v>
+        <v>1244.4</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>818.1</v>
+        <v>1246.4</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K29" s="6" t="n">
-        <v>-0.02</v>
+      <c r="K29" s="5" t="n">
+        <v>0.16</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>31.2</v>
+        <v>32.9</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>788.0929</v>
+        <v>1205.9572</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2867,17 +2867,17 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.67</v>
+        <v>3.24</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-3.69</v>
+        <v>-3.09</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>866.9299999999999</v>
+        <v>1294.16</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
+          <t>IND-R2-AXISBANK-20260909-3abb74</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>370</v>
+        <v>818.3</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>369.8</v>
+        <v>818.1</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -2934,14 +2934,14 @@
         </is>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="L30" s="4" t="n">
         <v>31.2</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>352.9</v>
+        <v>788.0929</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2968,17 +2968,17 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.57</v>
+        <v>3.67</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-4.62</v>
+        <v>-3.69</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>397.71</v>
+        <v>866.9299999999999</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
+          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3015,19 +3015,19 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>464.25</v>
+        <v>370</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>464</v>
+        <v>369.8</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>440.6143</v>
+        <v>352.9</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3069,22 +3069,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.04</v>
+        <v>4.57</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-5.09</v>
+        <v>-4.62</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>499.7</v>
+        <v>397.71</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3116,19 +3116,19 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1232</v>
+        <v>464.25</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1229.4</v>
+        <v>464</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -3136,14 +3136,14 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>28.3</v>
+        <v>31.2</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1199.9714</v>
+        <v>440.6143</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3170,22 +3170,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>2.39</v>
+        <v>5.04</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-2.6</v>
+        <v>-5.09</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1280.04</v>
+        <v>499.7</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ACC-20260911-3a092f</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3217,19 +3217,19 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>11644</v>
+        <v>1232</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11620</v>
+        <v>1229.4</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -3240,11 +3240,11 @@
         <v>-0.21</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>43.6</v>
+        <v>28.3</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>11221</v>
+        <v>1199.9714</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3271,22 +3271,22 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.43</v>
+        <v>2.39</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-3.63</v>
+        <v>-2.6</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>12467.93</v>
+        <v>1280.04</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260909-1e09a0</t>
+          <t>IND-R2-ACC-20260911-3a092f</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1260</v>
+        <v>11644</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1257.1</v>
+        <v>11620</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -3338,14 +3338,14 @@
         </is>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>33.3</v>
+        <v>43.6</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1195.8571</v>
+        <v>11221</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3372,17 +3372,17 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>4.87</v>
+        <v>3.43</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-5.09</v>
+        <v>-3.63</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1348.37</v>
+        <v>12467.93</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NAUKRI-20260909-930931</t>
+          <t>IND-R2-OFSS-20260909-1e09a0</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>19.11</v>
+        <v>1260</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>19.02</v>
+        <v>1257.1</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -3439,14 +3439,14 @@
         </is>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.47</v>
+        <v>-0.23</v>
       </c>
       <c r="L35" s="4" t="n">
         <v>33.3</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>18.43</v>
+        <v>1195.8571</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>3.1</v>
+        <v>4.87</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-3.56</v>
+        <v>-5.09</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>20.21</v>
+        <v>1348.37</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260909-153c95</t>
+          <t>IND-R2-NAUKRI-20260909-930931</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1949</v>
+        <v>19.11</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1933</v>
+        <v>19.02</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -3540,14 +3540,14 @@
         </is>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.82</v>
+        <v>-0.47</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>40.6</v>
+        <v>33.3</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>1891.4857</v>
+        <v>18.43</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3574,22 +3574,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-2.95</v>
+        <v>-3.56</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>2054.6</v>
+        <v>20.21</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IPCALAB-20260909-af9aea</t>
+          <t>IND-R2-IRB-20260909-153c95</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>315.55</v>
+        <v>1949</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>312.75</v>
+        <v>1933</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -3641,14 +3641,14 @@
         </is>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.89</v>
+        <v>-0.82</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>31.2</v>
+        <v>40.6</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>303.0643</v>
+        <v>1891.4857</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3675,22 +3675,22 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-3.96</v>
+        <v>-2.95</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>329.25</v>
+        <v>2054.6</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RECLTD-20260909-84e6d1</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>172.76</v>
+        <v>315.55</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>171.2</v>
+        <v>312.75</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.9</v>
+        <v>-0.89</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>30.1</v>
+        <v>31.2</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>165.6072</v>
+        <v>303.0643</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3776,22 +3776,22 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-4.14</v>
+        <v>-3.96</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>184.71</v>
+        <v>329.25</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
+          <t>IND-R2-RECLTD-20260909-84e6d1</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3823,19 +3823,19 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>285</v>
+        <v>172.76</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>282.4</v>
+        <v>171.2</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -3843,14 +3843,14 @@
         </is>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.91</v>
+        <v>-0.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>35.4</v>
+        <v>30.1</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>277.2643</v>
+        <v>165.6072</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3877,22 +3877,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>1.82</v>
+        <v>3.27</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-2.71</v>
+        <v>-4.14</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>296.6</v>
+        <v>184.71</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3924,19 +3924,19 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>2410.1</v>
+        <v>285</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>2385.1</v>
+        <v>282.4</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -3944,14 +3944,14 @@
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-1.04</v>
+        <v>-0.91</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>2288.3428</v>
+        <v>277.2643</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3978,22 +3978,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>4.06</v>
+        <v>1.82</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-5.05</v>
+        <v>-2.71</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>2579.94</v>
+        <v>296.6</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GLENMARK-20260909-ef0373</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4025,19 +4025,19 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>388.4</v>
+        <v>2410.1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>382.9</v>
+        <v>2385.1</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -4045,14 +4045,14 @@
         </is>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-1.42</v>
+        <v>-1.04</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>31.2</v>
+        <v>40.6</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>376.1785</v>
+        <v>2288.3428</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4079,22 +4079,22 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>1.76</v>
+        <v>4.06</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-3.15</v>
+        <v>-5.05</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>406.73</v>
+        <v>2579.94</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
+          <t>IND-R2-GLENMARK-20260909-ef0373</t>
         </is>
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1725</v>
+        <v>388.4</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1700</v>
+        <v>382.9</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -4146,14 +4146,14 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-1.45</v>
+        <v>-1.42</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>1649.0429</v>
+        <v>376.1785</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4180,22 +4180,22 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-4.4</v>
+        <v>-3.15</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>1838.94</v>
+        <v>406.73</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
+          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4227,19 +4227,19 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>3134.7</v>
+        <v>1725</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>3087.5</v>
+        <v>1700</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -4247,14 +4247,14 @@
         </is>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-1.51</v>
+        <v>-1.45</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>11.2</v>
+        <v>31.3</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>2965.8715</v>
+        <v>1649.0429</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="S43" s="4" t="n">
-        <v>3.94</v>
+        <v>3</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-5.39</v>
+        <v>-4.4</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>3307.14</v>
+        <v>1838.94</v>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MM-20260909-3a8a06</t>
+          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>2825</v>
+        <v>3134.7</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>2778.3</v>
+        <v>3087.5</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -4348,14 +4348,14 @@
         </is>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-1.65</v>
+        <v>-1.51</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>36.1</v>
+        <v>11.2</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>2625.3002</v>
+        <v>2965.8715</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
@@ -4382,17 +4382,17 @@
         </is>
       </c>
       <c r="S44" s="4" t="n">
-        <v>5.51</v>
+        <v>3.94</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>-7.07</v>
+        <v>-5.39</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>3067.12</v>
+        <v>3307.14</v>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
+          <t>IND-R2-MM-20260909-3a8a06</t>
         </is>
       </c>
       <c r="W44" s="4" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>860.45</v>
+        <v>2825</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>844.6</v>
+        <v>2778.3</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-1.84</v>
+        <v>-1.65</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>811.05</v>
+        <v>2625.3002</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4483,22 +4483,22 @@
         </is>
       </c>
       <c r="S45" s="4" t="n">
-        <v>3.97</v>
+        <v>5.51</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>-5.74</v>
+        <v>-7.07</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>903.71</v>
+        <v>3067.12</v>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260909-3ab469</t>
+          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4530,19 +4530,19 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>400.4</v>
+        <v>860.45</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>392.3</v>
+        <v>844.6</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-2.02</v>
+        <v>-1.84</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>386.3857</v>
+        <v>811.05</v>
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
@@ -4584,22 +4584,22 @@
         </is>
       </c>
       <c r="S46" s="4" t="n">
-        <v>1.51</v>
+        <v>3.97</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>-3.5</v>
+        <v>-5.74</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>421.42</v>
+        <v>903.71</v>
       </c>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260911-098cc1</t>
+          <t>IND-R2-INDIANB-20260909-3ab469</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4631,19 +4631,19 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>12603</v>
+        <v>400.4</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>12296</v>
+        <v>392.3</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -4651,14 +4651,14 @@
         </is>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-2.44</v>
+        <v>-2.02</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>31.3</v>
+        <v>32.3</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>12048.8571</v>
+        <v>386.3857</v>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
@@ -4685,22 +4685,22 @@
         </is>
       </c>
       <c r="S47" s="4" t="n">
-        <v>2.01</v>
+        <v>1.51</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>-4.4</v>
+        <v>-3.5</v>
       </c>
       <c r="U47" s="4" t="n">
-        <v>13267.29</v>
+        <v>421.42</v>
       </c>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARUTI-20260909-c59a94</t>
+          <t>IND-R2-LICI-20260911-098cc1</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1007.2</v>
+        <v>12603</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>981.8</v>
+        <v>12296</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -4752,14 +4752,14 @@
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-2.52</v>
+        <v>-2.44</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>35</v>
+        <v>31.3</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>967.7286</v>
+        <v>12048.8571</v>
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -4786,17 +4786,17 @@
         </is>
       </c>
       <c r="S48" s="4" t="n">
-        <v>1.43</v>
+        <v>2.01</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>-3.92</v>
+        <v>-4.4</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>1050.01</v>
+        <v>13267.29</v>
       </c>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20260909-a73231</t>
+          <t>IND-R2-MARUTI-20260909-c59a94</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>6291</v>
+        <v>1007.2</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>6129.5</v>
+        <v>981.8</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -4853,14 +4853,14 @@
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-2.57</v>
+        <v>-2.52</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>5959.1429</v>
+        <v>967.7286</v>
       </c>
       <c r="R49" s="4" t="inlineStr">
         <is>
@@ -4887,22 +4887,22 @@
         </is>
       </c>
       <c r="S49" s="4" t="n">
-        <v>2.78</v>
+        <v>1.43</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>-5.28</v>
+        <v>-3.92</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>6638.36</v>
+        <v>1050.01</v>
       </c>
       <c r="V49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260909-2f64b0</t>
+          <t>IND-R2-SBIN-20260909-a73231</t>
         </is>
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>500</v>
+        <v>6291</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>484.7</v>
+        <v>6129.5</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -4954,14 +4954,14 @@
         </is>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-3.06</v>
+        <v>-2.57</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>35.4</v>
+        <v>33.3</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>482.9429</v>
+        <v>5959.1429</v>
       </c>
       <c r="R50" s="4" t="inlineStr">
         <is>
@@ -4988,17 +4988,17 @@
         </is>
       </c>
       <c r="S50" s="4" t="n">
-        <v>0.36</v>
+        <v>2.78</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>-3.41</v>
+        <v>-5.28</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>530.45</v>
+        <v>6638.36</v>
       </c>
       <c r="V50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260909-82436d</t>
+          <t>IND-R2-ATUL-20260909-2f64b0</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -5035,19 +5035,19 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-14</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>412.55</v>
+        <v>500</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>399.8</v>
+        <v>484.7</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -5055,14 +5055,14 @@
         </is>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-3.09</v>
+        <v>-3.06</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>37</v>
+        <v>35.4</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5081,7 +5081,7 @@
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>391.6786</v>
+        <v>482.9429</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -5089,22 +5089,22 @@
         </is>
       </c>
       <c r="S51" s="4" t="n">
-        <v>2.03</v>
+        <v>0.36</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>-5.06</v>
+        <v>-3.41</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>435.12</v>
+        <v>530.45</v>
       </c>
       <c r="V51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
+          <t>IND-R2-OIL-20260909-82436d</t>
         </is>
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -5136,19 +5136,19 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-14</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>434.2</v>
+        <v>412.55</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>420.75</v>
+        <v>399.8</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -5156,14 +5156,14 @@
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-3.1</v>
+        <v>-3.09</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>33.3</v>
+        <v>37</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>417.55</v>
+        <v>391.6786</v>
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
@@ -5190,22 +5190,22 @@
         </is>
       </c>
       <c r="S52" s="4" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>-3.83</v>
+        <v>-5.06</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>456.13</v>
+        <v>435.12</v>
       </c>
       <c r="V52" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260909-3c298a</t>
+          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
         </is>
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -5237,19 +5237,19 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>233.86</v>
+        <v>434.2</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>226.4</v>
+        <v>420.75</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -5257,16 +5257,14 @@
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-3.19</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-3.1</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5285,7 +5283,7 @@
         </is>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>220.1271</v>
+        <v>417.55</v>
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
@@ -5293,22 +5291,22 @@
         </is>
       </c>
       <c r="S53" s="4" t="n">
-        <v>2.77</v>
+        <v>0.76</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>-5.87</v>
+        <v>-3.83</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>244.86</v>
+        <v>456.13</v>
       </c>
       <c r="V53" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
+          <t>IND-R2-COALINDIA-20260909-3c298a</t>
         </is>
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5318,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -5340,19 +5338,19 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>154.28</v>
+        <v>233.86</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>148.23</v>
+        <v>226.4</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -5360,14 +5358,16 @@
         </is>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-3.92</v>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v>33.3</v>
+        <v>-3.19</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>145.5286</v>
+        <v>220.1271</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
@@ -5394,22 +5394,22 @@
         </is>
       </c>
       <c r="S54" s="4" t="n">
-        <v>1.82</v>
+        <v>2.77</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>-5.67</v>
+        <v>-5.87</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>163.68</v>
+        <v>244.86</v>
       </c>
       <c r="V54" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20260909-938c43</t>
+          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
         </is>
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -5441,19 +5441,19 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>117.05</v>
+        <v>154.28</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>111.85</v>
+        <v>148.23</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -5461,16 +5461,14 @@
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-3.92</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5489,7 +5487,7 @@
         </is>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>109.1857</v>
+        <v>145.5286</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5497,22 +5495,22 @@
         </is>
       </c>
       <c r="S55" s="4" t="n">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>-6.72</v>
+        <v>-5.67</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>121.93</v>
+        <v>163.68</v>
       </c>
       <c r="V55" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260908-d0ae28</t>
+          <t>IND-R2-IGL-20260909-938c43</t>
         </is>
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5522,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -5544,19 +5542,19 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>273.3</v>
+        <v>117.05</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>258.6</v>
+        <v>111.85</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -5564,14 +5562,16 @@
         </is>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="L56" s="4" t="n">
-        <v>28.4</v>
+        <v>-4.44</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>255.3143</v>
+        <v>109.1857</v>
       </c>
       <c r="R56" s="4" t="inlineStr">
         <is>
@@ -5598,22 +5598,22 @@
         </is>
       </c>
       <c r="S56" s="4" t="n">
-        <v>1.27</v>
+        <v>2.38</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>-6.58</v>
+        <v>-6.72</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>289.39</v>
+        <v>121.93</v>
       </c>
       <c r="V56" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
+          <t>IND-R2-IEX-20260908-d0ae28</t>
         </is>
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>275</v>
+        <v>273.3</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>255.2</v>
+        <v>258.6</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -5665,14 +5665,14 @@
         </is>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-7.2</v>
+        <v>-5.38</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>35.4</v>
+        <v>28.4</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>245.8929</v>
+        <v>255.3143</v>
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
@@ -5699,22 +5699,22 @@
         </is>
       </c>
       <c r="S57" s="4" t="n">
-        <v>3.65</v>
+        <v>1.27</v>
       </c>
       <c r="T57" s="4" t="n">
-        <v>-10.58</v>
+        <v>-6.58</v>
       </c>
       <c r="U57" s="4" t="n">
-        <v>296.13</v>
+        <v>289.39</v>
       </c>
       <c r="V57" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260909-bbba1f</t>
+          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
         </is>
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>187.94</v>
+        <v>275</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>174.2</v>
+        <v>255.2</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-7.31</v>
+        <v>-7.2</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>169.1236</v>
+        <v>245.8929</v>
       </c>
       <c r="R58" s="4" t="inlineStr">
         <is>
@@ -5800,17 +5800,17 @@
         </is>
       </c>
       <c r="S58" s="4" t="n">
-        <v>2.91</v>
+        <v>3.65</v>
       </c>
       <c r="T58" s="4" t="n">
-        <v>-10.01</v>
+        <v>-10.58</v>
       </c>
       <c r="U58" s="4" t="n">
-        <v>206.77</v>
+        <v>296.13</v>
       </c>
       <c r="V58" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260909-29ffd5</t>
+          <t>IND-R2-VEDL-20260909-bbba1f</t>
         </is>
       </c>
       <c r="W58" s="4" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>3365.2</v>
+        <v>187.94</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3115</v>
+        <v>174.2</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -5867,14 +5867,14 @@
         </is>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-7.43</v>
+        <v>-7.31</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>3085.7715</v>
+        <v>169.1236</v>
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
@@ -5901,22 +5901,22 @@
         </is>
       </c>
       <c r="S59" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.91</v>
       </c>
       <c r="T59" s="4" t="n">
-        <v>-8.300000000000001</v>
+        <v>-10.01</v>
       </c>
       <c r="U59" s="4" t="n">
-        <v>3608.33</v>
+        <v>206.77</v>
       </c>
       <c r="V59" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MCX-20260909-1bc45f</t>
+          <t>IND-R2-SAIL-20260909-29ffd5</t>
         </is>
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -5957,10 +5957,10 @@
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>385.3</v>
+        <v>3365.2</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>356.15</v>
+        <v>3115</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -5968,14 +5968,14 @@
         </is>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-7.57</v>
+        <v>-7.43</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>335.0214</v>
+        <v>3085.7715</v>
       </c>
       <c r="R60" s="4" t="inlineStr">
         <is>
@@ -6002,22 +6002,22 @@
         </is>
       </c>
       <c r="S60" s="4" t="n">
-        <v>5.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="T60" s="4" t="n">
-        <v>-13.05</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>412.84</v>
+        <v>3608.33</v>
       </c>
       <c r="V60" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
+          <t>IND-R2-MCX-20260909-1bc45f</t>
         </is>
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -6044,41 +6044,39 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>397</v>
+        <v>385.3</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>413.1</v>
+        <v>356.15</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K61" s="5" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+      <c r="K61" s="6" t="n">
+        <v>-7.57</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6097,7 +6095,7 @@
         </is>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>386.4571</v>
+        <v>335.0214</v>
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
@@ -6105,24 +6103,22 @@
         </is>
       </c>
       <c r="S61" s="4" t="n">
-        <v>6.45</v>
+        <v>5.93</v>
       </c>
       <c r="T61" s="4" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="U61" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-13.05</v>
+      </c>
+      <c r="U61" s="4" t="n">
+        <v>412.84</v>
       </c>
       <c r="V61" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
         </is>
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6130,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -6154,19 +6150,19 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-05</t>
+          <t>Admitted 2026-08-04</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>417.6</v>
+        <v>397</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>420.75</v>
+        <v>413.1</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -6174,7 +6170,7 @@
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0.75</v>
+        <v>4.06</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -6183,7 +6179,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -6202,7 +6198,7 @@
         </is>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>407.3714</v>
+        <v>386.4571</v>
       </c>
       <c r="R62" s="4" t="inlineStr">
         <is>
@@ -6210,17 +6206,19 @@
         </is>
       </c>
       <c r="S62" s="4" t="n">
-        <v>3.18</v>
+        <v>6.45</v>
       </c>
       <c r="T62" s="4" t="n">
-        <v>-2.45</v>
-      </c>
-      <c r="U62" s="4" t="n">
-        <v>432.94</v>
+        <v>-2.66</v>
+      </c>
+      <c r="U62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V62" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
       <c r="W62" s="4" t="inlineStr">
@@ -6237,7 +6235,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -6257,27 +6255,27 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-08-05</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>389.85</v>
+        <v>417.6</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>389.35</v>
+        <v>420.75</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K63" s="6" t="n">
-        <v>-0.13</v>
+      <c r="K63" s="5" t="n">
+        <v>0.75</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6286,7 +6284,7 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -6305,7 +6303,7 @@
         </is>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>378.3286</v>
+        <v>407.3714</v>
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
@@ -6313,17 +6311,17 @@
         </is>
       </c>
       <c r="S63" s="4" t="n">
-        <v>2.83</v>
+        <v>3.18</v>
       </c>
       <c r="T63" s="4" t="n">
-        <v>-2.96</v>
+        <v>-2.45</v>
       </c>
       <c r="U63" s="4" t="n">
-        <v>407.13</v>
+        <v>432.94</v>
       </c>
       <c r="V63" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
         </is>
       </c>
       <c r="W63" s="4" t="inlineStr">
@@ -6340,7 +6338,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -6360,19 +6358,19 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-28</t>
+          <t>Admitted 2026-08-04</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>187.46</v>
+        <v>389.85</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>184.35</v>
+        <v>389.35</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
@@ -6380,7 +6378,7 @@
         </is>
       </c>
       <c r="K64" s="6" t="n">
-        <v>-1.66</v>
+        <v>-0.13</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -6389,7 +6387,7 @@
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -6408,7 +6406,7 @@
         </is>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>181.8114</v>
+        <v>378.3286</v>
       </c>
       <c r="R64" s="4" t="inlineStr">
         <is>
@@ -6416,17 +6414,17 @@
         </is>
       </c>
       <c r="S64" s="4" t="n">
-        <v>1.38</v>
+        <v>2.83</v>
       </c>
       <c r="T64" s="4" t="n">
-        <v>-3.01</v>
+        <v>-2.96</v>
       </c>
       <c r="U64" s="4" t="n">
-        <v>195.93</v>
+        <v>407.13</v>
       </c>
       <c r="V64" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
         </is>
       </c>
       <c r="W64" s="4" t="inlineStr">
@@ -6443,223 +6441,325 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-28</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>187.46</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>184.35</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="n">
+        <v>181.8114</v>
+      </c>
+      <c r="R65" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S65" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T65" s="4" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="U65" s="4" t="n">
+        <v>195.93</v>
+      </c>
+      <c r="V65" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+        </is>
+      </c>
+      <c r="W65" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
           <t>ONGC</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-11</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="H66" s="4" t="n">
         <v>239.45</v>
       </c>
-      <c r="I65" s="4" t="n">
+      <c r="I66" s="4" t="n">
         <v>235.03</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K65" s="6" t="n">
+      <c r="K66" s="6" t="n">
         <v>-1.85</v>
       </c>
-      <c r="L65" s="4" t="inlineStr">
+      <c r="L66" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M65" s="4" t="inlineStr">
+      <c r="M66" s="4" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="N65" s="4" t="inlineStr">
+      <c r="N66" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O65" s="4" t="inlineStr">
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P65" s="4" t="inlineStr">
+      <c r="P66" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q65" s="4" t="n">
+      <c r="Q66" s="4" t="n">
         <v>232.2186</v>
       </c>
-      <c r="R65" s="4" t="inlineStr">
+      <c r="R66" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S65" s="4" t="n">
+      <c r="S66" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="T65" s="4" t="n">
+      <c r="T66" s="4" t="n">
         <v>-3.02</v>
       </c>
-      <c r="U65" s="4" t="n">
+      <c r="U66" s="4" t="n">
         <v>250.3</v>
       </c>
-      <c r="V65" s="4" t="inlineStr">
+      <c r="V66" s="4" t="inlineStr">
         <is>
           <t>IND-R1-ONGC-20260811-326ea2</t>
         </is>
       </c>
-      <c r="W65" s="4" t="inlineStr">
+      <c r="W66" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A68:W68"/>
     <mergeCell ref="A77:W77"/>
     <mergeCell ref="A83:W83"/>
     <mergeCell ref="A82:W82"/>
@@ -6677,6 +6777,7 @@
     <mergeCell ref="A3:W3"/>
     <mergeCell ref="A71:W71"/>
     <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A85:W85"/>
     <mergeCell ref="A76:W76"/>
     <mergeCell ref="A5:W5"/>
     <mergeCell ref="A4:W4"/>
@@ -6941,7 +7042,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-09-15 ·</t>
+          <t>Stop-loss triggered</t>
         </is>
       </c>
       <c r="M6" s="4" t="n">
@@ -7013,7 +7114,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-09-16 ·</t>
+          <t>Stop-loss triggered</t>
         </is>
       </c>
       <c r="M7" s="4" t="n">
@@ -7233,7 +7334,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-09-16 ·</t>
+          <t>Stop-loss triggered</t>
         </is>
       </c>
       <c r="M10" s="4" t="n">

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W85"/>
+  <dimension ref="A1:W86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,21 +508,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-16 · prices = 2026-09-16 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-09-17 · prices = 2026-09-16 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>59 investable · NEW 8 · ACTIVE+ 51 · ACTIVE 0   ·   R2 54 · MOMENTUM 0 · R1 5 (advisory)   ·   8 row(s) read 0.00%: admitted at the 2026-09-16 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>60 investable · NEW 1 · ACTIVE+ 59 · ACTIVE 0   ·   R2 55 · MOMENTUM 0 · R1 5 (advisory)   ·   8 row(s) read 0.00%: admitted at the 2026-09-16 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 59 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.14% from entry, worst single -13.05%</t>
+          <t>🛡 DOWNSIDE · 60 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.16% from entry, worst single -13.05%</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=8 · 228 scored · 57 already in CURRENT · biggest blocker: model disagreement (161) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=1 · 228 scored · 58 already in CURRENT · biggest blocker: model disagreement (162) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 57 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 55 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>AARTIIND</t>
+          <t>BALKRISIND</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -697,14 +697,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>468.8</v>
+        <v>2128.8</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>468.8</v>
+        <v>2128.8</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -715,11 +715,11 @@
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>31.1</v>
+        <v>35.2</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>443.3714</v>
+        <v>2016.4429</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,22 +746,22 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>5.42</v>
+        <v>5.28</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-5.42</v>
+        <v>-5.28</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>506.94</v>
+        <v>2297.34</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AARTIIND-20260916-4cc858</t>
+          <t>IND-R2-BALKRISIND-20260917-29543a</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -793,34 +793,34 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>339.55</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>407.75</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>407.75</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
+      <c r="K9" s="5" t="n">
+        <v>3.83</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>390.4</v>
+        <v>339.7714</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>4.26</v>
+        <v>3.62</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-4.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>436.95</v>
+        <v>353.62</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
+          <t>IND-R2-PATANJALI-20260909-508e75</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -894,34 +894,34 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>373.25</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>386.1</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>133.9</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>133.9</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
+      <c r="K10" s="5" t="n">
+        <v>3.44</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>28.7</v>
+        <v>28.4</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>129.8171</v>
+        <v>374.1643</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.05</v>
+        <v>0.24</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>140.02</v>
+        <v>389.48</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IOC-20260916-b0f93c</t>
+          <t>IND-R2-DABUR-20260911-8f250f</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -995,30 +995,30 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>694.35</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>716.25</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>321.75</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>321.75</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
+      <c r="K11" s="5" t="n">
+        <v>3.15</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>33.2</v>
+        <v>34.8</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>306.2946</v>
+        <v>688.1929</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1049,22 +1049,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.8</v>
+        <v>3.92</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-4.8</v>
+        <v>-0.89</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>352.66</v>
+        <v>729</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MANAPPURAM-20260916-6576e5</t>
+          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1096,34 +1096,34 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>25455</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>26140</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>1065.9</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>1065.9</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
+      <c r="K12" s="5" t="n">
+        <v>2.69</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>29.1</v>
+        <v>31.3</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1023.6857</v>
+        <v>25235</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>3.96</v>
+        <v>3.46</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.96</v>
+        <v>-0.86</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1129.22</v>
+        <v>26635.71</v>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MGL-20260916-149e8e</t>
+          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1197,34 +1197,34 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1038.3</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>1065.3</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>80.52</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>80.52</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
+      <c r="K13" s="5" t="n">
+        <v>2.6</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>31.2</v>
+        <v>38.3</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>77.14570000000001</v>
+        <v>1014.9714</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1251,22 +1251,22 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>4.19</v>
+        <v>4.72</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-4.19</v>
+        <v>-2.25</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>85.58</v>
+        <v>1120.78</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NMDC-20260916-75297f</t>
+          <t>IND-R2-INFY-20260909-f2b7ad</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1298,34 +1298,34 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>292.9</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>296.35</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>3389.4</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>3389.4</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
+      <c r="K14" s="5" t="n">
+        <v>1.18</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>31.1</v>
+        <v>34.3</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3235.2428</v>
+        <v>283.3839</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.55</v>
+        <v>4.38</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-4.55</v>
+        <v>-3.25</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3620.64</v>
+        <v>315.92</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATAELXSI-20260916-69ea7c</t>
+          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1399,34 +1399,34 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1952</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>1974</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>177.94</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>177.94</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
+      <c r="K15" s="5" t="n">
+        <v>1.13</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>30.1</v>
+        <v>31.2</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>170.5643</v>
+        <v>1926.3857</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.15</v>
+        <v>2.41</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-4.15</v>
+        <v>-1.31</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>189</v>
+        <v>2020.51</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20260916-d5e59d</t>
+          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1500,19 +1500,19 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>339.55</v>
+        <v>8128.5</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>352.55</v>
+        <v>8217</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1520,14 +1520,14 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>3.83</v>
+        <v>1.09</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>32.3</v>
+        <v>38.7</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>339.7714</v>
+        <v>7841.2143</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.62</v>
+        <v>4.57</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-3.53</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>353.62</v>
+        <v>8660.25</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PATANJALI-20260909-508e75</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1601,19 +1601,19 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>373.25</v>
+        <v>5163.5</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>386.1</v>
+        <v>5209.5</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1621,14 +1621,14 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>3.44</v>
+        <v>0.89</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>28.4</v>
+        <v>31.3</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>374.1643</v>
+        <v>5048.2143</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.24</v>
+        <v>-2.23</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>389.48</v>
+        <v>5385.18</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DABUR-20260911-8f250f</t>
+          <t>IND-R2-ALKEM-20260909-517913</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>694.35</v>
+        <v>409.8</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>716.25</v>
+        <v>413.1</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>3.15</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>34.8</v>
+        <v>34.1</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>688.1929</v>
+        <v>401.05</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.92</v>
+        <v>2.92</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.89</v>
+        <v>-2.14</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>729</v>
+        <v>432.43</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HDFCBANK-20260909-6b0b7e</t>
+          <t>IND-R2-KOTAKBANK-20260915-bbcfac</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1803,19 +1803,19 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>25455</v>
+        <v>1350.1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>26140</v>
+        <v>1358.9</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>2.69</v>
+        <v>0.65</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>31.3</v>
+        <v>33.3</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>25235</v>
+        <v>1321.3286</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1857,22 +1857,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>3.46</v>
+        <v>2.76</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.86</v>
+        <v>-2.13</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>26635.71</v>
+        <v>1401.85</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
+          <t>IND-R2-CIPLA-20260911-5f4a49</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1038.3</v>
+        <v>2197.4</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1065.3</v>
+        <v>2211.4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>2.6</v>
+        <v>0.64</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>38.3</v>
+        <v>37.1</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1014.9714</v>
+        <v>2142.5</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>4.72</v>
+        <v>3.12</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.25</v>
+        <v>-2.5</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1120.78</v>
+        <v>2341.29</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260909-f2b7ad</t>
+          <t>IND-R2-TCS-20260909-fb0a7f</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2005,19 +2005,19 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>292.9</v>
+        <v>122.37</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>296.35</v>
+        <v>122.94</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>1.18</v>
+        <v>0.47</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>34.3</v>
+        <v>30.2</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>283.3839</v>
+        <v>118.8757</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.38</v>
+        <v>3.31</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.25</v>
+        <v>-2.86</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>315.92</v>
+        <v>128.89</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20260909-43aaa1</t>
+          <t>IND-R2-CANBK-20260915-4a780b</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1952</v>
+        <v>1244.4</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1974</v>
+        <v>1246.4</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -2126,14 +2126,14 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1.13</v>
+        <v>0.16</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>31.2</v>
+        <v>32.9</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1926.3857</v>
+        <v>1205.9572</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2160,22 +2160,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.41</v>
+        <v>3.24</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.31</v>
+        <v>-3.09</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2020.51</v>
+        <v>1294.16</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDUNILVR-20260909-fdf984</t>
+          <t>IND-R2-AXISBANK-20260909-3abb74</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>AARTIIND</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2207,34 +2207,34 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>8128.5</v>
+        <v>468.8</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8217</v>
+        <v>468.8</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K23" s="5" t="n">
-        <v>1.09</v>
+      <c r="K23" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>38.7</v>
+        <v>31.1</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>7841.2143</v>
+        <v>443.3714</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2261,22 +2261,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>4.57</v>
+        <v>5.42</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-3.53</v>
+        <v>-5.42</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>8660.25</v>
+        <v>506.94</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-AARTIIND-20260916-4cc858</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2308,34 +2308,34 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5163.5</v>
+        <v>407.75</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5209.5</v>
+        <v>407.75</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K24" s="5" t="n">
-        <v>0.89</v>
+      <c r="K24" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>31.3</v>
+        <v>33.3</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5048.2143</v>
+        <v>390.4</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2362,22 +2362,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-2.23</v>
+        <v>-4.26</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>5385.18</v>
+        <v>436.95</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ALKEM-20260909-517913</t>
+          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2409,34 +2409,34 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>409.8</v>
+        <v>133.9</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>413.1</v>
+        <v>133.9</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K25" s="5" t="n">
-        <v>0.8100000000000001</v>
+      <c r="K25" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>34.1</v>
+        <v>28.7</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>401.05</v>
+        <v>129.8171</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2463,22 +2463,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-2.14</v>
+        <v>-3.05</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>432.43</v>
+        <v>140.02</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260915-bbcfac</t>
+          <t>IND-R2-IOC-20260916-b0f93c</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2510,34 +2510,34 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1350.1</v>
+        <v>321.75</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1358.9</v>
+        <v>321.75</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K26" s="5" t="n">
-        <v>0.65</v>
+      <c r="K26" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1321.3286</v>
+        <v>306.2946</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2564,22 +2564,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.76</v>
+        <v>4.8</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-2.13</v>
+        <v>-4.8</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1401.85</v>
+        <v>352.66</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CIPLA-20260911-5f4a49</t>
+          <t>IND-R2-MANAPPURAM-20260916-6576e5</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2611,34 +2611,34 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2197.4</v>
+        <v>1065.9</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2211.4</v>
+        <v>1065.9</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K27" s="5" t="n">
-        <v>0.64</v>
+      <c r="K27" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>37.1</v>
+        <v>29.1</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2142.5</v>
+        <v>1023.6857</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>3.12</v>
+        <v>3.96</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.5</v>
+        <v>-3.96</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2341.29</v>
+        <v>1129.22</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260909-fb0a7f</t>
+          <t>IND-R2-MGL-20260916-149e8e</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2712,34 +2712,34 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>122.37</v>
+        <v>80.52</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>122.94</v>
+        <v>80.52</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K28" s="5" t="n">
-        <v>0.47</v>
+      <c r="K28" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>30.2</v>
+        <v>31.2</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>118.8757</v>
+        <v>77.14570000000001</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.31</v>
+        <v>4.19</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-2.86</v>
+        <v>-4.19</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>128.89</v>
+        <v>85.58</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260915-4a780b</t>
+          <t>IND-R2-NMDC-20260916-75297f</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2813,34 +2813,34 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1244.4</v>
+        <v>3389.4</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1246.4</v>
+        <v>3389.4</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K29" s="5" t="n">
-        <v>0.16</v>
+      <c r="K29" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>32.9</v>
+        <v>31.1</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1205.9572</v>
+        <v>3235.2428</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2867,22 +2867,22 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.24</v>
+        <v>4.55</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-3.09</v>
+        <v>-4.55</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1294.16</v>
+        <v>3620.64</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AXISBANK-20260909-3abb74</t>
+          <t>IND-R2-TATAELXSI-20260916-69ea7c</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2914,34 +2914,34 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>818.3</v>
+        <v>177.94</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>818.1</v>
+        <v>177.94</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K30" s="6" t="n">
-        <v>-0.02</v>
+      <c r="K30" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>31.2</v>
+        <v>30.1</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>788.0929</v>
+        <v>170.5643</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.67</v>
+        <v>4.15</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.69</v>
+        <v>-4.15</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>866.9299999999999</v>
+        <v>189</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
+          <t>IND-R2-UNIONBANK-20260916-d5e59d</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>370</v>
+        <v>818.3</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>369.8</v>
+        <v>818.1</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -3035,14 +3035,14 @@
         </is>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="L31" s="4" t="n">
         <v>31.2</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>352.9</v>
+        <v>788.0929</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3069,22 +3069,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>4.57</v>
+        <v>3.67</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-4.62</v>
+        <v>-3.69</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>397.71</v>
+        <v>866.9299999999999</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
+          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3116,19 +3116,19 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>464.25</v>
+        <v>370</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>464</v>
+        <v>369.8</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>440.6143</v>
+        <v>352.9</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3170,22 +3170,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>5.04</v>
+        <v>4.57</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-5.09</v>
+        <v>-4.62</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>499.7</v>
+        <v>397.71</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-EMAMILTD-20260909-0f7729</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3217,19 +3217,19 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1232</v>
+        <v>464.25</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1229.4</v>
+        <v>464</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -3237,14 +3237,14 @@
         </is>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>28.3</v>
+        <v>31.2</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>1199.9714</v>
+        <v>440.6143</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3271,22 +3271,22 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>2.39</v>
+        <v>5.04</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-2.6</v>
+        <v>-5.09</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1280.04</v>
+        <v>499.7</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ACC-20260911-3a092f</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3318,19 +3318,19 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>11644</v>
+        <v>1232</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11620</v>
+        <v>1229.4</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -3341,11 +3341,11 @@
         <v>-0.21</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>43.6</v>
+        <v>28.3</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>11221</v>
+        <v>1199.9714</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3372,22 +3372,22 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>3.43</v>
+        <v>2.39</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-3.63</v>
+        <v>-2.6</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>12467.93</v>
+        <v>1280.04</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260909-1e09a0</t>
+          <t>IND-R2-ACC-20260911-3a092f</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1260</v>
+        <v>11644</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1257.1</v>
+        <v>11620</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -3439,14 +3439,14 @@
         </is>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>33.3</v>
+        <v>43.6</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>1195.8571</v>
+        <v>11221</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>4.87</v>
+        <v>3.43</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-5.09</v>
+        <v>-3.63</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1348.37</v>
+        <v>12467.93</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NAUKRI-20260909-930931</t>
+          <t>IND-R2-OFSS-20260909-1e09a0</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>19.11</v>
+        <v>1260</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>19.02</v>
+        <v>1257.1</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -3540,14 +3540,14 @@
         </is>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.47</v>
+        <v>-0.23</v>
       </c>
       <c r="L36" s="4" t="n">
         <v>33.3</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>18.43</v>
+        <v>1195.8571</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3574,22 +3574,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>3.1</v>
+        <v>4.87</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-3.56</v>
+        <v>-5.09</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>20.21</v>
+        <v>1348.37</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260909-153c95</t>
+          <t>IND-R2-NAUKRI-20260909-930931</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1949</v>
+        <v>19.11</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>1933</v>
+        <v>19.02</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -3641,14 +3641,14 @@
         </is>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.82</v>
+        <v>-0.47</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>40.6</v>
+        <v>33.3</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>1891.4857</v>
+        <v>18.43</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3675,22 +3675,22 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-2.95</v>
+        <v>-3.56</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>2054.6</v>
+        <v>20.21</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IPCALAB-20260909-af9aea</t>
+          <t>IND-R2-IRB-20260909-153c95</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>315.55</v>
+        <v>1949</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>312.75</v>
+        <v>1933</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -3742,14 +3742,14 @@
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.89</v>
+        <v>-0.82</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>31.2</v>
+        <v>40.6</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>303.0643</v>
+        <v>1891.4857</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3776,22 +3776,22 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-3.96</v>
+        <v>-2.95</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>329.25</v>
+        <v>2054.6</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RECLTD-20260909-84e6d1</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>172.76</v>
+        <v>315.55</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>171.2</v>
+        <v>312.75</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.9</v>
+        <v>-0.89</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>30.1</v>
+        <v>31.2</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>165.6072</v>
+        <v>303.0643</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3877,22 +3877,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-4.14</v>
+        <v>-3.96</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>184.71</v>
+        <v>329.25</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
+          <t>IND-R2-RECLTD-20260909-84e6d1</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3924,19 +3924,19 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>285</v>
+        <v>172.76</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>282.4</v>
+        <v>171.2</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -3944,14 +3944,14 @@
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.91</v>
+        <v>-0.9</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>35.4</v>
+        <v>30.1</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>277.2643</v>
+        <v>165.6072</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3978,22 +3978,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>1.82</v>
+        <v>3.27</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-2.71</v>
+        <v>-4.14</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>296.6</v>
+        <v>184.71</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4025,19 +4025,19 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>2410.1</v>
+        <v>285</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>2385.1</v>
+        <v>282.4</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -4045,14 +4045,14 @@
         </is>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-1.04</v>
+        <v>-0.91</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>2288.3428</v>
+        <v>277.2643</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4079,22 +4079,22 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>4.06</v>
+        <v>1.82</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-5.05</v>
+        <v>-2.71</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>2579.94</v>
+        <v>296.6</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GLENMARK-20260909-ef0373</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4126,19 +4126,19 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>388.4</v>
+        <v>2410.1</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>382.9</v>
+        <v>2385.1</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -4146,14 +4146,14 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-1.42</v>
+        <v>-1.04</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>31.2</v>
+        <v>40.6</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>376.1785</v>
+        <v>2288.3428</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4180,22 +4180,22 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>1.76</v>
+        <v>4.06</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-3.15</v>
+        <v>-5.05</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>406.73</v>
+        <v>2579.94</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
+          <t>IND-R2-GLENMARK-20260909-ef0373</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1725</v>
+        <v>388.4</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>1700</v>
+        <v>382.9</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -4247,14 +4247,14 @@
         </is>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-1.45</v>
+        <v>-1.42</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>1649.0429</v>
+        <v>376.1785</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="S43" s="4" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-4.4</v>
+        <v>-3.15</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>1838.94</v>
+        <v>406.73</v>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
+          <t>IND-R2-AMBUJACEM-20260911-d69e22</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4328,19 +4328,19 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>3134.7</v>
+        <v>1725</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>3087.5</v>
+        <v>1700</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -4348,14 +4348,14 @@
         </is>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-1.51</v>
+        <v>-1.45</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>11.2</v>
+        <v>31.3</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>2965.8715</v>
+        <v>1649.0429</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
@@ -4382,22 +4382,22 @@
         </is>
       </c>
       <c r="S44" s="4" t="n">
-        <v>3.94</v>
+        <v>3</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>-5.39</v>
+        <v>-4.4</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>3307.14</v>
+        <v>1838.94</v>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MM-20260909-3a8a06</t>
+          <t>IND-R2-OBEROIRLTY-20260911-9b84ec</t>
         </is>
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>2825</v>
+        <v>3134.7</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>2778.3</v>
+        <v>3087.5</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -4449,14 +4449,14 @@
         </is>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-1.65</v>
+        <v>-1.51</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>36.1</v>
+        <v>11.2</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>2625.3002</v>
+        <v>2965.8715</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4483,22 +4483,22 @@
         </is>
       </c>
       <c r="S45" s="4" t="n">
-        <v>5.51</v>
+        <v>3.94</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>-7.07</v>
+        <v>-5.39</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>3067.12</v>
+        <v>3307.14</v>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
+          <t>IND-R2-MM-20260909-3a8a06</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4539,10 +4539,10 @@
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>860.45</v>
+        <v>2825</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>844.6</v>
+        <v>2778.3</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-1.84</v>
+        <v>-1.65</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>811.05</v>
+        <v>2625.3002</v>
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
@@ -4584,22 +4584,22 @@
         </is>
       </c>
       <c r="S46" s="4" t="n">
-        <v>3.97</v>
+        <v>5.51</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>-5.74</v>
+        <v>-7.07</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>903.71</v>
+        <v>3067.12</v>
       </c>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260909-3ab469</t>
+          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4631,19 +4631,19 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>400.4</v>
+        <v>860.45</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>392.3</v>
+        <v>844.6</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-2.02</v>
+        <v>-1.84</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>386.3857</v>
+        <v>811.05</v>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
@@ -4685,22 +4685,22 @@
         </is>
       </c>
       <c r="S47" s="4" t="n">
-        <v>1.51</v>
+        <v>3.97</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>-3.5</v>
+        <v>-5.74</v>
       </c>
       <c r="U47" s="4" t="n">
-        <v>421.42</v>
+        <v>903.71</v>
       </c>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260911-098cc1</t>
+          <t>IND-R2-INDIANB-20260909-3ab469</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4732,19 +4732,19 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>12603</v>
+        <v>400.4</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>12296</v>
+        <v>392.3</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -4752,14 +4752,14 @@
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-2.44</v>
+        <v>-2.02</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>31.3</v>
+        <v>32.3</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>12048.8571</v>
+        <v>386.3857</v>
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -4786,22 +4786,22 @@
         </is>
       </c>
       <c r="S48" s="4" t="n">
-        <v>2.01</v>
+        <v>1.51</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>-4.4</v>
+        <v>-3.5</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>13267.29</v>
+        <v>421.42</v>
       </c>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARUTI-20260909-c59a94</t>
+          <t>IND-R2-LICI-20260911-098cc1</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>1007.2</v>
+        <v>12603</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>981.8</v>
+        <v>12296</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -4853,14 +4853,14 @@
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-2.52</v>
+        <v>-2.44</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>35</v>
+        <v>31.3</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>967.7286</v>
+        <v>12048.8571</v>
       </c>
       <c r="R49" s="4" t="inlineStr">
         <is>
@@ -4887,22 +4887,22 @@
         </is>
       </c>
       <c r="S49" s="4" t="n">
-        <v>1.43</v>
+        <v>2.01</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>-3.92</v>
+        <v>-4.4</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>1050.01</v>
+        <v>13267.29</v>
       </c>
       <c r="V49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20260909-a73231</t>
+          <t>IND-R2-MARUTI-20260909-c59a94</t>
         </is>
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>6291</v>
+        <v>1007.2</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>6129.5</v>
+        <v>981.8</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -4954,14 +4954,14 @@
         </is>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-2.57</v>
+        <v>-2.52</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>5959.1429</v>
+        <v>967.7286</v>
       </c>
       <c r="R50" s="4" t="inlineStr">
         <is>
@@ -4988,22 +4988,22 @@
         </is>
       </c>
       <c r="S50" s="4" t="n">
-        <v>2.78</v>
+        <v>1.43</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>-5.28</v>
+        <v>-3.92</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>6638.36</v>
+        <v>1050.01</v>
       </c>
       <c r="V50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260909-2f64b0</t>
+          <t>IND-R2-SBIN-20260909-a73231</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>500</v>
+        <v>6291</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>484.7</v>
+        <v>6129.5</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -5055,14 +5055,14 @@
         </is>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-3.06</v>
+        <v>-2.57</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>35.4</v>
+        <v>33.3</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5081,7 +5081,7 @@
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>482.9429</v>
+        <v>5959.1429</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -5089,22 +5089,22 @@
         </is>
       </c>
       <c r="S51" s="4" t="n">
-        <v>0.36</v>
+        <v>2.78</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>-3.41</v>
+        <v>-5.28</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>530.45</v>
+        <v>6638.36</v>
       </c>
       <c r="V51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260909-82436d</t>
+          <t>IND-R2-ATUL-20260909-2f64b0</t>
         </is>
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -5136,19 +5136,19 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-14</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>412.55</v>
+        <v>500</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>399.8</v>
+        <v>484.7</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -5156,14 +5156,14 @@
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-3.09</v>
+        <v>-3.06</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>37</v>
+        <v>35.4</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>391.6786</v>
+        <v>482.9429</v>
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
@@ -5190,22 +5190,22 @@
         </is>
       </c>
       <c r="S52" s="4" t="n">
-        <v>2.03</v>
+        <v>0.36</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>-5.06</v>
+        <v>-3.41</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>435.12</v>
+        <v>530.45</v>
       </c>
       <c r="V52" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
+          <t>IND-R2-OIL-20260909-82436d</t>
         </is>
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -5237,19 +5237,19 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-14</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>434.2</v>
+        <v>412.55</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>420.75</v>
+        <v>399.8</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -5257,14 +5257,14 @@
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-3.1</v>
+        <v>-3.09</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>33.3</v>
+        <v>37</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>417.55</v>
+        <v>391.6786</v>
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
@@ -5291,22 +5291,22 @@
         </is>
       </c>
       <c r="S53" s="4" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>-3.83</v>
+        <v>-5.06</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>456.13</v>
+        <v>435.12</v>
       </c>
       <c r="V53" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260909-3c298a</t>
+          <t>IND-R2-RBLBANK-20260914-7f5a60</t>
         </is>
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -5338,19 +5338,19 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>233.86</v>
+        <v>434.2</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>226.4</v>
+        <v>420.75</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -5358,16 +5358,14 @@
         </is>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-3.19</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-3.1</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5386,7 +5384,7 @@
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>220.1271</v>
+        <v>417.55</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
@@ -5394,22 +5392,22 @@
         </is>
       </c>
       <c r="S54" s="4" t="n">
-        <v>2.77</v>
+        <v>0.76</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>-5.87</v>
+        <v>-3.83</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>244.86</v>
+        <v>456.13</v>
       </c>
       <c r="V54" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
+          <t>IND-R2-COALINDIA-20260909-3c298a</t>
         </is>
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5419,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -5441,19 +5439,19 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>154.28</v>
+        <v>233.86</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>148.23</v>
+        <v>226.4</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -5461,14 +5459,16 @@
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-3.92</v>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v>33.3</v>
+        <v>-3.19</v>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>145.5286</v>
+        <v>220.1271</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5495,22 +5495,22 @@
         </is>
       </c>
       <c r="S55" s="4" t="n">
-        <v>1.82</v>
+        <v>2.77</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>-5.67</v>
+        <v>-5.87</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>163.68</v>
+        <v>244.86</v>
       </c>
       <c r="V55" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20260909-938c43</t>
+          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
         </is>
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -5542,19 +5542,19 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>117.05</v>
+        <v>154.28</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>111.85</v>
+        <v>148.23</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -5562,16 +5562,14 @@
         </is>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-3.92</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -5590,7 +5588,7 @@
         </is>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>109.1857</v>
+        <v>145.5286</v>
       </c>
       <c r="R56" s="4" t="inlineStr">
         <is>
@@ -5598,17 +5596,17 @@
         </is>
       </c>
       <c r="S56" s="4" t="n">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>-6.72</v>
+        <v>-5.67</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>121.93</v>
+        <v>163.68</v>
       </c>
       <c r="V56" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260908-d0ae28</t>
+          <t>IND-R2-IGL-20260909-938c43</t>
         </is>
       </c>
       <c r="W56" s="4" t="inlineStr">
@@ -5625,7 +5623,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -5645,19 +5643,19 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>273.3</v>
+        <v>117.05</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>258.6</v>
+        <v>111.85</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -5665,14 +5663,16 @@
         </is>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="L57" s="4" t="n">
-        <v>28.4</v>
+        <v>-4.44</v>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>255.3143</v>
+        <v>109.1857</v>
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
@@ -5699,22 +5699,22 @@
         </is>
       </c>
       <c r="S57" s="4" t="n">
-        <v>1.27</v>
+        <v>2.38</v>
       </c>
       <c r="T57" s="4" t="n">
-        <v>-6.58</v>
+        <v>-6.72</v>
       </c>
       <c r="U57" s="4" t="n">
-        <v>289.39</v>
+        <v>121.93</v>
       </c>
       <c r="V57" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
+          <t>IND-R2-IEX-20260908-d0ae28</t>
         </is>
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>275</v>
+        <v>273.3</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>255.2</v>
+        <v>258.6</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -5766,14 +5766,14 @@
         </is>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-7.2</v>
+        <v>-5.38</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>35.4</v>
+        <v>28.4</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>245.8929</v>
+        <v>255.3143</v>
       </c>
       <c r="R58" s="4" t="inlineStr">
         <is>
@@ -5800,22 +5800,22 @@
         </is>
       </c>
       <c r="S58" s="4" t="n">
-        <v>3.65</v>
+        <v>1.27</v>
       </c>
       <c r="T58" s="4" t="n">
-        <v>-10.58</v>
+        <v>-6.58</v>
       </c>
       <c r="U58" s="4" t="n">
-        <v>296.13</v>
+        <v>289.39</v>
       </c>
       <c r="V58" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260909-bbba1f</t>
+          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
         </is>
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>187.94</v>
+        <v>275</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>174.2</v>
+        <v>255.2</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-7.31</v>
+        <v>-7.2</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>169.1236</v>
+        <v>245.8929</v>
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
@@ -5901,22 +5901,22 @@
         </is>
       </c>
       <c r="S59" s="4" t="n">
-        <v>2.91</v>
+        <v>3.65</v>
       </c>
       <c r="T59" s="4" t="n">
-        <v>-10.01</v>
+        <v>-10.58</v>
       </c>
       <c r="U59" s="4" t="n">
-        <v>206.77</v>
+        <v>296.13</v>
       </c>
       <c r="V59" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260909-29ffd5</t>
+          <t>IND-R2-VEDL-20260909-bbba1f</t>
         </is>
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -5957,10 +5957,10 @@
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>3365.2</v>
+        <v>187.94</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>3115</v>
+        <v>174.2</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -5968,14 +5968,14 @@
         </is>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-7.43</v>
+        <v>-7.31</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>3085.7715</v>
+        <v>169.1236</v>
       </c>
       <c r="R60" s="4" t="inlineStr">
         <is>
@@ -6002,22 +6002,22 @@
         </is>
       </c>
       <c r="S60" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.91</v>
       </c>
       <c r="T60" s="4" t="n">
-        <v>-8.300000000000001</v>
+        <v>-10.01</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>3608.33</v>
+        <v>206.77</v>
       </c>
       <c r="V60" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MCX-20260909-1bc45f</t>
+          <t>IND-R2-SAIL-20260909-29ffd5</t>
         </is>
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>385.3</v>
+        <v>3365.2</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>356.15</v>
+        <v>3115</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -6069,14 +6069,14 @@
         </is>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-7.57</v>
+        <v>-7.43</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>335.0214</v>
+        <v>3085.7715</v>
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
@@ -6103,22 +6103,22 @@
         </is>
       </c>
       <c r="S61" s="4" t="n">
-        <v>5.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="T61" s="4" t="n">
-        <v>-13.05</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>412.84</v>
+        <v>3608.33</v>
       </c>
       <c r="V61" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
+          <t>IND-R2-MCX-20260909-1bc45f</t>
         </is>
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -6145,41 +6145,39 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>397</v>
+        <v>385.3</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>413.1</v>
+        <v>356.15</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K62" s="5" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+      <c r="K62" s="6" t="n">
+        <v>-7.57</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -6198,7 +6196,7 @@
         </is>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>386.4571</v>
+        <v>335.0214</v>
       </c>
       <c r="R62" s="4" t="inlineStr">
         <is>
@@ -6206,24 +6204,22 @@
         </is>
       </c>
       <c r="S62" s="4" t="n">
-        <v>6.45</v>
+        <v>5.93</v>
       </c>
       <c r="T62" s="4" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-13.05</v>
+      </c>
+      <c r="U62" s="4" t="n">
+        <v>412.84</v>
       </c>
       <c r="V62" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
         </is>
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6231,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -6255,19 +6251,19 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-05</t>
+          <t>Admitted 2026-08-04</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>417.6</v>
+        <v>397</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>420.75</v>
+        <v>413.1</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -6275,7 +6271,7 @@
         </is>
       </c>
       <c r="K63" s="5" t="n">
-        <v>0.75</v>
+        <v>4.06</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6284,7 +6280,7 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -6303,7 +6299,7 @@
         </is>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>407.3714</v>
+        <v>386.4571</v>
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
@@ -6311,17 +6307,19 @@
         </is>
       </c>
       <c r="S63" s="4" t="n">
-        <v>3.18</v>
+        <v>6.45</v>
       </c>
       <c r="T63" s="4" t="n">
-        <v>-2.45</v>
-      </c>
-      <c r="U63" s="4" t="n">
-        <v>432.94</v>
+        <v>-2.66</v>
+      </c>
+      <c r="U63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V63" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
       <c r="W63" s="4" t="inlineStr">
@@ -6338,7 +6336,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -6358,27 +6356,27 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-08-05</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>389.85</v>
+        <v>417.6</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>389.35</v>
+        <v>420.75</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K64" s="6" t="n">
-        <v>-0.13</v>
+      <c r="K64" s="5" t="n">
+        <v>0.75</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -6387,7 +6385,7 @@
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -6406,7 +6404,7 @@
         </is>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>378.3286</v>
+        <v>407.3714</v>
       </c>
       <c r="R64" s="4" t="inlineStr">
         <is>
@@ -6414,17 +6412,17 @@
         </is>
       </c>
       <c r="S64" s="4" t="n">
-        <v>2.83</v>
+        <v>3.18</v>
       </c>
       <c r="T64" s="4" t="n">
-        <v>-2.96</v>
+        <v>-2.45</v>
       </c>
       <c r="U64" s="4" t="n">
-        <v>407.13</v>
+        <v>432.94</v>
       </c>
       <c r="V64" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
         </is>
       </c>
       <c r="W64" s="4" t="inlineStr">
@@ -6441,7 +6439,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -6461,19 +6459,19 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-28</t>
+          <t>Admitted 2026-08-04</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>187.46</v>
+        <v>389.85</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>184.35</v>
+        <v>389.35</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
@@ -6481,7 +6479,7 @@
         </is>
       </c>
       <c r="K65" s="6" t="n">
-        <v>-1.66</v>
+        <v>-0.13</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -6490,7 +6488,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -6509,7 +6507,7 @@
         </is>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>181.8114</v>
+        <v>378.3286</v>
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
@@ -6517,17 +6515,17 @@
         </is>
       </c>
       <c r="S65" s="4" t="n">
-        <v>1.38</v>
+        <v>2.83</v>
       </c>
       <c r="T65" s="4" t="n">
-        <v>-3.01</v>
+        <v>-2.96</v>
       </c>
       <c r="U65" s="4" t="n">
-        <v>195.93</v>
+        <v>407.13</v>
       </c>
       <c r="V65" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
         </is>
       </c>
       <c r="W65" s="4" t="inlineStr">
@@ -6544,215 +6542,318 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-28</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>187.46</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>184.35</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="n">
+        <v>181.8114</v>
+      </c>
+      <c r="R66" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S66" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T66" s="4" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="U66" s="4" t="n">
+        <v>195.93</v>
+      </c>
+      <c r="V66" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+        </is>
+      </c>
+      <c r="W66" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
           <t>ONGC</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-11</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="H66" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <v>239.45</v>
       </c>
-      <c r="I66" s="4" t="n">
+      <c r="I67" s="4" t="n">
         <v>235.03</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="J67" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="K66" s="6" t="n">
+      <c r="K67" s="6" t="n">
         <v>-1.85</v>
       </c>
-      <c r="L66" s="4" t="inlineStr">
+      <c r="L67" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M66" s="4" t="inlineStr">
+      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O66" s="4" t="inlineStr">
+      <c r="O67" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P66" s="4" t="inlineStr">
+      <c r="P67" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q66" s="4" t="n">
+      <c r="Q67" s="4" t="n">
         <v>232.2186</v>
       </c>
-      <c r="R66" s="4" t="inlineStr">
+      <c r="R67" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S66" s="4" t="n">
+      <c r="S67" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="T66" s="4" t="n">
+      <c r="T67" s="4" t="n">
         <v>-3.02</v>
       </c>
-      <c r="U66" s="4" t="n">
+      <c r="U67" s="4" t="n">
         <v>250.3</v>
       </c>
-      <c r="V66" s="4" t="inlineStr">
+      <c r="V67" s="4" t="inlineStr">
         <is>
           <t>IND-R1-ONGC-20260811-326ea2</t>
         </is>
       </c>
-      <c r="W66" s="4" t="inlineStr">
+      <c r="W67" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -6768,13 +6869,13 @@
     <mergeCell ref="A70:W70"/>
     <mergeCell ref="A79:W79"/>
     <mergeCell ref="A6:W6"/>
-    <mergeCell ref="A69:W69"/>
     <mergeCell ref="A78:W78"/>
     <mergeCell ref="A84:W84"/>
     <mergeCell ref="A80:W80"/>
     <mergeCell ref="A75:W75"/>
     <mergeCell ref="A74:W74"/>
     <mergeCell ref="A3:W3"/>
+    <mergeCell ref="A86:W86"/>
     <mergeCell ref="A71:W71"/>
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="A85:W85"/>
@@ -6818,7 +6919,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · 2026-09-16</t>
+          <t>AEGIS INDIA · EXIT HISTORY · 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -6921,7 +7022,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -6964,7 +7065,7 @@
         <v>-7.77</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -6995,17 +7096,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -7015,69 +7116,71 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1276.6</v>
+        <v>1449.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1242.7</v>
+        <v>1350</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-2.66</v>
+        <v>-6.86</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Stop-loss triggered</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>40.6</v>
+          <t>Stop breached</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-09-15 · stop_source=dynamic</t>
+          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWSTEEL-20260911-176cf3</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -7087,52 +7190,54 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>470.4</v>
+        <v>1413.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>450.7</v>
+        <v>1358.9</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-4.19</v>
+        <v>-3.86</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Stop-loss triggered</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>28.4</v>
+          <t>Stop breached</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-09-16 · stop_source=dynamic</t>
+          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRCTC-20260909-add681</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7249,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -7159,54 +7264,52 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1449.5</v>
+        <v>1276.6</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1350</v>
+        <v>1242.7</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-6.86</v>
+        <v>-2.66</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-09-15 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R2-JSWSTEEL-20260911-176cf3</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7321,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -7233,54 +7336,52 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1413.5</v>
+        <v>470.4</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1358.9</v>
+        <v>450.7</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-3.86</v>
+        <v>-4.19</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>28.4</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-09-16 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R2-IRCTC-20260909-add681</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -529,21 +529,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 11 position(s) left CURRENT on a STOP BREACH (R1 11 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>🔴 11 position(s) left CURRENT on a STOP BREACH (R1 11 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 3 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=1 · 228 scored · 58 already in CURRENT · biggest blocker: model disagreement (162) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 55 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (9 day(s) old) · ensemble STALE (9 day(s) old) · feature_store STALE (58 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 55 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -529,21 +529,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 11 position(s) left CURRENT on a STOP BREACH (R1 11 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>🔴 11 position(s) left CURRENT on a STOP BREACH (R1 11 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 3 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=4 · 228 scored · 61 already in CURRENT · biggest blocker: model disagreement (158) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 58 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (10 day(s) old) · ensemble STALE (10 day(s) old) · feature_store STALE (59 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 58 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -529,21 +529,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 9 position(s) left CURRENT on a STOP BREACH (R1 9 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>🔴 9 position(s) left CURRENT on a STOP BREACH (R1 9 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 1 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=2 · 228 scored · 65 already in CURRENT · biggest blocker: model disagreement (153) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 60 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (15 day(s) old) · ensemble STALE (15 day(s) old) · feature_store STALE (64 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 60 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -529,21 +529,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 9 position(s) left CURRENT on a STOP BREACH (R1 9 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>🔴 9 position(s) left CURRENT on a STOP BREACH (R1 9 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 1 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=1 · 228 scored · 60 already in CURRENT · biggest blocker: model disagreement (153) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 54 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (17 day(s) old) · ensemble STALE (17 day(s) old) · feature_store STALE (66 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 54 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -529,21 +529,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 9 position(s) left CURRENT on a STOP BREACH (R1 9 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>🔴 9 position(s) left CURRENT on a STOP BREACH (R1 9 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 1 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=7 · 228 scored · 56 already in CURRENT · biggest blocker: model disagreement (150) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 51 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (20 day(s) old) · ensemble STALE (20 day(s) old) · feature_store STALE (69 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 51 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -529,21 +529,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 11 position(s) left CURRENT on a STOP BREACH (R1 11 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>🔴 11 position(s) left CURRENT on a STOP BREACH (R1 11 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 3 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=2 · 228 scored · 40 already in CURRENT · biggest blocker: model disagreement (165) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 36 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (22 day(s) old) · ensemble STALE (22 day(s) old) · feature_store STALE (71 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 36 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W62"/>
+  <dimension ref="A1:W66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,21 +508,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-01 · prices = 2026-10-01 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-02 · prices = 2026-10-01 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>36 investable · NEW 1 · ACTIVE+ 35 · ACTIVE 0   ·   R2 32 · MOMENTUM 0 · R1 4 (advisory)   ·   1 row(s) read 0.00%: admitted at the 2026-10-01 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>40 investable · NEW 4 · ACTIVE+ 36 · ACTIVE 0   ·   R2 36 · MOMENTUM 0 · R1 4 (advisory)   ·   1 row(s) read 0.00%: admitted at the 2026-10-01 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 36 position(s) with an INTACT stop · if all of them fired today the average outcome is -1.84% from entry, worst single -6.46%</t>
+          <t>🛡 DOWNSIDE · 40 position(s) with an INTACT stop · if all of them fired today the average outcome is -2.04% from entry, worst single -6.46%</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=1 · 228 scored · 35 already in CURRENT · biggest blocker: model disagreement (172) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=4 · 228 scored · 38 already in CURRENT · biggest blocker: model disagreement (174) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 32 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 36 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -697,14 +697,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>223.39</v>
+        <v>142.41</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>223.39</v>
+        <v>142.41</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -715,11 +715,11 @@
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>31.2</v>
+        <v>33.3</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>216.2243</v>
+        <v>136.8286</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,22 +746,22 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.21</v>
+        <v>3.92</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.21</v>
+        <v>-3.92</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>234.14</v>
+        <v>150.78</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ONGC-20261001-b42383</t>
+          <t>IND-R2-IGL-20261002-27ac34</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -793,34 +793,34 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>464.25</v>
+        <v>1010.1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>592.1</v>
+        <v>1010.1</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K9" s="5" t="n">
-        <v>27.54</v>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>31.2</v>
+        <v>38.3</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>569.9213999999999</v>
+        <v>966.0714</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,24 +847,22 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>3.75</v>
+        <v>4.36</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>22.76</v>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-4.36</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>1076.14</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-INFY-20261002-20a2cb</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -876,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -886,7 +884,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -896,34 +894,34 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>25455</v>
+        <v>424.55</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>27120</v>
+        <v>424.55</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K10" s="5" t="n">
-        <v>6.54</v>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>31.3</v>
+        <v>34.1</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -942,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>26451.4286</v>
+        <v>408.05</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -950,24 +948,22 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>2.47</v>
+        <v>3.89</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-3.89</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>449.3</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
+          <t>IND-R2-KOTAKBANK-20261002-563392</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -979,7 +975,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -989,7 +985,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -999,34 +995,34 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>172.76</v>
+        <v>11671</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>179.4</v>
+        <v>11671</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K11" s="5" t="n">
-        <v>3.84</v>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>30.1</v>
+        <v>31.3</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1045,7 +1041,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>179.0471</v>
+        <v>11319</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1053,22 +1049,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.2</v>
+        <v>3.02</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>3.64</v>
+        <v>-3.02</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>184.71</v>
+        <v>12199</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
+          <t>IND-R2-MARUTI-20261002-ee9f86</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1076,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1100,19 +1096,19 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>373.25</v>
+        <v>464.25</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>383</v>
+        <v>592.1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1120,14 +1116,14 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.61</v>
+        <v>27.54</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>28.4</v>
+        <v>31.2</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1146,7 +1142,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>378.45</v>
+        <v>569.9213999999999</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1154,22 +1150,24 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.19</v>
+        <v>3.75</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>389.48</v>
+        <v>22.76</v>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DABUR-20260911-8f250f</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1179,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AARTIIND</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1201,19 +1199,19 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-16</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>468.8</v>
+        <v>25455</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>475.05</v>
+        <v>27120</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1221,14 +1219,14 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1.33</v>
+        <v>6.54</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1247,7 +1245,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>474.3928</v>
+        <v>26451.4286</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1255,22 +1253,24 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.14</v>
+        <v>2.47</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>506.94</v>
+        <v>3.91</v>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AARTIIND-20260916-4cc858</t>
+          <t>IND-R2-ABBOTINDIA-20260909-c04f79</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1302,19 +1302,19 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-18</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>588.9</v>
+        <v>172.76</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>595.5</v>
+        <v>179.4</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1322,14 +1322,14 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.12</v>
+        <v>3.84</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>31.9</v>
+        <v>30.1</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>595.0196</v>
+        <v>179.0471</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1356,22 +1356,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.04</v>
+        <v>3.64</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>643.11</v>
+        <v>184.71</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20260918-0ba353</t>
+          <t>IND-R2-BANDHANBNK-20260909-1c7660</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1403,19 +1403,19 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>818.3</v>
+        <v>373.25</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>823.85</v>
+        <v>383</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1423,14 +1423,14 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.68</v>
+        <v>2.61</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>31.2</v>
+        <v>28.4</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>815.9143</v>
+        <v>378.45</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1457,22 +1457,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.29</v>
+        <v>1.39</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>866.9299999999999</v>
+        <v>389.48</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
+          <t>IND-R2-DABUR-20260911-8f250f</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>AARTIIND</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1504,19 +1504,19 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2056.8</v>
+        <v>468.8</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2068.8</v>
+        <v>475.05</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1524,14 +1524,14 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.58</v>
+        <v>1.33</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>34.9</v>
+        <v>31.1</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1963.457</v>
+        <v>474.3928</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1558,22 +1558,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>5.09</v>
+        <v>0.14</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-4.54</v>
+        <v>1.19</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2224.78</v>
+        <v>506.94</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260928-f23b4c</t>
+          <t>IND-R2-AARTIIND-20260916-4cc858</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1605,19 +1605,19 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-18</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>285</v>
+        <v>588.9</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>285.55</v>
+        <v>595.5</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1625,14 +1625,14 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.19</v>
+        <v>1.12</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>35.4</v>
+        <v>31.9</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>282.5857</v>
+        <v>595.0196</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1659,22 +1659,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T17" s="4" t="n">
         <v>1.04</v>
       </c>
-      <c r="T17" s="4" t="n">
-        <v>-0.85</v>
-      </c>
       <c r="U17" s="4" t="n">
-        <v>296.6</v>
+        <v>643.11</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-GNFC-20260918-0ba353</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1706,34 +1706,34 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-30</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>17.07</v>
+        <v>818.3</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>17.05</v>
+        <v>823.85</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K18" s="6" t="n">
-        <v>-0.12</v>
+      <c r="K18" s="5" t="n">
+        <v>0.68</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>16.2</v>
+        <v>815.9143</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1760,22 +1760,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>4.99</v>
+        <v>0.96</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-5.1</v>
+        <v>-0.29</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>18.41</v>
+        <v>866.9299999999999</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260930-4c1d2d</t>
+          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1807,34 +1807,34 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-30</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>946.1</v>
+        <v>2056.8</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>944.7</v>
+        <v>2068.8</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K19" s="6" t="n">
-        <v>-0.15</v>
+      <c r="K19" s="5" t="n">
+        <v>0.58</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>38.2</v>
+        <v>34.9</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>911.6571</v>
+        <v>1963.457</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1861,22 +1861,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>3.5</v>
+        <v>5.09</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.64</v>
+        <v>-4.54</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>997.76</v>
+        <v>2224.78</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDALCO-20260930-e02b35</t>
+          <t>IND-R2-TCS-20260928-f23b4c</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1908,34 +1908,34 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1949</v>
+        <v>285</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1945.5</v>
+        <v>285.55</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K20" s="6" t="n">
-        <v>-0.18</v>
+      <c r="K20" s="5" t="n">
+        <v>0.19</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1925.8</v>
+        <v>282.5857</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1962,22 +1962,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.19</v>
+        <v>-0.85</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>2054.6</v>
+        <v>296.6</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IPCALAB-20260909-af9aea</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2009,34 +2009,34 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-10-01</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>8128.5</v>
+        <v>223.39</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>8076</v>
+        <v>223.39</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K21" s="6" t="n">
-        <v>-0.65</v>
+      <c r="K21" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>38.7</v>
+        <v>31.2</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>8064.2857</v>
+        <v>216.2243</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2063,22 +2063,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.15</v>
+        <v>3.21</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.79</v>
+        <v>-3.21</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>8660.25</v>
+        <v>234.14</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-ONGC-20261001-b42383</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2110,19 +2110,19 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-21</t>
+          <t>Admitted 2026-09-30</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>124830</v>
+        <v>17.07</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>123995</v>
+        <v>17.05</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -2130,14 +2130,14 @@
         </is>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.67</v>
+        <v>-0.12</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>29.3</v>
+        <v>31.3</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>121363.5714</v>
+        <v>16.2</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2164,22 +2164,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.12</v>
+        <v>4.99</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.78</v>
+        <v>-5.1</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>130238.57</v>
+        <v>18.41</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MRF-20260921-31a31a</t>
+          <t>IND-R2-IRB-20260930-4c1d2d</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-29</t>
+          <t>Admitted 2026-09-30</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3150.4</v>
+        <v>946.1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3106.8</v>
+        <v>944.7</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -2231,14 +2231,14 @@
         </is>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-1.38</v>
+        <v>-0.15</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>29.2</v>
+        <v>38.2</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3019.3428</v>
+        <v>911.6571</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-4.16</v>
+        <v>-3.64</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3346.99</v>
+        <v>997.76</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
+          <t>IND-R2-HINDALCO-20260930-e02b35</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2312,19 +2312,19 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>453.15</v>
+        <v>1949</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>446.85</v>
+        <v>1945.5</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -2332,14 +2332,14 @@
         </is>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-1.39</v>
+        <v>-0.18</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>33.3</v>
+        <v>40.6</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>430.3428</v>
+        <v>1925.8</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2366,22 +2366,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.69</v>
+        <v>1.01</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-5.03</v>
+        <v>-1.19</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>487.36</v>
+        <v>2054.6</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CONCOR-20260928-51a3e4</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2413,19 +2413,19 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>427.3</v>
+        <v>8128.5</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>421.2</v>
+        <v>8076</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -2433,14 +2433,14 @@
         </is>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-1.43</v>
+        <v>-0.65</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>31.3</v>
+        <v>38.7</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>417.5214</v>
+        <v>8064.2857</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2467,22 +2467,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.87</v>
+        <v>0.15</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-2.29</v>
+        <v>-0.79</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>449.01</v>
+        <v>8660.25</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260928-5e50fa</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2514,19 +2514,19 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-24</t>
+          <t>Admitted 2026-09-21</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1790.3</v>
+        <v>124830</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1764.2</v>
+        <v>123995</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -2534,14 +2534,14 @@
         </is>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-1.46</v>
+        <v>-0.67</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>33.3</v>
+        <v>29.3</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1719.7429</v>
+        <v>121363.5714</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2568,22 +2568,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.52</v>
+        <v>2.12</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-3.94</v>
+        <v>-2.78</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1896.14</v>
+        <v>130238.57</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIPORTS-20260924-58df63</t>
+          <t>IND-R2-MRF-20260921-31a31a</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>BALKRISIND</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2615,19 +2615,19 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-17</t>
+          <t>Admitted 2026-09-29</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2128.8</v>
+        <v>3150.4</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2094.7</v>
+        <v>3106.8</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2635,14 +2635,14 @@
         </is>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-1.6</v>
+        <v>-1.38</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>35.2</v>
+        <v>29.2</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2084.4</v>
+        <v>3019.3428</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2669,22 +2669,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.49</v>
+        <v>2.82</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.09</v>
+        <v>-4.16</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2297.34</v>
+        <v>3346.99</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BALKRISIND-20260917-29543a</t>
+          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2716,19 +2716,19 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>400.4</v>
+        <v>453.15</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>393.55</v>
+        <v>446.85</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -2736,14 +2736,14 @@
         </is>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-1.71</v>
+        <v>-1.39</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>32.3</v>
+        <v>33.3</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>391.1143</v>
+        <v>430.3428</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2770,22 +2770,22 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.62</v>
+        <v>3.69</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-2.32</v>
+        <v>-5.03</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>421.42</v>
+        <v>487.36</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260911-098cc1</t>
+          <t>IND-R2-CONCOR-20260928-51a3e4</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2817,19 +2817,19 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-16</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>321.75</v>
+        <v>427.3</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>315.8</v>
+        <v>421.2</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2837,14 +2837,14 @@
         </is>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-1.85</v>
+        <v>-1.43</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>33.2</v>
+        <v>31.3</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>311.9286</v>
+        <v>417.5214</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>1.23</v>
+        <v>0.87</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-3.05</v>
+        <v>-2.29</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>352.66</v>
+        <v>449.01</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MANAPPURAM-20260916-6576e5</t>
+          <t>IND-R2-COALINDIA-20260928-5e50fa</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2918,19 +2918,19 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-09-24</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>10700</v>
+        <v>1790.3</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10483</v>
+        <v>1764.2</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -2938,14 +2938,14 @@
         </is>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-2.03</v>
+        <v>-1.46</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>43.6</v>
+        <v>33.3</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>10182.9286</v>
+        <v>1719.7429</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2972,22 +2972,22 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>2.86</v>
+        <v>2.52</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-4.83</v>
+        <v>-3.94</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>11796.71</v>
+        <v>1896.14</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260928-d4ee3d</t>
+          <t>IND-R2-ADANIPORTS-20260924-58df63</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>BALKRISIND</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3019,19 +3019,19 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-23</t>
+          <t>Admitted 2026-09-17</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3897</v>
+        <v>2128.8</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3815.1</v>
+        <v>2094.7</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -3039,14 +3039,14 @@
         </is>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-2.1</v>
+        <v>-1.6</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>3727.7429</v>
+        <v>2084.4</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3073,22 +3073,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>2.29</v>
+        <v>0.49</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-4.34</v>
+        <v>-2.09</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4235.85</v>
+        <v>2297.34</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AIAENG-20260923-be0111</t>
+          <t>IND-R2-BALKRISIND-20260917-29543a</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3120,19 +3120,19 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3365.2</v>
+        <v>400.4</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3290.7</v>
+        <v>393.55</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-2.21</v>
+        <v>-1.71</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>40.4</v>
+        <v>32.3</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>3231.1714</v>
+        <v>391.1143</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3174,22 +3174,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>1.81</v>
+        <v>0.62</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-3.98</v>
+        <v>-2.32</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3608.33</v>
+        <v>421.42</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MCX-20260909-1bc45f</t>
+          <t>IND-R2-LICI-20260911-098cc1</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3221,19 +3221,19 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2825</v>
+        <v>321.75</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2748.6</v>
+        <v>315.8</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-2.7</v>
+        <v>-1.85</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>36.1</v>
+        <v>33.2</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>2723.2573</v>
+        <v>311.9286</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3275,22 +3275,22 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-3.6</v>
+        <v>-3.05</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3067.12</v>
+        <v>352.66</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
+          <t>IND-R2-MANAPPURAM-20260916-6576e5</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>698.65</v>
+        <v>10700</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>679.25</v>
+        <v>10483</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -3342,14 +3342,14 @@
         </is>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-2.78</v>
+        <v>-2.03</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>30.9</v>
+        <v>43.6</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>664.7714999999999</v>
+        <v>10182.9286</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3376,22 +3376,22 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>2.13</v>
+        <v>2.86</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-4.85</v>
+        <v>-4.83</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>749.47</v>
+        <v>11796.71</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CAMS-20260928-86e0a0</t>
+          <t>IND-R2-OFSS-20260928-d4ee3d</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>VINATIORGA</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3423,19 +3423,19 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-09-23</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1193.8</v>
+        <v>3897</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1159.3</v>
+        <v>3815.1</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -3443,14 +3443,14 @@
         </is>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-2.89</v>
+        <v>-2.1</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>27.5</v>
+        <v>35</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>1141.0287</v>
+        <v>3727.7429</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3477,22 +3477,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>1.58</v>
+        <v>2.29</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-4.42</v>
+        <v>-4.34</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1272.96</v>
+        <v>4235.85</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VINATIORGA-20260928-756b01</t>
+          <t>IND-R2-AIAENG-20260923-be0111</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3524,19 +3524,19 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-23</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1284.5</v>
+        <v>3365.2</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1246.2</v>
+        <v>3290.7</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -3544,14 +3544,14 @@
         </is>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-2.98</v>
+        <v>-2.21</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>1245.5</v>
+        <v>3231.1714</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3578,22 +3578,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>0.06</v>
+        <v>1.81</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-3.04</v>
+        <v>-3.98</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>1353.91</v>
+        <v>3608.33</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWSTEEL-20260923-8ac9fe</t>
+          <t>IND-R2-MCX-20260909-1bc45f</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3625,19 +3625,19 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-16</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>407.75</v>
+        <v>2825</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>395.5</v>
+        <v>2748.6</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -3645,14 +3645,14 @@
         </is>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-3</v>
+        <v>-2.7</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>33.3</v>
+        <v>36.1</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>392.3429</v>
+        <v>2723.2573</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3679,22 +3679,22 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-3.78</v>
+        <v>-3.6</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>436.95</v>
+        <v>3067.12</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
+          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3726,19 +3726,19 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>187.94</v>
+        <v>698.65</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>179.43</v>
+        <v>679.25</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -3746,14 +3746,14 @@
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-4.53</v>
+        <v>-2.78</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>40.6</v>
+        <v>30.9</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>179.2129</v>
+        <v>664.7714999999999</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3780,22 +3780,22 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.12</v>
+        <v>2.13</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-4.64</v>
+        <v>-4.85</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>206.77</v>
+        <v>749.47</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260909-29ffd5</t>
+          <t>IND-R2-CAMS-20260928-86e0a0</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>VINATIORGA</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3827,19 +3827,19 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>273.3</v>
+        <v>1193.8</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>255.75</v>
+        <v>1159.3</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -3847,14 +3847,14 @@
         </is>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-6.42</v>
+        <v>-2.89</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>28.4</v>
+        <v>27.5</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>255.6428</v>
+        <v>1141.0287</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3881,22 +3881,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>0.04</v>
+        <v>1.58</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-6.46</v>
+        <v>-4.42</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>289.39</v>
+        <v>1272.96</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
+          <t>IND-R2-VINATIORGA-20260928-756b01</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -3923,41 +3923,39 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-09-23</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>397</v>
+        <v>1284.5</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>424.55</v>
+        <v>1246.2</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K40" s="5" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+      <c r="K40" s="6" t="n">
+        <v>-2.98</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3976,7 +3974,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>386.4571</v>
+        <v>1245.5</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3984,24 +3982,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>8.970000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-3.04</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>1353.91</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-JSWSTEEL-20260923-8ac9fe</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4013,12 +4009,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4028,41 +4024,39 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-05</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>417.6</v>
+        <v>407.75</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>421.2</v>
+        <v>395.5</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K41" s="5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+      <c r="K41" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4081,7 +4075,7 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>407.3714</v>
+        <v>392.3429</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4089,22 +4083,22 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>3.28</v>
+        <v>0.8</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-2.45</v>
+        <v>-3.78</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>432.94</v>
+        <v>436.95</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
         </is>
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4116,12 +4110,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -4131,24 +4125,24 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>389.85</v>
+        <v>187.94</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>384.2</v>
+        <v>179.43</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -4156,16 +4150,14 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-4.53</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>40.6</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4184,7 +4176,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>378.3286</v>
+        <v>179.2129</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4192,22 +4184,22 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>1.53</v>
+        <v>0.12</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-2.96</v>
+        <v>-4.64</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>407.13</v>
+        <v>206.77</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R2-SAIL-20260909-29ffd5</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4219,215 +4211,627 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-09</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>273.3</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>255.75</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>-6.42</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>255.6428</v>
+      </c>
+      <c r="R43" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S43" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T43" s="4" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>289.39</v>
+      </c>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
+        </is>
+      </c>
+      <c r="W43" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>397</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>424.55</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="n">
+        <v>386.4571</v>
+      </c>
+      <c r="R44" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S44" s="4" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="T44" s="4" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="U44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+        </is>
+      </c>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-05</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>407.3714</v>
+      </c>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S45" s="4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T45" s="4" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>432.94</v>
+      </c>
+      <c r="V45" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+        </is>
+      </c>
+      <c r="W45" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>384.2</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>378.3286</v>
+      </c>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S46" s="4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T46" s="4" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>407.13</v>
+      </c>
+      <c r="V46" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
+        </is>
+      </c>
+      <c r="W46" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
           <t>TATASTEEL</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-28</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>187.46</v>
       </c>
-      <c r="I43" s="4" t="n">
+      <c r="I47" s="4" t="n">
         <v>181.98</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K43" s="6" t="n">
+      <c r="K47" s="6" t="n">
         <v>-2.92</v>
       </c>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O43" s="4" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P43" s="4" t="inlineStr">
+      <c r="P47" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q43" s="4" t="n">
+      <c r="Q47" s="4" t="n">
         <v>181.8114</v>
       </c>
-      <c r="R43" s="4" t="inlineStr">
+      <c r="R47" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S43" s="4" t="n">
+      <c r="S47" s="4" t="n">
         <v>0.09</v>
       </c>
-      <c r="T43" s="4" t="n">
+      <c r="T47" s="4" t="n">
         <v>-3.01</v>
       </c>
-      <c r="U43" s="4" t="n">
+      <c r="U47" s="4" t="n">
         <v>195.93</v>
       </c>
-      <c r="V43" s="4" t="inlineStr">
+      <c r="V47" s="4" t="inlineStr">
         <is>
           <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
-      <c r="W43" s="4" t="inlineStr">
+      <c r="W47" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -4436,28 +4840,28 @@
   </sheetData>
   <mergeCells count="23">
     <mergeCell ref="A58:W58"/>
-    <mergeCell ref="A48:W48"/>
+    <mergeCell ref="A64:W64"/>
     <mergeCell ref="A59:W59"/>
-    <mergeCell ref="A49:W49"/>
     <mergeCell ref="A51:W51"/>
     <mergeCell ref="A60:W60"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A61:W61"/>
     <mergeCell ref="A6:W6"/>
     <mergeCell ref="A54:W54"/>
-    <mergeCell ref="A46:W46"/>
+    <mergeCell ref="A65:W65"/>
+    <mergeCell ref="A66:W66"/>
     <mergeCell ref="A56:W56"/>
     <mergeCell ref="A50:W50"/>
     <mergeCell ref="A3:W3"/>
     <mergeCell ref="A55:W55"/>
     <mergeCell ref="A57:W57"/>
     <mergeCell ref="A2:W2"/>
-    <mergeCell ref="A47:W47"/>
     <mergeCell ref="A5:W5"/>
     <mergeCell ref="A53:W53"/>
     <mergeCell ref="A4:W4"/>
     <mergeCell ref="A62:W62"/>
     <mergeCell ref="A52:W52"/>
+    <mergeCell ref="A63:W63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4493,7 +4897,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-01</t>
+          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4596,7 +5000,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -4639,7 +5043,7 @@
         <v>-3.85</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -4670,17 +5074,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4690,69 +5094,71 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>166.83</v>
+        <v>239.45</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>159.15</v>
+        <v>223.39</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-4.6</v>
+        <v>-6.71</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Stop-loss triggered</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>35.8</v>
+          <t>Stop breached</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-10-01 · stop_source=dynamic</t>
+          <t>STOP BREACHED - stop 232.2186 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-WIPRO-20260918-3e25ae</t>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -4762,69 +5168,71 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>275</v>
+        <v>1449.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>253.9</v>
+        <v>1325.3</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-7.67</v>
+        <v>-8.57</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Stop-loss triggered</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>35.4</v>
+          <t>Stop breached</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-10-01 · stop_source=dynamic</t>
+          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260909-bbba1f</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -4834,52 +5242,54 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2811</v>
+        <v>1413.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2645.7</v>
+        <v>1340.8</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-5.88</v>
+        <v>-5.14</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Stop-loss triggered</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>26.5</v>
+          <t>Stop breached</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-10-01 · stop_source=dynamic</t>
+          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-RATNAMANI-20260921-d9d49b</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
@@ -4891,12 +5301,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -4906,54 +5316,52 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>239.45</v>
+        <v>166.83</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>223.39</v>
+        <v>159.15</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-6.71</v>
+        <v>-4.6</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>35.8</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 232.2186 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-10-01 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R2-WIPRO-20260918-3e25ae</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -4965,7 +5373,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -4994,13 +5402,13 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>385.3</v>
+        <v>275</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>337.4</v>
+        <v>253.9</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-12.43</v>
+        <v>-7.67</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>22</v>
@@ -5011,7 +5419,7 @@
         </is>
       </c>
       <c r="M10" s="4" t="n">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
@@ -5020,7 +5428,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
+          <t>IND-R2-VEDL-20260909-bbba1f</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -5037,12 +5445,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -5052,54 +5460,52 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1449.5</v>
+        <v>2811</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1325.3</v>
+        <v>2645.7</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-8.57</v>
+        <v>-5.88</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>26.5</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-10-01 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R2-RATNAMANI-20260921-d9d49b</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -5111,12 +5517,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -5136,20 +5542,20 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7238.5</v>
+        <v>385.3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6990</v>
+        <v>337.4</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-3.43</v>
+        <v>-12.43</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -5157,7 +5563,7 @@
         </is>
       </c>
       <c r="M12" s="4" t="n">
-        <v>33.3</v>
+        <v>40.6</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
@@ -5166,7 +5572,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EICHERMOT-20260928-aa07a8</t>
+          <t>IND-R2-NATIONALUM-20260909-36e82f</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -5183,12 +5589,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -5198,54 +5604,52 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1413.5</v>
+        <v>7238.5</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1340.8</v>
+        <v>6990</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-5.14</v>
+        <v>-3.43</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-10-01 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R2-EICHERMOT-20260928-aa07a8</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -529,21 +529,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 12 position(s) left CURRENT on a STOP BREACH (R1 12 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>🔴 12 position(s) left CURRENT on a STOP BREACH (R1 12 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 4 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=4 · 228 scored · 38 already in CURRENT · biggest blocker: model disagreement (174) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 36 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (24 day(s) old) · ensemble STALE (24 day(s) old) · feature_store STALE (73 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 36 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,42 +508,42 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-05 · prices = 2026-10-05 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-06 · prices = 2026-10-06 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>30 investable · NEW 5 · ACTIVE+ 25 · ACTIVE 0   ·   R2 27 · MOMENTUM 0 · R1 3 (advisory)   ·   5 row(s) read 0.00%: admitted at the 2026-10-05 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>39 investable · NEW 9 · ACTIVE+ 30 · ACTIVE 0   ·   R2 35 · MOMENTUM 0 · R1 4 (advisory)   ·   9 row(s) read 0.00%: admitted at the 2026-10-06 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 30 position(s) with an INTACT stop · if all of them fired today the average outcome is -2.46% from entry, worst single -5.14%</t>
+          <t>🛡 DOWNSIDE · 39 position(s) with an INTACT stop · if all of them fired today the average outcome is -2.68% from entry, worst single -9.02%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 13 position(s) left CURRENT on a STOP BREACH (R1 13 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>🔴 12 position(s) left CURRENT on a STOP BREACH (R1 12 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=5 · 228 scored · 28 already in CURRENT · biggest blocker: model disagreement (172) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=9 · 228 scored · 38 already in CURRENT · biggest blocker: model disagreement (174) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 27 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 35 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -697,29 +697,29 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>363.4</v>
+        <v>293.95</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>363.4</v>
+        <v>293.95</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>33.3</v>
+        <v>34.3</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>348.3928</v>
+        <v>278.3</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,17 +746,17 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>4.13</v>
+        <v>5.32</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-4.13</v>
+        <v>-5.32</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>385.91</v>
+        <v>317.43</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBUJACEM-20261005-e13c8d</t>
+          <t>IND-R2-ANGELONE-20261006-fc497f</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -798,25 +798,25 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3110.4</v>
+        <v>1243</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3110.4</v>
+        <v>1243</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2950.5571</v>
+        <v>1200.2857</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,17 +847,17 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>5.14</v>
+        <v>3.44</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-5.14</v>
+        <v>-3.44</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>3350.16</v>
+        <v>1307.07</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BSE-20261005-7af4a1</t>
+          <t>IND-R2-AXISBANK-20261006-79c723</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -899,29 +899,29 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>119.47</v>
+        <v>1552.3</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>119.47</v>
+        <v>1552.3</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>30.2</v>
+        <v>35.4</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>115.3486</v>
+        <v>1482.0857</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,17 +948,17 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>3.45</v>
+        <v>4.52</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.45</v>
+        <v>-4.52</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>125.65</v>
+        <v>1657.62</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20261005-19551d</t>
+          <t>IND-R2-DEEPAKNTR-20261006-676b03</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1000,29 +1000,29 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>71.23</v>
+        <v>814.35</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>71.23</v>
+        <v>814.35</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>31.3</v>
+        <v>32.9</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>68.8886</v>
+        <v>785.9786</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1049,22 +1049,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>3.29</v>
+        <v>3.48</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.29</v>
+        <v>-3.48</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>74.73999999999999</v>
+        <v>856.91</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NHPC-20261005-cad510</t>
+          <t>IND-R2-INDIANB-20261006-0d13b1</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1101,29 +1101,29 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>961</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>961</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>37.2</v>
+        <v>31.2</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>932.8714</v>
+        <v>70.90860000000001</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>2.93</v>
+        <v>4.23</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.93</v>
+        <v>-4.23</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1003.19</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20261005-104400</t>
+          <t>IND-R2-NMDC-20261006-2acbae</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1197,34 +1197,34 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>464.25</v>
+        <v>323.6</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>626</v>
+        <v>323.6</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>34.84</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>31.2</v>
+        <v>29.2</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>587.45</v>
+        <v>311.3143</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1251,24 +1251,22 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>6.16</v>
+        <v>3.8</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>26.54</v>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-3.8</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>342.03</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-PFC-20261006-e91ac2</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1278,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1290,7 +1288,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1300,34 +1298,34 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2056.8</v>
+        <v>112.03</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2108</v>
+        <v>112.03</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>2.49</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1346,7 +1344,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1991.8715</v>
+        <v>108.1043</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1354,22 +1352,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>5.51</v>
+        <v>3.5</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.16</v>
+        <v>-3.5</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2224.78</v>
+        <v>117.92</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260928-f23b4c</t>
+          <t>IND-R2-PNB-20261006-66ccb3</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1379,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1391,7 +1389,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1401,34 +1399,34 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>285</v>
+        <v>617.4</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>289.35</v>
+        <v>617.4</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>1.53</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>35.4</v>
+        <v>20.6</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1447,7 +1445,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>282.5857</v>
+        <v>561.7018</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1455,22 +1453,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.34</v>
+        <v>9.02</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.85</v>
+        <v>-9.02</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>296.6</v>
+        <v>728.8</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-TATACHEM-20261006-fc5587</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1480,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1492,7 +1490,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1502,34 +1500,34 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1010.1</v>
+        <v>167.95</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1018.85</v>
+        <v>167.95</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0.87</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>38.3</v>
+        <v>32.9</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1548,7 +1546,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>969.4213999999999</v>
+        <v>160.5157</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1556,22 +1554,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.85</v>
+        <v>4.43</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-4.03</v>
+        <v>-4.43</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1076.14</v>
+        <v>179.1</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20261002-20a2cb</t>
+          <t>IND-R2-UNIONBANK-20261006-801564</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1581,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1603,34 +1601,34 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1949</v>
+        <v>464.25</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1960.2</v>
+        <v>634</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.57</v>
+        <v>36.56</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>40.6</v>
+        <v>31.2</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1649,7 +1647,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1925.8</v>
+        <v>594.7963999999999</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1657,22 +1655,24 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.75</v>
+        <v>6.18</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="U17" s="4" t="n">
-        <v>2054.6</v>
+        <v>28.12</v>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IPCALAB-20260909-af9aea</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1704,34 +1704,34 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-01</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>223.39</v>
+        <v>3110.4</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>222.66</v>
+        <v>3283</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>-0.33</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>5.55</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>31.2</v>
+        <v>34.8</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>216.2243</v>
+        <v>3119.7</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1758,22 +1758,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2.89</v>
+        <v>4.97</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-3.21</v>
+        <v>0.3</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>234.14</v>
+        <v>3350.16</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ONGC-20261001-b42383</t>
+          <t>IND-R2-BSE-20261005-7af4a1</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1805,34 +1805,34 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>142.41</v>
+        <v>285</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>141.8</v>
+        <v>296.25</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>-0.43</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>3.95</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>33.3</v>
+        <v>35.4</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>136.8286</v>
+        <v>284.6429</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1859,22 +1859,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>3.51</v>
+        <v>3.92</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.92</v>
+        <v>-0.13</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>150.78</v>
+        <v>296.6</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20261002-27ac34</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1906,34 +1906,34 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>8128.5</v>
+        <v>2056.8</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8089</v>
+        <v>2089.8</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>-0.49</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>1.6</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>38.7</v>
+        <v>34.9</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>8064.2857</v>
+        <v>1991.8715</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1960,22 +1960,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.31</v>
+        <v>4.69</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.79</v>
+        <v>-3.16</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>8660.25</v>
+        <v>2224.78</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-TCS-20260928-f23b4c</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2007,34 +2007,34 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-23</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3897</v>
+        <v>424.55</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3876.4</v>
+        <v>431.25</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>-0.53</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>1.58</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>35</v>
+        <v>34.1</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3727.7429</v>
+        <v>413.5929</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2061,22 +2061,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.83</v>
+        <v>4.09</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-4.34</v>
+        <v>-2.58</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>4235.85</v>
+        <v>449.3</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AIAENG-20260923-be0111</t>
+          <t>IND-R2-KOTAKBANK-20261002-563392</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2108,34 +2108,34 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>427.3</v>
+        <v>71.23</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>424.75</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>-0.6</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1.33</v>
       </c>
       <c r="L22" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>417.5214</v>
+        <v>69.8943</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2162,22 +2162,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.7</v>
+        <v>3.17</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.29</v>
+        <v>-1.88</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>449.01</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260928-5e50fa</t>
+          <t>IND-R2-NHPC-20261005-cad510</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>VINATIORGA</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2209,30 +2209,30 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1193.8</v>
+        <v>363.4</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1184.8</v>
+        <v>366.5</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>-0.75</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.85</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>27.5</v>
+        <v>33.3</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1141.0287</v>
+        <v>352.7286</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-4.42</v>
+        <v>-2.94</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1272.96</v>
+        <v>385.91</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VINATIORGA-20260928-756b01</t>
+          <t>IND-R2-AMBUJACEM-20261005-e13c8d</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2319,25 +2319,25 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>946.1</v>
+        <v>17.07</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>936.45</v>
+        <v>17.08</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>-1.02</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>38.2</v>
+        <v>31.3</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>911.6571</v>
+        <v>16.2586</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2364,22 +2364,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.65</v>
+        <v>4.81</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-3.64</v>
+        <v>-4.75</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>997.76</v>
+        <v>18.41</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDALCO-20260930-e02b35</t>
+          <t>IND-R2-IRB-20260930-4c1d2d</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2411,30 +2411,30 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-30</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>17.07</v>
+        <v>8128.5</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>16.87</v>
+        <v>8106.5</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-1.17</v>
+        <v>-0.27</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>31.3</v>
+        <v>38.7</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>16.2</v>
+        <v>8064.2857</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.97</v>
+        <v>0.52</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-5.1</v>
+        <v>-0.79</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>18.41</v>
+        <v>8660.25</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260930-4c1d2d</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2512,34 +2512,34 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-16</t>
+          <t>Admitted 2026-09-23</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>407.75</v>
+        <v>3897</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>402.2</v>
+        <v>3886.1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-1.36</v>
+        <v>-0.28</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>392.3429</v>
+        <v>3727.7429</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2566,22 +2566,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.45</v>
+        <v>4.07</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-3.78</v>
+        <v>-4.34</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>436.95</v>
+        <v>4235.85</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
+          <t>IND-R2-AIAENG-20260923-be0111</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>VINATIORGA</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2613,34 +2613,34 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-21</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>124830</v>
+        <v>1193.8</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>123030</v>
+        <v>1190.4</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-1.44</v>
+        <v>-0.28</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>29.3</v>
+        <v>27.5</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>121363.5714</v>
+        <v>1141.0287</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2667,22 +2667,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.35</v>
+        <v>4.15</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.78</v>
+        <v>-4.42</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>130238.57</v>
+        <v>1272.96</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MRF-20260921-31a31a</t>
+          <t>IND-R2-VINATIORGA-20260928-756b01</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2723,25 +2723,25 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>11671</v>
+        <v>1010.1</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11489</v>
+        <v>1006.7</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-1.56</v>
+        <v>-0.34</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>31.3</v>
+        <v>38.3</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>11319</v>
+        <v>969.4213999999999</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2768,22 +2768,22 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.48</v>
+        <v>3.7</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-3.02</v>
+        <v>-4.03</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>12199</v>
+        <v>1076.14</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARUTI-20261002-ee9f86</t>
+          <t>IND-R2-INFY-20261002-20a2cb</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2815,34 +2815,34 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>424.55</v>
+        <v>1949</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>417</v>
+        <v>1939</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-1.78</v>
+        <v>-0.51</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>34.1</v>
+        <v>40.6</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>408.05</v>
+        <v>1925.8</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2869,22 +2869,22 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2.15</v>
+        <v>0.68</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-3.89</v>
+        <v>-1.19</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>449.3</v>
+        <v>2054.6</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20261002-563392</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2916,34 +2916,34 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-24</t>
+          <t>Admitted 2026-09-30</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1790.3</v>
+        <v>946.1</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1758.1</v>
+        <v>941.15</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-1.8</v>
+        <v>-0.52</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>33.3</v>
+        <v>38.2</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1719.7429</v>
+        <v>911.6571</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2970,22 +2970,22 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>2.18</v>
+        <v>3.13</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.94</v>
+        <v>-3.64</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1896.14</v>
+        <v>997.76</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIPORTS-20260924-58df63</t>
+          <t>IND-R2-HINDALCO-20260930-e02b35</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3017,34 +3017,34 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-29</t>
+          <t>Admitted 2026-10-01</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3150.4</v>
+        <v>223.39</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3086.6</v>
+        <v>221.92</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-2.03</v>
+        <v>-0.66</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>29.2</v>
+        <v>31.2</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>3019.3428</v>
+        <v>216.2243</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3071,22 +3071,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>2.18</v>
+        <v>2.57</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-4.16</v>
+        <v>-3.21</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3346.99</v>
+        <v>234.14</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
+          <t>IND-R2-ONGC-20261001-b42383</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3118,34 +3118,34 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-09-24</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10700</v>
+        <v>1790.3</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10463</v>
+        <v>1775.6</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-2.21</v>
+        <v>-0.82</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>43.6</v>
+        <v>33.3</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>10182.9286</v>
+        <v>1719.7429</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3172,22 +3172,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-4.83</v>
+        <v>-3.94</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>11796.71</v>
+        <v>1896.14</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260928-d4ee3d</t>
+          <t>IND-R2-ADANIPORTS-20260924-58df63</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3219,30 +3219,30 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>698.65</v>
+        <v>961</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>683.1</v>
+        <v>952.75</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-2.23</v>
+        <v>-0.86</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>30.9</v>
+        <v>37.2</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>664.7714999999999</v>
+        <v>932.8714</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3273,22 +3273,22 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>2.68</v>
+        <v>2.09</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-4.85</v>
+        <v>-2.93</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>749.47</v>
+        <v>1003.19</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CAMS-20260928-86e0a0</t>
+          <t>IND-R2-SBIN-20261005-104400</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3320,34 +3320,34 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>453.15</v>
+        <v>142.41</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>438.9</v>
+        <v>141.1</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-3.14</v>
+        <v>-0.92</v>
       </c>
       <c r="L34" s="4" t="n">
         <v>33.3</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>430.3428</v>
+        <v>136.8286</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3374,22 +3374,22 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>1.95</v>
+        <v>3.03</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-5.03</v>
+        <v>-3.92</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>487.36</v>
+        <v>150.78</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CONCOR-20260928-51a3e4</t>
+          <t>IND-R2-IGL-20261002-27ac34</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -3416,41 +3416,39 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>397</v>
+        <v>11671</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>417</v>
+        <v>11560</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>31.3</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3469,7 +3467,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>386.4571</v>
+        <v>11319</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3477,24 +3475,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>7.32</v>
+        <v>2.08</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="U35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-3.02</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>12199</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-MARUTI-20261002-ee9f86</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3502,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -3521,41 +3517,39 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-05</t>
+          <t>Admitted 2026-09-21</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>417.6</v>
+        <v>124830</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>424.75</v>
+        <v>123610</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>29.3</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3574,7 +3568,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>407.3714</v>
+        <v>121363.5714</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3582,22 +3576,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>4.09</v>
+        <v>1.82</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-2.45</v>
+        <v>-2.78</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>432.94</v>
+        <v>130238.57</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R2-MRF-20260921-31a31a</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3609,245 +3603,1162 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-10-05</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>119.47</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>118.27</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>115.3486</v>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S37" s="4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>125.65</v>
+      </c>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-CANBK-20261005-19551d</t>
+        </is>
+      </c>
+      <c r="W37" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-29</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>3150.4</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>3095.5</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>3019.3428</v>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>3346.99</v>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-28</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>698.65</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>685.85</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="n">
+        <v>664.7714999999999</v>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S39" s="4" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="T39" s="4" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>749.47</v>
+      </c>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-CAMS-20260928-86e0a0</t>
+        </is>
+      </c>
+      <c r="W39" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>407.75</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>392.3429</v>
+      </c>
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>436.95</v>
+      </c>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
+        </is>
+      </c>
+      <c r="W40" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-28</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>10700</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>10461</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="n">
+        <v>10182.9286</v>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S41" s="4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T41" s="4" t="n">
+        <v>-4.83</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>11796.71</v>
+      </c>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-OFSS-20260928-d4ee3d</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-28</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>453.15</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>442.3</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>430.3428</v>
+      </c>
+      <c r="R42" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S42" s="4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T42" s="4" t="n">
+        <v>-5.03</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>487.36</v>
+      </c>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-CONCOR-20260928-51a3e4</t>
+        </is>
+      </c>
+      <c r="W42" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>397</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>431.25</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>386.4571</v>
+      </c>
+      <c r="R43" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S43" s="4" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="T43" s="4" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+        </is>
+      </c>
+      <c r="W43" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-05</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>416.75</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="n">
+        <v>407.3714</v>
+      </c>
+      <c r="R44" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S44" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T44" s="4" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>432.94</v>
+      </c>
+      <c r="V44" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+        </is>
+      </c>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
           <t>BEL</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-04</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>389.85</v>
       </c>
-      <c r="I37" s="4" t="n">
-        <v>380.05</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="I45" s="4" t="n">
+        <v>386.05</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P37" s="4" t="inlineStr">
+      <c r="P45" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q37" s="4" t="n">
+      <c r="Q45" s="4" t="n">
         <v>378.3286</v>
       </c>
-      <c r="R37" s="4" t="inlineStr">
+      <c r="R45" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S37" s="4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="T37" s="4" t="n">
+      <c r="S45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T45" s="4" t="n">
         <v>-2.96</v>
       </c>
-      <c r="U37" s="4" t="n">
+      <c r="U45" s="4" t="n">
         <v>407.13</v>
       </c>
-      <c r="V37" s="4" t="inlineStr">
+      <c r="V45" s="4" t="inlineStr">
         <is>
           <t>IND-R1-BEL-20260804-c9f4d0</t>
         </is>
       </c>
-      <c r="W37" s="4" t="inlineStr">
+      <c r="W45" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-11</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1191</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>1150.9</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>1149.2286</v>
+      </c>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S46" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T46" s="4" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>1253.66</v>
+      </c>
+      <c r="V46" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
+        </is>
+      </c>
+      <c r="W46" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A44:W44"/>
-    <mergeCell ref="A40:W40"/>
-    <mergeCell ref="A48:W48"/>
+    <mergeCell ref="A58:W58"/>
+    <mergeCell ref="A64:W64"/>
+    <mergeCell ref="A59:W59"/>
     <mergeCell ref="A49:W49"/>
     <mergeCell ref="A51:W51"/>
+    <mergeCell ref="A60:W60"/>
     <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A45:W45"/>
+    <mergeCell ref="A61:W61"/>
     <mergeCell ref="A6:W6"/>
     <mergeCell ref="A54:W54"/>
-    <mergeCell ref="A41:W41"/>
-    <mergeCell ref="A46:W46"/>
+    <mergeCell ref="A65:W65"/>
     <mergeCell ref="A56:W56"/>
     <mergeCell ref="A50:W50"/>
     <mergeCell ref="A3:W3"/>
     <mergeCell ref="A55:W55"/>
+    <mergeCell ref="A57:W57"/>
     <mergeCell ref="A2:W2"/>
-    <mergeCell ref="A47:W47"/>
-    <mergeCell ref="A42:W42"/>
     <mergeCell ref="A5:W5"/>
     <mergeCell ref="A53:W53"/>
     <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A62:W62"/>
     <mergeCell ref="A52:W52"/>
-    <mergeCell ref="A43:W43"/>
+    <mergeCell ref="A63:W63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3883,21 +4794,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-05</t>
+          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>134 records · ADMINISTRATIVE 21 · ADVISORY/HISTORICAL 5 · REALIZED EXIT 95 · STOP-BREACH MARK 13   ·   Canonical lifecycle historical coverage begins 2026-08-04 · earlier closures are not held in any provable AEGIS source</t>
+          <t>134 records · ADMINISTRATIVE 21 · ADVISORY/HISTORICAL 5 · REALIZED EXIT 96 · STOP-BREACH MARK 12   ·   Canonical lifecycle historical coverage begins 2026-08-04 · earlier closures are not held in any provable AEGIS source</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>📊 REALIZED PRODUCTION PERFORMANCE · 95 closed trade(s) · win 20/95 · avg -2.57%   ·   EXCLUDED from this line: orphan auto-closes, administrative records, advisory rows, and 13 STOP-BREACH MARK(s) whose stop was passed but which are NOT sold - their price and P&amp;L are today's mark, not a realized result</t>
+          <t>📊 REALIZED PRODUCTION PERFORMANCE · 96 closed trade(s) · win 20/96 · avg -2.57%   ·   EXCLUDED from this line: orphan auto-closes, administrative records, advisory rows, and 12 STOP-BREACH MARK(s) whose stop was passed but which are NOT sold - their price and P&amp;L are today's mark, not a realized result</t>
         </is>
       </c>
     </row>
@@ -3986,17 +4897,17 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -4016,20 +4927,20 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1191</v>
+        <v>187.46</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1135.5</v>
+        <v>179.45</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-4.66</v>
+        <v>-4.27</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -4043,12 +4954,12 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1149.2286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 181.8114 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
+          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
@@ -4060,17 +4971,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4090,20 +5001,20 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>187.46</v>
+        <v>239.45</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>177.93</v>
+        <v>221.92</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-5.08</v>
+        <v>-7.32</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -4117,12 +5028,12 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 181.8114 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 232.2186 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
@@ -4134,17 +5045,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -4154,64 +5065,66 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>187.94</v>
+        <v>1449.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>174.34</v>
+        <v>1334.3</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-7.24</v>
+        <v>-7.95</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Stop-loss triggered</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>40.6</v>
+          <t>Stop breached</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-09-11 · stop_source=dynamic</t>
+          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260909-29ffd5</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4226,71 +5139,69 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>239.45</v>
+        <v>427.3</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>222.66</v>
+        <v>416.75</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-7.01</v>
+        <v>-2.47</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>31.3</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 232.2186 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-10-06 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R2-COALINDIA-20260928-5e50fa</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -4300,52 +5211,54 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>273.3</v>
+        <v>1413.5</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>253.35</v>
+        <v>1335.6</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-7.3</v>
+        <v>-5.51</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Stop-loss triggered</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>28.4</v>
+          <t>Stop breached</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-10-05 · stop_source=dynamic</t>
+          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
@@ -4357,12 +5270,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -4386,13 +5299,13 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>818.3</v>
+        <v>187.94</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>806.6</v>
+        <v>174.34</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-1.43</v>
+        <v>-7.24</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>26</v>
@@ -4403,7 +5316,7 @@
         </is>
       </c>
       <c r="M10" s="4" t="n">
-        <v>31.2</v>
+        <v>40.6</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
@@ -4412,7 +5325,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
+          <t>IND-R2-SAIL-20260909-29ffd5</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -4429,12 +5342,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -4458,13 +5371,13 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2825</v>
+        <v>273.3</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2719.7</v>
+        <v>253.35</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-3.73</v>
+        <v>-7.3</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>26</v>
@@ -4475,7 +5388,7 @@
         </is>
       </c>
       <c r="M11" s="4" t="n">
-        <v>36.1</v>
+        <v>28.4</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -4484,7 +5397,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
+          <t>IND-R2-NLCINDIA-20260909-24d7ce</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -4501,12 +5414,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -4530,13 +5443,13 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3365.2</v>
+        <v>818.3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3228</v>
+        <v>806.6</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-4.08</v>
+        <v>-1.43</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>26</v>
@@ -4547,16 +5460,16 @@
         </is>
       </c>
       <c r="M12" s="4" t="n">
-        <v>40.4</v>
+        <v>31.2</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-09-15 · stop_source=dynamic</t>
+          <t>EXIT_STOP · trigger crossed 2026-09-11 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MCX-20260909-1bc45f</t>
+          <t>IND-R2-NATCOPHARM-20260909-c00756</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -4573,7 +5486,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4598,20 +5511,20 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>321.75</v>
+        <v>2825</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>311.45</v>
+        <v>2719.7</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-3.2</v>
+        <v>-3.73</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -4619,7 +5532,7 @@
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>33.2</v>
+        <v>36.1</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
@@ -4628,7 +5541,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MANAPPURAM-20260916-6576e5</t>
+          <t>IND-R2-MUTHOOTFIN-20260909-0c1090</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -4645,7 +5558,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4670,20 +5583,20 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>400.4</v>
+        <v>3365.2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>389.6</v>
+        <v>3228</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-2.7</v>
+        <v>-4.08</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -4691,16 +5604,16 @@
         </is>
       </c>
       <c r="M14" s="4" t="n">
-        <v>32.3</v>
+        <v>40.4</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-10-05 · stop_source=dynamic</t>
+          <t>EXIT_STOP · trigger crossed 2026-09-15 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260911-098cc1</t>
+          <t>IND-R2-MCX-20260909-1bc45f</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -4717,12 +5630,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -4742,20 +5655,20 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1284.5</v>
+        <v>321.75</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1237.6</v>
+        <v>311.45</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-3.65</v>
+        <v>-3.2</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -4763,7 +5676,7 @@
         </is>
       </c>
       <c r="M15" s="4" t="n">
-        <v>40.6</v>
+        <v>33.2</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
@@ -4772,7 +5685,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWSTEEL-20260923-8ac9fe</t>
+          <t>IND-R2-MANAPPURAM-20260916-6576e5</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -4789,7 +5702,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4804,54 +5717,52 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1449.5</v>
+        <v>400.4</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1318.3</v>
+        <v>389.6</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-9.050000000000001</v>
+        <v>-2.7</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>32.3</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-10-05 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R2-LICI-20260911-098cc1</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -4863,7 +5774,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -4888,20 +5799,20 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>588.9</v>
+        <v>1284.5</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>586.35</v>
+        <v>1237.6</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.43</v>
+        <v>-3.65</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -4909,16 +5820,16 @@
         </is>
       </c>
       <c r="M17" s="4" t="n">
-        <v>31.9</v>
+        <v>40.6</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-09-18 · stop_source=dynamic</t>
+          <t>EXIT_STOP · trigger crossed 2026-10-05 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20260918-0ba353</t>
+          <t>IND-R2-JSWSTEEL-20260923-8ac9fe</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
@@ -4935,12 +5846,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -4960,20 +5871,20 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>373.25</v>
+        <v>588.9</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>376.35</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>0.83</v>
+        <v>586.35</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-0.43</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -4981,16 +5892,16 @@
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>28.4</v>
+        <v>31.9</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-09-11 · stop_source=dynamic</t>
+          <t>EXIT_STOP · trigger crossed 2026-09-18 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DABUR-20260911-8f250f</t>
+          <t>IND-R2-GNFC-20260918-0ba353</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
@@ -5007,12 +5918,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -5022,54 +5933,52 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1413.5</v>
+        <v>373.25</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1333.1</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>-5.69</v>
+        <v>376.35</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0.83</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>28.4</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-09-11 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R2-DABUR-20260911-8f250f</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -9741,10 +10650,10 @@
         <v>381.6</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>350.3</v>
+        <v>355.6</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>-8.199999999999999</v>
+        <v>-6.81</v>
       </c>
       <c r="K84" s="4" t="n">
         <v>35</v>
@@ -9889,10 +10798,10 @@
         <v>1048.7</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>961</v>
+        <v>952.75</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>-8.359999999999999</v>
+        <v>-9.15</v>
       </c>
       <c r="K86" s="4" t="n">
         <v>18</v>
@@ -9963,10 +10872,10 @@
         <v>1642.5</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>1465.2</v>
+        <v>1506.9</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>-10.79</v>
+        <v>-8.26</v>
       </c>
       <c r="K87" s="4" t="n">
         <v>35</v>
@@ -10111,10 +11020,10 @@
         <v>2410</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>2013.3</v>
+        <v>2023.1</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>-16.46</v>
+        <v>-16.05</v>
       </c>
       <c r="K89" s="4" t="n">
         <v>34</v>
@@ -10185,10 +11094,10 @@
         <v>507.9</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>456.15</v>
+        <v>454.9</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>-10.19</v>
+        <v>-10.44</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>35</v>
@@ -10259,10 +11168,10 @@
         <v>2064.9</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1833.3</v>
+        <v>1864.5</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>-11.22</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="K91" s="4" t="n">
         <v>27</v>
@@ -10333,10 +11242,10 @@
         <v>385.15</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>376.35</v>
-      </c>
-      <c r="J92" s="6" t="n">
-        <v>-2.28</v>
+        <v>385.65</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>0.13</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>11</v>
@@ -10407,10 +11316,10 @@
         <v>5454.5</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>4759.6</v>
+        <v>4862.7</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>-12.74</v>
+        <v>-10.85</v>
       </c>
       <c r="K93" s="4" t="n">
         <v>35</v>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W65"/>
+  <dimension ref="A1:W71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,21 +508,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-06 · prices = 2026-10-06 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-07 · prices = 2026-10-07 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>39 investable · NEW 9 · ACTIVE+ 30 · ACTIVE 0   ·   R2 35 · MOMENTUM 0 · R1 4 (advisory)   ·   9 row(s) read 0.00%: admitted at the 2026-10-06 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>45 investable · NEW 6 · ACTIVE+ 39 · ACTIVE 0   ·   R2 41 · MOMENTUM 0 · R1 4 (advisory)   ·   6 row(s) read 0.00%: admitted at the 2026-10-07 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 39 position(s) with an INTACT stop · if all of them fired today the average outcome is -2.68% from entry, worst single -9.02%</t>
+          <t>🛡 DOWNSIDE · 45 position(s) with an INTACT stop · if all of them fired today the average outcome is -2.40% from entry, worst single -8.13%</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=9 · 228 scored · 38 already in CURRENT · biggest blocker: model disagreement (174) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=6 · 228 scored · 44 already in CURRENT · biggest blocker: model disagreement (172) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 35 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 41 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -697,29 +697,29 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>293.95</v>
+        <v>5961</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>293.95</v>
+        <v>5961</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>34.3</v>
+        <v>33.3</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>278.3</v>
+        <v>5734.1429</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,22 +746,22 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>5.32</v>
+        <v>3.81</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-5.32</v>
+        <v>-3.81</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>317.43</v>
+        <v>6301.29</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20261006-fc497f</t>
+          <t>IND-R2-ATUL-20261007-6aad3b</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -798,25 +798,25 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1243</v>
+        <v>324.7</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1243</v>
+        <v>324.7</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>35</v>
+        <v>39.3</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1200.2857</v>
+        <v>310.3143</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>3.44</v>
+        <v>4.43</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.44</v>
+        <v>-4.43</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1307.07</v>
+        <v>346.28</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AXISBANK-20261006-79c723</t>
+          <t>IND-R2-FEDERALBNK-20261007-b739c0</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -899,29 +899,29 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1552.3</v>
+        <v>2074.1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1552.3</v>
+        <v>2074.1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1482.0857</v>
+        <v>1986.7145</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,17 +948,17 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>4.52</v>
+        <v>4.21</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-4.52</v>
+        <v>-4.21</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1657.62</v>
+        <v>2205.18</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20261006-676b03</t>
+          <t>IND-R2-MAZDOCK-20261007-e84c93</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1000,29 +1000,29 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>814.35</v>
+        <v>2813.6</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>814.35</v>
+        <v>2813.6</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>32.9</v>
+        <v>11.2</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>785.9786</v>
+        <v>2714.9858</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1049,22 +1049,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.48</v>
+        <v>-3.5</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>856.91</v>
+        <v>2961.52</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20261006-0d13b1</t>
+          <t>IND-R2-MM-20261007-c1210c</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1101,29 +1101,29 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>74.04000000000001</v>
+        <v>449.45</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>74.04000000000001</v>
+        <v>449.45</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>31.2</v>
+        <v>35.4</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>70.90860000000001</v>
+        <v>429.9857</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1150,17 +1150,17 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-4.23</v>
+        <v>-4.33</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>78.73999999999999</v>
+        <v>478.65</v>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NMDC-20261006-2acbae</t>
+          <t>IND-R2-OIL-20261007-ed8f2f</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1202,29 +1202,29 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>323.6</v>
+        <v>358</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>323.6</v>
+        <v>358</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>29.2</v>
+        <v>36.4</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>311.3143</v>
+        <v>339.5286</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1251,17 +1251,17 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.8</v>
+        <v>5.16</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.8</v>
+        <v>-5.16</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>342.03</v>
+        <v>394.94</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PFC-20261006-e91ac2</t>
+          <t>IND-R2-PATANJALI-20261007-ff8244</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1298,34 +1298,34 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>112.03</v>
+        <v>464.25</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>112.03</v>
+        <v>633.8</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>36.52</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>35</v>
+        <v>31.2</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>108.1043</v>
+        <v>594.7963999999999</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1352,22 +1352,24 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.5</v>
+        <v>6.15</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="U14" s="4" t="n">
-        <v>117.92</v>
+        <v>28.12</v>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20261006-66ccb3</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1381,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1389,7 +1391,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1399,34 +1401,34 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>617.4</v>
+        <v>3110.4</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>617.4</v>
+        <v>3353.3</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7.81</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>20.6</v>
+        <v>34.8</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1445,7 +1447,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>561.7018</v>
+        <v>3183.8001</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1453,22 +1455,24 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>9.02</v>
+        <v>5.05</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-9.02</v>
-      </c>
-      <c r="U15" s="4" t="n">
-        <v>728.8</v>
+        <v>2.36</v>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACHEM-20261006-fc5587</t>
+          <t>IND-R2-BSE-20261005-7af4a1</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1484,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1490,7 +1494,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1500,34 +1504,34 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>167.95</v>
+        <v>285</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>167.95</v>
+        <v>296.85</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>4.16</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>32.9</v>
+        <v>35.4</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1546,7 +1550,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>160.5157</v>
+        <v>285.4429</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1554,22 +1558,24 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.43</v>
+        <v>3.84</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-4.43</v>
-      </c>
-      <c r="U16" s="4" t="n">
-        <v>179.1</v>
+        <v>0.16</v>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20261006-801564</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1587,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1601,34 +1607,34 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>464.25</v>
+        <v>293.95</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>634</v>
+        <v>304.7</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>36.56</v>
+        <v>3.66</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>31.2</v>
+        <v>34.3</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1647,7 +1653,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>594.7963999999999</v>
+        <v>288.7214</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1655,24 +1661,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>6.18</v>
+        <v>5.24</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>28.12</v>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-1.78</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>317.43</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-ANGELONE-20261006-fc497f</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1704,30 +1708,30 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3110.4</v>
+        <v>424.55</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3283</v>
+        <v>440</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>5.55</v>
+        <v>3.64</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>34.8</v>
+        <v>34.1</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -1750,7 +1754,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>3119.7</v>
+        <v>421.3643</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1758,22 +1762,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>4.97</v>
+        <v>4.24</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.3</v>
+        <v>-0.75</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3350.16</v>
+        <v>449.3</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BSE-20261005-7af4a1</t>
+          <t>IND-R2-KOTAKBANK-20261002-563392</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1789,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1805,34 +1809,34 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-30</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>285</v>
+        <v>17.07</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>296.25</v>
+        <v>17.62</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>3.95</v>
+        <v>3.22</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>35.4</v>
+        <v>31.3</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1851,7 +1855,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>284.6429</v>
+        <v>16.7686</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1859,22 +1863,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>3.92</v>
+        <v>4.83</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.13</v>
+        <v>-1.77</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>296.6</v>
+        <v>18.41</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-IRB-20260930-4c1d2d</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1890,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1906,34 +1910,34 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2056.8</v>
+        <v>167.95</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2089.8</v>
+        <v>173.17</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1.6</v>
+        <v>3.11</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>34.9</v>
+        <v>32.9</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1952,7 +1956,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1991.8715</v>
+        <v>164.9643</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1960,22 +1964,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-3.16</v>
+        <v>-1.78</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>2224.78</v>
+        <v>179.1</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260928-f23b4c</t>
+          <t>IND-R2-UNIONBANK-20261006-801564</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1991,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2007,34 +2011,34 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>424.55</v>
+        <v>71.23</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>431.25</v>
+        <v>72.8</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>34.1</v>
+        <v>31.3</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2053,7 +2057,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>413.5929</v>
+        <v>70.5686</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2061,22 +2065,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.09</v>
+        <v>3.07</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.58</v>
+        <v>-0.93</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>449.3</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20261002-563392</t>
+          <t>IND-R2-NHPC-20261005-cad510</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2092,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2108,34 +2112,34 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>71.23</v>
+        <v>112.03</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>72.18000000000001</v>
+        <v>114.41</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>31.3</v>
+        <v>35</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2154,7 +2158,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>69.8943</v>
+        <v>110.2143</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2162,17 +2166,17 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>3.17</v>
+        <v>3.67</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.88</v>
+        <v>-1.62</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>74.73999999999999</v>
+        <v>117.92</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NHPC-20261005-cad510</t>
+          <t>IND-R2-PNB-20261006-66ccb3</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
@@ -2189,7 +2193,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2209,34 +2213,34 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>363.4</v>
+        <v>2056.8</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>366.5</v>
+        <v>2092.8</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.85</v>
+        <v>1.75</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>33.3</v>
+        <v>34.9</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2255,7 +2259,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>352.7286</v>
+        <v>1995.5715</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2263,22 +2267,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.76</v>
+        <v>4.65</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.94</v>
+        <v>-2.98</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>385.91</v>
+        <v>2224.78</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBUJACEM-20261005-e13c8d</t>
+          <t>IND-R2-TCS-20260928-f23b4c</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2294,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2310,34 +2314,34 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-30</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>17.07</v>
+        <v>814.35</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>17.08</v>
+        <v>825.5</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.06</v>
+        <v>1.37</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>31.3</v>
+        <v>32.9</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2356,7 +2360,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>16.2586</v>
+        <v>796.7786</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2364,22 +2368,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.81</v>
+        <v>3.48</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-4.75</v>
+        <v>-2.16</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>18.41</v>
+        <v>856.91</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260930-4c1d2d</t>
+          <t>IND-R2-INDIANB-20261006-0d13b1</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2395,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2411,34 +2415,34 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>8128.5</v>
+        <v>1243</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8106.5</v>
+        <v>1258</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>-0.27</v>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>1.21</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>38.7</v>
+        <v>35</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2457,7 +2461,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>8064.2857</v>
+        <v>1215.4286</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2465,22 +2469,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.52</v>
+        <v>3.38</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.79</v>
+        <v>-2.22</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>8660.25</v>
+        <v>1307.07</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-AXISBANK-20261006-79c723</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2496,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2512,34 +2516,34 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-23</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3897</v>
+        <v>323.6</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3886.1</v>
+        <v>326.7</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>-0.28</v>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0.96</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>35</v>
+        <v>29.2</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2558,7 +2562,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3727.7429</v>
+        <v>314.2929</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2566,22 +2570,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.07</v>
+        <v>3.8</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-4.34</v>
+        <v>-2.88</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4235.85</v>
+        <v>342.03</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AIAENG-20260923-be0111</t>
+          <t>IND-R2-PFC-20261006-e91ac2</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2597,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>VINATIORGA</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2613,34 +2617,34 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1193.8</v>
+        <v>119.47</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1190.4</v>
+        <v>120.05</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>-0.28</v>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0.49</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>27.5</v>
+        <v>30.2</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2659,7 +2663,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1141.0287</v>
+        <v>115.81</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2667,22 +2671,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.15</v>
+        <v>3.53</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-4.42</v>
+        <v>-3.06</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1272.96</v>
+        <v>125.65</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VINATIORGA-20260928-756b01</t>
+          <t>IND-R2-CANBK-20261005-19551d</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2698,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2714,34 +2718,34 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1010.1</v>
+        <v>698.65</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1006.7</v>
+        <v>699.45</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>-0.34</v>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.11</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>38.3</v>
+        <v>30.9</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2760,7 +2764,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>969.4213999999999</v>
+        <v>668.4357</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2768,22 +2772,22 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.7</v>
+        <v>4.43</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-4.03</v>
+        <v>-4.32</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1076.14</v>
+        <v>749.47</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20261002-20a2cb</t>
+          <t>IND-R2-CAMS-20260928-86e0a0</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2815,34 +2819,34 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1949</v>
+        <v>1552.3</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1939</v>
+        <v>1554</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>-0.51</v>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0.11</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2861,7 +2865,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1925.8</v>
+        <v>1486.5571</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2869,22 +2873,22 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.68</v>
+        <v>4.34</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-1.19</v>
+        <v>-4.24</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2054.6</v>
+        <v>1657.62</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IPCALAB-20260909-af9aea</t>
+          <t>IND-R2-DEEPAKNTR-20261006-676b03</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2900,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2916,34 +2920,34 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-30</t>
+          <t>Admitted 2026-09-23</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>946.1</v>
+        <v>3897</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>941.15</v>
+        <v>3897.9</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>-0.52</v>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>38.2</v>
+        <v>35</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2962,7 +2966,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>911.6571</v>
+        <v>3727.7429</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2970,22 +2974,22 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.13</v>
+        <v>4.37</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.64</v>
+        <v>-4.34</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>997.76</v>
+        <v>4235.85</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDALCO-20260930-e02b35</t>
+          <t>IND-R2-AIAENG-20260923-be0111</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3001,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3017,34 +3021,34 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-01</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>223.39</v>
+        <v>8128.5</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>221.92</v>
+        <v>8117</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.66</v>
+        <v>-0.14</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>31.2</v>
+        <v>38.7</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3063,7 +3067,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>216.2243</v>
+        <v>8064.2857</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3071,22 +3075,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>2.57</v>
+        <v>0.65</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-3.21</v>
+        <v>-0.79</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>234.14</v>
+        <v>8660.25</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ONGC-20261001-b42383</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3102,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3118,34 +3122,34 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-24</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1790.3</v>
+        <v>961</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1775.6</v>
+        <v>959.55</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.82</v>
+        <v>-0.15</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>33.3</v>
+        <v>37.2</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3164,7 +3168,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1719.7429</v>
+        <v>934.9285</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3172,22 +3176,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-3.94</v>
+        <v>-2.71</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1896.14</v>
+        <v>1003.19</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIPORTS-20260924-58df63</t>
+          <t>IND-R2-SBIN-20261005-104400</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3203,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3219,34 +3223,34 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>961</v>
+        <v>1949</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>952.75</v>
+        <v>1943.4</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.86</v>
+        <v>-0.29</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>37.2</v>
+        <v>40.6</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3265,7 +3269,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>932.8714</v>
+        <v>1925.8</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3273,22 +3277,22 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>2.09</v>
+        <v>0.91</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-2.93</v>
+        <v>-1.19</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1003.19</v>
+        <v>2054.6</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20261005-104400</t>
+          <t>IND-R2-IPCALAB-20260909-af9aea</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3332,15 +3336,15 @@
         <v>142.41</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>141.1</v>
+        <v>141.77</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.92</v>
+        <v>-0.45</v>
       </c>
       <c r="L34" s="4" t="n">
         <v>33.3</v>
@@ -3374,7 +3378,7 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>3.03</v>
+        <v>3.49</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>-3.92</v>
@@ -3389,7 +3393,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3405,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3421,34 +3425,34 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>11671</v>
+        <v>617.4</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11560</v>
+        <v>613.45</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.95</v>
+        <v>-0.64</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>31.3</v>
+        <v>20.6</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3467,7 +3471,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>11319</v>
+        <v>567.2232</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3475,22 +3479,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.08</v>
+        <v>7.54</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-3.02</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>12199</v>
+        <v>728.8</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARUTI-20261002-ee9f86</t>
+          <t>IND-R2-TATACHEM-20261006-fc5587</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3506,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3522,34 +3526,34 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-21</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>124830</v>
+        <v>10700</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>123610</v>
+        <v>10628</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.98</v>
+        <v>-0.67</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>29.3</v>
+        <v>43.6</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3568,7 +3572,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>121363.5714</v>
+        <v>10182.9286</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3576,22 +3580,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>1.82</v>
+        <v>4.19</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-2.78</v>
+        <v>-4.83</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>130238.57</v>
+        <v>11796.71</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MRF-20260921-31a31a</t>
+          <t>IND-R2-OFSS-20260928-d4ee3d</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3607,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3623,34 +3627,34 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>119.47</v>
+        <v>1010.1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>118.27</v>
+        <v>1002.5</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>30.2</v>
+        <v>38.3</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3669,7 +3673,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>115.3486</v>
+        <v>969.4213999999999</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3677,22 +3681,22 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-3.45</v>
+        <v>-4.03</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>125.65</v>
+        <v>1076.14</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20261005-19551d</t>
+          <t>IND-R2-INFY-20261002-20a2cb</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3708,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3724,34 +3728,34 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-29</t>
+          <t>Admitted 2026-09-24</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>3150.4</v>
+        <v>1790.3</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>3095.5</v>
+        <v>1773.3</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-1.74</v>
+        <v>-0.95</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>29.2</v>
+        <v>33.3</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3770,7 +3774,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>3019.3428</v>
+        <v>1719.7429</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3778,22 +3782,22 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>2.46</v>
+        <v>3.02</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-4.16</v>
+        <v>-3.94</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>3346.99</v>
+        <v>1896.14</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
+          <t>IND-R2-ADANIPORTS-20260924-58df63</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3809,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3825,34 +3829,34 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-01</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>698.65</v>
+        <v>223.39</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>685.85</v>
+        <v>221.06</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-1.83</v>
+        <v>-1.04</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>30.9</v>
+        <v>31.2</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3871,7 +3875,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>664.7714999999999</v>
+        <v>216.2243</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3879,22 +3883,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>3.07</v>
+        <v>2.19</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-4.85</v>
+        <v>-3.21</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>749.47</v>
+        <v>234.14</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CAMS-20260928-86e0a0</t>
+          <t>IND-R2-ONGC-20261001-b42383</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3910,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3926,30 +3930,30 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-16</t>
+          <t>Admitted 2026-09-21</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>407.75</v>
+        <v>124830</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>400.25</v>
+        <v>123360</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-1.84</v>
+        <v>-1.18</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>33.3</v>
+        <v>29.3</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
@@ -3972,7 +3976,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>392.3429</v>
+        <v>121363.5714</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3980,22 +3984,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-3.78</v>
+        <v>-2.78</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>436.95</v>
+        <v>130238.57</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
+          <t>IND-R2-MRF-20260921-31a31a</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4011,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4027,30 +4031,30 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-09-29</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>10700</v>
+        <v>3150.4</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>10461</v>
+        <v>3107.8</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-2.23</v>
+        <v>-1.35</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>43.6</v>
+        <v>29.2</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
@@ -4073,7 +4077,7 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>10182.9286</v>
+        <v>3019.3428</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4081,22 +4085,22 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-4.83</v>
+        <v>-4.16</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>11796.71</v>
+        <v>3346.99</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260928-d4ee3d</t>
+          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
         </is>
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4112,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4128,34 +4132,34 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>453.15</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>442.3</v>
+        <v>72.97</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-2.39</v>
+        <v>-1.45</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4174,7 +4178,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>430.3428</v>
+        <v>70.90860000000001</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4182,22 +4186,22 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-5.03</v>
+        <v>-4.23</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>487.36</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CONCOR-20260928-51a3e4</t>
+          <t>IND-R2-NMDC-20261006-2acbae</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4209,12 +4213,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4224,41 +4228,39 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>397</v>
+        <v>363.4</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>431.25</v>
+        <v>358.05</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4277,7 +4279,7 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>386.4571</v>
+        <v>352.7286</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4285,24 +4287,22 @@
         </is>
       </c>
       <c r="S43" s="4" t="n">
-        <v>10.39</v>
+        <v>1.49</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="U43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-2.94</v>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>385.91</v>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-AMBUJACEM-20261005-e13c8d</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -4329,41 +4329,39 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-05</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>417.6</v>
+        <v>407.75</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>416.75</v>
+        <v>400.85</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-1.69</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4382,7 +4380,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>407.3714</v>
+        <v>392.3429</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
@@ -4390,22 +4388,22 @@
         </is>
       </c>
       <c r="S44" s="4" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>-2.45</v>
+        <v>-3.78</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>432.94</v>
+        <v>436.95</v>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
         </is>
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4417,12 +4415,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -4432,37 +4430,35 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>389.85</v>
+        <v>453.15</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>386.05</v>
+        <v>445</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+        <v>-1.8</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>33.3</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
@@ -4485,7 +4481,7 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>378.3286</v>
+        <v>430.3428</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4493,22 +4489,22 @@
         </is>
       </c>
       <c r="S45" s="4" t="n">
-        <v>2</v>
+        <v>3.29</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>-2.96</v>
+        <v>-5.03</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>407.13</v>
+        <v>487.36</v>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R2-CONCOR-20260928-51a3e4</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4520,244 +4516,858 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-10-02</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>11671</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>11416</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>11319</v>
+      </c>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S46" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="T46" s="4" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>12199</v>
+      </c>
+      <c r="V46" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-MARUTI-20261002-ee9f86</t>
+        </is>
+      </c>
+      <c r="W46" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-30</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>946.1</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>918.75</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>911.6571</v>
+      </c>
+      <c r="R47" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S47" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="T47" s="4" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>997.76</v>
+      </c>
+      <c r="V47" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-HINDALCO-20260930-e02b35</t>
+        </is>
+      </c>
+      <c r="W47" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>VINATIORGA</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-28</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>1193.8</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>1150</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>1141.0287</v>
+      </c>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S48" s="4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="T48" s="4" t="n">
+        <v>-4.42</v>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>1272.96</v>
+      </c>
+      <c r="V48" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-VINATIORGA-20260928-756b01</t>
+        </is>
+      </c>
+      <c r="W48" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>397</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>386.4571</v>
+      </c>
+      <c r="R49" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S49" s="4" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="T49" s="4" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="U49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V49" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+        </is>
+      </c>
+      <c r="W49" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-05</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>414.9</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>407.3714</v>
+      </c>
+      <c r="R50" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S50" s="4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T50" s="4" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>432.94</v>
+      </c>
+      <c r="V50" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+        </is>
+      </c>
+      <c r="W50" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>378.3286</v>
+      </c>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S51" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="T51" s="4" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="U51" s="4" t="n">
+        <v>407.13</v>
+      </c>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
+        </is>
+      </c>
+      <c r="W51" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-11</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>1191</v>
       </c>
-      <c r="I46" s="4" t="n">
-        <v>1150.9</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>-3.37</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
+      <c r="I52" s="4" t="n">
+        <v>1157.8</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O46" s="4" t="inlineStr">
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P46" s="4" t="inlineStr">
+      <c r="P52" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q46" s="4" t="n">
+      <c r="Q52" s="4" t="n">
         <v>1149.2286</v>
       </c>
-      <c r="R46" s="4" t="inlineStr">
+      <c r="R52" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S46" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="T46" s="4" t="n">
+      <c r="S52" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T52" s="4" t="n">
         <v>-3.51</v>
       </c>
-      <c r="U46" s="4" t="n">
+      <c r="U52" s="4" t="n">
         <v>1253.66</v>
       </c>
-      <c r="V46" s="4" t="inlineStr">
+      <c r="V52" s="4" t="inlineStr">
         <is>
           <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
         </is>
       </c>
-      <c r="W46" s="4" t="inlineStr">
+      <c r="W52" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A68:W68"/>
+    <mergeCell ref="A67:W67"/>
     <mergeCell ref="A58:W58"/>
     <mergeCell ref="A64:W64"/>
     <mergeCell ref="A59:W59"/>
-    <mergeCell ref="A49:W49"/>
-    <mergeCell ref="A51:W51"/>
     <mergeCell ref="A60:W60"/>
     <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A70:W70"/>
     <mergeCell ref="A61:W61"/>
     <mergeCell ref="A6:W6"/>
-    <mergeCell ref="A54:W54"/>
+    <mergeCell ref="A69:W69"/>
     <mergeCell ref="A65:W65"/>
+    <mergeCell ref="A66:W66"/>
     <mergeCell ref="A56:W56"/>
-    <mergeCell ref="A50:W50"/>
     <mergeCell ref="A3:W3"/>
     <mergeCell ref="A55:W55"/>
     <mergeCell ref="A57:W57"/>
     <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A71:W71"/>
     <mergeCell ref="A5:W5"/>
-    <mergeCell ref="A53:W53"/>
     <mergeCell ref="A4:W4"/>
     <mergeCell ref="A62:W62"/>
-    <mergeCell ref="A52:W52"/>
     <mergeCell ref="A63:W63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4794,7 +5404,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-06</t>
+          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4897,7 +5507,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -4934,13 +5544,13 @@
         <v>187.46</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>179.45</v>
+        <v>176.54</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-4.27</v>
+        <v>-5.83</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -4971,7 +5581,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -5008,13 +5618,13 @@
         <v>239.45</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>221.92</v>
+        <v>221.06</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-7.32</v>
+        <v>-7.68</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -5045,7 +5655,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -5082,13 +5692,13 @@
         <v>1449.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1334.3</v>
+        <v>1349.9</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-7.95</v>
+        <v>-6.87</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -5119,17 +5729,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -5139,52 +5749,54 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>427.3</v>
+        <v>1413.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>416.75</v>
+        <v>1328.6</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-2.47</v>
+        <v>-6.01</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Stop-loss triggered</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>31.3</v>
+          <t>Stop breached</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-10-06 · stop_source=dynamic</t>
+          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260928-5e50fa</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5808,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -5211,54 +5823,52 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1413.5</v>
+        <v>427.3</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1335.6</v>
+        <v>416.75</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-5.51</v>
+        <v>-2.47</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>31.3</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-10-06 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R2-COALINDIA-20260928-5e50fa</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -10650,10 +11260,10 @@
         <v>381.6</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>355.6</v>
+        <v>346.05</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>-6.81</v>
+        <v>-9.32</v>
       </c>
       <c r="K84" s="4" t="n">
         <v>35</v>
@@ -10798,10 +11408,10 @@
         <v>1048.7</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>952.75</v>
+        <v>959.55</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>-9.15</v>
+        <v>-8.5</v>
       </c>
       <c r="K86" s="4" t="n">
         <v>18</v>
@@ -10872,10 +11482,10 @@
         <v>1642.5</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>1506.9</v>
+        <v>1496.3</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>-8.26</v>
+        <v>-8.9</v>
       </c>
       <c r="K87" s="4" t="n">
         <v>35</v>
@@ -11020,10 +11630,10 @@
         <v>2410</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>2023.1</v>
+        <v>2018.5</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>-16.05</v>
+        <v>-16.24</v>
       </c>
       <c r="K89" s="4" t="n">
         <v>34</v>
@@ -11094,10 +11704,10 @@
         <v>507.9</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>454.9</v>
+        <v>455.7</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>-10.44</v>
+        <v>-10.28</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>35</v>
@@ -11168,10 +11778,10 @@
         <v>2064.9</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1864.5</v>
+        <v>1866.4</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="K91" s="4" t="n">
         <v>27</v>
@@ -11242,10 +11852,10 @@
         <v>385.15</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>385.65</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>0.13</v>
+        <v>380.15</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>-1.3</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>11</v>
@@ -11316,10 +11926,10 @@
         <v>5454.5</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>4862.7</v>
+        <v>4792.1</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>-10.85</v>
+        <v>-12.14</v>
       </c>
       <c r="K93" s="4" t="n">
         <v>35</v>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W75"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,42 +508,42 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-12 · prices = 2026-10-12 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-13 · prices = 2026-10-13 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>49 investable · NEW 6 · ACTIVE+ 43 · ACTIVE 0   ·   R2 48 · MOMENTUM 0 · R1 1 (advisory)   ·   6 row(s) read 0.00%: admitted at the 2026-10-12 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>53 investable · NEW 4 · ACTIVE+ 49 · ACTIVE 0   ·   R2 51 · MOMENTUM 0 · R1 2 (advisory)   ·   4 row(s) read 0.00%: admitted at the 2026-10-13 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 49 position(s) with an INTACT stop · if all of them fired today the average outcome is -2.10% from entry, worst single -7.50%</t>
+          <t>🛡 DOWNSIDE · 53 position(s) with an INTACT stop · if all of them fired today the average outcome is -1.74% from entry, worst single -5.25%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 15 position(s) left CURRENT on a STOP BREACH (R1 15 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>🔴 14 position(s) left CURRENT on a STOP BREACH (R1 14 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=6 · 228 scored · 48 already in CURRENT · biggest blocker: model disagreement (163) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=4 · 228 scored · 52 already in CURRENT · biggest blocker: model disagreement (160) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 48 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 51 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -697,29 +697,29 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1129.3</v>
+        <v>10581</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1129.3</v>
+        <v>10581</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>26.2</v>
+        <v>35.9</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1093.2572</v>
+        <v>10140.4286</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,17 +746,17 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.19</v>
+        <v>4.16</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.19</v>
+        <v>-4.16</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1183.36</v>
+        <v>11241.86</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ACC-20261012-f1f022</t>
+          <t>IND-R2-BAJAJHLDNG-20261013-3e863a</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>BALKRISIND</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -798,29 +798,29 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>158.38</v>
+        <v>1987</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>158.38</v>
+        <v>1987</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>28.1</v>
+        <v>33.2</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>149.4304</v>
+        <v>1908.6428</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,17 +847,17 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>5.65</v>
+        <v>3.94</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-5.65</v>
+        <v>-3.94</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>176.28</v>
+        <v>2104.54</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20261012-efab94</t>
+          <t>IND-R2-BALKRISIND-20261013-38dd43</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -899,29 +899,29 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2254.5</v>
+        <v>1315.4</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2254.5</v>
+        <v>1315.4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2148.1429</v>
+        <v>1246.3428</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>4.72</v>
+        <v>5.25</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-4.72</v>
+        <v>-5.25</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2414.04</v>
+        <v>1418.99</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GLENMARK-20261012-f70810</t>
+          <t>IND-R2-HCLTECH-20261013-955276</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1000,29 +1000,29 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>589.55</v>
+        <v>167.79</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>589.55</v>
+        <v>167.79</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>31.9</v>
+        <v>38.2</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>562.0732</v>
+        <v>161.0314</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1049,22 +1049,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.66</v>
+        <v>4.03</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-4.66</v>
+        <v>-4.03</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>644.5</v>
+        <v>177.93</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20261012-e5db63</t>
+          <t>IND-R2-WIPRO-20261013-d844f1</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1096,34 +1096,34 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1173.3</v>
+        <v>464.25</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1173.3</v>
+        <v>626.35</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>34.92</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>38.2</v>
+        <v>31.2</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1128.3429</v>
+        <v>594.7963999999999</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1150,22 +1150,24 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>3.83</v>
+        <v>5.04</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>1240.74</v>
+        <v>28.12</v>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWSTEEL-20261012-af40fc</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1179,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1187,7 +1189,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1197,34 +1199,34 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2629</v>
+        <v>2056.8</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2629</v>
+        <v>2259</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>9.83</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>35.9</v>
+        <v>34.9</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1243,7 +1245,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2530.3143</v>
+        <v>2155.5429</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1251,22 +1253,24 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.75</v>
+        <v>4.58</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>2777.03</v>
+        <v>4.8</v>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20261012-9e0c35</t>
+          <t>IND-R2-TCS-20260928-f23b4c</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1282,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1298,34 +1302,34 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-29</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>464.25</v>
+        <v>3150.4</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>634.2</v>
+        <v>3394.4</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>36.61</v>
+        <v>7.75</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>31.2</v>
+        <v>29.2</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1344,7 +1348,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>594.7963999999999</v>
+        <v>3229.2572</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1352,10 +1356,10 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>6.21</v>
+        <v>4.87</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>28.12</v>
+        <v>2.5</v>
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
@@ -1364,12 +1368,12 @@
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1385,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1401,30 +1405,30 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3110.4</v>
+        <v>158.38</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3315.1</v>
+        <v>169.49</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>6.58</v>
+        <v>7.01</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>34.8</v>
+        <v>28.1</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
@@ -1447,7 +1451,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>3183.8001</v>
+        <v>159.3714</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1455,22 +1459,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>3.96</v>
+        <v>5.97</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.36</v>
+        <v>0.63</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3350.16</v>
+        <v>176.28</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BSE-20261005-7af4a1</t>
+          <t>IND-R2-BANDHANBNK-20261012-efab94</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1486,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1502,34 +1506,34 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2056.8</v>
+        <v>3110.4</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2154.5</v>
+        <v>3311</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4.75</v>
+        <v>6.45</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1548,7 +1552,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>2060.9857</v>
+        <v>3183.8001</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1556,22 +1560,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.34</v>
+        <v>3.84</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.2</v>
+        <v>2.36</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2224.78</v>
+        <v>3350.16</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260928-f23b4c</t>
+          <t>IND-R2-BSE-20261005-7af4a1</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1587,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1603,34 +1607,34 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-30</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>17.07</v>
+        <v>323.6</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>17.85</v>
+        <v>337.35</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>31.3</v>
+        <v>29.2</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1649,7 +1653,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>16.9243</v>
+        <v>323.0786</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1657,22 +1661,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.19</v>
+        <v>4.23</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.85</v>
+        <v>-0.16</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>18.41</v>
+        <v>342.03</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260930-4c1d2d</t>
+          <t>IND-R2-PFC-20261006-e91ac2</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1713,25 +1717,25 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>424.55</v>
+        <v>1010.1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>440.5</v>
+        <v>1052.55</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>34.1</v>
+        <v>38.3</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1750,7 +1754,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>424.4929</v>
+        <v>1009.4429</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1758,22 +1762,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.63</v>
+        <v>4.1</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>449.3</v>
+        <v>1076.14</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20261002-563392</t>
+          <t>IND-R2-INFY-20261002-20a2cb</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1817,15 +1821,15 @@
         <v>1552.3</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1608.2</v>
+        <v>1609</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>35.4</v>
@@ -1851,7 +1855,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1536.4714</v>
+        <v>1538.1143</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1859,10 +1863,10 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.02</v>
+        <v>-0.91</v>
       </c>
       <c r="U19" s="4" t="n">
         <v>1657.62</v>
@@ -1874,7 +1878,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1890,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1906,34 +1910,34 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>8128.5</v>
+        <v>112.03</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8416</v>
+        <v>116.12</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>38.7</v>
+        <v>35</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1952,7 +1956,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>8127.1429</v>
+        <v>112.3543</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1960,22 +1964,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>3.43</v>
+        <v>3.24</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.02</v>
+        <v>0.29</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>8660.25</v>
+        <v>117.92</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-PNB-20261006-66ccb3</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1991,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2007,34 +2011,34 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-08</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6886</v>
+        <v>424.55</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>7119</v>
+        <v>439.2</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>33.3</v>
+        <v>34.1</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2053,7 +2057,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>6875.0714</v>
+        <v>424.4929</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2061,22 +2065,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>7201.32</v>
+        <v>449.3</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EICHERMOT-20261008-56f58a</t>
+          <t>IND-R2-KOTAKBANK-20261002-563392</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2092,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2108,34 +2112,34 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-29</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3150.4</v>
+        <v>293.95</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3257</v>
+        <v>303.2</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>29.2</v>
+        <v>34.3</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2154,7 +2158,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>3104.343</v>
+        <v>288.7214</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2162,22 +2166,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>4.69</v>
+        <v>4.78</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.46</v>
+        <v>-1.78</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>3346.99</v>
+        <v>317.43</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
+          <t>IND-R2-ANGELONE-20261006-fc497f</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2193,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2209,34 +2213,34 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-08</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>323.6</v>
+        <v>6886</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>332.7</v>
+        <v>7095.5</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>29.2</v>
+        <v>33.3</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2255,7 +2259,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>319.1929</v>
+        <v>6875.0714</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2263,22 +2267,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>4.06</v>
+        <v>3.11</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.36</v>
+        <v>-0.16</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>342.03</v>
+        <v>7201.32</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PFC-20261006-e91ac2</t>
+          <t>IND-R2-EICHERMOT-20261008-56f58a</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2294,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2310,34 +2314,34 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-09-30</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>112.03</v>
+        <v>17.07</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>114.93</v>
+        <v>17.58</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>35</v>
+        <v>31.3</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2356,7 +2360,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>112.3543</v>
+        <v>16.9243</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2364,22 +2368,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.24</v>
+        <v>3.73</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.29</v>
+        <v>-0.85</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>117.92</v>
+        <v>18.41</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20261006-66ccb3</t>
+          <t>IND-R2-IRB-20260930-4c1d2d</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2395,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2420,21 +2424,21 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>293.95</v>
+        <v>814.35</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>301.35</v>
+        <v>832.55</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>34.3</v>
+        <v>32.9</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
@@ -2457,7 +2461,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>288.7214</v>
+        <v>800.45</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2465,22 +2469,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>4.19</v>
+        <v>3.86</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.78</v>
+        <v>-1.71</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>317.43</v>
+        <v>856.91</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20261006-fc497f</t>
+          <t>IND-R2-INDIANB-20261006-0d13b1</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2496,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2512,34 +2516,34 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>540.65</v>
+        <v>71.23</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>552.2</v>
+        <v>72.58</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>33.2</v>
+        <v>31.3</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2558,7 +2562,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>528.65</v>
+        <v>70.5686</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2566,22 +2570,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.26</v>
+        <v>2.77</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-2.22</v>
+        <v>-0.93</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>574.4299999999999</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20261009-2eeb63</t>
+          <t>IND-R2-NHPC-20261005-cad510</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2597,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2622,25 +2626,25 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>167.95</v>
+        <v>617.4</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>170.83</v>
+        <v>628.9</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>32.9</v>
+        <v>20.6</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2659,7 +2663,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>165.0171</v>
+        <v>599.0232</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2667,22 +2671,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.75</v>
+        <v>-2.98</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>179.1</v>
+        <v>728.8</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20261006-801564</t>
+          <t>IND-R2-TATACHEM-20261006-fc5587</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2698,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2714,34 +2718,34 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>142.41</v>
+        <v>358</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>144.68</v>
+        <v>362.9</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>33.3</v>
+        <v>36.4</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2760,7 +2764,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>138.4</v>
+        <v>345.4286</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2768,22 +2772,22 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.34</v>
+        <v>4.81</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-2.82</v>
+        <v>-3.51</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>150.78</v>
+        <v>394.94</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20261002-27ac34</t>
+          <t>IND-R2-PATANJALI-20261007-ff8244</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2815,34 +2819,34 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>71.23</v>
+        <v>285</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>72.36</v>
+        <v>288.8</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>31.3</v>
+        <v>35.4</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2861,7 +2865,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>70.5686</v>
+        <v>285.4429</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2869,22 +2873,22 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2.48</v>
+        <v>1.16</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.93</v>
+        <v>0.16</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>74.73999999999999</v>
+        <v>296.6</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NHPC-20261005-cad510</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2900,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2916,34 +2920,34 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>284.4</v>
+        <v>324.7</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>288.65</v>
+        <v>328.5</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>26.7</v>
+        <v>39.3</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2962,7 +2966,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>275.7786</v>
+        <v>315.2571</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2970,22 +2974,22 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.46</v>
+        <v>4.03</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.03</v>
+        <v>-2.91</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>302.94</v>
+        <v>346.28</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BPCL-20261009-8784b5</t>
+          <t>IND-R2-FEDERALBNK-20261007-b739c0</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3001,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3017,34 +3021,34 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>126.05</v>
+        <v>167.95</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>127.63</v>
+        <v>169.79</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>26.7</v>
+        <v>32.9</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3063,7 +3067,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>123.0171</v>
+        <v>165.0171</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3071,22 +3075,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>3.61</v>
+        <v>2.81</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-2.41</v>
+        <v>-1.75</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>132.8</v>
+        <v>179.1</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IOC-20261009-774a1b</t>
+          <t>IND-R2-UNIONBANK-20261006-801564</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3102,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3118,34 +3122,34 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>285</v>
+        <v>1243</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>288.55</v>
+        <v>1256.6</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>35.4</v>
+        <v>35</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3164,7 +3168,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>285.4429</v>
+        <v>1215.4286</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3172,22 +3176,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>1.08</v>
+        <v>3.28</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.16</v>
+        <v>-2.22</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>296.6</v>
+        <v>1307.07</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-AXISBANK-20261006-79c723</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3203,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3219,34 +3223,34 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1010.1</v>
+        <v>540.65</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1020.35</v>
+        <v>545.7</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>1.01</v>
+        <v>0.93</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>38.3</v>
+        <v>33.2</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3265,7 +3269,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>978.9857</v>
+        <v>528.65</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3273,22 +3277,22 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.05</v>
+        <v>3.12</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-3.08</v>
+        <v>-2.22</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1076.14</v>
+        <v>574.4299999999999</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20261002-20a2cb</t>
+          <t>IND-R2-HINDZINC-20261009-2eeb63</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3304,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3320,34 +3324,34 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-09-11</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>324.7</v>
+        <v>8128.5</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>327.85</v>
+        <v>8192.5</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.97</v>
+        <v>0.79</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>39.3</v>
+        <v>38.7</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3366,7 +3370,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>314.5214</v>
+        <v>8127.1429</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3374,22 +3378,22 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>4.07</v>
+        <v>0.8</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-3.13</v>
+        <v>-0.02</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>346.28</v>
+        <v>8660.25</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-FEDERALBNK-20261007-b739c0</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3405,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3421,34 +3425,34 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>166.84</v>
+        <v>2813.6</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>168.26</v>
+        <v>2831.3</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.85</v>
+        <v>0.63</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>37.3</v>
+        <v>11.2</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3467,7 +3471,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>162.3571</v>
+        <v>2734.5571</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3475,22 +3479,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-2.69</v>
+        <v>-2.81</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>175.28</v>
+        <v>2961.52</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GAIL-20261009-ea012b</t>
+          <t>IND-R2-MM-20261007-c1210c</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3506,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3531,25 +3535,25 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2813.6</v>
+        <v>2074.1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2833</v>
+        <v>2086.7</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>11.2</v>
+        <v>32.3</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3568,7 +3572,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>2734.5571</v>
+        <v>1997.3429</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3576,22 +3580,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>3.47</v>
+        <v>4.28</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-2.81</v>
+        <v>-3.7</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>2961.52</v>
+        <v>2205.18</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MM-20261007-c1210c</t>
+          <t>IND-R2-MAZDOCK-20261007-e84c93</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3607,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3623,34 +3627,34 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-08</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1243</v>
+        <v>315.6</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>1249</v>
+        <v>317.4</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>35</v>
+        <v>38.2</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3669,7 +3673,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>1215.4286</v>
+        <v>299.5571</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3677,22 +3681,22 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>2.69</v>
+        <v>5.62</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-2.22</v>
+        <v>-5.08</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>1307.07</v>
+        <v>343.17</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AXISBANK-20261006-79c723</t>
+          <t>IND-R2-NATIONALUM-20261008-b77474</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3708,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3724,34 +3728,34 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>814.35</v>
+        <v>2254.5</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>816.95</v>
+        <v>2263.1</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>32.9</v>
+        <v>40.5</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3770,7 +3774,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>796.7786</v>
+        <v>2156.2858</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3778,22 +3782,22 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>2.47</v>
+        <v>4.72</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-2.16</v>
+        <v>-4.36</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>856.91</v>
+        <v>2414.04</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20261006-0d13b1</t>
+          <t>IND-R2-GLENMARK-20261012-f70810</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3809,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3825,34 +3829,34 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-08</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>933.95</v>
+        <v>5961</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>934.25</v>
+        <v>5977</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0.03</v>
+        <v>0.27</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>40.7</v>
+        <v>33.3</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3871,7 +3875,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>904.05</v>
+        <v>5793.5714</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3879,22 +3883,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-3.2</v>
+        <v>-2.81</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>982.13</v>
+        <v>6301.29</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SHRIRAMFIN-20261008-db2dc4</t>
+          <t>IND-R2-ATUL-20261007-6aad3b</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3910,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3926,34 +3930,34 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>5961</v>
+        <v>142.41</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>5953</v>
+        <v>142.77</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>-0.13</v>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0.25</v>
       </c>
       <c r="L40" s="4" t="n">
         <v>33.3</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3972,7 +3976,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>5793.5714</v>
+        <v>138.4</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3980,22 +3984,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>2.68</v>
+        <v>3.06</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-2.81</v>
+        <v>-2.82</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>6301.29</v>
+        <v>150.78</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20261007-6aad3b</t>
+          <t>IND-R2-IGL-20261002-27ac34</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4011,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4027,34 +4031,34 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-08</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>315.6</v>
+        <v>166.84</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>314.85</v>
+        <v>166.99</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v>-0.24</v>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.09</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>38.2</v>
+        <v>37.3</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4073,7 +4077,7 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>298.2357</v>
+        <v>162.3571</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4081,17 +4085,17 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>5.28</v>
+        <v>2.77</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-5.5</v>
+        <v>-2.69</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>343.17</v>
+        <v>175.28</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20261008-b77474</t>
+          <t>IND-R2-GAIL-20261009-ea012b</t>
         </is>
       </c>
       <c r="W41" s="4" t="inlineStr">
@@ -4108,7 +4112,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4128,34 +4132,34 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>358</v>
+        <v>1129.3</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>357.05</v>
+        <v>1129.1</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.27</v>
+        <v>-0.02</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>36.4</v>
+        <v>26.2</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4174,7 +4178,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>339.5286</v>
+        <v>1093.2572</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4182,22 +4186,22 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>4.91</v>
+        <v>3.17</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-5.16</v>
+        <v>-3.19</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>394.94</v>
+        <v>1183.36</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PATANJALI-20261007-ff8244</t>
+          <t>IND-R2-ACC-20261012-f1f022</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4213,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4229,34 +4233,34 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2074.1</v>
+        <v>1173.3</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>2060</v>
+        <v>1173</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.68</v>
+        <v>-0.03</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>32.3</v>
+        <v>38.2</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4275,7 +4279,7 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>1986.7145</v>
+        <v>1128.3429</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4283,22 +4287,22 @@
         </is>
       </c>
       <c r="S43" s="4" t="n">
-        <v>3.56</v>
+        <v>3.81</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-4.21</v>
+        <v>-3.83</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>2205.18</v>
+        <v>1240.74</v>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MAZDOCK-20261007-e84c93</t>
+          <t>IND-R2-JSWSTEEL-20261012-af40fc</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4314,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4330,30 +4334,30 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>449.45</v>
+        <v>284.4</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>444.95</v>
+        <v>283.9</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-1</v>
+        <v>-0.18</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>35.4</v>
+        <v>26.7</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
@@ -4376,7 +4380,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>429.9857</v>
+        <v>275.7786</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
@@ -4384,22 +4388,22 @@
         </is>
       </c>
       <c r="S44" s="4" t="n">
-        <v>3.36</v>
+        <v>2.86</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>-4.33</v>
+        <v>-3.03</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>478.65</v>
+        <v>302.94</v>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20261007-ed8f2f</t>
+          <t>IND-R2-BPCL-20261009-8784b5</t>
         </is>
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4415,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4431,30 +4435,30 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-10-08</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>119.47</v>
+        <v>933.95</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>117.88</v>
+        <v>931.85</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-1.33</v>
+        <v>-0.22</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>30.2</v>
+        <v>40.7</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
@@ -4477,7 +4481,7 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>115.81</v>
+        <v>904.05</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4485,22 +4489,22 @@
         </is>
       </c>
       <c r="S45" s="4" t="n">
-        <v>1.76</v>
+        <v>2.98</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>-3.06</v>
+        <v>-3.2</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>125.65</v>
+        <v>982.13</v>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20261005-19551d</t>
+          <t>IND-R2-SHRIRAMFIN-20261008-db2dc4</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4516,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4532,34 +4536,34 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-16</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>407.75</v>
+        <v>2629</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>401.6</v>
+        <v>2622.8</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-1.51</v>
+        <v>-0.24</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>33.3</v>
+        <v>35.9</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -4578,7 +4582,7 @@
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>392.3429</v>
+        <v>2530.3143</v>
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
@@ -4586,22 +4590,22 @@
         </is>
       </c>
       <c r="S46" s="4" t="n">
-        <v>2.31</v>
+        <v>3.53</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>-3.78</v>
+        <v>-3.75</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>436.95</v>
+        <v>2777.03</v>
       </c>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
+          <t>IND-R2-MUTHOOTFIN-20261012-9e0c35</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4617,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4633,34 +4637,34 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-01</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>223.39</v>
+        <v>698.65</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>219.9</v>
+        <v>695</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-1.56</v>
+        <v>-0.52</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>31.2</v>
+        <v>30.9</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4679,7 +4683,7 @@
         </is>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>216.2243</v>
+        <v>668.4357</v>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
@@ -4687,22 +4691,22 @@
         </is>
       </c>
       <c r="S47" s="4" t="n">
-        <v>1.67</v>
+        <v>3.82</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>-3.21</v>
+        <v>-4.32</v>
       </c>
       <c r="U47" s="4" t="n">
-        <v>234.14</v>
+        <v>749.47</v>
       </c>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ONGC-20261001-b42383</t>
+          <t>IND-R2-CAMS-20260928-86e0a0</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4718,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4734,34 +4738,34 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-21</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>124830</v>
+        <v>126.05</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>122510</v>
+        <v>125.24</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-1.86</v>
+        <v>-0.64</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>29.3</v>
+        <v>26.7</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -4780,7 +4784,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>121363.5714</v>
+        <v>123.0171</v>
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -4788,22 +4792,22 @@
         </is>
       </c>
       <c r="S48" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.77</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>-2.78</v>
+        <v>-2.41</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>130238.57</v>
+        <v>132.8</v>
       </c>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MRF-20260921-31a31a</t>
+          <t>IND-R2-IOC-20261009-774a1b</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4847,15 +4851,15 @@
         <v>10700</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>10500</v>
+        <v>10624</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-1.87</v>
+        <v>-0.71</v>
       </c>
       <c r="L49" s="4" t="n">
         <v>43.6</v>
@@ -4889,7 +4893,7 @@
         </is>
       </c>
       <c r="S49" s="4" t="n">
-        <v>3.02</v>
+        <v>4.15</v>
       </c>
       <c r="T49" s="4" t="n">
         <v>-4.83</v>
@@ -4904,7 +4908,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4920,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4936,34 +4940,34 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-01</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>698.65</v>
+        <v>223.39</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>685.3</v>
+        <v>221.7</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-1.91</v>
+        <v>-0.76</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>30.9</v>
+        <v>31.2</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -4982,7 +4986,7 @@
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>668.4357</v>
+        <v>216.2243</v>
       </c>
       <c r="R50" s="4" t="inlineStr">
         <is>
@@ -4990,22 +4994,22 @@
         </is>
       </c>
       <c r="S50" s="4" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>-4.32</v>
+        <v>-3.21</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>749.47</v>
+        <v>234.14</v>
       </c>
       <c r="V50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CAMS-20260928-86e0a0</t>
+          <t>IND-R2-ONGC-20261001-b42383</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5021,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -5046,21 +5050,21 @@
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>961</v>
+        <v>119.47</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>940.55</v>
+        <v>118.46</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-2.13</v>
+        <v>-0.85</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>37.2</v>
+        <v>30.2</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
@@ -5083,7 +5087,7 @@
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>934.9285</v>
+        <v>115.81</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -5091,22 +5095,22 @@
         </is>
       </c>
       <c r="S51" s="4" t="n">
-        <v>0.6</v>
+        <v>2.24</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>-2.71</v>
+        <v>-3.06</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>1003.19</v>
+        <v>125.65</v>
       </c>
       <c r="V51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20261005-104400</t>
+          <t>IND-R2-CANBK-20261005-19551d</t>
         </is>
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5150,15 +5154,15 @@
         <v>453.15</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>441.45</v>
+        <v>448.25</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-2.58</v>
+        <v>-1.08</v>
       </c>
       <c r="L52" s="4" t="n">
         <v>33.3</v>
@@ -5184,7 +5188,7 @@
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>430.3428</v>
+        <v>430.6857</v>
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
@@ -5192,10 +5196,10 @@
         </is>
       </c>
       <c r="S52" s="4" t="n">
-        <v>2.52</v>
+        <v>3.92</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>-5.03</v>
+        <v>-4.96</v>
       </c>
       <c r="U52" s="4" t="n">
         <v>487.36</v>
@@ -5207,7 +5211,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5223,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -5239,34 +5243,34 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>11671</v>
+        <v>449.45</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>11359</v>
+        <v>443.9</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-2.67</v>
+        <v>-1.23</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>31.3</v>
+        <v>35.4</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5285,7 +5289,7 @@
         </is>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>11319</v>
+        <v>429.9857</v>
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
@@ -5293,22 +5297,22 @@
         </is>
       </c>
       <c r="S53" s="4" t="n">
-        <v>0.35</v>
+        <v>3.13</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>-3.02</v>
+        <v>-4.33</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>12199</v>
+        <v>478.65</v>
       </c>
       <c r="V53" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARUTI-20261002-ee9f86</t>
+          <t>IND-R2-OIL-20261007-ed8f2f</t>
         </is>
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5324,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -5340,34 +5344,34 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>74.04000000000001</v>
+        <v>407.75</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>70.94</v>
+        <v>400.85</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-4.19</v>
+        <v>-1.69</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>31.2</v>
+        <v>33.3</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5386,7 +5390,7 @@
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>70.90860000000001</v>
+        <v>392.3429</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
@@ -5394,22 +5398,22 @@
         </is>
       </c>
       <c r="S54" s="4" t="n">
-        <v>0.04</v>
+        <v>2.12</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>-4.23</v>
+        <v>-3.78</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>78.73999999999999</v>
+        <v>436.95</v>
       </c>
       <c r="V54" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NMDC-20261006-2acbae</t>
+          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
         </is>
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5425,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -5441,34 +5445,34 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>617.4</v>
+        <v>961</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>589.95</v>
+        <v>942.8</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-4.45</v>
+        <v>-1.89</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>20.6</v>
+        <v>37.2</v>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5487,7 +5491,7 @@
         </is>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>571.1142</v>
+        <v>934.9285</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5495,22 +5499,22 @@
         </is>
       </c>
       <c r="S55" s="4" t="n">
-        <v>3.19</v>
+        <v>0.83</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>-7.5</v>
+        <v>-2.71</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>728.8</v>
+        <v>1003.19</v>
       </c>
       <c r="V55" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACHEM-20261006-fc5587</t>
+          <t>IND-R2-SBIN-20261005-104400</t>
         </is>
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5522,217 +5526,623 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-09-21</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>124830</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>122450</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>121363.5714</v>
+      </c>
+      <c r="R56" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S56" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="T56" s="4" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="U56" s="4" t="n">
+        <v>130238.57</v>
+      </c>
+      <c r="V56" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-MRF-20260921-31a31a</t>
+        </is>
+      </c>
+      <c r="W56" s="4" t="inlineStr">
+        <is>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-10-12</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>589.55</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>570.5</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>562.0732</v>
+      </c>
+      <c r="R57" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S57" s="4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T57" s="4" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>644.5</v>
+      </c>
+      <c r="V57" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-GNFC-20261012-e5db63</t>
+        </is>
+      </c>
+      <c r="W57" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Not rated yet · R3 is still gathering evidence</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-10-06</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>70.90860000000001</v>
+      </c>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S58" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>78.73999999999999</v>
+      </c>
+      <c r="V58" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-NMDC-20261006-2acbae</t>
+        </is>
+      </c>
+      <c r="W58" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-04</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>397</v>
       </c>
-      <c r="I56" s="4" t="n">
-        <v>440.5</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
+      <c r="I59" s="4" t="n">
+        <v>439.2</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="M59" s="4" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="N59" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O56" s="4" t="inlineStr">
+      <c r="O59" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P56" s="4" t="inlineStr">
+      <c r="P59" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q56" s="4" t="n">
+      <c r="Q59" s="4" t="n">
         <v>386.4571</v>
       </c>
-      <c r="R56" s="4" t="inlineStr">
+      <c r="R59" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S56" s="4" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="T56" s="4" t="n">
+      <c r="S59" s="4" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="T59" s="4" t="n">
         <v>-2.66</v>
       </c>
-      <c r="U56" s="4" t="inlineStr">
+      <c r="U59" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="V56" s="4" t="inlineStr">
+      <c r="V59" s="4" t="inlineStr">
         <is>
           <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
-      <c r="W56" s="4" t="inlineStr">
+      <c r="W59" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
-        </is>
-      </c>
-    </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-05</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>408.9</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="n">
+        <v>407.3714</v>
+      </c>
+      <c r="R60" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S60" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="T60" s="4" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="U60" s="4" t="n">
+        <v>432.94</v>
+      </c>
+      <c r="V60" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+        </is>
+      </c>
+      <c r="W60" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -5742,15 +6152,15 @@
   <mergeCells count="23">
     <mergeCell ref="A68:W68"/>
     <mergeCell ref="A67:W67"/>
+    <mergeCell ref="A77:W77"/>
     <mergeCell ref="A64:W64"/>
-    <mergeCell ref="A59:W59"/>
     <mergeCell ref="A73:W73"/>
-    <mergeCell ref="A60:W60"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A70:W70"/>
-    <mergeCell ref="A61:W61"/>
+    <mergeCell ref="A79:W79"/>
     <mergeCell ref="A6:W6"/>
     <mergeCell ref="A69:W69"/>
+    <mergeCell ref="A78:W78"/>
     <mergeCell ref="A65:W65"/>
     <mergeCell ref="A66:W66"/>
     <mergeCell ref="A75:W75"/>
@@ -5758,9 +6168,9 @@
     <mergeCell ref="A3:W3"/>
     <mergeCell ref="A71:W71"/>
     <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A76:W76"/>
     <mergeCell ref="A5:W5"/>
     <mergeCell ref="A4:W4"/>
-    <mergeCell ref="A62:W62"/>
     <mergeCell ref="A72:W72"/>
     <mergeCell ref="A63:W63"/>
   </mergeCells>
@@ -5798,21 +6208,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-12</t>
+          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>143 records · ADMINISTRATIVE 21 · ADVISORY/HISTORICAL 5 · REALIZED EXIT 102 · STOP-BREACH MARK 15   ·   Canonical lifecycle historical coverage begins 2026-08-04 · earlier closures are not held in any provable AEGIS source</t>
+          <t>143 records · ADMINISTRATIVE 21 · ADVISORY/HISTORICAL 5 · REALIZED EXIT 103 · STOP-BREACH MARK 14   ·   Canonical lifecycle historical coverage begins 2026-08-04 · earlier closures are not held in any provable AEGIS source</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>📊 REALIZED PRODUCTION PERFORMANCE · 102 closed trade(s) · win 20/102 · avg -2.68%   ·   EXCLUDED from this line: orphan auto-closes, administrative records, advisory rows, and 15 STOP-BREACH MARK(s) whose stop was passed but which are NOT sold - their price and P&amp;L are today's mark, not a realized result</t>
+          <t>📊 REALIZED PRODUCTION PERFORMANCE · 103 closed trade(s) · win 20/103 · avg -2.69%   ·   EXCLUDED from this line: orphan auto-closes, administrative records, advisory rows, and 14 STOP-BREACH MARK(s) whose stop was passed but which are NOT sold - their price and P&amp;L are today's mark, not a realized result</t>
         </is>
       </c>
     </row>
@@ -5901,7 +6311,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -5938,13 +6348,13 @@
         <v>1191</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1117.4</v>
+        <v>1129.5</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-6.18</v>
+        <v>-5.16</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -5975,7 +6385,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -6012,13 +6422,13 @@
         <v>187.46</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>173.34</v>
+        <v>173.68</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-7.53</v>
+        <v>-7.35</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -6049,7 +6459,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -6086,13 +6496,13 @@
         <v>239.45</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>219.9</v>
+        <v>221.7</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-8.16</v>
+        <v>-7.41</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -6123,17 +6533,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -6143,71 +6553,69 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1449.5</v>
+        <v>11671</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1336.4</v>
+        <v>11231</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-7.8</v>
+        <v>-3.77</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>31.3</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-10-13 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R2-MARUTI-20261002-ee9f86</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -6227,20 +6635,20 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>417.6</v>
+        <v>1449.5</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>404.8</v>
+        <v>1349.8</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-3.07</v>
+        <v>-6.88</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -6254,12 +6662,12 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 407.3714 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -6271,7 +6679,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -6308,13 +6716,13 @@
         <v>1413.5</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1304.5</v>
+        <v>1323.2</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-7.71</v>
+        <v>-6.39</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -6345,7 +6753,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -6382,13 +6790,13 @@
         <v>389.85</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>370.4</v>
+        <v>376.2</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-4.99</v>
+        <v>-3.5</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -12308,10 +12716,10 @@
         <v>381.6</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>341.45</v>
+        <v>343</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>-10.52</v>
+        <v>-10.12</v>
       </c>
       <c r="K93" s="4" t="n">
         <v>35</v>
@@ -12456,10 +12864,10 @@
         <v>1048.7</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>940.55</v>
+        <v>942.8</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>-10.31</v>
+        <v>-10.1</v>
       </c>
       <c r="K95" s="4" t="n">
         <v>18</v>
@@ -12530,10 +12938,10 @@
         <v>1642.5</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>1462.3</v>
+        <v>1472</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>-10.97</v>
+        <v>-10.38</v>
       </c>
       <c r="K96" s="4" t="n">
         <v>35</v>
@@ -12678,10 +13086,10 @@
         <v>2410</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>1939.9</v>
+        <v>1942.8</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>-19.51</v>
+        <v>-19.39</v>
       </c>
       <c r="K98" s="4" t="n">
         <v>34</v>
@@ -12752,10 +13160,10 @@
         <v>507.9</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>465.3</v>
+        <v>464.8</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>-8.390000000000001</v>
+        <v>-8.49</v>
       </c>
       <c r="K99" s="4" t="n">
         <v>35</v>
@@ -12826,10 +13234,10 @@
         <v>2064.9</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>1826.6</v>
+        <v>1865.9</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>-11.54</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>27</v>
@@ -12900,10 +13308,10 @@
         <v>385.15</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>377.9</v>
+        <v>375.6</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>-1.88</v>
+        <v>-2.48</v>
       </c>
       <c r="K101" s="4" t="n">
         <v>11</v>
@@ -12974,10 +13382,10 @@
         <v>5454.5</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>4764.3</v>
+        <v>4792</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>-12.65</v>
+        <v>-12.15</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>35</v>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,35 +508,35 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-13 · prices = 2026-10-13 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-14 · prices = 2026-10-14 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>53 investable · NEW 4 · ACTIVE+ 49 · ACTIVE 0   ·   R2 51 · MOMENTUM 0 · R1 2 (advisory)   ·   4 row(s) read 0.00%: admitted at the 2026-10-13 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>54 investable · NEW 1 · ACTIVE+ 53 · ACTIVE 0   ·   R2 51 · MOMENTUM 0 · R1 3 (advisory)   ·   1 row(s) read 0.00%: admitted at the 2026-10-14 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 53 position(s) with an INTACT stop · if all of them fired today the average outcome is -1.74% from entry, worst single -5.25%</t>
+          <t>🛡 DOWNSIDE · 54 position(s) with an INTACT stop · if all of them fired today the average outcome is -1.08% from entry, worst single -4.83%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 14 position(s) left CURRENT on a STOP BREACH (R1 14 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>🔴 13 position(s) left CURRENT on a STOP BREACH (R1 13 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=4 · 228 scored · 52 already in CURRENT · biggest blocker: model disagreement (160) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=1 · 228 scored · 53 already in CURRENT · biggest blocker: model disagreement (160) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -697,29 +697,29 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>10581</v>
+        <v>373.9</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10581</v>
+        <v>373.9</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>35.9</v>
+        <v>35.2</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>10140.4286</v>
+        <v>357.1714</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,17 +746,17 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>4.16</v>
+        <v>4.47</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-4.16</v>
+        <v>-4.47</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>11241.86</v>
+        <v>398.99</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BAJAJHLDNG-20261013-3e863a</t>
+          <t>IND-R2-EMAMILTD-20261014-d5bbe7</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BALKRISIND</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -793,34 +793,34 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1987</v>
+        <v>464.25</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1987</v>
+        <v>639.6</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>37.77</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>33.2</v>
+        <v>31.2</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1908.6428</v>
+        <v>600.3321</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,22 +847,24 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>3.94</v>
+        <v>6.14</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.94</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>2104.54</v>
+        <v>29.31</v>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BALKRISIND-20261013-38dd43</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -874,7 +876,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -884,7 +886,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -894,30 +896,30 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-29</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1315.4</v>
+        <v>3150.4</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1315.4</v>
+        <v>3673</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>16.59</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>40.6</v>
+        <v>29.2</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
@@ -940,7 +942,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1246.3428</v>
+        <v>3468.9715</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,22 +950,24 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>5.25</v>
+        <v>5.55</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-5.25</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>1418.99</v>
+        <v>10.11</v>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20261013-955276</t>
+          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -975,7 +979,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -985,7 +989,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -995,30 +999,30 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>167.79</v>
+        <v>2056.8</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>167.79</v>
+        <v>2315</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>12.55</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>38.2</v>
+        <v>34.9</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
@@ -1041,7 +1045,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>161.0314</v>
+        <v>2203.5429</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1049,22 +1053,24 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.03</v>
+        <v>4.81</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-4.03</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>177.93</v>
+        <v>7.13</v>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-WIPRO-20261013-d844f1</t>
+          <t>IND-R2-TCS-20260928-f23b4c</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1082,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1096,34 +1102,34 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>464.25</v>
+        <v>3110.4</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>626.35</v>
+        <v>3391.2</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>34.92</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>31.2</v>
+        <v>34.8</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1142,7 +1148,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>594.7963999999999</v>
+        <v>3218.4714</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1150,10 +1156,10 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>5.04</v>
+        <v>5.09</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>28.12</v>
+        <v>3.47</v>
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
@@ -1162,12 +1168,12 @@
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-BSE-20261005-7af4a1</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1185,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1199,30 +1205,30 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2056.8</v>
+        <v>1010.1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2259</v>
+        <v>1086</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>9.83</v>
+        <v>7.51</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>34.9</v>
+        <v>38.3</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
@@ -1245,7 +1251,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2155.5429</v>
+        <v>1038.8571</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1253,10 +1259,10 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>4.58</v>
+        <v>4.34</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
@@ -1265,12 +1271,12 @@
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260928-f23b4c</t>
+          <t>IND-R2-INFY-20261002-20a2cb</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1288,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1302,34 +1308,34 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-29</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3150.4</v>
+        <v>158.38</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3394.4</v>
+        <v>169</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>7.75</v>
+        <v>6.71</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>29.2</v>
+        <v>28.1</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1348,7 +1354,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3229.2572</v>
+        <v>159.5714</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1356,24 +1362,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.87</v>
+        <v>5.58</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.75</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>176.28</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
+          <t>IND-R2-BANDHANBNK-20261012-efab94</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1389,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1405,30 +1409,30 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>158.38</v>
+        <v>323.6</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>169.49</v>
+        <v>345.2</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>7.01</v>
+        <v>6.67</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>28.1</v>
+        <v>29.2</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
@@ -1451,7 +1455,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>159.3714</v>
+        <v>330.2929</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1459,22 +1463,24 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.97</v>
+        <v>4.32</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="U15" s="4" t="n">
-        <v>176.28</v>
+        <v>2.07</v>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20261012-efab94</t>
+          <t>IND-R2-PFC-20261006-e91ac2</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1492,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1506,34 +1512,34 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3110.4</v>
+        <v>1552.3</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3311</v>
+        <v>1643.8</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>6.45</v>
+        <v>5.89</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>34.8</v>
+        <v>35.4</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1552,7 +1558,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>3183.8001</v>
+        <v>1569.1</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1560,17 +1566,17 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.84</v>
+        <v>4.54</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>2.36</v>
+        <v>1.08</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3350.16</v>
+        <v>1657.62</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BSE-20261005-7af4a1</t>
+          <t>IND-R2-DEEPAKNTR-20261006-676b03</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
@@ -1587,7 +1593,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1607,34 +1613,34 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-09-30</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>323.6</v>
+        <v>17.07</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>337.35</v>
+        <v>17.94</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>4.25</v>
+        <v>5.1</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>29.2</v>
+        <v>31.3</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1653,7 +1659,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>323.0786</v>
+        <v>16.9871</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1661,22 +1667,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>4.23</v>
+        <v>5.31</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.16</v>
+        <v>-0.49</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>342.03</v>
+        <v>18.41</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PFC-20261006-e91ac2</t>
+          <t>IND-R2-IRB-20260930-4c1d2d</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1694,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1708,34 +1714,34 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1010.1</v>
+        <v>293.95</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1052.55</v>
+        <v>307.95</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>4.2</v>
+        <v>4.76</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>38.3</v>
+        <v>34.3</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1754,7 +1760,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1009.4429</v>
+        <v>290.2357</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1762,22 +1768,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>4.1</v>
+        <v>5.75</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.26</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1076.14</v>
+        <v>317.43</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20261002-20a2cb</t>
+          <t>IND-R2-ANGELONE-20261006-fc497f</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1795,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1809,34 +1815,34 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1552.3</v>
+        <v>424.55</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1609</v>
+        <v>443.5</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>3.65</v>
+        <v>4.46</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>35.4</v>
+        <v>34.1</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1855,7 +1861,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1538.1143</v>
+        <v>424.4929</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1863,22 +1869,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>4.41</v>
+        <v>4.29</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.91</v>
+        <v>-0.01</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1657.62</v>
+        <v>449.3</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20261006-676b03</t>
+          <t>IND-R2-KOTAKBANK-20261002-563392</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1896,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1919,25 +1925,25 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>112.03</v>
+        <v>617.4</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>116.12</v>
+        <v>639.55</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>35</v>
+        <v>20.6</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1956,7 +1962,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>112.3543</v>
+        <v>609.8928</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1964,22 +1970,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>3.24</v>
+        <v>4.64</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.29</v>
+        <v>-1.22</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>117.92</v>
+        <v>728.8</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20261006-66ccb3</t>
+          <t>IND-R2-TATACHEM-20261006-fc5587</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1997,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2011,30 +2017,30 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>424.55</v>
+        <v>112.03</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>439.2</v>
+        <v>115.97</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>34.1</v>
+        <v>35</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -2057,7 +2063,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>424.4929</v>
+        <v>112.3543</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2065,22 +2071,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.01</v>
+        <v>0.29</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>449.3</v>
+        <v>117.92</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20261002-563392</t>
+          <t>IND-R2-PNB-20261006-66ccb3</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2098,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2112,34 +2118,34 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-08</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>293.95</v>
+        <v>315.6</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>303.2</v>
+        <v>325.85</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>34.3</v>
+        <v>38.2</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2158,7 +2164,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>288.7214</v>
+        <v>307.7143</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2166,22 +2172,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>4.78</v>
+        <v>5.57</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.78</v>
+        <v>-2.5</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>317.43</v>
+        <v>343.17</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20261006-fc497f</t>
+          <t>IND-R2-NATIONALUM-20261008-b77474</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2225,11 +2231,11 @@
         <v>6886</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7095.5</v>
+        <v>7095</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
@@ -2267,7 +2273,7 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>-0.16</v>
@@ -2282,7 +2288,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2300,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2314,34 +2320,34 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-30</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>17.07</v>
+        <v>71.23</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>17.58</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L24" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2360,7 +2366,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>16.9243</v>
+        <v>71.0514</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2368,22 +2374,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.73</v>
+        <v>3.13</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.85</v>
+        <v>-0.25</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>18.41</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260930-4c1d2d</t>
+          <t>IND-R2-NHPC-20261005-cad510</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2401,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2415,30 +2421,30 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>814.35</v>
+        <v>10581</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>832.55</v>
+        <v>10886</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>32.9</v>
+        <v>35.9</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
@@ -2461,7 +2467,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>800.45</v>
+        <v>10427.1429</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2469,22 +2475,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.86</v>
+        <v>4.22</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.71</v>
+        <v>-1.45</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>856.91</v>
+        <v>11241.86</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20261006-0d13b1</t>
+          <t>IND-R2-BAJAJHLDNG-20261013-3e863a</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2502,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2516,34 +2522,34 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>71.23</v>
+        <v>2074.1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>72.58</v>
+        <v>2126.8</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>1.9</v>
+        <v>2.54</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>31.3</v>
+        <v>32.3</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2562,7 +2568,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>70.5686</v>
+        <v>2033.3572</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2570,22 +2576,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.77</v>
+        <v>4.39</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.93</v>
+        <v>-1.96</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>74.73999999999999</v>
+        <v>2205.18</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NHPC-20261005-cad510</t>
+          <t>IND-R2-MAZDOCK-20261007-e84c93</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2603,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2626,25 +2632,25 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>617.4</v>
+        <v>814.35</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>628.9</v>
+        <v>834.35</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1.86</v>
+        <v>2.46</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>20.6</v>
+        <v>32.9</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2663,7 +2669,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>599.0232</v>
+        <v>801.3071</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2671,22 +2677,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.75</v>
+        <v>3.96</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.98</v>
+        <v>-1.6</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>728.8</v>
+        <v>856.91</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACHEM-20261006-fc5587</t>
+          <t>IND-R2-INDIANB-20261006-0d13b1</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2704,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2718,34 +2724,34 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-08</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>358</v>
+        <v>933.95</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>362.9</v>
+        <v>956.75</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>1.37</v>
+        <v>2.44</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>36.4</v>
+        <v>40.7</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2764,7 +2770,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>345.4286</v>
+        <v>916.2357</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2772,17 +2778,17 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.81</v>
+        <v>4.23</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-3.51</v>
+        <v>-1.9</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>394.94</v>
+        <v>982.13</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PATANJALI-20261007-ff8244</t>
+          <t>IND-R2-SHRIRAMFIN-20261008-db2dc4</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
@@ -2799,7 +2805,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2819,34 +2825,34 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>285</v>
+        <v>1243</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>288.8</v>
+        <v>1271.8</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1.33</v>
+        <v>2.32</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>35.4</v>
+        <v>35</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2865,7 +2871,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>285.4429</v>
+        <v>1225.0286</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2873,22 +2879,22 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>1.16</v>
+        <v>3.68</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.16</v>
+        <v>-1.45</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>296.6</v>
+        <v>1307.07</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-AXISBANK-20261006-79c723</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2906,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2929,25 +2935,25 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>324.7</v>
+        <v>358</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>328.5</v>
+        <v>365.95</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>1.17</v>
+        <v>2.22</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>39.3</v>
+        <v>36.4</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2966,7 +2972,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>315.2571</v>
+        <v>348.9643</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2974,22 +2980,22 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.03</v>
+        <v>4.64</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-2.91</v>
+        <v>-2.52</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>346.28</v>
+        <v>394.94</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-FEDERALBNK-20261007-b739c0</t>
+          <t>IND-R2-PATANJALI-20261007-ff8244</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3033,15 +3039,15 @@
         <v>167.95</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>169.79</v>
+        <v>171.65</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="L31" s="4" t="n">
         <v>32.9</v>
@@ -3075,7 +3081,7 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>2.81</v>
+        <v>3.86</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-1.75</v>
@@ -3090,7 +3096,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3108,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3122,34 +3128,34 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1243</v>
+        <v>285</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1256.6</v>
+        <v>290.95</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1.09</v>
+        <v>2.09</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>35</v>
+        <v>35.4</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3168,7 +3174,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1215.4286</v>
+        <v>285.4429</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3176,22 +3182,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.28</v>
+        <v>1.89</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-2.22</v>
+        <v>0.16</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1307.07</v>
+        <v>296.6</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AXISBANK-20261006-79c723</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3209,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3223,34 +3229,34 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>540.65</v>
+        <v>119.47</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>545.7</v>
+        <v>121.74</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.93</v>
+        <v>1.9</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>33.2</v>
+        <v>30.2</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3269,7 +3275,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>528.65</v>
+        <v>116.8086</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3277,22 +3283,22 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.12</v>
+        <v>4.05</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-2.22</v>
+        <v>-2.23</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>574.4299999999999</v>
+        <v>125.65</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20261009-2eeb63</t>
+          <t>IND-R2-CANBK-20261005-19551d</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3310,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3324,34 +3330,34 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-11</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>8128.5</v>
+        <v>167.79</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8192.5</v>
+        <v>170.92</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.79</v>
+        <v>1.87</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3370,7 +3376,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8127.1429</v>
+        <v>163.9186</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3378,22 +3384,22 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.02</v>
+        <v>-2.31</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>8660.25</v>
+        <v>177.93</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-POLYCAB-20260911-8559ee</t>
+          <t>IND-R2-WIPRO-20261013-d844f1</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3411,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3434,25 +3440,25 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2813.6</v>
+        <v>324.7</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2831.3</v>
+        <v>330.5</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.63</v>
+        <v>1.79</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>11.2</v>
+        <v>39.3</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3471,7 +3477,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>2734.5571</v>
+        <v>317.1786</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3479,22 +3485,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>3.42</v>
+        <v>4.03</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-2.81</v>
+        <v>-2.32</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>2961.52</v>
+        <v>346.28</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MM-20261007-c1210c</t>
+          <t>IND-R2-FEDERALBNK-20261007-b739c0</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3512,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3526,34 +3532,34 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2074.1</v>
+        <v>1315.4</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2086.7</v>
+        <v>1333</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.61</v>
+        <v>1.34</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>32.3</v>
+        <v>40.6</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3572,7 +3578,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>1997.3429</v>
+        <v>1262.8714</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3580,22 +3586,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>4.28</v>
+        <v>5.26</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-3.7</v>
+        <v>-3.99</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>2205.18</v>
+        <v>1418.99</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MAZDOCK-20261007-e84c93</t>
+          <t>IND-R2-HCLTECH-20261013-955276</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3613,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3627,30 +3633,30 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-08</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>315.6</v>
+        <v>5961</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>317.4</v>
+        <v>6034.5</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0.57</v>
+        <v>1.23</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>38.2</v>
+        <v>33.3</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
@@ -3673,7 +3679,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>299.5571</v>
+        <v>5812.8571</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3681,22 +3687,22 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>5.62</v>
+        <v>3.67</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-5.08</v>
+        <v>-2.49</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>343.17</v>
+        <v>6301.29</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20261008-b77474</t>
+          <t>IND-R2-ATUL-20261007-6aad3b</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3714,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3737,25 +3743,25 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2254.5</v>
+        <v>1129.3</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>2263.1</v>
+        <v>1140</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.38</v>
+        <v>0.95</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>40.5</v>
+        <v>26.2</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3774,7 +3780,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>2156.2858</v>
+        <v>1103.5571</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3782,22 +3788,22 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>4.72</v>
+        <v>3.2</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-4.36</v>
+        <v>-2.28</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>2414.04</v>
+        <v>1183.36</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GLENMARK-20261012-f70810</t>
+          <t>IND-R2-ACC-20261012-f1f022</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3815,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3829,34 +3835,34 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>5961</v>
+        <v>284.4</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>5977</v>
+        <v>287.1</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0.27</v>
+        <v>0.95</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3875,7 +3881,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>5793.5714</v>
+        <v>275.7786</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3883,22 +3889,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>3.07</v>
+        <v>3.94</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>6301.29</v>
+        <v>302.94</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20261007-6aad3b</t>
+          <t>IND-R2-BPCL-20261009-8784b5</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3916,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3930,34 +3936,34 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>142.41</v>
+        <v>2813.6</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>142.77</v>
+        <v>2838.9</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.25</v>
+        <v>0.9</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>33.3</v>
+        <v>11.2</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3976,7 +3982,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>138.4</v>
+        <v>2735.4856</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3984,22 +3990,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>3.06</v>
+        <v>3.64</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-2.82</v>
+        <v>-2.78</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>150.78</v>
+        <v>2961.52</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20261002-27ac34</t>
+          <t>IND-R2-MM-20261007-c1210c</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4017,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>BALKRISIND</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4031,34 +4037,34 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>166.84</v>
+        <v>1987</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>166.99</v>
+        <v>2002.7</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.09</v>
+        <v>0.79</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>37.3</v>
+        <v>33.2</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4077,7 +4083,7 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>162.3571</v>
+        <v>1925.4428</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4085,22 +4091,22 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>2.77</v>
+        <v>3.86</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-2.69</v>
+        <v>-3.1</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>175.28</v>
+        <v>2104.54</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GAIL-20261009-ea012b</t>
+          <t>IND-R2-BALKRISIND-20261013-38dd43</t>
         </is>
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4118,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4132,34 +4138,34 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1129.3</v>
+        <v>126.05</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1129.1</v>
+        <v>126.88</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="K42" s="6" t="n">
-        <v>-0.02</v>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0.66</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>26.2</v>
+        <v>26.7</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4178,7 +4184,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>1093.2572</v>
+        <v>123.0171</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4186,22 +4192,22 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-3.19</v>
+        <v>-2.41</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>1183.36</v>
+        <v>132.8</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ACC-20261012-f1f022</t>
+          <t>IND-R2-IOC-20261009-774a1b</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4219,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4233,34 +4239,34 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1173.3</v>
+        <v>142.41</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>1173</v>
+        <v>143.3</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>-0.03</v>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0.62</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>38.2</v>
+        <v>33.3</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4279,7 +4285,7 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>1128.3429</v>
+        <v>138.4</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4287,22 +4293,22 @@
         </is>
       </c>
       <c r="S43" s="4" t="n">
-        <v>3.81</v>
+        <v>3.42</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-3.83</v>
+        <v>-2.82</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>1240.74</v>
+        <v>150.78</v>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWSTEEL-20261012-af40fc</t>
+          <t>IND-R2-IGL-20261002-27ac34</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4320,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4334,30 +4340,30 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-01</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>284.4</v>
+        <v>223.39</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>283.9</v>
+        <v>224.59</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="K44" s="6" t="n">
-        <v>-0.18</v>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0.54</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>26.7</v>
+        <v>31.2</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
@@ -4380,7 +4386,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>275.7786</v>
+        <v>217.4157</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
@@ -4388,22 +4394,22 @@
         </is>
       </c>
       <c r="S44" s="4" t="n">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>-3.03</v>
+        <v>-2.67</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>302.94</v>
+        <v>234.14</v>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BPCL-20261009-8784b5</t>
+          <t>IND-R2-ONGC-20261001-b42383</t>
         </is>
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4421,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4435,34 +4441,34 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-08</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>933.95</v>
+        <v>540.65</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>931.85</v>
+        <v>543.25</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>-0.22</v>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.48</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>40.7</v>
+        <v>33.2</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -4481,7 +4487,7 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>904.05</v>
+        <v>528.65</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4489,17 +4495,17 @@
         </is>
       </c>
       <c r="S45" s="4" t="n">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>-3.2</v>
+        <v>-2.22</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>982.13</v>
+        <v>574.4299999999999</v>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SHRIRAMFIN-20261008-db2dc4</t>
+          <t>IND-R2-HINDZINC-20261009-2eeb63</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
@@ -4516,7 +4522,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4536,34 +4542,34 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>2629</v>
+        <v>166.84</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>2622.8</v>
+        <v>167.12</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>-0.24</v>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0.17</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>35.9</v>
+        <v>37.3</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -4582,7 +4588,7 @@
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>2530.3143</v>
+        <v>162.3571</v>
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
@@ -4590,22 +4596,22 @@
         </is>
       </c>
       <c r="S46" s="4" t="n">
-        <v>3.53</v>
+        <v>2.85</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>-3.75</v>
+        <v>-2.69</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>2777.03</v>
+        <v>175.28</v>
       </c>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20261012-9e0c35</t>
+          <t>IND-R2-GAIL-20261009-ea012b</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4623,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4637,34 +4643,34 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>698.65</v>
+        <v>1173.3</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>695</v>
+        <v>1174</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>-0.52</v>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>30.9</v>
+        <v>38.2</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4683,7 +4689,7 @@
         </is>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>668.4357</v>
+        <v>1128.3429</v>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
@@ -4691,22 +4697,22 @@
         </is>
       </c>
       <c r="S47" s="4" t="n">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>-4.32</v>
+        <v>-3.83</v>
       </c>
       <c r="U47" s="4" t="n">
-        <v>749.47</v>
+        <v>1240.74</v>
       </c>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CAMS-20260928-86e0a0</t>
+          <t>IND-R2-JSWSTEEL-20261012-af40fc</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4724,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4738,34 +4744,34 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>126.05</v>
+        <v>2254.5</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>125.24</v>
+        <v>2252.8</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.64</v>
+        <v>-0.08</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>26.7</v>
+        <v>40.5</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -4784,7 +4790,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>123.0171</v>
+        <v>2156.2858</v>
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -4792,22 +4798,22 @@
         </is>
       </c>
       <c r="S48" s="4" t="n">
-        <v>1.77</v>
+        <v>4.28</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>-2.41</v>
+        <v>-4.36</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>132.8</v>
+        <v>2414.04</v>
       </c>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IOC-20261009-774a1b</t>
+          <t>IND-R2-GLENMARK-20261012-f70810</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4819,7 +4825,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4839,34 +4845,34 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>10700</v>
+        <v>449.45</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>10624</v>
+        <v>448.7</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.71</v>
+        <v>-0.17</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>43.6</v>
+        <v>35.4</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4885,7 +4891,7 @@
         </is>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>10182.9286</v>
+        <v>431.85</v>
       </c>
       <c r="R49" s="4" t="inlineStr">
         <is>
@@ -4893,22 +4899,22 @@
         </is>
       </c>
       <c r="S49" s="4" t="n">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>-4.83</v>
+        <v>-3.92</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>11796.71</v>
+        <v>478.65</v>
       </c>
       <c r="V49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260928-d4ee3d</t>
+          <t>IND-R2-OIL-20261007-ed8f2f</t>
         </is>
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4926,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4940,34 +4946,34 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-01</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>223.39</v>
+        <v>453.15</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>221.7</v>
+        <v>451.5</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.76</v>
+        <v>-0.36</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>31.2</v>
+        <v>33.3</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -4986,7 +4992,7 @@
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>216.2243</v>
+        <v>434.7143</v>
       </c>
       <c r="R50" s="4" t="inlineStr">
         <is>
@@ -4994,22 +5000,22 @@
         </is>
       </c>
       <c r="S50" s="4" t="n">
-        <v>2.47</v>
+        <v>3.72</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>-3.21</v>
+        <v>-4.07</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>234.14</v>
+        <v>487.36</v>
       </c>
       <c r="V50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ONGC-20261001-b42383</t>
+          <t>IND-R2-CONCOR-20260928-51a3e4</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5027,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -5041,30 +5047,30 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>119.47</v>
+        <v>698.65</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>118.46</v>
+        <v>694.85</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.85</v>
+        <v>-0.54</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>30.2</v>
+        <v>30.9</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5093,7 @@
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>115.81</v>
+        <v>668.4357</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -5095,22 +5101,22 @@
         </is>
       </c>
       <c r="S51" s="4" t="n">
-        <v>2.24</v>
+        <v>3.8</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>-3.06</v>
+        <v>-4.32</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>125.65</v>
+        <v>749.47</v>
       </c>
       <c r="V51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20261005-19551d</t>
+          <t>IND-R2-CAMS-20260928-86e0a0</t>
         </is>
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5128,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -5142,34 +5148,34 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>453.15</v>
+        <v>2629</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>448.25</v>
+        <v>2597.9</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-1.08</v>
+        <v>-1.18</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>33.3</v>
+        <v>35.9</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5188,7 +5194,7 @@
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>430.6857</v>
+        <v>2530.3143</v>
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
@@ -5196,22 +5202,22 @@
         </is>
       </c>
       <c r="S52" s="4" t="n">
-        <v>3.92</v>
+        <v>2.6</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>-4.96</v>
+        <v>-3.75</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>487.36</v>
+        <v>2777.03</v>
       </c>
       <c r="V52" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CONCOR-20260928-51a3e4</t>
+          <t>IND-R2-MUTHOOTFIN-20261012-9e0c35</t>
         </is>
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5229,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -5243,34 +5249,34 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>449.45</v>
+        <v>10700</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>443.9</v>
+        <v>10567</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-1.23</v>
+        <v>-1.24</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>35.4</v>
+        <v>43.6</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5289,7 +5295,7 @@
         </is>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>429.9857</v>
+        <v>10182.9286</v>
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
@@ -5297,22 +5303,22 @@
         </is>
       </c>
       <c r="S53" s="4" t="n">
-        <v>3.13</v>
+        <v>3.63</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>-4.33</v>
+        <v>-4.83</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>478.65</v>
+        <v>11796.71</v>
       </c>
       <c r="V53" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20261007-ed8f2f</t>
+          <t>IND-R2-OFSS-20260928-d4ee3d</t>
         </is>
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5330,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -5344,34 +5350,34 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-16</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>407.75</v>
+        <v>961</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>400.85</v>
+        <v>947</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-1.69</v>
+        <v>-1.46</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>33.3</v>
+        <v>37.2</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5390,7 +5396,7 @@
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>392.3429</v>
+        <v>934.9285</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
@@ -5398,22 +5404,22 @@
         </is>
       </c>
       <c r="S54" s="4" t="n">
-        <v>2.12</v>
+        <v>1.27</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>-3.78</v>
+        <v>-2.71</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>436.95</v>
+        <v>1003.19</v>
       </c>
       <c r="V54" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
+          <t>IND-R2-SBIN-20261005-104400</t>
         </is>
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5431,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -5445,34 +5451,34 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>961</v>
+        <v>407.75</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>942.8</v>
+        <v>401.45</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-1.89</v>
+        <v>-1.55</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>37.2</v>
+        <v>33.3</v>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5491,7 +5497,7 @@
         </is>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>934.9285</v>
+        <v>392.3429</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5499,22 +5505,22 @@
         </is>
       </c>
       <c r="S55" s="4" t="n">
-        <v>0.83</v>
+        <v>2.27</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>-2.71</v>
+        <v>-3.78</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>1003.19</v>
+        <v>436.95</v>
       </c>
       <c r="V55" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20261005-104400</t>
+          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
         </is>
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5532,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -5546,34 +5552,34 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-21</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>124830</v>
+        <v>589.55</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>122450</v>
+        <v>579.1</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-1.91</v>
+        <v>-1.77</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>29.3</v>
+        <v>31.9</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -5592,7 +5598,7 @@
         </is>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>121363.5714</v>
+        <v>562.0732</v>
       </c>
       <c r="R56" s="4" t="inlineStr">
         <is>
@@ -5600,22 +5606,22 @@
         </is>
       </c>
       <c r="S56" s="4" t="n">
-        <v>0.89</v>
+        <v>2.94</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>-2.78</v>
+        <v>-4.66</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>130238.57</v>
+        <v>644.5</v>
       </c>
       <c r="V56" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MRF-20260921-31a31a</t>
+          <t>IND-R2-GNFC-20261012-e5db63</t>
         </is>
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5633,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -5647,34 +5653,34 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-09-21</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>589.55</v>
+        <v>124830</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>570.5</v>
+        <v>122460</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-3.23</v>
+        <v>-1.9</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>31.9</v>
+        <v>29.3</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -5693,7 +5699,7 @@
         </is>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>562.0732</v>
+        <v>121363.5714</v>
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
@@ -5701,22 +5707,22 @@
         </is>
       </c>
       <c r="S57" s="4" t="n">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="T57" s="4" t="n">
-        <v>-4.66</v>
+        <v>-2.78</v>
       </c>
       <c r="U57" s="4" t="n">
-        <v>644.5</v>
+        <v>130238.57</v>
       </c>
       <c r="V57" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20261012-e5db63</t>
+          <t>IND-R2-MRF-20260921-31a31a</t>
         </is>
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5760,15 +5766,15 @@
         <v>74.04000000000001</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>71.14</v>
+        <v>71.66</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-3.92</v>
+        <v>-3.21</v>
       </c>
       <c r="L58" s="4" t="n">
         <v>31.2</v>
@@ -5802,7 +5808,7 @@
         </is>
       </c>
       <c r="S58" s="4" t="n">
-        <v>0.33</v>
+        <v>1.05</v>
       </c>
       <c r="T58" s="4" t="n">
         <v>-4.23</v>
@@ -5817,7 +5823,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5861,15 +5867,15 @@
         <v>397</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>439.2</v>
+        <v>443.5</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>10.63</v>
+        <v>11.71</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -5905,7 +5911,7 @@
         </is>
       </c>
       <c r="S59" s="4" t="n">
-        <v>12.01</v>
+        <v>12.86</v>
       </c>
       <c r="T59" s="4" t="n">
         <v>-2.66</v>
@@ -5966,15 +5972,15 @@
         <v>417.6</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>408.9</v>
+        <v>416.7</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-2.08</v>
+        <v>-0.22</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6010,7 +6016,7 @@
         </is>
       </c>
       <c r="S60" s="4" t="n">
-        <v>0.37</v>
+        <v>2.24</v>
       </c>
       <c r="T60" s="4" t="n">
         <v>-2.45</v>
@@ -6029,120 +6035,223 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="n">
+        <v>378.3286</v>
+      </c>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="T61" s="4" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="U61" s="4" t="n">
+        <v>407.13</v>
+      </c>
+      <c r="V61" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
+        </is>
+      </c>
+      <c r="W61" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -6163,6 +6272,7 @@
     <mergeCell ref="A78:W78"/>
     <mergeCell ref="A65:W65"/>
     <mergeCell ref="A66:W66"/>
+    <mergeCell ref="A80:W80"/>
     <mergeCell ref="A75:W75"/>
     <mergeCell ref="A74:W74"/>
     <mergeCell ref="A3:W3"/>
@@ -6172,7 +6282,6 @@
     <mergeCell ref="A5:W5"/>
     <mergeCell ref="A4:W4"/>
     <mergeCell ref="A72:W72"/>
-    <mergeCell ref="A63:W63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6208,21 +6317,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-13</t>
+          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>143 records · ADMINISTRATIVE 21 · ADVISORY/HISTORICAL 5 · REALIZED EXIT 103 · STOP-BREACH MARK 14   ·   Canonical lifecycle historical coverage begins 2026-08-04 · earlier closures are not held in any provable AEGIS source</t>
+          <t>143 records · ADMINISTRATIVE 21 · ADVISORY/HISTORICAL 5 · REALIZED EXIT 104 · STOP-BREACH MARK 13   ·   Canonical lifecycle historical coverage begins 2026-08-04 · earlier closures are not held in any provable AEGIS source</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>📊 REALIZED PRODUCTION PERFORMANCE · 103 closed trade(s) · win 20/103 · avg -2.69%   ·   EXCLUDED from this line: orphan auto-closes, administrative records, advisory rows, and 14 STOP-BREACH MARK(s) whose stop was passed but which are NOT sold - their price and P&amp;L are today's mark, not a realized result</t>
+          <t>📊 REALIZED PRODUCTION PERFORMANCE · 104 closed trade(s) · win 20/104 · avg -2.67%   ·   EXCLUDED from this line: orphan auto-closes, administrative records, advisory rows, and 13 STOP-BREACH MARK(s) whose stop was passed but which are NOT sold - their price and P&amp;L are today's mark, not a realized result</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6420,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -6348,13 +6457,13 @@
         <v>1191</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1129.5</v>
+        <v>1114</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-5.16</v>
+        <v>-6.47</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -6385,7 +6494,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -6422,13 +6531,13 @@
         <v>187.46</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>173.68</v>
+        <v>175.44</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-7.35</v>
+        <v>-6.41</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -6459,17 +6568,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -6479,71 +6588,69 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>239.45</v>
+        <v>8128.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>221.7</v>
+        <v>8080</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-7.41</v>
+        <v>-0.6</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>38.7</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 232.2186 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-09-30 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R2-POLYCAB-20260911-8559ee</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -6553,59 +6660,61 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>11671</v>
+        <v>239.45</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11231</v>
+        <v>224.59</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-3.77</v>
+        <v>-6.21</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Stop-loss triggered</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>31.3</v>
+          <t>Stop breached</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-10-13 · stop_source=dynamic</t>
+          <t>STOP BREACHED - stop 232.2186 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARUTI-20261002-ee9f86</t>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -6642,13 +6751,13 @@
         <v>1449.5</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1349.8</v>
+        <v>1349.4</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-6.88</v>
+        <v>-6.91</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -6679,7 +6788,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -6716,13 +6825,13 @@
         <v>1413.5</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1323.2</v>
+        <v>1316.2</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-6.39</v>
+        <v>-6.88</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -6758,12 +6867,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -6773,54 +6882,52 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>389.85</v>
+        <v>11671</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>376.2</v>
+        <v>11231</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-3.5</v>
+        <v>-3.77</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>31.3</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 378.3286 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-10-13 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R2-MARUTI-20261002-ee9f86</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -12716,10 +12823,10 @@
         <v>381.6</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>343</v>
+        <v>349.15</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>-10.12</v>
+        <v>-8.5</v>
       </c>
       <c r="K93" s="4" t="n">
         <v>35</v>
@@ -12864,10 +12971,10 @@
         <v>1048.7</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>942.8</v>
+        <v>947</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>-10.1</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="K95" s="4" t="n">
         <v>18</v>
@@ -12938,10 +13045,10 @@
         <v>1642.5</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>1472</v>
+        <v>1501.7</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>-10.38</v>
+        <v>-8.57</v>
       </c>
       <c r="K96" s="4" t="n">
         <v>35</v>
@@ -13086,10 +13193,10 @@
         <v>2410</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>1942.8</v>
+        <v>1934.8</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>-19.39</v>
+        <v>-19.72</v>
       </c>
       <c r="K98" s="4" t="n">
         <v>34</v>
@@ -13160,10 +13267,10 @@
         <v>507.9</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>464.8</v>
+        <v>472.05</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>-8.49</v>
+        <v>-7.06</v>
       </c>
       <c r="K99" s="4" t="n">
         <v>35</v>
@@ -13234,10 +13341,10 @@
         <v>2064.9</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>1865.9</v>
+        <v>1895.8</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>-9.640000000000001</v>
+        <v>-8.19</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>27</v>
@@ -13308,10 +13415,10 @@
         <v>385.15</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>375.6</v>
+        <v>379.9</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>-2.48</v>
+        <v>-1.36</v>
       </c>
       <c r="K101" s="4" t="n">
         <v>11</v>
@@ -13382,10 +13489,10 @@
         <v>5454.5</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>4792</v>
+        <v>4855.2</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>-12.15</v>
+        <v>-10.99</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>35</v>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W80"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -515,14 +515,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>54 investable · NEW 1 · ACTIVE+ 53 · ACTIVE 0   ·   R2 51 · MOMENTUM 0 · R1 3 (advisory)   ·   1 row(s) read 0.00%: admitted at the 2026-10-14 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>55 investable · NEW 2 · ACTIVE+ 53 · ACTIVE 0   ·   R2 52 · MOMENTUM 0 · R1 3 (advisory)   ·   2 row(s) read 0.00%: admitted at the 2026-10-14 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 54 position(s) with an INTACT stop · if all of them fired today the average outcome is -1.08% from entry, worst single -4.83%</t>
+          <t>🛡 DOWNSIDE · 55 position(s) with an INTACT stop · if all of them fired today the average outcome is -1.14% from entry, worst single -4.83%</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=1 · 228 scored · 53 already in CURRENT · biggest blocker: model disagreement (160) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 54 already in CURRENT · biggest blocker: model disagreement (159) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 51 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 52 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -793,34 +793,34 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>464.25</v>
+        <v>1721.4</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>639.6</v>
+        <v>1721.4</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="K9" s="5" t="n">
-        <v>37.77</v>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>600.3321</v>
+        <v>1646.6858</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,24 +847,22 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>6.14</v>
+        <v>4.34</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>29.31</v>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-4.34</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>1833.47</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-OBEROIRLTY-20261014-adf111</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -876,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -896,19 +894,19 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-29</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3150.4</v>
+        <v>464.25</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3673</v>
+        <v>639.6</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -916,14 +914,14 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>16.59</v>
+        <v>37.77</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>29.2</v>
+        <v>31.2</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -942,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3468.9715</v>
+        <v>600.3321</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -950,10 +948,10 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>5.55</v>
+        <v>6.14</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>10.11</v>
+        <v>29.31</v>
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
@@ -962,12 +960,12 @@
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -979,7 +977,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -999,19 +997,19 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-09-29</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2056.8</v>
+        <v>3150.4</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2315</v>
+        <v>3673</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1019,10 +1017,10 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>12.55</v>
+        <v>16.59</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>34.9</v>
+        <v>29.2</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
@@ -1045,7 +1043,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2203.5429</v>
+        <v>3468.9715</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1053,10 +1051,10 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.81</v>
+        <v>5.55</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>7.13</v>
+        <v>10.11</v>
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
@@ -1065,12 +1063,12 @@
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260928-f23b4c</t>
+          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1080,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1102,19 +1100,19 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3110.4</v>
+        <v>2056.8</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3391.2</v>
+        <v>2315</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1122,14 +1120,14 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>9.029999999999999</v>
+        <v>12.55</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1148,7 +1146,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3218.4714</v>
+        <v>2203.5429</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1156,10 +1154,10 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>5.09</v>
+        <v>4.81</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>3.47</v>
+        <v>7.13</v>
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
@@ -1168,12 +1166,12 @@
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BSE-20261005-7af4a1</t>
+          <t>IND-R2-TCS-20260928-f23b4c</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1183,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1205,19 +1203,19 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1010.1</v>
+        <v>3110.4</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1086</v>
+        <v>3391.2</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1225,14 +1223,14 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>7.51</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>38.3</v>
+        <v>34.8</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1251,7 +1249,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1038.8571</v>
+        <v>3218.4714</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1259,10 +1257,10 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>4.34</v>
+        <v>5.09</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>2.85</v>
+        <v>3.47</v>
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
@@ -1271,12 +1269,12 @@
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20261002-20a2cb</t>
+          <t>IND-R2-BSE-20261005-7af4a1</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1286,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1308,19 +1306,19 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>158.38</v>
+        <v>1010.1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>169</v>
+        <v>1086</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1328,14 +1326,14 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>6.71</v>
+        <v>7.51</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>28.1</v>
+        <v>38.3</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1354,7 +1352,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>159.5714</v>
+        <v>1038.8571</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1362,22 +1360,24 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>5.58</v>
+        <v>4.34</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U14" s="4" t="n">
-        <v>176.28</v>
+        <v>2.85</v>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20261012-efab94</t>
+          <t>IND-R2-INFY-20261002-20a2cb</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1409,19 +1409,19 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>323.6</v>
+        <v>158.38</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>345.2</v>
+        <v>169</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>6.67</v>
+        <v>6.71</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>29.2</v>
+        <v>28.1</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>330.2929</v>
+        <v>159.5714</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1463,24 +1463,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.32</v>
+        <v>5.58</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.75</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>176.28</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PFC-20261006-e91ac2</t>
+          <t>IND-R2-BANDHANBNK-20261012-efab94</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1490,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1521,10 +1519,10 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1552.3</v>
+        <v>323.6</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1643.8</v>
+        <v>345.2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1532,14 +1530,14 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>5.89</v>
+        <v>6.67</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>35.4</v>
+        <v>29.2</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1558,7 +1556,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1569.1</v>
+        <v>330.2929</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1566,17 +1564,19 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.54</v>
+        <v>4.32</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="U16" s="4" t="n">
-        <v>1657.62</v>
+        <v>2.07</v>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20261006-676b03</t>
+          <t>IND-R2-PFC-20261006-e91ac2</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1613,19 +1613,19 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-30</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>17.07</v>
+        <v>1552.3</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>17.94</v>
+        <v>1643.8</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1633,14 +1633,14 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>5.1</v>
+        <v>5.89</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>31.3</v>
+        <v>35.4</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>16.9871</v>
+        <v>1569.1</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1667,22 +1667,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.31</v>
+        <v>4.54</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.49</v>
+        <v>1.08</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>18.41</v>
+        <v>1657.62</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260930-4c1d2d</t>
+          <t>IND-R2-DEEPAKNTR-20261006-676b03</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-09-30</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>293.95</v>
+        <v>17.07</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>307.95</v>
+        <v>17.94</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1734,14 +1734,14 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>4.76</v>
+        <v>5.1</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>34.3</v>
+        <v>31.3</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>290.2357</v>
+        <v>16.9871</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1768,22 +1768,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>5.75</v>
+        <v>5.31</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.26</v>
+        <v>-0.49</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>317.43</v>
+        <v>18.41</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20261006-fc497f</t>
+          <t>IND-R2-IRB-20260930-4c1d2d</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1815,19 +1815,19 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>424.55</v>
+        <v>293.95</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>443.5</v>
+        <v>307.95</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>4.46</v>
+        <v>4.76</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>424.4929</v>
+        <v>290.2357</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1869,22 +1869,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>4.29</v>
+        <v>5.75</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.01</v>
+        <v>-1.26</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>449.3</v>
+        <v>317.43</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20261002-563392</t>
+          <t>IND-R2-ANGELONE-20261006-fc497f</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1916,19 +1916,19 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>617.4</v>
+        <v>424.55</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>639.55</v>
+        <v>443.5</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1936,14 +1936,14 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>3.59</v>
+        <v>4.46</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>20.6</v>
+        <v>34.1</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>609.8928</v>
+        <v>424.4929</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1970,22 +1970,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>4.64</v>
+        <v>4.29</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.22</v>
+        <v>-0.01</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>728.8</v>
+        <v>449.3</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACHEM-20261006-fc5587</t>
+          <t>IND-R2-KOTAKBANK-20261002-563392</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>112.03</v>
+        <v>617.4</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>115.97</v>
+        <v>639.55</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -2037,14 +2037,14 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>3.52</v>
+        <v>3.59</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>35</v>
+        <v>20.6</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>112.3543</v>
+        <v>609.8928</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2071,17 +2071,17 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.12</v>
+        <v>4.64</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.29</v>
+        <v>-1.22</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>117.92</v>
+        <v>728.8</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20261006-66ccb3</t>
+          <t>IND-R2-TATACHEM-20261006-fc5587</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2118,19 +2118,19 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-08</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>315.6</v>
+        <v>112.03</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>325.85</v>
+        <v>115.97</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -2138,14 +2138,14 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>38.2</v>
+        <v>35</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>307.7143</v>
+        <v>112.3543</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2172,22 +2172,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>5.57</v>
+        <v>3.12</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.5</v>
+        <v>0.29</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>343.17</v>
+        <v>117.92</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20261008-b77474</t>
+          <t>IND-R2-PNB-20261006-66ccb3</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>6886</v>
+        <v>315.6</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7095</v>
+        <v>325.85</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -2239,14 +2239,14 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>33.3</v>
+        <v>38.2</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>6875.0714</v>
+        <v>307.7143</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2273,17 +2273,17 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.1</v>
+        <v>5.57</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.16</v>
+        <v>-2.5</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>7201.32</v>
+        <v>343.17</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EICHERMOT-20261008-56f58a</t>
+          <t>IND-R2-NATIONALUM-20261008-b77474</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-10-08</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>71.23</v>
+        <v>6886</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>73.34999999999999</v>
+        <v>7095</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -2340,14 +2340,14 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>31.3</v>
+        <v>33.3</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>71.0514</v>
+        <v>6875.0714</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2374,22 +2374,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.25</v>
+        <v>-0.16</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>74.73999999999999</v>
+        <v>7201.32</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NHPC-20261005-cad510</t>
+          <t>IND-R2-EICHERMOT-20261008-56f58a</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-13</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>10581</v>
+        <v>71.23</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10886</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -2441,14 +2441,14 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>35.9</v>
+        <v>31.3</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>10427.1429</v>
+        <v>71.0514</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2475,22 +2475,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>4.22</v>
+        <v>3.13</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.45</v>
+        <v>-0.25</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>11241.86</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BAJAJHLDNG-20261013-3e863a</t>
+          <t>IND-R2-NHPC-20261005-cad510</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2522,19 +2522,19 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2074.1</v>
+        <v>10581</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2126.8</v>
+        <v>10886</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -2542,14 +2542,14 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>32.3</v>
+        <v>35.9</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2033.3572</v>
+        <v>10427.1429</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2576,22 +2576,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.39</v>
+        <v>4.22</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.96</v>
+        <v>-1.45</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2205.18</v>
+        <v>11241.86</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MAZDOCK-20261007-e84c93</t>
+          <t>IND-R2-BAJAJHLDNG-20261013-3e863a</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2623,19 +2623,19 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>814.35</v>
+        <v>2074.1</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>834.35</v>
+        <v>2126.8</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2643,14 +2643,14 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>32.9</v>
+        <v>32.3</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>801.3071</v>
+        <v>2033.3572</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2677,22 +2677,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>3.96</v>
+        <v>4.39</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.6</v>
+        <v>-1.96</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>856.91</v>
+        <v>2205.18</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20261006-0d13b1</t>
+          <t>IND-R2-MAZDOCK-20261007-e84c93</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2724,19 +2724,19 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-08</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>933.95</v>
+        <v>814.35</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>956.75</v>
+        <v>834.35</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>40.7</v>
+        <v>32.9</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>916.2357</v>
+        <v>801.3071</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2778,22 +2778,22 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.23</v>
+        <v>3.96</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.9</v>
+        <v>-1.6</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>982.13</v>
+        <v>856.91</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SHRIRAMFIN-20261008-db2dc4</t>
+          <t>IND-R2-INDIANB-20261006-0d13b1</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2825,19 +2825,19 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-08</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1243</v>
+        <v>933.95</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1271.8</v>
+        <v>956.75</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>35</v>
+        <v>40.7</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1225.0286</v>
+        <v>916.2357</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2879,22 +2879,22 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.68</v>
+        <v>4.23</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-1.45</v>
+        <v>-1.9</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1307.07</v>
+        <v>982.13</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AXISBANK-20261006-79c723</t>
+          <t>IND-R2-SHRIRAMFIN-20261008-db2dc4</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2926,19 +2926,19 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>358</v>
+        <v>1243</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>365.95</v>
+        <v>1271.8</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -2946,14 +2946,14 @@
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>36.4</v>
+        <v>35</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>348.9643</v>
+        <v>1225.0286</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2980,22 +2980,22 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.64</v>
+        <v>3.68</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-2.52</v>
+        <v>-1.45</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>394.94</v>
+        <v>1307.07</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PATANJALI-20261007-ff8244</t>
+          <t>IND-R2-AXISBANK-20261006-79c723</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3027,19 +3027,19 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>167.95</v>
+        <v>358</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>171.65</v>
+        <v>365.95</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -3047,14 +3047,14 @@
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>32.9</v>
+        <v>36.4</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>165.0171</v>
+        <v>348.9643</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3081,22 +3081,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>3.86</v>
+        <v>4.64</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-1.75</v>
+        <v>-2.52</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>179.1</v>
+        <v>394.94</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20261006-801564</t>
+          <t>IND-R2-PATANJALI-20261007-ff8244</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3128,19 +3128,19 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>285</v>
+        <v>167.95</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>290.95</v>
+        <v>171.65</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -3148,14 +3148,14 @@
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>35.4</v>
+        <v>32.9</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>285.4429</v>
+        <v>165.0171</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3182,22 +3182,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>1.89</v>
+        <v>3.86</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.16</v>
+        <v>-1.75</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>296.6</v>
+        <v>179.1</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-UNIONBANK-20261006-801564</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3229,19 +3229,19 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>119.47</v>
+        <v>285</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>121.74</v>
+        <v>290.95</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -3249,14 +3249,14 @@
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>30.2</v>
+        <v>35.4</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>116.8086</v>
+        <v>285.4429</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3283,22 +3283,22 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.05</v>
+        <v>1.89</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-2.23</v>
+        <v>0.16</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>125.65</v>
+        <v>296.6</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20261005-19551d</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3330,19 +3330,19 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-13</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>167.79</v>
+        <v>119.47</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>170.92</v>
+        <v>121.74</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -3350,14 +3350,14 @@
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>38.2</v>
+        <v>30.2</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>163.9186</v>
+        <v>116.8086</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3384,22 +3384,22 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-2.31</v>
+        <v>-2.23</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>177.93</v>
+        <v>125.65</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-WIPRO-20261013-d844f1</t>
+          <t>IND-R2-CANBK-20261005-19551d</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3431,19 +3431,19 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>324.7</v>
+        <v>167.79</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>330.5</v>
+        <v>170.92</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -3451,14 +3451,14 @@
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>39.3</v>
+        <v>38.2</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>317.1786</v>
+        <v>163.9186</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3485,22 +3485,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>4.03</v>
+        <v>4.1</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-2.32</v>
+        <v>-2.31</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>346.28</v>
+        <v>177.93</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-FEDERALBNK-20261007-b739c0</t>
+          <t>IND-R2-WIPRO-20261013-d844f1</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3532,19 +3532,19 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-13</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1315.4</v>
+        <v>324.7</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1333</v>
+        <v>330.5</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -3552,14 +3552,14 @@
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>40.6</v>
+        <v>39.3</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>1262.8714</v>
+        <v>317.1786</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3586,22 +3586,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>5.26</v>
+        <v>4.03</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-3.99</v>
+        <v>-2.32</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>1418.99</v>
+        <v>346.28</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20261013-955276</t>
+          <t>IND-R2-FEDERALBNK-20261007-b739c0</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3633,19 +3633,19 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>5961</v>
+        <v>1315.4</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>6034.5</v>
+        <v>1333</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -3653,14 +3653,14 @@
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>33.3</v>
+        <v>40.6</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>5812.8571</v>
+        <v>1262.8714</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3687,22 +3687,22 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>3.67</v>
+        <v>5.26</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-2.49</v>
+        <v>-3.99</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>6301.29</v>
+        <v>1418.99</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20261007-6aad3b</t>
+          <t>IND-R2-HCLTECH-20261013-955276</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3734,19 +3734,19 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1129.3</v>
+        <v>5961</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>1140</v>
+        <v>6034.5</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -3754,10 +3754,10 @@
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.95</v>
+        <v>1.23</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>26.2</v>
+        <v>33.3</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>1103.5571</v>
+        <v>5812.8571</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3788,22 +3788,22 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-2.28</v>
+        <v>-2.49</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>1183.36</v>
+        <v>6301.29</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ACC-20261012-f1f022</t>
+          <t>IND-R2-ATUL-20261007-6aad3b</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3835,19 +3835,19 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>284.4</v>
+        <v>1129.3</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>287.1</v>
+        <v>1140</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -3858,11 +3858,11 @@
         <v>0.95</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>26.7</v>
+        <v>26.2</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>275.7786</v>
+        <v>1103.5571</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3889,22 +3889,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>3.94</v>
+        <v>3.2</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-3.03</v>
+        <v>-2.28</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>302.94</v>
+        <v>1183.36</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BPCL-20261009-8784b5</t>
+          <t>IND-R2-ACC-20261012-f1f022</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3936,19 +3936,19 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>2813.6</v>
+        <v>284.4</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>2838.9</v>
+        <v>287.1</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -3956,14 +3956,14 @@
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>11.2</v>
+        <v>26.7</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>2735.4856</v>
+        <v>275.7786</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3990,22 +3990,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>3.64</v>
+        <v>3.94</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-2.78</v>
+        <v>-3.03</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>2961.52</v>
+        <v>302.94</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MM-20261007-c1210c</t>
+          <t>IND-R2-BPCL-20261009-8784b5</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>BALKRISIND</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4037,19 +4037,19 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-13</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1987</v>
+        <v>2813.6</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>2002.7</v>
+        <v>2838.9</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>33.2</v>
+        <v>11.2</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>1925.4428</v>
+        <v>2735.4856</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4091,22 +4091,22 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>3.86</v>
+        <v>3.64</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-3.1</v>
+        <v>-2.78</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>2104.54</v>
+        <v>2961.52</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BALKRISIND-20261013-38dd43</t>
+          <t>IND-R2-MM-20261007-c1210c</t>
         </is>
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>BALKRISIND</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4138,19 +4138,19 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>126.05</v>
+        <v>1987</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>126.88</v>
+        <v>2002.7</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -4158,14 +4158,14 @@
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>26.7</v>
+        <v>33.2</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>123.0171</v>
+        <v>1925.4428</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4192,22 +4192,22 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>3.04</v>
+        <v>3.86</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-2.41</v>
+        <v>-3.1</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>132.8</v>
+        <v>2104.54</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IOC-20261009-774a1b</t>
+          <t>IND-R2-BALKRISIND-20261013-38dd43</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4239,19 +4239,19 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>142.41</v>
+        <v>126.05</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>143.3</v>
+        <v>126.88</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -4259,14 +4259,14 @@
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>138.4</v>
+        <v>123.0171</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4293,22 +4293,22 @@
         </is>
       </c>
       <c r="S43" s="4" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-2.82</v>
+        <v>-2.41</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>150.78</v>
+        <v>132.8</v>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20261002-27ac34</t>
+          <t>IND-R2-IOC-20261009-774a1b</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4340,19 +4340,19 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-01</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>223.39</v>
+        <v>142.41</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>224.59</v>
+        <v>143.3</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -4360,14 +4360,14 @@
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>31.2</v>
+        <v>33.3</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>217.4157</v>
+        <v>138.4</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
@@ -4394,22 +4394,22 @@
         </is>
       </c>
       <c r="S44" s="4" t="n">
-        <v>3.19</v>
+        <v>3.42</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>-2.67</v>
+        <v>-2.82</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>234.14</v>
+        <v>150.78</v>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ONGC-20261001-b42383</t>
+          <t>IND-R2-IGL-20261002-27ac34</t>
         </is>
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4441,19 +4441,19 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-01</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>540.65</v>
+        <v>223.39</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>543.25</v>
+        <v>224.59</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -4461,14 +4461,14 @@
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>33.2</v>
+        <v>31.2</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>528.65</v>
+        <v>217.4157</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4495,22 +4495,22 @@
         </is>
       </c>
       <c r="S45" s="4" t="n">
-        <v>2.69</v>
+        <v>3.19</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>-2.22</v>
+        <v>-2.67</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>574.4299999999999</v>
+        <v>234.14</v>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20261009-2eeb63</t>
+          <t>IND-R2-ONGC-20261001-b42383</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>166.84</v>
+        <v>540.65</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>167.12</v>
+        <v>543.25</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -4562,14 +4562,14 @@
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0.17</v>
+        <v>0.48</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>37.3</v>
+        <v>33.2</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>162.3571</v>
+        <v>528.65</v>
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
@@ -4596,22 +4596,22 @@
         </is>
       </c>
       <c r="S46" s="4" t="n">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>-2.69</v>
+        <v>-2.22</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>175.28</v>
+        <v>574.4299999999999</v>
       </c>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GAIL-20261009-ea012b</t>
+          <t>IND-R2-HINDZINC-20261009-2eeb63</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4643,19 +4643,19 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1173.3</v>
+        <v>166.84</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1174</v>
+        <v>167.12</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -4663,14 +4663,14 @@
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>38.2</v>
+        <v>37.3</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>1128.3429</v>
+        <v>162.3571</v>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
@@ -4697,22 +4697,22 @@
         </is>
       </c>
       <c r="S47" s="4" t="n">
-        <v>3.89</v>
+        <v>2.85</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>-3.83</v>
+        <v>-2.69</v>
       </c>
       <c r="U47" s="4" t="n">
-        <v>1240.74</v>
+        <v>175.28</v>
       </c>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWSTEEL-20261012-af40fc</t>
+          <t>IND-R2-GAIL-20261009-ea012b</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4753,25 +4753,25 @@
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>2254.5</v>
+        <v>1173.3</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2252.8</v>
+        <v>1174</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="K48" s="6" t="n">
-        <v>-0.08</v>
+      <c r="K48" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>40.5</v>
+        <v>38.2</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>2156.2858</v>
+        <v>1128.3429</v>
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -4798,17 +4798,17 @@
         </is>
       </c>
       <c r="S48" s="4" t="n">
-        <v>4.28</v>
+        <v>3.89</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>-4.36</v>
+        <v>-3.83</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>2414.04</v>
+        <v>1240.74</v>
       </c>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GLENMARK-20261012-f70810</t>
+          <t>IND-R2-JSWSTEEL-20261012-af40fc</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4845,19 +4845,19 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>449.45</v>
+        <v>2254.5</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>448.7</v>
+        <v>2252.8</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -4865,14 +4865,14 @@
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.17</v>
+        <v>-0.08</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>35.4</v>
+        <v>40.5</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>431.85</v>
+        <v>2156.2858</v>
       </c>
       <c r="R49" s="4" t="inlineStr">
         <is>
@@ -4899,22 +4899,22 @@
         </is>
       </c>
       <c r="S49" s="4" t="n">
-        <v>3.76</v>
+        <v>4.28</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>-3.92</v>
+        <v>-4.36</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>478.65</v>
+        <v>2414.04</v>
       </c>
       <c r="V49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20261007-ed8f2f</t>
+          <t>IND-R2-GLENMARK-20261012-f70810</t>
         </is>
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4946,19 +4946,19 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>453.15</v>
+        <v>449.45</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>451.5</v>
+        <v>448.7</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -4966,14 +4966,14 @@
         </is>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.36</v>
+        <v>-0.17</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>33.3</v>
+        <v>35.4</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>434.7143</v>
+        <v>431.85</v>
       </c>
       <c r="R50" s="4" t="inlineStr">
         <is>
@@ -5000,22 +5000,22 @@
         </is>
       </c>
       <c r="S50" s="4" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>-4.07</v>
+        <v>-3.92</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>487.36</v>
+        <v>478.65</v>
       </c>
       <c r="V50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CONCOR-20260928-51a3e4</t>
+          <t>IND-R2-OIL-20261007-ed8f2f</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>698.65</v>
+        <v>453.15</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>694.85</v>
+        <v>451.5</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -5067,14 +5067,14 @@
         </is>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.54</v>
+        <v>-0.36</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>30.9</v>
+        <v>33.3</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>668.4357</v>
+        <v>434.7143</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -5101,17 +5101,17 @@
         </is>
       </c>
       <c r="S51" s="4" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>-4.32</v>
+        <v>-4.07</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>749.47</v>
+        <v>487.36</v>
       </c>
       <c r="V51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CAMS-20260928-86e0a0</t>
+          <t>IND-R2-CONCOR-20260928-51a3e4</t>
         </is>
       </c>
       <c r="W51" s="4" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -5148,19 +5148,19 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>2629</v>
+        <v>698.65</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>2597.9</v>
+        <v>694.85</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-1.18</v>
+        <v>-0.54</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>35.9</v>
+        <v>30.9</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>2530.3143</v>
+        <v>668.4357</v>
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
@@ -5202,22 +5202,22 @@
         </is>
       </c>
       <c r="S52" s="4" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>-3.75</v>
+        <v>-4.32</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>2777.03</v>
+        <v>749.47</v>
       </c>
       <c r="V52" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20261012-9e0c35</t>
+          <t>IND-R2-CAMS-20260928-86e0a0</t>
         </is>
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -5249,19 +5249,19 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>10700</v>
+        <v>2629</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10567</v>
+        <v>2597.9</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -5269,14 +5269,14 @@
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-1.24</v>
+        <v>-1.18</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>43.6</v>
+        <v>35.9</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>10182.9286</v>
+        <v>2530.3143</v>
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
@@ -5303,22 +5303,22 @@
         </is>
       </c>
       <c r="S53" s="4" t="n">
-        <v>3.63</v>
+        <v>2.6</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>-4.83</v>
+        <v>-3.75</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>11796.71</v>
+        <v>2777.03</v>
       </c>
       <c r="V53" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260928-d4ee3d</t>
+          <t>IND-R2-MUTHOOTFIN-20261012-9e0c35</t>
         </is>
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -5350,19 +5350,19 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>961</v>
+        <v>10700</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>947</v>
+        <v>10567</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -5370,14 +5370,14 @@
         </is>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-1.46</v>
+        <v>-1.24</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>37.2</v>
+        <v>43.6</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>934.9285</v>
+        <v>10182.9286</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
@@ -5404,22 +5404,22 @@
         </is>
       </c>
       <c r="S54" s="4" t="n">
-        <v>1.27</v>
+        <v>3.63</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>-2.71</v>
+        <v>-4.83</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>1003.19</v>
+        <v>11796.71</v>
       </c>
       <c r="V54" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SBIN-20261005-104400</t>
+          <t>IND-R2-OFSS-20260928-d4ee3d</t>
         </is>
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -5451,19 +5451,19 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-16</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>407.75</v>
+        <v>961</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>401.45</v>
+        <v>947</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -5471,14 +5471,14 @@
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-1.55</v>
+        <v>-1.46</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>33.3</v>
+        <v>37.2</v>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>392.3429</v>
+        <v>934.9285</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5505,22 +5505,22 @@
         </is>
       </c>
       <c r="S55" s="4" t="n">
-        <v>2.27</v>
+        <v>1.27</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>-3.78</v>
+        <v>-2.71</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>436.95</v>
+        <v>1003.19</v>
       </c>
       <c r="V55" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
+          <t>IND-R2-SBIN-20261005-104400</t>
         </is>
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -5552,19 +5552,19 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>589.55</v>
+        <v>407.75</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>579.1</v>
+        <v>401.45</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -5572,14 +5572,14 @@
         </is>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-1.77</v>
+        <v>-1.55</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>31.9</v>
+        <v>33.3</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>562.0732</v>
+        <v>392.3429</v>
       </c>
       <c r="R56" s="4" t="inlineStr">
         <is>
@@ -5606,22 +5606,22 @@
         </is>
       </c>
       <c r="S56" s="4" t="n">
-        <v>2.94</v>
+        <v>2.27</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>-4.66</v>
+        <v>-3.78</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>644.5</v>
+        <v>436.95</v>
       </c>
       <c r="V56" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20261012-e5db63</t>
+          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
         </is>
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -5653,19 +5653,19 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-21</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>124830</v>
+        <v>589.55</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>122460</v>
+        <v>579.1</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -5673,14 +5673,14 @@
         </is>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-1.9</v>
+        <v>-1.77</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>29.3</v>
+        <v>31.9</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>121363.5714</v>
+        <v>562.0732</v>
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
@@ -5707,22 +5707,22 @@
         </is>
       </c>
       <c r="S57" s="4" t="n">
-        <v>0.9</v>
+        <v>2.94</v>
       </c>
       <c r="T57" s="4" t="n">
-        <v>-2.78</v>
+        <v>-4.66</v>
       </c>
       <c r="U57" s="4" t="n">
-        <v>130238.57</v>
+        <v>644.5</v>
       </c>
       <c r="V57" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MRF-20260921-31a31a</t>
+          <t>IND-R2-GNFC-20261012-e5db63</t>
         </is>
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -5754,19 +5754,19 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-09-21</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>74.04000000000001</v>
+        <v>124830</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>71.66</v>
+        <v>122460</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -5774,14 +5774,14 @@
         </is>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-3.21</v>
+        <v>-1.9</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>31.2</v>
+        <v>29.3</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>70.90860000000001</v>
+        <v>121363.5714</v>
       </c>
       <c r="R58" s="4" t="inlineStr">
         <is>
@@ -5808,22 +5808,22 @@
         </is>
       </c>
       <c r="S58" s="4" t="n">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="T58" s="4" t="n">
-        <v>-4.23</v>
+        <v>-2.78</v>
       </c>
       <c r="U58" s="4" t="n">
-        <v>78.73999999999999</v>
+        <v>130238.57</v>
       </c>
       <c r="V58" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NMDC-20261006-2acbae</t>
+          <t>IND-R2-MRF-20260921-31a31a</t>
         </is>
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -5850,41 +5850,39 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>397</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>443.5</v>
+        <v>71.66</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="K59" s="5" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+      <c r="K59" s="6" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>31.2</v>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -5903,7 +5901,7 @@
         </is>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>386.4571</v>
+        <v>70.90860000000001</v>
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
@@ -5911,24 +5909,22 @@
         </is>
       </c>
       <c r="S59" s="4" t="n">
-        <v>12.86</v>
+        <v>1.05</v>
       </c>
       <c r="T59" s="4" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="U59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-4.23</v>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>78.73999999999999</v>
       </c>
       <c r="V59" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-NMDC-20261006-2acbae</t>
         </is>
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5936,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -5960,27 +5956,27 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-05</t>
+          <t>Admitted 2026-08-04</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>417.6</v>
+        <v>397</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>416.7</v>
+        <v>443.5</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="K60" s="6" t="n">
-        <v>-0.22</v>
+      <c r="K60" s="5" t="n">
+        <v>11.71</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -5989,7 +5985,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6008,7 +6004,7 @@
         </is>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>407.3714</v>
+        <v>386.4571</v>
       </c>
       <c r="R60" s="4" t="inlineStr">
         <is>
@@ -6016,17 +6012,19 @@
         </is>
       </c>
       <c r="S60" s="4" t="n">
-        <v>2.24</v>
+        <v>12.86</v>
       </c>
       <c r="T60" s="4" t="n">
-        <v>-2.45</v>
-      </c>
-      <c r="U60" s="4" t="n">
-        <v>432.94</v>
+        <v>-2.66</v>
+      </c>
+      <c r="U60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V60" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
       <c r="W60" s="4" t="inlineStr">
@@ -6043,215 +6041,318 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-05</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>416.7</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="n">
+        <v>407.3714</v>
+      </c>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T61" s="4" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="U61" s="4" t="n">
+        <v>432.94</v>
+      </c>
+      <c r="V61" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+        </is>
+      </c>
+      <c r="W61" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
           <t>BEL</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-04</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="H61" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>389.85</v>
       </c>
-      <c r="I61" s="4" t="n">
+      <c r="I62" s="4" t="n">
         <v>381.6</v>
       </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="K61" s="6" t="n">
+      <c r="K62" s="6" t="n">
         <v>-2.12</v>
       </c>
-      <c r="L61" s="4" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M61" s="4" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N61" s="4" t="inlineStr">
+      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O61" s="4" t="inlineStr">
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P61" s="4" t="inlineStr">
+      <c r="P62" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q61" s="4" t="n">
+      <c r="Q62" s="4" t="n">
         <v>378.3286</v>
       </c>
-      <c r="R61" s="4" t="inlineStr">
+      <c r="R62" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S61" s="4" t="n">
+      <c r="S62" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="T61" s="4" t="n">
+      <c r="T62" s="4" t="n">
         <v>-2.96</v>
       </c>
-      <c r="U61" s="4" t="n">
+      <c r="U62" s="4" t="n">
         <v>407.13</v>
       </c>
-      <c r="V61" s="4" t="inlineStr">
+      <c r="V62" s="4" t="inlineStr">
         <is>
           <t>IND-R1-BEL-20260804-c9f4d0</t>
         </is>
       </c>
-      <c r="W61" s="4" t="inlineStr">
+      <c r="W62" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -6262,7 +6363,6 @@
     <mergeCell ref="A68:W68"/>
     <mergeCell ref="A67:W67"/>
     <mergeCell ref="A77:W77"/>
-    <mergeCell ref="A64:W64"/>
     <mergeCell ref="A73:W73"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A70:W70"/>
@@ -6282,6 +6382,7 @@
     <mergeCell ref="A5:W5"/>
     <mergeCell ref="A4:W4"/>
     <mergeCell ref="A72:W72"/>
+    <mergeCell ref="A81:W81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W84"/>
+  <dimension ref="A1:W86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,21 +508,21 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-15 · prices = 2026-10-15 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-16 · prices = 2026-10-16 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>58 investable · NEW 4 · ACTIVE+ 54 · ACTIVE 0   ·   R2 55 · MOMENTUM 0 · R1 3 (advisory)   ·   4 row(s) read 0.00%: admitted at the 2026-10-15 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>60 investable · NEW 2 · ACTIVE+ 58 · ACTIVE 0   ·   R2 57 · MOMENTUM 0 · R1 3 (advisory)   ·   2 row(s) read 0.00%: admitted at the 2026-10-16 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 58 position(s) with an INTACT stop · if all of them fired today the average outcome is -0.83% from entry, worst single -6.00%</t>
+          <t>🛡 DOWNSIDE · 60 position(s) with an INTACT stop · if all of them fired today the average outcome is -0.30% from entry, worst single -5.45%</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=4 · 228 scored · 57 already in CURRENT · biggest blocker: model disagreement (156) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 59 already in CURRENT · biggest blocker: model disagreement (155) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 55 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 57 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -697,29 +697,29 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>352.3</v>
+        <v>3677.2</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>352.3</v>
+        <v>3677.2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>33.2</v>
+        <v>34.9</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>336.6571</v>
+        <v>3496.4428</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,17 +746,17 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>4.44</v>
+        <v>4.92</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-4.44</v>
+        <v>-4.92</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>375.76</v>
+        <v>3948.34</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBUJACEM-20261015-8d9ef6</t>
+          <t>IND-R2-AIAENG-20261016-4b46fa</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -798,29 +798,29 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>886.4</v>
+        <v>785.95</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>886.4</v>
+        <v>785.95</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>38.2</v>
+        <v>31.1</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>848.6643</v>
+        <v>749.9857</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,17 +847,17 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>4.26</v>
+        <v>4.58</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-4.26</v>
+        <v>-4.58</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>943</v>
+        <v>839.9</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDALCO-20261015-90a1fd</t>
+          <t>IND-R2-NATCOPHARM-20261016-fbbf8d</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -894,34 +894,34 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>170.17</v>
+        <v>464.25</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>170.17</v>
+        <v>636.95</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>37.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>40.5</v>
+        <v>31.2</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>159.9643</v>
+        <v>622.9393</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,22 +948,24 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>185.48</v>
+        <v>34.18</v>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20261015-5cdb61</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -975,7 +977,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -985,7 +987,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -995,34 +997,34 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-29</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>246.4</v>
+        <v>3150.4</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>246.4</v>
+        <v>3805</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>20.78</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>33.2</v>
+        <v>29.2</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1041,7 +1043,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>233</v>
+        <v>3588.3286</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1049,22 +1051,24 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>5.44</v>
+        <v>5.69</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-5.44</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>266.5</v>
+        <v>13.9</v>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20261015-a93a60</t>
+          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1080,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1096,34 +1100,34 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>464.25</v>
+        <v>2056.8</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>663.3</v>
+        <v>2440</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>42.88</v>
+        <v>18.63</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>31.2</v>
+        <v>34.9</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1142,7 +1146,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>622.9393</v>
+        <v>2318.1286</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1150,10 +1154,10 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>6.08</v>
+        <v>4.99</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>34.18</v>
+        <v>12.71</v>
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
@@ -1162,12 +1166,12 @@
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-TCS-20260928-f23b4c</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1183,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1199,30 +1203,30 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-29</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3150.4</v>
+        <v>1010.1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3681.3</v>
+        <v>1158.85</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>16.85</v>
+        <v>14.73</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>29.2</v>
+        <v>38.3</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
@@ -1245,7 +1249,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>3471.743</v>
+        <v>1104.5857</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1253,10 +1257,10 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>5.69</v>
+        <v>4.68</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>10.2</v>
+        <v>9.35</v>
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
@@ -1265,12 +1269,12 @@
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
+          <t>IND-R2-INFY-20261002-20a2cb</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1286,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1302,30 +1306,30 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2056.8</v>
+        <v>167.79</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2365.7</v>
+        <v>183.99</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>15.02</v>
+        <v>9.65</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>34.9</v>
+        <v>38.2</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
@@ -1348,7 +1352,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2247.8</v>
+        <v>175.0071</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1356,10 +1360,10 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.98</v>
+        <v>4.88</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>9.289999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
@@ -1368,12 +1372,12 @@
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260928-f23b4c</t>
+          <t>IND-R2-WIPRO-20261013-d844f1</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1389,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1405,34 +1409,34 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1010.1</v>
+        <v>3110.4</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1115.6</v>
+        <v>3352</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>10.44</v>
+        <v>7.77</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>38.3</v>
+        <v>34.8</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1451,7 +1455,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1064.4857</v>
+        <v>3218.4714</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1459,10 +1463,10 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.58</v>
+        <v>3.98</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>5.38</v>
+        <v>3.47</v>
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
@@ -1471,12 +1475,12 @@
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20261002-20a2cb</t>
+          <t>IND-R2-BSE-20261005-7af4a1</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1520,15 +1524,15 @@
         <v>158.38</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>172.74</v>
+        <v>169.93</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>9.07</v>
+        <v>7.29</v>
       </c>
       <c r="L16" s="4" t="n">
         <v>28.1</v>
@@ -1562,7 +1566,7 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>5.36</v>
+        <v>3.79</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>3.22</v>
@@ -1577,7 +1581,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1593,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1609,30 +1613,30 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3110.4</v>
+        <v>424.55</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3371.1</v>
+        <v>452.4</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>8.380000000000001</v>
+        <v>6.56</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>34.8</v>
+        <v>34.1</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
@@ -1655,7 +1659,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3218.4714</v>
+        <v>432.9857</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1663,10 +1667,10 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>4.53</v>
+        <v>4.29</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>3.47</v>
+        <v>1.99</v>
       </c>
       <c r="U17" s="4" t="inlineStr">
         <is>
@@ -1675,12 +1679,12 @@
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BSE-20261005-7af4a1</t>
+          <t>IND-R2-KOTAKBANK-20261002-563392</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1696,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1712,30 +1716,30 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>323.6</v>
+        <v>10581</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>346.75</v>
+        <v>11209</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>7.15</v>
+        <v>5.94</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>29.2</v>
+        <v>35.9</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -1758,7 +1762,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>331.5571</v>
+        <v>10764.4286</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1766,24 +1770,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>4.38</v>
+        <v>3.97</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1.73</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>11241.86</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PFC-20261006-e91ac2</t>
+          <t>IND-R2-BAJAJHLDNG-20261013-3e863a</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1797,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1824,21 +1826,21 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>293.95</v>
+        <v>323.6</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>312.3</v>
+        <v>341.25</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>6.24</v>
+        <v>5.45</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>34.3</v>
+        <v>29.2</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -1861,7 +1863,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>294.7214</v>
+        <v>331.5571</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1869,22 +1871,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>5.63</v>
+        <v>2.84</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.26</v>
+        <v>2.46</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>317.43</v>
+        <v>342.03</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ANGELONE-20261006-fc497f</t>
+          <t>IND-R2-PFC-20261006-e91ac2</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1898,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1916,34 +1918,34 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-08</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1552.3</v>
+        <v>6886</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1641.1</v>
+        <v>7252</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>5.72</v>
+        <v>5.32</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>35.4</v>
+        <v>33.3</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1962,7 +1964,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1569.1</v>
+        <v>6994.2857</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1970,22 +1972,24 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>4.39</v>
+        <v>3.55</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="U20" s="4" t="n">
-        <v>1657.62</v>
+        <v>1.57</v>
+      </c>
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20261006-676b03</t>
+          <t>IND-R2-EICHERMOT-20261008-56f58a</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2001,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2026,21 +2030,21 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>112.03</v>
+        <v>814.35</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>117.54</v>
+        <v>856.3</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>4.92</v>
+        <v>5.15</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>35</v>
+        <v>32.9</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -2063,7 +2067,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>112.3543</v>
+        <v>819.8857</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2071,22 +2075,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.41</v>
+        <v>4.25</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.29</v>
+        <v>0.68</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>117.92</v>
+        <v>856.91</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20261006-66ccb3</t>
+          <t>IND-R2-INDIANB-20261006-0d13b1</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2102,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2118,34 +2122,34 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-08</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>6886</v>
+        <v>1315.4</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>7195</v>
+        <v>1381</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>4.49</v>
+        <v>4.99</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>33.3</v>
+        <v>40.6</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2164,7 +2168,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>6933.4286</v>
+        <v>1307.3428</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2172,22 +2176,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>3.64</v>
+        <v>5.33</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.61</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>7201.32</v>
+        <v>1418.99</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EICHERMOT-20261008-56f58a</t>
+          <t>IND-R2-HCLTECH-20261013-955276</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2203,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2219,34 +2223,34 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-13</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1315.4</v>
+        <v>293.95</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1368.6</v>
+        <v>306.2</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>4.04</v>
+        <v>4.17</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>40.6</v>
+        <v>34.3</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2265,7 +2269,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1296.3428</v>
+        <v>294.7214</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2273,22 +2277,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>5.28</v>
+        <v>3.75</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.45</v>
+        <v>0.26</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1418.99</v>
+        <v>317.43</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20261013-955276</t>
+          <t>IND-R2-ANGELONE-20261006-fc497f</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2304,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2320,34 +2324,34 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-30</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>17.07</v>
+        <v>1552.3</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>17.75</v>
+        <v>1613.6</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>31.3</v>
+        <v>35.4</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2366,7 +2370,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>16.9871</v>
+        <v>1569.1</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2374,22 +2378,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.3</v>
+        <v>2.76</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.49</v>
+        <v>1.08</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>18.41</v>
+        <v>1657.62</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IRB-20260930-4c1d2d</t>
+          <t>IND-R2-DEEPAKNTR-20261006-676b03</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2405,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>BALKRISIND</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2421,34 +2425,34 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>424.55</v>
+        <v>1987</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>441.1</v>
+        <v>2064</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>34.1</v>
+        <v>33.2</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2467,7 +2471,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>424.4929</v>
+        <v>1983.7999</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2475,22 +2479,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.76</v>
+        <v>3.89</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.16</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>449.3</v>
+        <v>2104.54</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20261002-563392</t>
+          <t>IND-R2-BALKRISIND-20261013-38dd43</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2506,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2522,34 +2526,34 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-13</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>10581</v>
+        <v>5961</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10950</v>
+        <v>6191</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>3.49</v>
+        <v>3.86</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>35.9</v>
+        <v>33.3</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2568,7 +2572,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>10478.5714</v>
+        <v>5966.5714</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2576,22 +2580,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.31</v>
+        <v>3.63</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.97</v>
+        <v>0.09</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>11241.86</v>
+        <v>6301.29</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BAJAJHLDNG-20261013-3e863a</t>
+          <t>IND-R2-ATUL-20261007-6aad3b</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2607,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2623,34 +2627,34 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-13</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>167.79</v>
+        <v>1173.3</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>173.65</v>
+        <v>1216.3</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>3.49</v>
+        <v>3.66</v>
       </c>
       <c r="L27" s="4" t="n">
         <v>38.2</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2669,7 +2673,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>166.2714</v>
+        <v>1167.1</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2677,22 +2681,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.91</v>
+        <v>-0.53</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>177.93</v>
+        <v>1240.74</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-WIPRO-20261013-d844f1</t>
+          <t>IND-R2-JSWSTEEL-20261012-af40fc</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2724,34 +2728,34 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>814.35</v>
+        <v>2813.6</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>841.8</v>
+        <v>2915</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>3.37</v>
+        <v>3.6</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>32.9</v>
+        <v>11.2</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2770,7 +2774,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>807.5071</v>
+        <v>2803.1286</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2778,22 +2782,22 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.07</v>
+        <v>3.84</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.84</v>
+        <v>-0.37</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>856.91</v>
+        <v>2961.52</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20261006-0d13b1</t>
+          <t>IND-R2-MM-20261007-c1210c</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2837,15 +2841,15 @@
         <v>1243</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="L29" s="4" t="n">
         <v>35</v>
@@ -2871,7 +2875,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1241.8857</v>
+        <v>1243.1285</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2879,10 +2883,10 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="U29" s="4" t="n">
         <v>1307.07</v>
@@ -2894,7 +2898,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2910,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2926,34 +2930,34 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>324.7</v>
+        <v>284.4</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>335.25</v>
+        <v>293.9</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>39.3</v>
+        <v>26.7</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2972,7 +2976,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>322.1</v>
+        <v>280.8857</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2980,22 +2984,22 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.92</v>
+        <v>4.43</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.8</v>
+        <v>-1.24</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>346.28</v>
+        <v>302.94</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-FEDERALBNK-20261007-b739c0</t>
+          <t>IND-R2-BPCL-20261009-8784b5</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3011,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3027,34 +3031,34 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-10-08</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>285</v>
+        <v>315.6</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>294.2</v>
+        <v>325.75</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>35.4</v>
+        <v>38.2</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3073,7 +3077,7 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>285.4429</v>
+        <v>310.9696</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3081,22 +3085,22 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>2.98</v>
+        <v>4.54</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.16</v>
+        <v>-1.47</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>296.6</v>
+        <v>343.17</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PETRONET-20260915-3767de</t>
+          <t>IND-R2-NATIONALUM-20261008-b77474</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3112,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3137,21 +3141,21 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>167.95</v>
+        <v>112.03</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>173.08</v>
+        <v>115.55</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>32.9</v>
+        <v>35</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
@@ -3174,7 +3178,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>165.0171</v>
+        <v>112.3543</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3182,22 +3186,22 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.66</v>
+        <v>2.77</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-1.75</v>
+        <v>0.29</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>179.1</v>
+        <v>117.92</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20261006-801564</t>
+          <t>IND-R2-PNB-20261006-66ccb3</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3241,15 +3245,15 @@
         <v>617.4</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>634.55</v>
+        <v>635.9</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="L33" s="4" t="n">
         <v>20.6</v>
@@ -3283,7 +3287,7 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.89</v>
+        <v>4.09</v>
       </c>
       <c r="T33" s="4" t="n">
         <v>-1.22</v>
@@ -3298,7 +3302,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3314,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3330,30 +3334,30 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-09-30</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2074.1</v>
+        <v>17.07</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2129</v>
+        <v>17.55</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>32.3</v>
+        <v>31.3</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
@@ -3376,7 +3380,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>2034.1286</v>
+        <v>16.9871</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3384,22 +3388,22 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>4.46</v>
+        <v>3.21</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-1.93</v>
+        <v>-0.49</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2205.18</v>
+        <v>18.41</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MAZDOCK-20261007-e84c93</t>
+          <t>IND-R2-IRB-20260930-4c1d2d</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3415,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3431,34 +3435,34 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>284.4</v>
+        <v>167.95</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>291.1</v>
+        <v>172.64</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>2.36</v>
+        <v>2.79</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>26.7</v>
+        <v>32.9</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3477,7 +3481,7 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>277.8572</v>
+        <v>165.0171</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3485,22 +3489,22 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-2.3</v>
+        <v>-1.75</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>302.94</v>
+        <v>179.1</v>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BPCL-20261009-8784b5</t>
+          <t>IND-R2-UNIONBANK-20261006-801564</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3516,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3532,34 +3536,34 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>71.23</v>
+        <v>285</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>72.91</v>
+        <v>292.6</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>31.3</v>
+        <v>35.4</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3578,7 +3582,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>71.0514</v>
+        <v>285.4429</v>
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -3586,22 +3590,22 @@
         </is>
       </c>
       <c r="S36" s="4" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>-0.25</v>
+        <v>0.16</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>74.73999999999999</v>
+        <v>296.6</v>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NHPC-20261005-cad510</t>
+          <t>IND-R2-PETRONET-20260915-3767de</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3617,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3642,25 +3646,25 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>5961</v>
+        <v>358</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>6096</v>
+        <v>367</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>2.26</v>
+        <v>2.51</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>33.3</v>
+        <v>36.4</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3679,7 +3683,7 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>5871.5</v>
+        <v>350.4214</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3687,22 +3691,22 @@
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v>3.68</v>
+        <v>4.52</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>-1.5</v>
+        <v>-2.12</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>6301.29</v>
+        <v>394.94</v>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20261007-6aad3b</t>
+          <t>IND-R2-PATANJALI-20261007-ff8244</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3718,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3734,34 +3738,34 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>358</v>
+        <v>126.05</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>365.9</v>
+        <v>128.61</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>2.21</v>
+        <v>2.03</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>36.4</v>
+        <v>26.7</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3780,7 +3784,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>348.9929</v>
+        <v>123.8814</v>
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
@@ -3788,22 +3792,22 @@
         </is>
       </c>
       <c r="S38" s="4" t="n">
-        <v>4.62</v>
+        <v>3.68</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>-2.52</v>
+        <v>-1.72</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>394.94</v>
+        <v>132.8</v>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PATANJALI-20261007-ff8244</t>
+          <t>IND-R2-IOC-20261009-774a1b</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3819,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>BALKRISIND</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3835,34 +3839,34 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-13</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1987</v>
+        <v>324.7</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>2023.9</v>
+        <v>331</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>33.2</v>
+        <v>39.3</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3881,7 +3885,7 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>1942.5714</v>
+        <v>322.1</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3889,22 +3893,22 @@
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v>4.02</v>
+        <v>2.69</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-2.24</v>
+        <v>-0.8</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>2104.54</v>
+        <v>346.28</v>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BALKRISIND-20261013-38dd43</t>
+          <t>IND-R2-FEDERALBNK-20261007-b739c0</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3920,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3936,34 +3940,34 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-08</t>
+          <t>Admitted 2026-10-15</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>933.95</v>
+        <v>886.4</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>951</v>
+        <v>903.6</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>40.7</v>
+        <v>38.2</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3982,7 +3986,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>916.2357</v>
+        <v>864.5357</v>
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
@@ -3990,22 +3994,22 @@
         </is>
       </c>
       <c r="S40" s="4" t="n">
-        <v>3.66</v>
+        <v>4.32</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>-1.9</v>
+        <v>-2.47</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>982.13</v>
+        <v>943</v>
       </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SHRIRAMFIN-20261008-db2dc4</t>
+          <t>IND-R2-HINDALCO-20261015-90a1fd</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4021,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4037,34 +4041,34 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1129.3</v>
+        <v>71.23</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>1146.8</v>
+        <v>72.47</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>26.2</v>
+        <v>31.3</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4083,7 +4087,7 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>1109.8429</v>
+        <v>71.0514</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4091,22 +4095,22 @@
         </is>
       </c>
       <c r="S41" s="4" t="n">
-        <v>3.22</v>
+        <v>1.96</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-1.72</v>
+        <v>-0.25</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>1183.36</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ACC-20261012-f1f022</t>
+          <t>IND-R2-NHPC-20261005-cad510</t>
         </is>
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4122,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4138,34 +4142,34 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>126.05</v>
+        <v>2074.1</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>127.99</v>
+        <v>2110</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>26.7</v>
+        <v>32.3</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4184,7 +4188,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>123.2343</v>
+        <v>2034.1286</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -4192,22 +4196,22 @@
         </is>
       </c>
       <c r="S42" s="4" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>-2.23</v>
+        <v>-1.93</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>132.8</v>
+        <v>2205.18</v>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IOC-20261009-774a1b</t>
+          <t>IND-R2-MAZDOCK-20261007-e84c93</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4223,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4239,34 +4243,34 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2813.6</v>
+        <v>142.41</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>2851.2</v>
+        <v>144.84</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>11.2</v>
+        <v>33.3</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4285,7 +4289,7 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>2743.1285</v>
+        <v>138.7643</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4293,22 +4297,22 @@
         </is>
       </c>
       <c r="S43" s="4" t="n">
-        <v>3.79</v>
+        <v>4.19</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-2.5</v>
+        <v>-2.56</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>2961.52</v>
+        <v>150.78</v>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MM-20261007-c1210c</t>
+          <t>IND-R2-IGL-20261002-27ac34</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4324,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4349,21 +4353,21 @@
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1173.3</v>
+        <v>1129.3</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>1187.9</v>
+        <v>1146.6</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>38.2</v>
+        <v>26.2</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
@@ -4386,7 +4390,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>1140.8857</v>
+        <v>1109.8429</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
@@ -4394,22 +4398,22 @@
         </is>
       </c>
       <c r="S44" s="4" t="n">
-        <v>3.96</v>
+        <v>3.21</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>-2.76</v>
+        <v>-1.72</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>1240.74</v>
+        <v>1183.36</v>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JSWSTEEL-20261012-af40fc</t>
+          <t>IND-R2-ACC-20261012-f1f022</t>
         </is>
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4425,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4441,34 +4445,34 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-14</t>
+          <t>Admitted 2026-09-16</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>373.9</v>
+        <v>407.75</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>378.5</v>
+        <v>411.75</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>1.23</v>
+        <v>0.98</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>35.2</v>
+        <v>33.3</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -4487,7 +4491,7 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>362.5643</v>
+        <v>392.3429</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4495,22 +4499,22 @@
         </is>
       </c>
       <c r="S45" s="4" t="n">
-        <v>4.21</v>
+        <v>4.71</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>-3.03</v>
+        <v>-3.78</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>398.99</v>
+        <v>436.95</v>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EMAMILTD-20261014-d5bbe7</t>
+          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4526,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4542,34 +4546,34 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-16</t>
+          <t>Admitted 2026-10-15</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>407.75</v>
+        <v>246.4</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>412</v>
+        <v>248.6</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>1.04</v>
+        <v>0.89</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -4588,7 +4592,7 @@
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>392.3429</v>
+        <v>235.2286</v>
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
@@ -4596,22 +4600,22 @@
         </is>
       </c>
       <c r="S46" s="4" t="n">
-        <v>4.77</v>
+        <v>5.38</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>-3.78</v>
+        <v>-4.53</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>436.95</v>
+        <v>266.5</v>
       </c>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOTYRE-20260916-440d86</t>
+          <t>IND-R2-VEDL-20261015-a93a60</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4627,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4643,34 +4647,34 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-15</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>698.65</v>
+        <v>352.3</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>705.9</v>
+        <v>355.2</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>1.04</v>
+        <v>0.82</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>30.9</v>
+        <v>33.2</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4689,7 +4693,7 @@
         </is>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>671.0643</v>
+        <v>339.9143</v>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
@@ -4697,22 +4701,22 @@
         </is>
       </c>
       <c r="S47" s="4" t="n">
-        <v>4.93</v>
+        <v>4.3</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>-3.95</v>
+        <v>-3.52</v>
       </c>
       <c r="U47" s="4" t="n">
-        <v>749.47</v>
+        <v>375.76</v>
       </c>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CAMS-20260928-86e0a0</t>
+          <t>IND-R2-AMBUJACEM-20261015-8d9ef6</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4728,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4744,34 +4748,34 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>142.41</v>
+        <v>698.65</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>143.79</v>
+        <v>704.2</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>0.97</v>
+        <v>0.79</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>33.3</v>
+        <v>30.9</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -4790,7 +4794,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>138.4</v>
+        <v>671.0643</v>
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -4798,22 +4802,22 @@
         </is>
       </c>
       <c r="S48" s="4" t="n">
-        <v>3.75</v>
+        <v>4.71</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>-2.82</v>
+        <v>-3.95</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>150.78</v>
+        <v>749.47</v>
       </c>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IGL-20261002-27ac34</t>
+          <t>IND-R2-CAMS-20260928-86e0a0</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4829,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4845,34 +4849,34 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>2254.5</v>
+        <v>166.84</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>2270.6</v>
+        <v>167.83</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>0.71</v>
+        <v>0.59</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>40.5</v>
+        <v>37.3</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4891,7 +4895,7 @@
         </is>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>2162.0287</v>
+        <v>162.3571</v>
       </c>
       <c r="R49" s="4" t="inlineStr">
         <is>
@@ -4899,22 +4903,22 @@
         </is>
       </c>
       <c r="S49" s="4" t="n">
-        <v>4.78</v>
+        <v>3.26</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>-4.1</v>
+        <v>-2.69</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>2414.04</v>
+        <v>175.28</v>
       </c>
       <c r="V49" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GLENMARK-20261012-f70810</t>
+          <t>IND-R2-GAIL-20261009-ea012b</t>
         </is>
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4930,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4946,30 +4950,30 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-08</t>
+          <t>Admitted 2026-10-15</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>315.6</v>
+        <v>170.17</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>317.8</v>
+        <v>170.52</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0.7</v>
+        <v>0.21</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>38.2</v>
+        <v>40.5</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
@@ -4992,7 +4996,7 @@
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>307.7143</v>
+        <v>160.89</v>
       </c>
       <c r="R50" s="4" t="inlineStr">
         <is>
@@ -5000,22 +5004,22 @@
         </is>
       </c>
       <c r="S50" s="4" t="n">
-        <v>3.17</v>
+        <v>5.65</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>-2.5</v>
+        <v>-5.45</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>343.17</v>
+        <v>185.48</v>
       </c>
       <c r="V50" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20261008-b77474</t>
+          <t>IND-R2-SAIL-20261015-5cdb61</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5031,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -5047,34 +5051,34 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-01</t>
+          <t>Admitted 2026-10-14</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>223.39</v>
+        <v>373.9</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>224.82</v>
+        <v>374.3</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>0.64</v>
+        <v>0.11</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>31.2</v>
+        <v>35.2</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5093,7 +5097,7 @@
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>217.6</v>
+        <v>362.5643</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -5101,22 +5105,22 @@
         </is>
       </c>
       <c r="S51" s="4" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>-2.59</v>
+        <v>-3.03</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>234.14</v>
+        <v>398.99</v>
       </c>
       <c r="V51" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ONGC-20261001-b42383</t>
+          <t>IND-R2-EMAMILTD-20261014-d5bbe7</t>
         </is>
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5132,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -5148,34 +5152,34 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-08</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>166.84</v>
+        <v>933.95</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>167.85</v>
+        <v>934.95</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0.61</v>
+        <v>0.11</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>37.3</v>
+        <v>40.7</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5194,7 +5198,7 @@
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>162.3571</v>
+        <v>916.2357</v>
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
@@ -5202,22 +5206,22 @@
         </is>
       </c>
       <c r="S52" s="4" t="n">
-        <v>3.27</v>
+        <v>2</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>-2.69</v>
+        <v>-1.9</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>175.28</v>
+        <v>982.13</v>
       </c>
       <c r="V52" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GAIL-20261009-ea012b</t>
+          <t>IND-R2-SHRIRAMFIN-20261008-db2dc4</t>
         </is>
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5233,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -5249,30 +5253,30 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-07</t>
+          <t>Admitted 2026-10-01</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>449.45</v>
+        <v>223.39</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>447.6</v>
+        <v>223.44</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="K53" s="6" t="n">
-        <v>-0.41</v>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>35.4</v>
+        <v>31.2</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
@@ -5295,7 +5299,7 @@
         </is>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>431.85</v>
+        <v>217.6</v>
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
@@ -5303,22 +5307,22 @@
         </is>
       </c>
       <c r="S53" s="4" t="n">
-        <v>3.52</v>
+        <v>2.61</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>-3.92</v>
+        <v>-2.59</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>478.65</v>
+        <v>234.14</v>
       </c>
       <c r="V53" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20261007-ed8f2f</t>
+          <t>IND-R2-ONGC-20261001-b42383</t>
         </is>
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5334,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -5350,34 +5354,34 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-09</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>453.15</v>
+        <v>540.65</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>450.95</v>
+        <v>540.55</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5396,7 +5400,7 @@
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>435.4214</v>
+        <v>528.65</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
@@ -5404,22 +5408,22 @@
         </is>
       </c>
       <c r="S54" s="4" t="n">
-        <v>3.44</v>
+        <v>2.2</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>-3.91</v>
+        <v>-2.22</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>487.36</v>
+        <v>574.4299999999999</v>
       </c>
       <c r="V54" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CONCOR-20260928-51a3e4</t>
+          <t>IND-R2-HINDZINC-20261009-2eeb63</t>
         </is>
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5463,15 +5467,15 @@
         <v>961</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>956.1</v>
+        <v>959.4</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.51</v>
+        <v>-0.17</v>
       </c>
       <c r="L55" s="4" t="n">
         <v>37.2</v>
@@ -5505,7 +5509,7 @@
         </is>
       </c>
       <c r="S55" s="4" t="n">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="T55" s="4" t="n">
         <v>-2.71</v>
@@ -5520,7 +5524,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5536,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -5552,34 +5556,34 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>119.47</v>
+        <v>2254.5</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>118.6</v>
+        <v>2249.5</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.73</v>
+        <v>-0.22</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>30.2</v>
+        <v>40.5</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -5598,7 +5602,7 @@
         </is>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>116.8086</v>
+        <v>2162.0287</v>
       </c>
       <c r="R56" s="4" t="inlineStr">
         <is>
@@ -5606,22 +5610,22 @@
         </is>
       </c>
       <c r="S56" s="4" t="n">
-        <v>1.51</v>
+        <v>3.89</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>-2.23</v>
+        <v>-4.1</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>125.65</v>
+        <v>2414.04</v>
       </c>
       <c r="V56" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20261005-19551d</t>
+          <t>IND-R2-GLENMARK-20261012-f70810</t>
         </is>
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5637,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -5653,34 +5657,34 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-14</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1721.4</v>
+        <v>119.47</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>1707.6</v>
+        <v>119.13</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.8</v>
+        <v>-0.28</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>31.1</v>
+        <v>30.2</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -5699,7 +5703,7 @@
         </is>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>1646.6858</v>
+        <v>116.8086</v>
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
@@ -5707,22 +5711,22 @@
         </is>
       </c>
       <c r="S57" s="4" t="n">
-        <v>3.57</v>
+        <v>1.95</v>
       </c>
       <c r="T57" s="4" t="n">
-        <v>-4.34</v>
+        <v>-2.23</v>
       </c>
       <c r="U57" s="4" t="n">
-        <v>1833.47</v>
+        <v>125.65</v>
       </c>
       <c r="V57" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OBEROIRLTY-20261014-adf111</t>
+          <t>IND-R2-CANBK-20261005-19551d</t>
         </is>
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5738,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -5754,34 +5758,34 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>2629</v>
+        <v>453.15</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>2590</v>
+        <v>450.45</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-1.48</v>
+        <v>-0.6</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>35.9</v>
+        <v>33.3</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -5800,7 +5804,7 @@
         </is>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>2530.3143</v>
+        <v>435.4214</v>
       </c>
       <c r="R58" s="4" t="inlineStr">
         <is>
@@ -5808,22 +5812,22 @@
         </is>
       </c>
       <c r="S58" s="4" t="n">
-        <v>2.3</v>
+        <v>3.34</v>
       </c>
       <c r="T58" s="4" t="n">
-        <v>-3.75</v>
+        <v>-3.91</v>
       </c>
       <c r="U58" s="4" t="n">
-        <v>2777.03</v>
+        <v>487.36</v>
       </c>
       <c r="V58" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MUTHOOTFIN-20261012-9e0c35</t>
+          <t>IND-R2-CONCOR-20260928-51a3e4</t>
         </is>
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5839,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -5855,34 +5859,34 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-09</t>
+          <t>Admitted 2026-10-14</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>540.65</v>
+        <v>1721.4</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>532</v>
+        <v>1710.2</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-1.6</v>
+        <v>-0.65</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>33.2</v>
+        <v>31.1</v>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -5901,7 +5905,7 @@
         </is>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>528.65</v>
+        <v>1646.6858</v>
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
@@ -5909,22 +5913,22 @@
         </is>
       </c>
       <c r="S59" s="4" t="n">
-        <v>0.63</v>
+        <v>3.71</v>
       </c>
       <c r="T59" s="4" t="n">
-        <v>-2.22</v>
+        <v>-4.34</v>
       </c>
       <c r="U59" s="4" t="n">
-        <v>574.4299999999999</v>
+        <v>1833.47</v>
       </c>
       <c r="V59" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20261009-2eeb63</t>
+          <t>IND-R2-OBEROIRLTY-20261014-adf111</t>
         </is>
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5940,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -5956,34 +5960,34 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-21</t>
+          <t>Admitted 2026-10-07</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>124830</v>
+        <v>449.45</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>121985</v>
+        <v>444.75</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-2.28</v>
+        <v>-1.05</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>29.3</v>
+        <v>35.4</v>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6002,7 +6006,7 @@
         </is>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>121363.5714</v>
+        <v>431.85</v>
       </c>
       <c r="R60" s="4" t="inlineStr">
         <is>
@@ -6010,22 +6014,22 @@
         </is>
       </c>
       <c r="S60" s="4" t="n">
-        <v>0.51</v>
+        <v>2.9</v>
       </c>
       <c r="T60" s="4" t="n">
-        <v>-2.78</v>
+        <v>-3.92</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>130238.57</v>
+        <v>478.65</v>
       </c>
       <c r="V60" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MRF-20260921-31a31a</t>
+          <t>IND-R2-OIL-20261007-ed8f2f</t>
         </is>
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6041,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -6066,25 +6070,25 @@
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>589.55</v>
+        <v>2629</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>572.85</v>
+        <v>2599</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-2.83</v>
+        <v>-1.14</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>31.9</v>
+        <v>35.9</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6103,7 +6107,7 @@
         </is>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>562.0732</v>
+        <v>2530.3143</v>
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
@@ -6111,22 +6115,22 @@
         </is>
       </c>
       <c r="S61" s="4" t="n">
-        <v>1.88</v>
+        <v>2.64</v>
       </c>
       <c r="T61" s="4" t="n">
-        <v>-4.66</v>
+        <v>-3.75</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>644.5</v>
+        <v>2777.03</v>
       </c>
       <c r="V61" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20261012-e5db63</t>
+          <t>IND-R2-MUTHOOTFIN-20261012-9e0c35</t>
         </is>
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6142,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -6158,34 +6162,34 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-06</t>
+          <t>Admitted 2026-09-21</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>74.04000000000001</v>
+        <v>124830</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>71.03</v>
+        <v>122350</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-4.07</v>
+        <v>-1.99</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>31.2</v>
+        <v>29.3</v>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -6204,7 +6208,7 @@
         </is>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>70.90860000000001</v>
+        <v>121363.5714</v>
       </c>
       <c r="R62" s="4" t="inlineStr">
         <is>
@@ -6212,22 +6216,22 @@
         </is>
       </c>
       <c r="S62" s="4" t="n">
-        <v>0.17</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T62" s="4" t="n">
-        <v>-4.23</v>
+        <v>-2.78</v>
       </c>
       <c r="U62" s="4" t="n">
-        <v>78.73999999999999</v>
+        <v>130238.57</v>
       </c>
       <c r="V62" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NMDC-20261006-2acbae</t>
+          <t>IND-R2-MRF-20260921-31a31a</t>
         </is>
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6243,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6254,41 +6258,39 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-04</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>397</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>441.1</v>
+        <v>71.75</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>31.2</v>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -6307,7 +6309,7 @@
         </is>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>386.4571</v>
+        <v>70.90860000000001</v>
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
@@ -6315,24 +6317,22 @@
         </is>
       </c>
       <c r="S63" s="4" t="n">
-        <v>12.39</v>
+        <v>1.17</v>
       </c>
       <c r="T63" s="4" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="U63" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-4.23</v>
+      </c>
+      <c r="U63" s="4" t="n">
+        <v>78.73999999999999</v>
       </c>
       <c r="V63" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-NMDC-20261006-2acbae</t>
         </is>
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -6359,41 +6359,39 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-05</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>417.6</v>
+        <v>589.55</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>418.05</v>
+        <v>568</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>31.9</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -6412,7 +6410,7 @@
         </is>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>407.3714</v>
+        <v>562.0732</v>
       </c>
       <c r="R64" s="4" t="inlineStr">
         <is>
@@ -6420,22 +6418,22 @@
         </is>
       </c>
       <c r="S64" s="4" t="n">
-        <v>2.55</v>
+        <v>1.04</v>
       </c>
       <c r="T64" s="4" t="n">
-        <v>-2.45</v>
+        <v>-4.66</v>
       </c>
       <c r="U64" s="4" t="n">
-        <v>432.94</v>
+        <v>644.5</v>
       </c>
       <c r="V64" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R2-GNFC-20261012-e5db63</t>
         </is>
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6447,223 +6445,430 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-04</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>397</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>452.4</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="n">
+        <v>386.4571</v>
+      </c>
+      <c r="R65" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S65" s="4" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="T65" s="4" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="U65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V65" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+        </is>
+      </c>
+      <c r="W65" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE+</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Admitted 2026-08-05</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>416.45</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="n">
+        <v>407.3714</v>
+      </c>
+      <c r="R66" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="S66" s="4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T66" s="4" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="U66" s="4" t="n">
+        <v>432.94</v>
+      </c>
+      <c r="V66" s="4" t="inlineStr">
+        <is>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+        </is>
+      </c>
+      <c r="W66" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
           <t>BEL</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>ACTIVE+</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>Admitted 2026-08-04</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <v>389.85</v>
       </c>
-      <c r="I65" s="4" t="n">
-        <v>380.8</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="K65" s="6" t="n">
-        <v>-2.32</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
+      <c r="I67" s="4" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
         <is>
           <t>Historical score unavailable</t>
         </is>
       </c>
-      <c r="M65" s="4" t="inlineStr">
+      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N65" s="4" t="inlineStr">
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>MARKET_CAP_UNAVAILABLE</t>
         </is>
       </c>
-      <c r="O65" s="4" t="inlineStr">
+      <c r="O67" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P65" s="4" t="inlineStr">
+      <c r="P67" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q65" s="4" t="n">
+      <c r="Q67" s="4" t="n">
         <v>378.3286</v>
       </c>
-      <c r="R65" s="4" t="inlineStr">
+      <c r="R67" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="S65" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="T65" s="4" t="n">
+      <c r="S67" s="4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="T67" s="4" t="n">
         <v>-2.96</v>
       </c>
-      <c r="U65" s="4" t="n">
+      <c r="U67" s="4" t="n">
         <v>407.13</v>
       </c>
-      <c r="V65" s="4" t="inlineStr">
+      <c r="V67" s="4" t="inlineStr">
         <is>
           <t>IND-R1-BEL-20260804-c9f4d0</t>
         </is>
       </c>
-      <c r="W65" s="4" t="inlineStr">
+      <c r="W67" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A68:W68"/>
     <mergeCell ref="A77:W77"/>
     <mergeCell ref="A83:W83"/>
     <mergeCell ref="A82:W82"/>
@@ -6672,15 +6877,16 @@
     <mergeCell ref="A70:W70"/>
     <mergeCell ref="A79:W79"/>
     <mergeCell ref="A6:W6"/>
-    <mergeCell ref="A69:W69"/>
     <mergeCell ref="A78:W78"/>
     <mergeCell ref="A84:W84"/>
     <mergeCell ref="A80:W80"/>
     <mergeCell ref="A75:W75"/>
     <mergeCell ref="A74:W74"/>
     <mergeCell ref="A3:W3"/>
+    <mergeCell ref="A86:W86"/>
     <mergeCell ref="A71:W71"/>
     <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A85:W85"/>
     <mergeCell ref="A76:W76"/>
     <mergeCell ref="A5:W5"/>
     <mergeCell ref="A4:W4"/>
@@ -6721,7 +6927,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-15</t>
+          <t>AEGIS INDIA · EXIT HISTORY · 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -6824,7 +7030,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -6861,13 +7067,13 @@
         <v>1191</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1132.4</v>
+        <v>1138.2</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-4.92</v>
+        <v>-4.43</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -6898,7 +7104,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -6935,13 +7141,13 @@
         <v>187.46</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>175.7</v>
+        <v>177.95</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-6.27</v>
+        <v>-5.07</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -6972,7 +7178,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -7009,13 +7215,13 @@
         <v>239.45</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>224.82</v>
+        <v>223.44</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-6.11</v>
+        <v>-6.69</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -7046,17 +7252,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -7066,69 +7272,71 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>REALIZED EXIT</t>
+          <t>STOP-BREACH MARK</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>10700</v>
+        <v>1449.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10167</v>
+        <v>1387.7</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-4.98</v>
+        <v>-4.26</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Stop-loss triggered</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>43.6</v>
+          <t>Stop breached</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>EXIT_STOP · trigger crossed 2026-10-15 · stop_source=dynamic</t>
+          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260928-d4ee3d</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>registry:production</t>
+          <t>lifecycle:stop-breach</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -7148,20 +7356,20 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1449.5</v>
+        <v>1413.5</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1361.2</v>
+        <v>1331</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-6.09</v>
+        <v>-5.84</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -7175,12 +7383,12 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1412.0571 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -7197,12 +7405,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -7212,54 +7420,52 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>STOP-BREACH MARK</t>
+          <t>REALIZED EXIT</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1413.5</v>
+        <v>10700</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1332.7</v>
+        <v>10167</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-5.72</v>
+        <v>-4.98</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Stop breached</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+          <t>Stop-loss triggered</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>43.6</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 1382.3857 - ATR14 SUGGESTED · advisory · NOT enforced - MARK, position still open in R1</t>
+          <t>EXIT_STOP · trigger crossed 2026-10-15 · stop_source=dynamic</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R2-OFSS-20260928-d4ee3d</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>lifecycle:stop-breach</t>
+          <t>registry:production</t>
         </is>
       </c>
     </row>
@@ -13299,10 +13505,10 @@
         <v>381.6</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>351</v>
+        <v>352.25</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>-8.02</v>
+        <v>-7.69</v>
       </c>
       <c r="K94" s="4" t="n">
         <v>35</v>
@@ -13447,10 +13653,10 @@
         <v>1048.7</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>956.1</v>
+        <v>959.4</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>-8.83</v>
+        <v>-8.52</v>
       </c>
       <c r="K96" s="4" t="n">
         <v>18</v>
@@ -13521,10 +13727,10 @@
         <v>1642.5</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>1510.8</v>
+        <v>1511</v>
       </c>
       <c r="J97" s="6" t="n">
-        <v>-8.02</v>
+        <v>-8.01</v>
       </c>
       <c r="K97" s="4" t="n">
         <v>35</v>
@@ -13669,10 +13875,10 @@
         <v>2410</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>1982</v>
+        <v>1962.2</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>-17.76</v>
+        <v>-18.58</v>
       </c>
       <c r="K99" s="4" t="n">
         <v>34</v>
@@ -13743,10 +13949,10 @@
         <v>507.9</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>474.3</v>
+        <v>469.2</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>-6.62</v>
+        <v>-7.62</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>35</v>
@@ -13817,10 +14023,10 @@
         <v>2064.9</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>1903.7</v>
+        <v>1889.4</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>-7.81</v>
+        <v>-8.5</v>
       </c>
       <c r="K101" s="4" t="n">
         <v>27</v>
@@ -13891,10 +14097,10 @@
         <v>385.15</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>390.15</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>1.3</v>
+        <v>384.8</v>
+      </c>
+      <c r="J102" s="6" t="n">
+        <v>-0.09</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>11</v>
@@ -13965,10 +14171,10 @@
         <v>5454.5</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>4911.3</v>
+        <v>4822.5</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>-9.960000000000001</v>
+        <v>-11.59</v>
       </c>
       <c r="K103" s="4" t="n">
         <v>35</v>

--- a/reports/telegram/aegis_history_india.xlsx
+++ b/reports/telegram/aegis_history_india.xlsx
@@ -508,14 +508,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-16 · prices = 2026-10-16 close</t>
+          <t>AEGIS INDIA · CURRENT · what is investable now · workbook 2026-10-17 · prices = 2026-10-16 close</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>60 investable · NEW 2 · ACTIVE+ 58 · ACTIVE 0   ·   R2 57 · MOMENTUM 0 · R1 3 (advisory)   ·   2 row(s) read 0.00%: admitted at the 2026-10-16 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>60 investable · NEW 0 · ACTIVE+ 60 · ACTIVE 0   ·   R2 57 · MOMENTUM 0 · R1 3 (advisory)   ·   2 row(s) read 0.00%: admitted at the 2026-10-16 close and still marked at it (same-close admission, not a stale price)</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=2 · 228 scored · 59 already in CURRENT · biggest blocker: model disagreement (155) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 57 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (39 day(s) old) · ensemble STALE (39 day(s) old) · dynamic_risk STALE (1 day(s) old) · feature_store STALE (32 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -682,44 +682,44 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-15</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>464.25</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>636.95</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>3677.2</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>3677.2</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0</v>
+      <c r="K8" s="5" t="n">
+        <v>37.2</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>34.9</v>
+        <v>31.2</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>3496.4428</v>
+        <v>622.9393</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -746,22 +746,24 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>4.92</v>
+        <v>2.2</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>3948.34</v>
+        <v>34.18</v>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AIAENG-20261016-4b46fa</t>
+          <t>IND-R2-SUNTV-20260915-459244</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -773,7 +775,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -783,44 +785,44 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-29</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>3150.4</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>3805</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>785.95</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>785.95</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
+      <c r="K9" s="5" t="n">
+        <v>20.78</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>31.1</v>
+        <v>29.2</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -839,7 +841,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>749.9857</v>
+        <v>3588.3286</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -847,22 +849,24 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>4.58</v>
+        <v>5.69</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-4.58</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>839.9</v>
+        <v>13.9</v>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATCOPHARM-20261016-fbbf8d</t>
+          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -874,7 +878,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -889,24 +893,24 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-15</t>
+          <t>Admitted 2026-09-28</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>464.25</v>
+        <v>2056.8</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>636.95</v>
+        <v>2440</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -914,14 +918,14 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>37.2</v>
+        <v>18.63</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>31.2</v>
+        <v>34.9</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -940,7 +944,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>622.9393</v>
+        <v>2318.1286</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -948,10 +952,10 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>2.2</v>
+        <v>4.99</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>34.18</v>
+        <v>12.71</v>
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
@@ -960,12 +964,12 @@
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SUNTV-20260915-459244</t>
+          <t>IND-R2-TCS-20260928-f23b4c</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -977,7 +981,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -992,24 +996,24 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-29</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3150.4</v>
+        <v>1010.1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3805</v>
+        <v>1158.85</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1017,10 +1021,10 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>20.78</v>
+        <v>14.73</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>29.2</v>
+        <v>38.3</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
@@ -1043,7 +1047,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>3588.3286</v>
+        <v>1104.5857</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>5.69</v>
+        <v>4.68</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>13.9</v>
+        <v>9.35</v>
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
@@ -1063,12 +1067,12 @@
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATAELXSI-20260929-d17e13</t>
+          <t>IND-R2-INFY-20261002-20a2cb</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1084,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1095,24 +1099,24 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-28</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2056.8</v>
+        <v>167.79</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2440</v>
+        <v>183.99</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1120,10 +1124,10 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>18.63</v>
+        <v>9.65</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>34.9</v>
+        <v>38.2</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
@@ -1146,7 +1150,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2318.1286</v>
+        <v>175.0071</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1154,10 +1158,10 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.99</v>
+        <v>4.88</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>12.71</v>
+        <v>4.3</v>
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
@@ -1166,12 +1170,12 @@
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260928-f23b4c</t>
+          <t>IND-R2-WIPRO-20261013-d844f1</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1187,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1198,24 +1202,24 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-05</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1010.1</v>
+        <v>3110.4</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1158.85</v>
+        <v>3352</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1223,14 +1227,14 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>14.73</v>
+        <v>7.77</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>38.3</v>
+        <v>34.8</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1249,7 +1253,7 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1104.5857</v>
+        <v>3218.4714</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1257,10 +1261,10 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>4.68</v>
+        <v>3.98</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>9.35</v>
+        <v>3.47</v>
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
@@ -1269,12 +1273,12 @@
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20261002-20a2cb</t>
+          <t>IND-R2-BSE-20261005-7af4a1</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1290,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1301,24 +1305,24 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-13</t>
+          <t>Admitted 2026-10-12</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>167.79</v>
+        <v>158.38</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>183.99</v>
+        <v>169.93</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1326,14 +1330,14 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>9.65</v>
+        <v>7.29</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>38.2</v>
+        <v>28.1</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1352,7 +1356,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>175.0071</v>
+        <v>163.4829</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1360,24 +1364,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.88</v>
+        <v>3.79</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3.22</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>176.28</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-WIPRO-20261013-d844f1</t>
+          <t>IND-R2-BANDHANBNK-20261012-efab94</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1391,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1404,24 +1406,24 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-05</t>
+          <t>Admitted 2026-10-02</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3110.4</v>
+        <v>424.55</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3352</v>
+        <v>452.4</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1429,10 +1431,10 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>7.77</v>
+        <v>6.56</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>34.8</v>
+        <v>34.1</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
@@ -1455,7 +1457,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>3218.4714</v>
+        <v>432.9857</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1463,10 +1465,10 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>3.98</v>
+        <v>4.29</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.47</v>
+        <v>1.99</v>
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
@@ -1475,12 +1477,12 @@
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BSE-20261005-7af4a1</t>
+          <t>IND-R2-KOTAKBANK-20261002-563392</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1494,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1507,24 +1509,24 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-12</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>158.38</v>
+        <v>10581</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>169.93</v>
+        <v>11209</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1532,10 +1534,10 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>7.29</v>
+        <v>5.94</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>28.1</v>
+        <v>35.9</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
@@ -1558,7 +1560,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>163.4829</v>
+        <v>10764.4286</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1566,17 +1568,17 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.79</v>
+        <v>3.97</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>3.22</v>
+        <v>1.73</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>176.28</v>
+        <v>11241.86</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BANDHANBNK-20261012-efab94</t>
+          <t>IND-R2-BAJAJHLDNG-20261013-3e863a</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
@@ -1593,7 +1595,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1608,24 +1610,24 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-02</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>424.55</v>
+        <v>323.6</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>452.4</v>
+        <v>341.25</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1633,10 +1635,10 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>6.56</v>
+        <v>5.45</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>34.1</v>
+        <v>29.2</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
@@ -1659,7 +1661,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>432.9857</v>
+        <v>331.5571</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1667,24 +1669,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>4.29</v>
+        <v>2.84</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2.46</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>342.03</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20261002-563392</t>
+          <t>IND-R2-PFC-20261006-e91ac2</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1711,24 +1711,24 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-13</t>
+          <t>Admitted 2026-10-08</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>10581</v>
+        <v>6886</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>11209</v>
+        <v>7252</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1736,14 +1736,14 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>5.94</v>
+        <v>5.32</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>35.9</v>
+        <v>33.3</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>10764.4286</v>
+        <v>6994.2857</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1770,22 +1770,24 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.97</v>
+        <v>3.55</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U18" s="4" t="n">
-        <v>11241.86</v>
+        <v>1.57</v>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BAJAJHLDNG-20261013-3e863a</t>
+          <t>IND-R2-EICHERMOT-20261008-56f58a</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1799,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1812,7 +1814,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1826,10 +1828,10 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>323.6</v>
+        <v>814.35</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>341.25</v>
+        <v>856.3</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1837,10 +1839,10 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>5.45</v>
+        <v>5.15</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>29.2</v>
+        <v>32.9</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -1863,7 +1865,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>331.5571</v>
+        <v>819.8857</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1871,22 +1873,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.84</v>
+        <v>4.25</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>2.46</v>
+        <v>0.68</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>342.03</v>
+        <v>856.91</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PFC-20261006-e91ac2</t>
+          <t>IND-R2-INDIANB-20261006-0d13b1</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1900,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1913,24 +1915,24 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-08</t>
+          <t>Admitted 2026-10-13</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>6886</v>
+        <v>1315.4</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7252</v>
+        <v>1381</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1938,14 +1940,14 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>5.32</v>
+        <v>4.99</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>33.3</v>
+        <v>40.6</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1964,7 +1966,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>6994.2857</v>
+        <v>1307.3428</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1972,24 +1974,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>3.55</v>
+        <v>5.33</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-0.61</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>1418.99</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-EICHERMOT-20261008-56f58a</t>
+          <t>IND-R2-HCLTECH-20261013-955276</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>814.35</v>
+        <v>293.95</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>856.3</v>
+        <v>306.2</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>5.15</v>
+        <v>4.17</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>32.9</v>
+        <v>34.3</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>819.8857</v>
+        <v>294.7214</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2075,22 +2075,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.68</v>
+        <v>0.26</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>856.91</v>
+        <v>317.43</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20261006-0d13b1</t>
+          <t>IND-R2-ANGELONE-20261006-fc497f</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2117,24 +2117,24 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-10-13</t>
+          <t>Admitted 2026-10-06</t>
         </is>
       </c>
       <c r="G22" s="